--- a/activity/M01A02/M01A02_PuntoEstudioCaudales.xlsx
+++ b/activity/M01A02/M01A02_PuntoEstudioCaudales.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6DEDF95-50B2-4C31-908D-9E8E55DA8B0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A117F6BB-0D61-4FF1-8B25-B5640C300FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Calificacion" sheetId="12" r:id="rId1"/>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="66">
   <si>
     <t>J4660</t>
   </si>
@@ -271,9 +271,6 @@
   </si>
   <si>
     <t>M01A02</t>
-  </si>
-  <si>
-    <t>https://github.com/rcfdtools/R.HCMC/blob/main/activity/M01A02/Readme.md</t>
   </si>
   <si>
     <t>Calificación 1.2. Modelación hidrológica para obtención de caudales de diseño e hidrogramas para tránsito de crecientes</t>
@@ -499,12 +496,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <color theme="10"/>
-      <name val="Segoe UI Light"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -512,6 +503,12 @@
     <font>
       <sz val="8"/>
       <color theme="1"/>
+      <name val="Segoe UI Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF0070C0"/>
       <name val="Segoe UI Light"/>
       <family val="2"/>
     </font>
@@ -709,7 +706,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="32">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -1021,15 +1018,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -1281,7 +1269,7 @@
     <xf numFmtId="2" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1316,81 +1304,6 @@
     <xf numFmtId="2" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="5" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
@@ -1412,6 +1325,81 @@
     </xf>
     <xf numFmtId="2" fontId="5" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="51">
@@ -2826,20 +2814,20 @@
       </c>
     </row>
     <row r="2" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="45" t="s">
-        <v>62</v>
-      </c>
-      <c r="C2" s="45"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
+      <c r="B2" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
     </row>
     <row r="3" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
     </row>
     <row r="4" spans="2:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="29" t="s">
@@ -3082,20 +3070,21 @@
       </c>
     </row>
     <row r="18" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B18" s="47" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" s="47"/>
-      <c r="D18" s="47"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="47"/>
+      <c r="B18" s="75" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F1," en GitHub."))</f>
+        <v>Ir a actividad M01A02 en GitHub.</v>
+      </c>
+      <c r="C18" s="75"/>
+      <c r="D18" s="75"/>
+      <c r="E18" s="75"/>
+      <c r="F18" s="75"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B19" s="32"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
+      <c r="B19" s="75"/>
+      <c r="C19" s="75"/>
+      <c r="D19" s="75"/>
+      <c r="E19" s="75"/>
+      <c r="F19" s="75"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B20" s="32"/>
@@ -3105,17 +3094,15 @@
       <c r="F20" s="32"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B2:F3"/>
     <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B19:F19"/>
   </mergeCells>
-  <phoneticPr fontId="29" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="B18" r:id="rId1" xr:uid="{0ED9F5D1-07FA-4304-A913-580B839EC9D2}"/>
-  </hyperlinks>
+  <phoneticPr fontId="28" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
-  <drawing r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -3330,219 +3317,219 @@
     </row>
     <row r="2" spans="1:165" s="7" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="6"/>
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="60" t="s">
+      <c r="C2" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="63" t="s">
+      <c r="D2" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="53" t="str">
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="69"/>
+      <c r="J2" s="58" t="str">
         <f>Calificacion!$B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="K2" s="54"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="55"/>
-      <c r="Q2" s="55"/>
-      <c r="R2" s="55"/>
-      <c r="S2" s="56"/>
-      <c r="T2" s="56"/>
-      <c r="U2" s="57"/>
-      <c r="V2" s="53" t="str">
+      <c r="K2" s="59"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="58" t="str">
         <f>Calificacion!$B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="W2" s="54"/>
-      <c r="X2" s="55"/>
-      <c r="Y2" s="55"/>
-      <c r="Z2" s="55"/>
-      <c r="AA2" s="55"/>
-      <c r="AB2" s="55"/>
-      <c r="AC2" s="55"/>
-      <c r="AD2" s="55"/>
-      <c r="AE2" s="56"/>
-      <c r="AF2" s="56"/>
-      <c r="AG2" s="57"/>
-      <c r="AH2" s="53" t="str">
+      <c r="W2" s="59"/>
+      <c r="X2" s="60"/>
+      <c r="Y2" s="60"/>
+      <c r="Z2" s="60"/>
+      <c r="AA2" s="60"/>
+      <c r="AB2" s="60"/>
+      <c r="AC2" s="60"/>
+      <c r="AD2" s="60"/>
+      <c r="AE2" s="61"/>
+      <c r="AF2" s="61"/>
+      <c r="AG2" s="62"/>
+      <c r="AH2" s="58" t="str">
         <f>Calificacion!$B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="AI2" s="54"/>
-      <c r="AJ2" s="55"/>
-      <c r="AK2" s="55"/>
-      <c r="AL2" s="55"/>
-      <c r="AM2" s="55"/>
-      <c r="AN2" s="55"/>
-      <c r="AO2" s="55"/>
-      <c r="AP2" s="55"/>
-      <c r="AQ2" s="56"/>
-      <c r="AR2" s="56"/>
-      <c r="AS2" s="57"/>
-      <c r="AT2" s="53" t="str">
+      <c r="AI2" s="59"/>
+      <c r="AJ2" s="60"/>
+      <c r="AK2" s="60"/>
+      <c r="AL2" s="60"/>
+      <c r="AM2" s="60"/>
+      <c r="AN2" s="60"/>
+      <c r="AO2" s="60"/>
+      <c r="AP2" s="60"/>
+      <c r="AQ2" s="61"/>
+      <c r="AR2" s="61"/>
+      <c r="AS2" s="62"/>
+      <c r="AT2" s="58" t="str">
         <f>Calificacion!$B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="AU2" s="54"/>
-      <c r="AV2" s="55"/>
-      <c r="AW2" s="55"/>
-      <c r="AX2" s="55"/>
-      <c r="AY2" s="55"/>
-      <c r="AZ2" s="55"/>
-      <c r="BA2" s="55"/>
-      <c r="BB2" s="55"/>
-      <c r="BC2" s="56"/>
-      <c r="BD2" s="56"/>
-      <c r="BE2" s="57"/>
-      <c r="BF2" s="53" t="str">
+      <c r="AU2" s="59"/>
+      <c r="AV2" s="60"/>
+      <c r="AW2" s="60"/>
+      <c r="AX2" s="60"/>
+      <c r="AY2" s="60"/>
+      <c r="AZ2" s="60"/>
+      <c r="BA2" s="60"/>
+      <c r="BB2" s="60"/>
+      <c r="BC2" s="61"/>
+      <c r="BD2" s="61"/>
+      <c r="BE2" s="62"/>
+      <c r="BF2" s="58" t="str">
         <f>Calificacion!$B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="BG2" s="55"/>
-      <c r="BH2" s="55"/>
-      <c r="BI2" s="55"/>
-      <c r="BJ2" s="55"/>
-      <c r="BK2" s="55"/>
-      <c r="BL2" s="55"/>
-      <c r="BM2" s="55"/>
-      <c r="BN2" s="55"/>
-      <c r="BO2" s="56"/>
-      <c r="BP2" s="56"/>
-      <c r="BQ2" s="57"/>
-      <c r="BR2" s="53" t="str">
+      <c r="BG2" s="60"/>
+      <c r="BH2" s="60"/>
+      <c r="BI2" s="60"/>
+      <c r="BJ2" s="60"/>
+      <c r="BK2" s="60"/>
+      <c r="BL2" s="60"/>
+      <c r="BM2" s="60"/>
+      <c r="BN2" s="60"/>
+      <c r="BO2" s="61"/>
+      <c r="BP2" s="61"/>
+      <c r="BQ2" s="62"/>
+      <c r="BR2" s="58" t="str">
         <f>Calificacion!$B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="BS2" s="54"/>
-      <c r="BT2" s="55"/>
-      <c r="BU2" s="55"/>
-      <c r="BV2" s="55"/>
-      <c r="BW2" s="55"/>
-      <c r="BX2" s="55"/>
-      <c r="BY2" s="55"/>
-      <c r="BZ2" s="55"/>
-      <c r="CA2" s="56"/>
-      <c r="CB2" s="56"/>
-      <c r="CC2" s="57"/>
-      <c r="CD2" s="53" t="str">
+      <c r="BS2" s="59"/>
+      <c r="BT2" s="60"/>
+      <c r="BU2" s="60"/>
+      <c r="BV2" s="60"/>
+      <c r="BW2" s="60"/>
+      <c r="BX2" s="60"/>
+      <c r="BY2" s="60"/>
+      <c r="BZ2" s="60"/>
+      <c r="CA2" s="61"/>
+      <c r="CB2" s="61"/>
+      <c r="CC2" s="62"/>
+      <c r="CD2" s="58" t="str">
         <f>Calificacion!$B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="CE2" s="54"/>
-      <c r="CF2" s="55"/>
-      <c r="CG2" s="55"/>
-      <c r="CH2" s="55"/>
-      <c r="CI2" s="55"/>
-      <c r="CJ2" s="55"/>
-      <c r="CK2" s="55"/>
-      <c r="CL2" s="55"/>
-      <c r="CM2" s="56"/>
-      <c r="CN2" s="56"/>
-      <c r="CO2" s="57"/>
-      <c r="CP2" s="53" t="str">
+      <c r="CE2" s="59"/>
+      <c r="CF2" s="60"/>
+      <c r="CG2" s="60"/>
+      <c r="CH2" s="60"/>
+      <c r="CI2" s="60"/>
+      <c r="CJ2" s="60"/>
+      <c r="CK2" s="60"/>
+      <c r="CL2" s="60"/>
+      <c r="CM2" s="61"/>
+      <c r="CN2" s="61"/>
+      <c r="CO2" s="62"/>
+      <c r="CP2" s="58" t="str">
         <f>Calificacion!$B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="CQ2" s="54"/>
-      <c r="CR2" s="55"/>
-      <c r="CS2" s="55"/>
-      <c r="CT2" s="55"/>
-      <c r="CU2" s="55"/>
-      <c r="CV2" s="55"/>
-      <c r="CW2" s="55"/>
-      <c r="CX2" s="55"/>
-      <c r="CY2" s="56"/>
-      <c r="CZ2" s="56"/>
-      <c r="DA2" s="57"/>
-      <c r="DB2" s="53" t="str">
+      <c r="CQ2" s="59"/>
+      <c r="CR2" s="60"/>
+      <c r="CS2" s="60"/>
+      <c r="CT2" s="60"/>
+      <c r="CU2" s="60"/>
+      <c r="CV2" s="60"/>
+      <c r="CW2" s="60"/>
+      <c r="CX2" s="60"/>
+      <c r="CY2" s="61"/>
+      <c r="CZ2" s="61"/>
+      <c r="DA2" s="62"/>
+      <c r="DB2" s="58" t="str">
         <f>Calificacion!$B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="DC2" s="54"/>
-      <c r="DD2" s="55"/>
-      <c r="DE2" s="55"/>
-      <c r="DF2" s="55"/>
-      <c r="DG2" s="55"/>
-      <c r="DH2" s="55"/>
-      <c r="DI2" s="55"/>
-      <c r="DJ2" s="55"/>
-      <c r="DK2" s="56"/>
-      <c r="DL2" s="56"/>
-      <c r="DM2" s="57"/>
-      <c r="DN2" s="53" t="str">
+      <c r="DC2" s="59"/>
+      <c r="DD2" s="60"/>
+      <c r="DE2" s="60"/>
+      <c r="DF2" s="60"/>
+      <c r="DG2" s="60"/>
+      <c r="DH2" s="60"/>
+      <c r="DI2" s="60"/>
+      <c r="DJ2" s="60"/>
+      <c r="DK2" s="61"/>
+      <c r="DL2" s="61"/>
+      <c r="DM2" s="62"/>
+      <c r="DN2" s="58" t="str">
         <f>Calificacion!$B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="DO2" s="54"/>
-      <c r="DP2" s="55"/>
-      <c r="DQ2" s="55"/>
-      <c r="DR2" s="55"/>
-      <c r="DS2" s="55"/>
-      <c r="DT2" s="55"/>
-      <c r="DU2" s="55"/>
-      <c r="DV2" s="55"/>
-      <c r="DW2" s="56"/>
-      <c r="DX2" s="56"/>
-      <c r="DY2" s="57"/>
-      <c r="DZ2" s="53" t="str">
+      <c r="DO2" s="59"/>
+      <c r="DP2" s="60"/>
+      <c r="DQ2" s="60"/>
+      <c r="DR2" s="60"/>
+      <c r="DS2" s="60"/>
+      <c r="DT2" s="60"/>
+      <c r="DU2" s="60"/>
+      <c r="DV2" s="60"/>
+      <c r="DW2" s="61"/>
+      <c r="DX2" s="61"/>
+      <c r="DY2" s="62"/>
+      <c r="DZ2" s="58" t="str">
         <f>Calificacion!$B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="EA2" s="55"/>
-      <c r="EB2" s="55"/>
-      <c r="EC2" s="55"/>
-      <c r="ED2" s="55"/>
-      <c r="EE2" s="55"/>
-      <c r="EF2" s="55"/>
-      <c r="EG2" s="55"/>
-      <c r="EH2" s="55"/>
-      <c r="EI2" s="56"/>
-      <c r="EJ2" s="56"/>
-      <c r="EK2" s="57"/>
-      <c r="EL2" s="53" t="str">
+      <c r="EA2" s="60"/>
+      <c r="EB2" s="60"/>
+      <c r="EC2" s="60"/>
+      <c r="ED2" s="60"/>
+      <c r="EE2" s="60"/>
+      <c r="EF2" s="60"/>
+      <c r="EG2" s="60"/>
+      <c r="EH2" s="60"/>
+      <c r="EI2" s="61"/>
+      <c r="EJ2" s="61"/>
+      <c r="EK2" s="62"/>
+      <c r="EL2" s="58" t="str">
         <f>Calificacion!$B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="EM2" s="55"/>
-      <c r="EN2" s="55"/>
-      <c r="EO2" s="55"/>
-      <c r="EP2" s="55"/>
-      <c r="EQ2" s="55"/>
-      <c r="ER2" s="55"/>
-      <c r="ES2" s="55"/>
-      <c r="ET2" s="55"/>
-      <c r="EU2" s="56"/>
-      <c r="EV2" s="56"/>
-      <c r="EW2" s="57"/>
-      <c r="EX2" s="53" t="str">
+      <c r="EM2" s="60"/>
+      <c r="EN2" s="60"/>
+      <c r="EO2" s="60"/>
+      <c r="EP2" s="60"/>
+      <c r="EQ2" s="60"/>
+      <c r="ER2" s="60"/>
+      <c r="ES2" s="60"/>
+      <c r="ET2" s="60"/>
+      <c r="EU2" s="61"/>
+      <c r="EV2" s="61"/>
+      <c r="EW2" s="62"/>
+      <c r="EX2" s="58" t="str">
         <f>Calificacion!$B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="EY2" s="55"/>
-      <c r="EZ2" s="55"/>
-      <c r="FA2" s="55"/>
-      <c r="FB2" s="55"/>
-      <c r="FC2" s="55"/>
-      <c r="FD2" s="55"/>
-      <c r="FE2" s="55"/>
-      <c r="FF2" s="55"/>
-      <c r="FG2" s="56"/>
-      <c r="FH2" s="56"/>
-      <c r="FI2" s="57"/>
+      <c r="EY2" s="60"/>
+      <c r="EZ2" s="60"/>
+      <c r="FA2" s="60"/>
+      <c r="FB2" s="60"/>
+      <c r="FC2" s="60"/>
+      <c r="FD2" s="60"/>
+      <c r="FE2" s="60"/>
+      <c r="FF2" s="60"/>
+      <c r="FG2" s="61"/>
+      <c r="FH2" s="61"/>
+      <c r="FI2" s="62"/>
     </row>
     <row r="3" spans="1:165" ht="30.75" x14ac:dyDescent="0.45">
-      <c r="B3" s="59"/>
-      <c r="C3" s="61"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="57"/>
       <c r="D3" s="8" t="s">
         <v>7</v>
       </c>
@@ -5889,16 +5876,16 @@
       <c r="FI13" s="39"/>
     </row>
     <row r="14" spans="1:165" x14ac:dyDescent="0.45">
-      <c r="B14" s="70" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" s="71"/>
-      <c r="D14" s="72"/>
-      <c r="E14" s="73"/>
-      <c r="F14" s="73"/>
-      <c r="G14" s="74"/>
-      <c r="H14" s="74"/>
-      <c r="I14" s="75"/>
+      <c r="B14" s="45" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="46"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="49"/>
+      <c r="I14" s="50"/>
       <c r="J14" s="37"/>
       <c r="K14" s="38"/>
       <c r="L14" s="22"/>
@@ -6229,7 +6216,7 @@
       <c r="A16" s="1"/>
       <c r="B16" s="23"/>
       <c r="C16" s="16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D16" s="24"/>
       <c r="E16" s="24"/>
@@ -6398,7 +6385,7 @@
       <c r="A17" s="1"/>
       <c r="B17" s="23"/>
       <c r="C17" s="24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D17" s="24"/>
       <c r="E17" s="24"/>
@@ -7074,7 +7061,7 @@
       <c r="A21" s="1"/>
       <c r="B21" s="23"/>
       <c r="C21" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D21" s="24"/>
       <c r="E21" s="24"/>
@@ -7241,369 +7228,369 @@
     </row>
     <row r="22" spans="1:165" s="2" customFormat="1" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="1"/>
-      <c r="B22" s="67" t="s">
+      <c r="B22" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="68"/>
-      <c r="D22" s="65" t="s">
+      <c r="C22" s="73"/>
+      <c r="D22" s="70" t="s">
         <v>28</v>
       </c>
-      <c r="E22" s="65"/>
-      <c r="F22" s="65"/>
-      <c r="G22" s="65"/>
-      <c r="H22" s="65"/>
-      <c r="I22" s="66"/>
-      <c r="J22" s="48"/>
-      <c r="K22" s="49"/>
-      <c r="L22" s="50"/>
-      <c r="M22" s="50"/>
-      <c r="N22" s="50"/>
-      <c r="O22" s="50"/>
-      <c r="P22" s="50"/>
-      <c r="Q22" s="50"/>
-      <c r="R22" s="50"/>
-      <c r="S22" s="51"/>
-      <c r="T22" s="51"/>
-      <c r="U22" s="52"/>
-      <c r="V22" s="48"/>
-      <c r="W22" s="49"/>
-      <c r="X22" s="50"/>
-      <c r="Y22" s="50"/>
-      <c r="Z22" s="50"/>
-      <c r="AA22" s="50"/>
-      <c r="AB22" s="50"/>
-      <c r="AC22" s="50"/>
-      <c r="AD22" s="50"/>
-      <c r="AE22" s="51"/>
-      <c r="AF22" s="51"/>
-      <c r="AG22" s="52"/>
-      <c r="AH22" s="48"/>
-      <c r="AI22" s="49"/>
-      <c r="AJ22" s="50"/>
-      <c r="AK22" s="50"/>
-      <c r="AL22" s="50"/>
-      <c r="AM22" s="50"/>
-      <c r="AN22" s="50"/>
-      <c r="AO22" s="50"/>
-      <c r="AP22" s="50"/>
-      <c r="AQ22" s="51"/>
-      <c r="AR22" s="51"/>
-      <c r="AS22" s="52"/>
-      <c r="AT22" s="48"/>
-      <c r="AU22" s="49"/>
-      <c r="AV22" s="50"/>
-      <c r="AW22" s="50"/>
-      <c r="AX22" s="50"/>
-      <c r="AY22" s="50"/>
-      <c r="AZ22" s="50"/>
-      <c r="BA22" s="50"/>
-      <c r="BB22" s="50"/>
-      <c r="BC22" s="51"/>
-      <c r="BD22" s="51"/>
-      <c r="BE22" s="52"/>
-      <c r="BF22" s="48"/>
-      <c r="BG22" s="49"/>
-      <c r="BH22" s="50"/>
-      <c r="BI22" s="50"/>
-      <c r="BJ22" s="50"/>
-      <c r="BK22" s="50"/>
-      <c r="BL22" s="50"/>
-      <c r="BM22" s="50"/>
-      <c r="BN22" s="50"/>
-      <c r="BO22" s="51"/>
-      <c r="BP22" s="51"/>
-      <c r="BQ22" s="52"/>
-      <c r="BR22" s="48"/>
-      <c r="BS22" s="49"/>
-      <c r="BT22" s="50"/>
-      <c r="BU22" s="50"/>
-      <c r="BV22" s="50"/>
-      <c r="BW22" s="50"/>
-      <c r="BX22" s="50"/>
-      <c r="BY22" s="50"/>
-      <c r="BZ22" s="50"/>
-      <c r="CA22" s="51"/>
-      <c r="CB22" s="51"/>
-      <c r="CC22" s="52"/>
-      <c r="CD22" s="48"/>
-      <c r="CE22" s="49"/>
-      <c r="CF22" s="50"/>
-      <c r="CG22" s="50"/>
-      <c r="CH22" s="50"/>
-      <c r="CI22" s="50"/>
-      <c r="CJ22" s="50"/>
-      <c r="CK22" s="50"/>
-      <c r="CL22" s="50"/>
-      <c r="CM22" s="51"/>
-      <c r="CN22" s="51"/>
-      <c r="CO22" s="52"/>
-      <c r="CP22" s="48"/>
-      <c r="CQ22" s="49"/>
-      <c r="CR22" s="50"/>
-      <c r="CS22" s="50"/>
-      <c r="CT22" s="50"/>
-      <c r="CU22" s="50"/>
-      <c r="CV22" s="50"/>
-      <c r="CW22" s="50"/>
-      <c r="CX22" s="50"/>
-      <c r="CY22" s="51"/>
-      <c r="CZ22" s="51"/>
-      <c r="DA22" s="52"/>
-      <c r="DB22" s="48"/>
-      <c r="DC22" s="49"/>
-      <c r="DD22" s="50"/>
-      <c r="DE22" s="50"/>
-      <c r="DF22" s="50"/>
-      <c r="DG22" s="50"/>
-      <c r="DH22" s="50"/>
-      <c r="DI22" s="50"/>
-      <c r="DJ22" s="50"/>
-      <c r="DK22" s="51"/>
-      <c r="DL22" s="51"/>
-      <c r="DM22" s="52"/>
-      <c r="DN22" s="48"/>
-      <c r="DO22" s="49"/>
-      <c r="DP22" s="50"/>
-      <c r="DQ22" s="50"/>
-      <c r="DR22" s="50"/>
-      <c r="DS22" s="50"/>
-      <c r="DT22" s="50"/>
-      <c r="DU22" s="50"/>
-      <c r="DV22" s="50"/>
-      <c r="DW22" s="51"/>
-      <c r="DX22" s="51"/>
-      <c r="DY22" s="52"/>
-      <c r="DZ22" s="48"/>
-      <c r="EA22" s="49"/>
-      <c r="EB22" s="50"/>
-      <c r="EC22" s="50"/>
-      <c r="ED22" s="50"/>
-      <c r="EE22" s="50"/>
-      <c r="EF22" s="50"/>
-      <c r="EG22" s="50"/>
-      <c r="EH22" s="50"/>
-      <c r="EI22" s="51"/>
-      <c r="EJ22" s="51"/>
-      <c r="EK22" s="52"/>
-      <c r="EL22" s="48"/>
-      <c r="EM22" s="49"/>
-      <c r="EN22" s="50"/>
-      <c r="EO22" s="50"/>
-      <c r="EP22" s="50"/>
-      <c r="EQ22" s="50"/>
-      <c r="ER22" s="50"/>
-      <c r="ES22" s="50"/>
-      <c r="ET22" s="50"/>
-      <c r="EU22" s="51"/>
-      <c r="EV22" s="51"/>
-      <c r="EW22" s="52"/>
-      <c r="EX22" s="48"/>
-      <c r="EY22" s="49"/>
-      <c r="EZ22" s="50"/>
-      <c r="FA22" s="50"/>
-      <c r="FB22" s="50"/>
-      <c r="FC22" s="50"/>
-      <c r="FD22" s="50"/>
-      <c r="FE22" s="50"/>
-      <c r="FF22" s="50"/>
-      <c r="FG22" s="51"/>
-      <c r="FH22" s="51"/>
-      <c r="FI22" s="52"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="71"/>
+      <c r="J22" s="63"/>
+      <c r="K22" s="64"/>
+      <c r="L22" s="65"/>
+      <c r="M22" s="65"/>
+      <c r="N22" s="65"/>
+      <c r="O22" s="65"/>
+      <c r="P22" s="65"/>
+      <c r="Q22" s="65"/>
+      <c r="R22" s="65"/>
+      <c r="S22" s="66"/>
+      <c r="T22" s="66"/>
+      <c r="U22" s="67"/>
+      <c r="V22" s="63"/>
+      <c r="W22" s="64"/>
+      <c r="X22" s="65"/>
+      <c r="Y22" s="65"/>
+      <c r="Z22" s="65"/>
+      <c r="AA22" s="65"/>
+      <c r="AB22" s="65"/>
+      <c r="AC22" s="65"/>
+      <c r="AD22" s="65"/>
+      <c r="AE22" s="66"/>
+      <c r="AF22" s="66"/>
+      <c r="AG22" s="67"/>
+      <c r="AH22" s="63"/>
+      <c r="AI22" s="64"/>
+      <c r="AJ22" s="65"/>
+      <c r="AK22" s="65"/>
+      <c r="AL22" s="65"/>
+      <c r="AM22" s="65"/>
+      <c r="AN22" s="65"/>
+      <c r="AO22" s="65"/>
+      <c r="AP22" s="65"/>
+      <c r="AQ22" s="66"/>
+      <c r="AR22" s="66"/>
+      <c r="AS22" s="67"/>
+      <c r="AT22" s="63"/>
+      <c r="AU22" s="64"/>
+      <c r="AV22" s="65"/>
+      <c r="AW22" s="65"/>
+      <c r="AX22" s="65"/>
+      <c r="AY22" s="65"/>
+      <c r="AZ22" s="65"/>
+      <c r="BA22" s="65"/>
+      <c r="BB22" s="65"/>
+      <c r="BC22" s="66"/>
+      <c r="BD22" s="66"/>
+      <c r="BE22" s="67"/>
+      <c r="BF22" s="63"/>
+      <c r="BG22" s="64"/>
+      <c r="BH22" s="65"/>
+      <c r="BI22" s="65"/>
+      <c r="BJ22" s="65"/>
+      <c r="BK22" s="65"/>
+      <c r="BL22" s="65"/>
+      <c r="BM22" s="65"/>
+      <c r="BN22" s="65"/>
+      <c r="BO22" s="66"/>
+      <c r="BP22" s="66"/>
+      <c r="BQ22" s="67"/>
+      <c r="BR22" s="63"/>
+      <c r="BS22" s="64"/>
+      <c r="BT22" s="65"/>
+      <c r="BU22" s="65"/>
+      <c r="BV22" s="65"/>
+      <c r="BW22" s="65"/>
+      <c r="BX22" s="65"/>
+      <c r="BY22" s="65"/>
+      <c r="BZ22" s="65"/>
+      <c r="CA22" s="66"/>
+      <c r="CB22" s="66"/>
+      <c r="CC22" s="67"/>
+      <c r="CD22" s="63"/>
+      <c r="CE22" s="64"/>
+      <c r="CF22" s="65"/>
+      <c r="CG22" s="65"/>
+      <c r="CH22" s="65"/>
+      <c r="CI22" s="65"/>
+      <c r="CJ22" s="65"/>
+      <c r="CK22" s="65"/>
+      <c r="CL22" s="65"/>
+      <c r="CM22" s="66"/>
+      <c r="CN22" s="66"/>
+      <c r="CO22" s="67"/>
+      <c r="CP22" s="63"/>
+      <c r="CQ22" s="64"/>
+      <c r="CR22" s="65"/>
+      <c r="CS22" s="65"/>
+      <c r="CT22" s="65"/>
+      <c r="CU22" s="65"/>
+      <c r="CV22" s="65"/>
+      <c r="CW22" s="65"/>
+      <c r="CX22" s="65"/>
+      <c r="CY22" s="66"/>
+      <c r="CZ22" s="66"/>
+      <c r="DA22" s="67"/>
+      <c r="DB22" s="63"/>
+      <c r="DC22" s="64"/>
+      <c r="DD22" s="65"/>
+      <c r="DE22" s="65"/>
+      <c r="DF22" s="65"/>
+      <c r="DG22" s="65"/>
+      <c r="DH22" s="65"/>
+      <c r="DI22" s="65"/>
+      <c r="DJ22" s="65"/>
+      <c r="DK22" s="66"/>
+      <c r="DL22" s="66"/>
+      <c r="DM22" s="67"/>
+      <c r="DN22" s="63"/>
+      <c r="DO22" s="64"/>
+      <c r="DP22" s="65"/>
+      <c r="DQ22" s="65"/>
+      <c r="DR22" s="65"/>
+      <c r="DS22" s="65"/>
+      <c r="DT22" s="65"/>
+      <c r="DU22" s="65"/>
+      <c r="DV22" s="65"/>
+      <c r="DW22" s="66"/>
+      <c r="DX22" s="66"/>
+      <c r="DY22" s="67"/>
+      <c r="DZ22" s="63"/>
+      <c r="EA22" s="64"/>
+      <c r="EB22" s="65"/>
+      <c r="EC22" s="65"/>
+      <c r="ED22" s="65"/>
+      <c r="EE22" s="65"/>
+      <c r="EF22" s="65"/>
+      <c r="EG22" s="65"/>
+      <c r="EH22" s="65"/>
+      <c r="EI22" s="66"/>
+      <c r="EJ22" s="66"/>
+      <c r="EK22" s="67"/>
+      <c r="EL22" s="63"/>
+      <c r="EM22" s="64"/>
+      <c r="EN22" s="65"/>
+      <c r="EO22" s="65"/>
+      <c r="EP22" s="65"/>
+      <c r="EQ22" s="65"/>
+      <c r="ER22" s="65"/>
+      <c r="ES22" s="65"/>
+      <c r="ET22" s="65"/>
+      <c r="EU22" s="66"/>
+      <c r="EV22" s="66"/>
+      <c r="EW22" s="67"/>
+      <c r="EX22" s="63"/>
+      <c r="EY22" s="64"/>
+      <c r="EZ22" s="65"/>
+      <c r="FA22" s="65"/>
+      <c r="FB22" s="65"/>
+      <c r="FC22" s="65"/>
+      <c r="FD22" s="65"/>
+      <c r="FE22" s="65"/>
+      <c r="FF22" s="65"/>
+      <c r="FG22" s="66"/>
+      <c r="FH22" s="66"/>
+      <c r="FI22" s="67"/>
     </row>
     <row r="23" spans="1:165" s="2" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="1"/>
-      <c r="B23" s="69" t="s">
+      <c r="B23" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="69"/>
-      <c r="D23" s="69"/>
-      <c r="E23" s="69"/>
-      <c r="F23" s="69"/>
-      <c r="G23" s="69"/>
-      <c r="H23" s="69"/>
-      <c r="I23" s="69"/>
-      <c r="J23" s="62">
+      <c r="C23" s="74"/>
+      <c r="D23" s="74"/>
+      <c r="E23" s="74"/>
+      <c r="F23" s="74"/>
+      <c r="G23" s="74"/>
+      <c r="H23" s="74"/>
+      <c r="I23" s="74"/>
+      <c r="J23" s="53">
         <v>0</v>
       </c>
-      <c r="K23" s="62"/>
-      <c r="L23" s="62"/>
-      <c r="M23" s="62"/>
-      <c r="N23" s="62"/>
-      <c r="O23" s="62"/>
-      <c r="P23" s="62"/>
-      <c r="Q23" s="62"/>
-      <c r="R23" s="62"/>
-      <c r="S23" s="62"/>
-      <c r="T23" s="62"/>
-      <c r="U23" s="62"/>
-      <c r="V23" s="62">
+      <c r="K23" s="53"/>
+      <c r="L23" s="53"/>
+      <c r="M23" s="53"/>
+      <c r="N23" s="53"/>
+      <c r="O23" s="53"/>
+      <c r="P23" s="53"/>
+      <c r="Q23" s="53"/>
+      <c r="R23" s="53"/>
+      <c r="S23" s="53"/>
+      <c r="T23" s="53"/>
+      <c r="U23" s="53"/>
+      <c r="V23" s="53">
         <v>0</v>
       </c>
-      <c r="W23" s="62"/>
-      <c r="X23" s="62"/>
-      <c r="Y23" s="62"/>
-      <c r="Z23" s="62"/>
-      <c r="AA23" s="62"/>
-      <c r="AB23" s="62"/>
-      <c r="AC23" s="62"/>
-      <c r="AD23" s="62"/>
-      <c r="AE23" s="62"/>
-      <c r="AF23" s="62"/>
-      <c r="AG23" s="62"/>
-      <c r="AH23" s="62">
+      <c r="W23" s="53"/>
+      <c r="X23" s="53"/>
+      <c r="Y23" s="53"/>
+      <c r="Z23" s="53"/>
+      <c r="AA23" s="53"/>
+      <c r="AB23" s="53"/>
+      <c r="AC23" s="53"/>
+      <c r="AD23" s="53"/>
+      <c r="AE23" s="53"/>
+      <c r="AF23" s="53"/>
+      <c r="AG23" s="53"/>
+      <c r="AH23" s="53">
         <v>0</v>
       </c>
-      <c r="AI23" s="62"/>
-      <c r="AJ23" s="62"/>
-      <c r="AK23" s="62"/>
-      <c r="AL23" s="62"/>
-      <c r="AM23" s="62"/>
-      <c r="AN23" s="62"/>
-      <c r="AO23" s="62"/>
-      <c r="AP23" s="62"/>
-      <c r="AQ23" s="62"/>
-      <c r="AR23" s="62"/>
-      <c r="AS23" s="62"/>
-      <c r="AT23" s="62">
+      <c r="AI23" s="53"/>
+      <c r="AJ23" s="53"/>
+      <c r="AK23" s="53"/>
+      <c r="AL23" s="53"/>
+      <c r="AM23" s="53"/>
+      <c r="AN23" s="53"/>
+      <c r="AO23" s="53"/>
+      <c r="AP23" s="53"/>
+      <c r="AQ23" s="53"/>
+      <c r="AR23" s="53"/>
+      <c r="AS23" s="53"/>
+      <c r="AT23" s="53">
         <v>0</v>
       </c>
-      <c r="AU23" s="62"/>
-      <c r="AV23" s="62"/>
-      <c r="AW23" s="62"/>
-      <c r="AX23" s="62"/>
-      <c r="AY23" s="62"/>
-      <c r="AZ23" s="62"/>
-      <c r="BA23" s="62"/>
-      <c r="BB23" s="62"/>
-      <c r="BC23" s="62"/>
-      <c r="BD23" s="62"/>
-      <c r="BE23" s="62"/>
-      <c r="BF23" s="62">
+      <c r="AU23" s="53"/>
+      <c r="AV23" s="53"/>
+      <c r="AW23" s="53"/>
+      <c r="AX23" s="53"/>
+      <c r="AY23" s="53"/>
+      <c r="AZ23" s="53"/>
+      <c r="BA23" s="53"/>
+      <c r="BB23" s="53"/>
+      <c r="BC23" s="53"/>
+      <c r="BD23" s="53"/>
+      <c r="BE23" s="53"/>
+      <c r="BF23" s="53">
         <v>0</v>
       </c>
-      <c r="BG23" s="62"/>
-      <c r="BH23" s="62"/>
-      <c r="BI23" s="62"/>
-      <c r="BJ23" s="62"/>
-      <c r="BK23" s="62"/>
-      <c r="BL23" s="62"/>
-      <c r="BM23" s="62"/>
-      <c r="BN23" s="62"/>
-      <c r="BO23" s="62"/>
-      <c r="BP23" s="62"/>
-      <c r="BQ23" s="62"/>
-      <c r="BR23" s="62">
+      <c r="BG23" s="53"/>
+      <c r="BH23" s="53"/>
+      <c r="BI23" s="53"/>
+      <c r="BJ23" s="53"/>
+      <c r="BK23" s="53"/>
+      <c r="BL23" s="53"/>
+      <c r="BM23" s="53"/>
+      <c r="BN23" s="53"/>
+      <c r="BO23" s="53"/>
+      <c r="BP23" s="53"/>
+      <c r="BQ23" s="53"/>
+      <c r="BR23" s="53">
         <v>0</v>
       </c>
-      <c r="BS23" s="62"/>
-      <c r="BT23" s="62"/>
-      <c r="BU23" s="62"/>
-      <c r="BV23" s="62"/>
-      <c r="BW23" s="62"/>
-      <c r="BX23" s="62"/>
-      <c r="BY23" s="62"/>
-      <c r="BZ23" s="62"/>
-      <c r="CA23" s="62"/>
-      <c r="CB23" s="62"/>
-      <c r="CC23" s="62"/>
-      <c r="CD23" s="62">
+      <c r="BS23" s="53"/>
+      <c r="BT23" s="53"/>
+      <c r="BU23" s="53"/>
+      <c r="BV23" s="53"/>
+      <c r="BW23" s="53"/>
+      <c r="BX23" s="53"/>
+      <c r="BY23" s="53"/>
+      <c r="BZ23" s="53"/>
+      <c r="CA23" s="53"/>
+      <c r="CB23" s="53"/>
+      <c r="CC23" s="53"/>
+      <c r="CD23" s="53">
         <v>0</v>
       </c>
-      <c r="CE23" s="62"/>
-      <c r="CF23" s="62"/>
-      <c r="CG23" s="62"/>
-      <c r="CH23" s="62"/>
-      <c r="CI23" s="62"/>
-      <c r="CJ23" s="62"/>
-      <c r="CK23" s="62"/>
-      <c r="CL23" s="62"/>
-      <c r="CM23" s="62"/>
-      <c r="CN23" s="62"/>
-      <c r="CO23" s="62"/>
-      <c r="CP23" s="62">
+      <c r="CE23" s="53"/>
+      <c r="CF23" s="53"/>
+      <c r="CG23" s="53"/>
+      <c r="CH23" s="53"/>
+      <c r="CI23" s="53"/>
+      <c r="CJ23" s="53"/>
+      <c r="CK23" s="53"/>
+      <c r="CL23" s="53"/>
+      <c r="CM23" s="53"/>
+      <c r="CN23" s="53"/>
+      <c r="CO23" s="53"/>
+      <c r="CP23" s="53">
         <v>0</v>
       </c>
-      <c r="CQ23" s="62"/>
-      <c r="CR23" s="62"/>
-      <c r="CS23" s="62"/>
-      <c r="CT23" s="62"/>
-      <c r="CU23" s="62"/>
-      <c r="CV23" s="62"/>
-      <c r="CW23" s="62"/>
-      <c r="CX23" s="62"/>
-      <c r="CY23" s="62"/>
-      <c r="CZ23" s="62"/>
-      <c r="DA23" s="62"/>
-      <c r="DB23" s="62">
+      <c r="CQ23" s="53"/>
+      <c r="CR23" s="53"/>
+      <c r="CS23" s="53"/>
+      <c r="CT23" s="53"/>
+      <c r="CU23" s="53"/>
+      <c r="CV23" s="53"/>
+      <c r="CW23" s="53"/>
+      <c r="CX23" s="53"/>
+      <c r="CY23" s="53"/>
+      <c r="CZ23" s="53"/>
+      <c r="DA23" s="53"/>
+      <c r="DB23" s="53">
         <v>0</v>
       </c>
-      <c r="DC23" s="62"/>
-      <c r="DD23" s="62"/>
-      <c r="DE23" s="62"/>
-      <c r="DF23" s="62"/>
-      <c r="DG23" s="62"/>
-      <c r="DH23" s="62"/>
-      <c r="DI23" s="62"/>
-      <c r="DJ23" s="62"/>
-      <c r="DK23" s="62"/>
-      <c r="DL23" s="62"/>
-      <c r="DM23" s="62"/>
-      <c r="DN23" s="62">
+      <c r="DC23" s="53"/>
+      <c r="DD23" s="53"/>
+      <c r="DE23" s="53"/>
+      <c r="DF23" s="53"/>
+      <c r="DG23" s="53"/>
+      <c r="DH23" s="53"/>
+      <c r="DI23" s="53"/>
+      <c r="DJ23" s="53"/>
+      <c r="DK23" s="53"/>
+      <c r="DL23" s="53"/>
+      <c r="DM23" s="53"/>
+      <c r="DN23" s="53">
         <v>0</v>
       </c>
-      <c r="DO23" s="62"/>
-      <c r="DP23" s="62"/>
-      <c r="DQ23" s="62"/>
-      <c r="DR23" s="62"/>
-      <c r="DS23" s="62"/>
-      <c r="DT23" s="62"/>
-      <c r="DU23" s="62"/>
-      <c r="DV23" s="62"/>
-      <c r="DW23" s="62"/>
-      <c r="DX23" s="62"/>
-      <c r="DY23" s="62"/>
-      <c r="DZ23" s="62">
+      <c r="DO23" s="53"/>
+      <c r="DP23" s="53"/>
+      <c r="DQ23" s="53"/>
+      <c r="DR23" s="53"/>
+      <c r="DS23" s="53"/>
+      <c r="DT23" s="53"/>
+      <c r="DU23" s="53"/>
+      <c r="DV23" s="53"/>
+      <c r="DW23" s="53"/>
+      <c r="DX23" s="53"/>
+      <c r="DY23" s="53"/>
+      <c r="DZ23" s="53">
         <v>0</v>
       </c>
-      <c r="EA23" s="62"/>
-      <c r="EB23" s="62"/>
-      <c r="EC23" s="62"/>
-      <c r="ED23" s="62"/>
-      <c r="EE23" s="62"/>
-      <c r="EF23" s="62"/>
-      <c r="EG23" s="62"/>
-      <c r="EH23" s="62"/>
-      <c r="EI23" s="62"/>
-      <c r="EJ23" s="62"/>
-      <c r="EK23" s="62"/>
-      <c r="EL23" s="62">
+      <c r="EA23" s="53"/>
+      <c r="EB23" s="53"/>
+      <c r="EC23" s="53"/>
+      <c r="ED23" s="53"/>
+      <c r="EE23" s="53"/>
+      <c r="EF23" s="53"/>
+      <c r="EG23" s="53"/>
+      <c r="EH23" s="53"/>
+      <c r="EI23" s="53"/>
+      <c r="EJ23" s="53"/>
+      <c r="EK23" s="53"/>
+      <c r="EL23" s="53">
         <v>0</v>
       </c>
-      <c r="EM23" s="62"/>
-      <c r="EN23" s="62"/>
-      <c r="EO23" s="62"/>
-      <c r="EP23" s="62"/>
-      <c r="EQ23" s="62"/>
-      <c r="ER23" s="62"/>
-      <c r="ES23" s="62"/>
-      <c r="ET23" s="62"/>
-      <c r="EU23" s="62"/>
-      <c r="EV23" s="62"/>
-      <c r="EW23" s="62"/>
-      <c r="EX23" s="62">
+      <c r="EM23" s="53"/>
+      <c r="EN23" s="53"/>
+      <c r="EO23" s="53"/>
+      <c r="EP23" s="53"/>
+      <c r="EQ23" s="53"/>
+      <c r="ER23" s="53"/>
+      <c r="ES23" s="53"/>
+      <c r="ET23" s="53"/>
+      <c r="EU23" s="53"/>
+      <c r="EV23" s="53"/>
+      <c r="EW23" s="53"/>
+      <c r="EX23" s="53">
         <v>0</v>
       </c>
-      <c r="EY23" s="62"/>
-      <c r="EZ23" s="62"/>
-      <c r="FA23" s="62"/>
-      <c r="FB23" s="62"/>
-      <c r="FC23" s="62"/>
-      <c r="FD23" s="62"/>
-      <c r="FE23" s="62"/>
-      <c r="FF23" s="62"/>
-      <c r="FG23" s="62"/>
-      <c r="FH23" s="62"/>
-      <c r="FI23" s="62"/>
+      <c r="EY23" s="53"/>
+      <c r="EZ23" s="53"/>
+      <c r="FA23" s="53"/>
+      <c r="FB23" s="53"/>
+      <c r="FC23" s="53"/>
+      <c r="FD23" s="53"/>
+      <c r="FE23" s="53"/>
+      <c r="FF23" s="53"/>
+      <c r="FG23" s="53"/>
+      <c r="FH23" s="53"/>
+      <c r="FI23" s="53"/>
     </row>
     <row r="24" spans="1:165" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B24" s="5"/>
@@ -11425,35 +11412,6 @@
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="BF23:BQ23"/>
-    <mergeCell ref="BR23:CC23"/>
-    <mergeCell ref="CD23:CO23"/>
-    <mergeCell ref="EX23:FI23"/>
-    <mergeCell ref="CP23:DA23"/>
-    <mergeCell ref="DB23:DM23"/>
-    <mergeCell ref="DN23:DY23"/>
-    <mergeCell ref="DZ23:EK23"/>
-    <mergeCell ref="EL23:EW23"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="AH23:AS23"/>
-    <mergeCell ref="AT23:BE23"/>
-    <mergeCell ref="J2:U2"/>
-    <mergeCell ref="J22:U22"/>
-    <mergeCell ref="J23:U23"/>
-    <mergeCell ref="V23:AG23"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="D22:I22"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:I23"/>
-    <mergeCell ref="DN22:DY22"/>
-    <mergeCell ref="DZ22:EK22"/>
-    <mergeCell ref="EL22:EW22"/>
-    <mergeCell ref="EL2:EW2"/>
-    <mergeCell ref="EX2:FI2"/>
-    <mergeCell ref="EX22:FI22"/>
-    <mergeCell ref="DZ2:EK2"/>
-    <mergeCell ref="DN2:DY2"/>
     <mergeCell ref="DB22:DM22"/>
     <mergeCell ref="DB2:DM2"/>
     <mergeCell ref="CP2:DA2"/>
@@ -11470,6 +11428,35 @@
     <mergeCell ref="AH2:AS2"/>
     <mergeCell ref="AH22:AS22"/>
     <mergeCell ref="V22:AG22"/>
+    <mergeCell ref="DN22:DY22"/>
+    <mergeCell ref="DZ22:EK22"/>
+    <mergeCell ref="EL22:EW22"/>
+    <mergeCell ref="EL2:EW2"/>
+    <mergeCell ref="EX2:FI2"/>
+    <mergeCell ref="EX22:FI22"/>
+    <mergeCell ref="DZ2:EK2"/>
+    <mergeCell ref="DN2:DY2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="AH23:AS23"/>
+    <mergeCell ref="AT23:BE23"/>
+    <mergeCell ref="J2:U2"/>
+    <mergeCell ref="J22:U22"/>
+    <mergeCell ref="J23:U23"/>
+    <mergeCell ref="V23:AG23"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="D22:I22"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:I23"/>
+    <mergeCell ref="BF23:BQ23"/>
+    <mergeCell ref="BR23:CC23"/>
+    <mergeCell ref="CD23:CO23"/>
+    <mergeCell ref="EX23:FI23"/>
+    <mergeCell ref="CP23:DA23"/>
+    <mergeCell ref="DB23:DM23"/>
+    <mergeCell ref="DN23:DY23"/>
+    <mergeCell ref="DZ23:EK23"/>
+    <mergeCell ref="EL23:EW23"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="62" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/activity/M01A02/M01A02_PuntoEstudioCaudales.xlsx
+++ b/activity/M01A02/M01A02_PuntoEstudioCaudales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A117F6BB-0D61-4FF1-8B25-B5640C300FFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D499D8D-B303-4176-87FA-EF432DA8E870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Detalle" sheetId="10" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Calificacion!$B$2:$F$19</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Calificacion!$B$2:$F$20</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Detalle!$B$1:$U$23</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="67">
   <si>
     <t>J4660</t>
   </si>
@@ -286,6 +286,9 @@
   </si>
   <si>
     <t>Varios</t>
+  </si>
+  <si>
+    <t>Grupo 14</t>
   </si>
 </sst>
 </file>
@@ -1332,6 +1335,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="2" fontId="11" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1396,10 +1402,7 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="51">
@@ -1562,7 +1565,7 @@
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="bg1">
-                <a:lumMod val="50000"/>
+                <a:lumMod val="85000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:ln>
@@ -1571,6 +1574,60 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Segoe UI Light" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CO"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>Calificacion!$B$5:$B$9</c:f>
@@ -1601,7 +1658,7 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>2.5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -2468,7 +2525,7 @@
       <xdr:col>14</xdr:col>
       <xdr:colOff>149689</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>108656</xdr:rowOff>
+      <xdr:rowOff>93772</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2796,7 +2853,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EF50BAE-D7A1-4B9B-8511-69070389923C}">
   <sheetPr codeName="Hoja2"/>
-  <dimension ref="B1:F20"/>
+  <dimension ref="B1:F21"/>
   <sheetFormatPr defaultColWidth="11.33203125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="17" customWidth="1"/>
@@ -2857,12 +2914,10 @@
         <f>Detalle!J23*C5/5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="33">
-        <v>5</v>
-      </c>
+      <c r="E5" s="33"/>
       <c r="F5" s="13">
         <f>AVERAGE(D5:E5)</f>
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.45">
@@ -3053,51 +3108,68 @@
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B17" s="19" t="s">
+      <c r="B17" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C17" s="34">
+      <c r="C17" s="33">
         <v>5</v>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="10">
         <f>Detalle!EX23*C17/5</f>
         <v>0</v>
       </c>
-      <c r="E17" s="34"/>
-      <c r="F17" s="36">
+      <c r="E17" s="33"/>
+      <c r="F17" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B18" s="75" t="str">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B18" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="34">
+        <v>5</v>
+      </c>
+      <c r="D18" s="28">
+        <f>Detalle!FJ23*C18/5</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="34"/>
+      <c r="F18" s="36">
+        <f t="shared" ref="F18" si="1">AVERAGE(D18:E18)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B19" s="53" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F1," en GitHub."))</f>
         <v>Ir a actividad M01A02 en GitHub.</v>
       </c>
-      <c r="C18" s="75"/>
-      <c r="D18" s="75"/>
-      <c r="E18" s="75"/>
-      <c r="F18" s="75"/>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B19" s="75"/>
-      <c r="C19" s="75"/>
-      <c r="D19" s="75"/>
-      <c r="E19" s="75"/>
-      <c r="F19" s="75"/>
+      <c r="C19" s="53"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B20" s="32"/>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="53"/>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="B21" s="32"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B2:F3"/>
-    <mergeCell ref="B18:F18"/>
     <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B20:F20"/>
   </mergeCells>
   <phoneticPr fontId="28" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3111,7 +3183,7 @@
   <sheetPr codeName="Hoja1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:FI46"/>
+  <dimension ref="A1:FU46"/>
   <sheetFormatPr defaultColWidth="11.33203125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="6" customWidth="1"/>
@@ -3168,10 +3240,13 @@
     <col min="154" max="154" width="8.53125" style="5" bestFit="1" customWidth="1"/>
     <col min="155" max="155" width="8.53125" style="5" customWidth="1"/>
     <col min="156" max="165" width="10.1328125" style="5" customWidth="1"/>
-    <col min="166" max="16384" width="11.33203125" style="4"/>
+    <col min="166" max="166" width="8.53125" style="5" bestFit="1" customWidth="1"/>
+    <col min="167" max="167" width="8.53125" style="5" customWidth="1"/>
+    <col min="168" max="177" width="10.1328125" style="5" customWidth="1"/>
+    <col min="178" max="16384" width="11.33203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:165" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:177" x14ac:dyDescent="0.45">
       <c r="A1" s="3"/>
       <c r="B1" s="7" t="str">
         <f>Calificacion!B2</f>
@@ -3314,222 +3389,247 @@
       <c r="FG1" s="4"/>
       <c r="FH1" s="4"/>
       <c r="FI1" s="4"/>
+      <c r="FL1" s="4"/>
+      <c r="FM1" s="4"/>
+      <c r="FN1" s="4"/>
+      <c r="FO1" s="4"/>
+      <c r="FP1" s="4"/>
+      <c r="FQ1" s="4"/>
+      <c r="FR1" s="4"/>
+      <c r="FS1" s="4"/>
+      <c r="FT1" s="4"/>
+      <c r="FU1" s="4"/>
     </row>
-    <row r="2" spans="1:165" s="7" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:177" s="7" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="6"/>
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="56" t="s">
+      <c r="C2" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="68" t="s">
+      <c r="D2" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="58" t="str">
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
+      <c r="G2" s="69"/>
+      <c r="H2" s="69"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="59" t="str">
         <f>Calificacion!$B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="K2" s="59"/>
-      <c r="L2" s="60"/>
-      <c r="M2" s="60"/>
-      <c r="N2" s="60"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="60"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="61"/>
-      <c r="T2" s="61"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="58" t="str">
+      <c r="K2" s="60"/>
+      <c r="L2" s="61"/>
+      <c r="M2" s="61"/>
+      <c r="N2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="63"/>
+      <c r="V2" s="59" t="str">
         <f>Calificacion!$B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="W2" s="59"/>
-      <c r="X2" s="60"/>
-      <c r="Y2" s="60"/>
-      <c r="Z2" s="60"/>
-      <c r="AA2" s="60"/>
-      <c r="AB2" s="60"/>
-      <c r="AC2" s="60"/>
-      <c r="AD2" s="60"/>
-      <c r="AE2" s="61"/>
-      <c r="AF2" s="61"/>
-      <c r="AG2" s="62"/>
-      <c r="AH2" s="58" t="str">
+      <c r="W2" s="60"/>
+      <c r="X2" s="61"/>
+      <c r="Y2" s="61"/>
+      <c r="Z2" s="61"/>
+      <c r="AA2" s="61"/>
+      <c r="AB2" s="61"/>
+      <c r="AC2" s="61"/>
+      <c r="AD2" s="61"/>
+      <c r="AE2" s="62"/>
+      <c r="AF2" s="62"/>
+      <c r="AG2" s="63"/>
+      <c r="AH2" s="59" t="str">
         <f>Calificacion!$B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="AI2" s="59"/>
-      <c r="AJ2" s="60"/>
-      <c r="AK2" s="60"/>
-      <c r="AL2" s="60"/>
-      <c r="AM2" s="60"/>
-      <c r="AN2" s="60"/>
-      <c r="AO2" s="60"/>
-      <c r="AP2" s="60"/>
-      <c r="AQ2" s="61"/>
-      <c r="AR2" s="61"/>
-      <c r="AS2" s="62"/>
-      <c r="AT2" s="58" t="str">
+      <c r="AI2" s="60"/>
+      <c r="AJ2" s="61"/>
+      <c r="AK2" s="61"/>
+      <c r="AL2" s="61"/>
+      <c r="AM2" s="61"/>
+      <c r="AN2" s="61"/>
+      <c r="AO2" s="61"/>
+      <c r="AP2" s="61"/>
+      <c r="AQ2" s="62"/>
+      <c r="AR2" s="62"/>
+      <c r="AS2" s="63"/>
+      <c r="AT2" s="59" t="str">
         <f>Calificacion!$B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="AU2" s="59"/>
-      <c r="AV2" s="60"/>
-      <c r="AW2" s="60"/>
-      <c r="AX2" s="60"/>
-      <c r="AY2" s="60"/>
-      <c r="AZ2" s="60"/>
-      <c r="BA2" s="60"/>
-      <c r="BB2" s="60"/>
-      <c r="BC2" s="61"/>
-      <c r="BD2" s="61"/>
-      <c r="BE2" s="62"/>
-      <c r="BF2" s="58" t="str">
+      <c r="AU2" s="60"/>
+      <c r="AV2" s="61"/>
+      <c r="AW2" s="61"/>
+      <c r="AX2" s="61"/>
+      <c r="AY2" s="61"/>
+      <c r="AZ2" s="61"/>
+      <c r="BA2" s="61"/>
+      <c r="BB2" s="61"/>
+      <c r="BC2" s="62"/>
+      <c r="BD2" s="62"/>
+      <c r="BE2" s="63"/>
+      <c r="BF2" s="59" t="str">
         <f>Calificacion!$B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="BG2" s="60"/>
-      <c r="BH2" s="60"/>
-      <c r="BI2" s="60"/>
-      <c r="BJ2" s="60"/>
-      <c r="BK2" s="60"/>
-      <c r="BL2" s="60"/>
-      <c r="BM2" s="60"/>
-      <c r="BN2" s="60"/>
-      <c r="BO2" s="61"/>
-      <c r="BP2" s="61"/>
-      <c r="BQ2" s="62"/>
-      <c r="BR2" s="58" t="str">
+      <c r="BG2" s="61"/>
+      <c r="BH2" s="61"/>
+      <c r="BI2" s="61"/>
+      <c r="BJ2" s="61"/>
+      <c r="BK2" s="61"/>
+      <c r="BL2" s="61"/>
+      <c r="BM2" s="61"/>
+      <c r="BN2" s="61"/>
+      <c r="BO2" s="62"/>
+      <c r="BP2" s="62"/>
+      <c r="BQ2" s="63"/>
+      <c r="BR2" s="59" t="str">
         <f>Calificacion!$B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="BS2" s="59"/>
-      <c r="BT2" s="60"/>
-      <c r="BU2" s="60"/>
-      <c r="BV2" s="60"/>
-      <c r="BW2" s="60"/>
-      <c r="BX2" s="60"/>
-      <c r="BY2" s="60"/>
-      <c r="BZ2" s="60"/>
-      <c r="CA2" s="61"/>
-      <c r="CB2" s="61"/>
-      <c r="CC2" s="62"/>
-      <c r="CD2" s="58" t="str">
+      <c r="BS2" s="60"/>
+      <c r="BT2" s="61"/>
+      <c r="BU2" s="61"/>
+      <c r="BV2" s="61"/>
+      <c r="BW2" s="61"/>
+      <c r="BX2" s="61"/>
+      <c r="BY2" s="61"/>
+      <c r="BZ2" s="61"/>
+      <c r="CA2" s="62"/>
+      <c r="CB2" s="62"/>
+      <c r="CC2" s="63"/>
+      <c r="CD2" s="59" t="str">
         <f>Calificacion!$B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="CE2" s="59"/>
-      <c r="CF2" s="60"/>
-      <c r="CG2" s="60"/>
-      <c r="CH2" s="60"/>
-      <c r="CI2" s="60"/>
-      <c r="CJ2" s="60"/>
-      <c r="CK2" s="60"/>
-      <c r="CL2" s="60"/>
-      <c r="CM2" s="61"/>
-      <c r="CN2" s="61"/>
-      <c r="CO2" s="62"/>
-      <c r="CP2" s="58" t="str">
+      <c r="CE2" s="60"/>
+      <c r="CF2" s="61"/>
+      <c r="CG2" s="61"/>
+      <c r="CH2" s="61"/>
+      <c r="CI2" s="61"/>
+      <c r="CJ2" s="61"/>
+      <c r="CK2" s="61"/>
+      <c r="CL2" s="61"/>
+      <c r="CM2" s="62"/>
+      <c r="CN2" s="62"/>
+      <c r="CO2" s="63"/>
+      <c r="CP2" s="59" t="str">
         <f>Calificacion!$B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="CQ2" s="59"/>
-      <c r="CR2" s="60"/>
-      <c r="CS2" s="60"/>
-      <c r="CT2" s="60"/>
-      <c r="CU2" s="60"/>
-      <c r="CV2" s="60"/>
-      <c r="CW2" s="60"/>
-      <c r="CX2" s="60"/>
-      <c r="CY2" s="61"/>
-      <c r="CZ2" s="61"/>
-      <c r="DA2" s="62"/>
-      <c r="DB2" s="58" t="str">
+      <c r="CQ2" s="60"/>
+      <c r="CR2" s="61"/>
+      <c r="CS2" s="61"/>
+      <c r="CT2" s="61"/>
+      <c r="CU2" s="61"/>
+      <c r="CV2" s="61"/>
+      <c r="CW2" s="61"/>
+      <c r="CX2" s="61"/>
+      <c r="CY2" s="62"/>
+      <c r="CZ2" s="62"/>
+      <c r="DA2" s="63"/>
+      <c r="DB2" s="59" t="str">
         <f>Calificacion!$B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="DC2" s="59"/>
-      <c r="DD2" s="60"/>
-      <c r="DE2" s="60"/>
-      <c r="DF2" s="60"/>
-      <c r="DG2" s="60"/>
-      <c r="DH2" s="60"/>
-      <c r="DI2" s="60"/>
-      <c r="DJ2" s="60"/>
-      <c r="DK2" s="61"/>
-      <c r="DL2" s="61"/>
-      <c r="DM2" s="62"/>
-      <c r="DN2" s="58" t="str">
+      <c r="DC2" s="60"/>
+      <c r="DD2" s="61"/>
+      <c r="DE2" s="61"/>
+      <c r="DF2" s="61"/>
+      <c r="DG2" s="61"/>
+      <c r="DH2" s="61"/>
+      <c r="DI2" s="61"/>
+      <c r="DJ2" s="61"/>
+      <c r="DK2" s="62"/>
+      <c r="DL2" s="62"/>
+      <c r="DM2" s="63"/>
+      <c r="DN2" s="59" t="str">
         <f>Calificacion!$B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="DO2" s="59"/>
-      <c r="DP2" s="60"/>
-      <c r="DQ2" s="60"/>
-      <c r="DR2" s="60"/>
-      <c r="DS2" s="60"/>
-      <c r="DT2" s="60"/>
-      <c r="DU2" s="60"/>
-      <c r="DV2" s="60"/>
-      <c r="DW2" s="61"/>
-      <c r="DX2" s="61"/>
-      <c r="DY2" s="62"/>
-      <c r="DZ2" s="58" t="str">
+      <c r="DO2" s="60"/>
+      <c r="DP2" s="61"/>
+      <c r="DQ2" s="61"/>
+      <c r="DR2" s="61"/>
+      <c r="DS2" s="61"/>
+      <c r="DT2" s="61"/>
+      <c r="DU2" s="61"/>
+      <c r="DV2" s="61"/>
+      <c r="DW2" s="62"/>
+      <c r="DX2" s="62"/>
+      <c r="DY2" s="63"/>
+      <c r="DZ2" s="59" t="str">
         <f>Calificacion!$B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="EA2" s="60"/>
-      <c r="EB2" s="60"/>
-      <c r="EC2" s="60"/>
-      <c r="ED2" s="60"/>
-      <c r="EE2" s="60"/>
-      <c r="EF2" s="60"/>
-      <c r="EG2" s="60"/>
-      <c r="EH2" s="60"/>
-      <c r="EI2" s="61"/>
-      <c r="EJ2" s="61"/>
-      <c r="EK2" s="62"/>
-      <c r="EL2" s="58" t="str">
+      <c r="EA2" s="61"/>
+      <c r="EB2" s="61"/>
+      <c r="EC2" s="61"/>
+      <c r="ED2" s="61"/>
+      <c r="EE2" s="61"/>
+      <c r="EF2" s="61"/>
+      <c r="EG2" s="61"/>
+      <c r="EH2" s="61"/>
+      <c r="EI2" s="62"/>
+      <c r="EJ2" s="62"/>
+      <c r="EK2" s="63"/>
+      <c r="EL2" s="59" t="str">
         <f>Calificacion!$B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="EM2" s="60"/>
-      <c r="EN2" s="60"/>
-      <c r="EO2" s="60"/>
-      <c r="EP2" s="60"/>
-      <c r="EQ2" s="60"/>
-      <c r="ER2" s="60"/>
-      <c r="ES2" s="60"/>
-      <c r="ET2" s="60"/>
-      <c r="EU2" s="61"/>
-      <c r="EV2" s="61"/>
-      <c r="EW2" s="62"/>
-      <c r="EX2" s="58" t="str">
+      <c r="EM2" s="61"/>
+      <c r="EN2" s="61"/>
+      <c r="EO2" s="61"/>
+      <c r="EP2" s="61"/>
+      <c r="EQ2" s="61"/>
+      <c r="ER2" s="61"/>
+      <c r="ES2" s="61"/>
+      <c r="ET2" s="61"/>
+      <c r="EU2" s="62"/>
+      <c r="EV2" s="62"/>
+      <c r="EW2" s="63"/>
+      <c r="EX2" s="59" t="str">
         <f>Calificacion!$B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="EY2" s="60"/>
-      <c r="EZ2" s="60"/>
-      <c r="FA2" s="60"/>
-      <c r="FB2" s="60"/>
-      <c r="FC2" s="60"/>
-      <c r="FD2" s="60"/>
-      <c r="FE2" s="60"/>
-      <c r="FF2" s="60"/>
-      <c r="FG2" s="61"/>
-      <c r="FH2" s="61"/>
-      <c r="FI2" s="62"/>
+      <c r="EY2" s="61"/>
+      <c r="EZ2" s="61"/>
+      <c r="FA2" s="61"/>
+      <c r="FB2" s="61"/>
+      <c r="FC2" s="61"/>
+      <c r="FD2" s="61"/>
+      <c r="FE2" s="61"/>
+      <c r="FF2" s="61"/>
+      <c r="FG2" s="62"/>
+      <c r="FH2" s="62"/>
+      <c r="FI2" s="63"/>
+      <c r="FJ2" s="59" t="str">
+        <f>Calificacion!$B18</f>
+        <v>Grupo 14</v>
+      </c>
+      <c r="FK2" s="61"/>
+      <c r="FL2" s="61"/>
+      <c r="FM2" s="61"/>
+      <c r="FN2" s="61"/>
+      <c r="FO2" s="61"/>
+      <c r="FP2" s="61"/>
+      <c r="FQ2" s="61"/>
+      <c r="FR2" s="61"/>
+      <c r="FS2" s="62"/>
+      <c r="FT2" s="62"/>
+      <c r="FU2" s="63"/>
     </row>
-    <row r="3" spans="1:165" ht="30.75" x14ac:dyDescent="0.45">
-      <c r="B3" s="55"/>
-      <c r="C3" s="57"/>
+    <row r="3" spans="1:177" ht="30.75" x14ac:dyDescent="0.45">
+      <c r="B3" s="56"/>
+      <c r="C3" s="58"/>
       <c r="D3" s="8" t="s">
         <v>7</v>
       </c>
@@ -4016,8 +4116,44 @@
       <c r="FI3" s="11" t="s">
         <v>20</v>
       </c>
+      <c r="FJ3" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="FK3" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="FL3" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="FM3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="FN3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="FO3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="FP3" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="FQ3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="FR3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="FS3" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="FT3" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="FU3" s="11" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="4" spans="1:165" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:177" x14ac:dyDescent="0.45">
       <c r="B4" s="12" t="s">
         <v>16</v>
       </c>
@@ -4227,8 +4363,20 @@
       <c r="FG4" s="22"/>
       <c r="FH4" s="22"/>
       <c r="FI4" s="39"/>
+      <c r="FJ4" s="37"/>
+      <c r="FK4" s="38"/>
+      <c r="FL4" s="22"/>
+      <c r="FM4" s="22"/>
+      <c r="FN4" s="22"/>
+      <c r="FO4" s="22"/>
+      <c r="FP4" s="22"/>
+      <c r="FQ4" s="22"/>
+      <c r="FR4" s="22"/>
+      <c r="FS4" s="22"/>
+      <c r="FT4" s="22"/>
+      <c r="FU4" s="39"/>
     </row>
-    <row r="5" spans="1:165" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:177" x14ac:dyDescent="0.45">
       <c r="B5" s="12" t="s">
         <v>17</v>
       </c>
@@ -4412,8 +4560,20 @@
       <c r="FG5" s="22"/>
       <c r="FH5" s="22"/>
       <c r="FI5" s="39"/>
+      <c r="FJ5" s="37"/>
+      <c r="FK5" s="38"/>
+      <c r="FL5" s="22"/>
+      <c r="FM5" s="22"/>
+      <c r="FN5" s="22"/>
+      <c r="FO5" s="22"/>
+      <c r="FP5" s="22"/>
+      <c r="FQ5" s="22"/>
+      <c r="FR5" s="22"/>
+      <c r="FS5" s="22"/>
+      <c r="FT5" s="22"/>
+      <c r="FU5" s="39"/>
     </row>
-    <row r="6" spans="1:165" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:177" x14ac:dyDescent="0.45">
       <c r="B6" s="12" t="s">
         <v>0</v>
       </c>
@@ -4597,8 +4757,20 @@
       <c r="FG6" s="22"/>
       <c r="FH6" s="22"/>
       <c r="FI6" s="39"/>
+      <c r="FJ6" s="37"/>
+      <c r="FK6" s="38"/>
+      <c r="FL6" s="22"/>
+      <c r="FM6" s="22"/>
+      <c r="FN6" s="22"/>
+      <c r="FO6" s="22"/>
+      <c r="FP6" s="22"/>
+      <c r="FQ6" s="22"/>
+      <c r="FR6" s="22"/>
+      <c r="FS6" s="22"/>
+      <c r="FT6" s="22"/>
+      <c r="FU6" s="39"/>
     </row>
-    <row r="7" spans="1:165" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:177" ht="46.15" x14ac:dyDescent="0.45">
       <c r="B7" s="12" t="s">
         <v>38</v>
       </c>
@@ -4782,8 +4954,20 @@
       <c r="FG7" s="22"/>
       <c r="FH7" s="22"/>
       <c r="FI7" s="39"/>
+      <c r="FJ7" s="37"/>
+      <c r="FK7" s="38"/>
+      <c r="FL7" s="22"/>
+      <c r="FM7" s="22"/>
+      <c r="FN7" s="22"/>
+      <c r="FO7" s="22"/>
+      <c r="FP7" s="22"/>
+      <c r="FQ7" s="22"/>
+      <c r="FR7" s="22"/>
+      <c r="FS7" s="22"/>
+      <c r="FT7" s="22"/>
+      <c r="FU7" s="39"/>
     </row>
-    <row r="8" spans="1:165" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:177" ht="46.15" x14ac:dyDescent="0.45">
       <c r="B8" s="12" t="s">
         <v>38</v>
       </c>
@@ -4965,8 +5149,20 @@
       <c r="FG8" s="22"/>
       <c r="FH8" s="22"/>
       <c r="FI8" s="39"/>
+      <c r="FJ8" s="37"/>
+      <c r="FK8" s="38"/>
+      <c r="FL8" s="22"/>
+      <c r="FM8" s="22"/>
+      <c r="FN8" s="22"/>
+      <c r="FO8" s="22"/>
+      <c r="FP8" s="22"/>
+      <c r="FQ8" s="22"/>
+      <c r="FR8" s="22"/>
+      <c r="FS8" s="22"/>
+      <c r="FT8" s="22"/>
+      <c r="FU8" s="39"/>
     </row>
-    <row r="9" spans="1:165" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:177" x14ac:dyDescent="0.45">
       <c r="B9" s="12" t="s">
         <v>1</v>
       </c>
@@ -5150,8 +5346,20 @@
       <c r="FG9" s="22"/>
       <c r="FH9" s="22"/>
       <c r="FI9" s="39"/>
+      <c r="FJ9" s="37"/>
+      <c r="FK9" s="38"/>
+      <c r="FL9" s="22"/>
+      <c r="FM9" s="22"/>
+      <c r="FN9" s="22"/>
+      <c r="FO9" s="22"/>
+      <c r="FP9" s="22"/>
+      <c r="FQ9" s="22"/>
+      <c r="FR9" s="22"/>
+      <c r="FS9" s="22"/>
+      <c r="FT9" s="22"/>
+      <c r="FU9" s="39"/>
     </row>
-    <row r="10" spans="1:165" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:177" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B10" s="12" t="s">
         <v>2</v>
       </c>
@@ -5335,8 +5543,20 @@
       <c r="FG10" s="22"/>
       <c r="FH10" s="22"/>
       <c r="FI10" s="39"/>
+      <c r="FJ10" s="37"/>
+      <c r="FK10" s="38"/>
+      <c r="FL10" s="22"/>
+      <c r="FM10" s="22"/>
+      <c r="FN10" s="22"/>
+      <c r="FO10" s="22"/>
+      <c r="FP10" s="22"/>
+      <c r="FQ10" s="22"/>
+      <c r="FR10" s="22"/>
+      <c r="FS10" s="22"/>
+      <c r="FT10" s="22"/>
+      <c r="FU10" s="39"/>
     </row>
-    <row r="11" spans="1:165" ht="33" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:177" ht="33" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B11" s="12" t="s">
         <v>2</v>
       </c>
@@ -5518,8 +5738,20 @@
       <c r="FG11" s="22"/>
       <c r="FH11" s="22"/>
       <c r="FI11" s="39"/>
+      <c r="FJ11" s="37"/>
+      <c r="FK11" s="38"/>
+      <c r="FL11" s="22"/>
+      <c r="FM11" s="22"/>
+      <c r="FN11" s="22"/>
+      <c r="FO11" s="22"/>
+      <c r="FP11" s="22"/>
+      <c r="FQ11" s="22"/>
+      <c r="FR11" s="22"/>
+      <c r="FS11" s="22"/>
+      <c r="FT11" s="22"/>
+      <c r="FU11" s="39"/>
     </row>
-    <row r="12" spans="1:165" ht="65.55" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:177" ht="65.55" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B12" s="12" t="s">
         <v>32</v>
       </c>
@@ -5696,8 +5928,20 @@
       <c r="FG12" s="22"/>
       <c r="FH12" s="22"/>
       <c r="FI12" s="39"/>
+      <c r="FJ12" s="37"/>
+      <c r="FK12" s="38"/>
+      <c r="FL12" s="22"/>
+      <c r="FM12" s="22"/>
+      <c r="FN12" s="22"/>
+      <c r="FO12" s="22"/>
+      <c r="FP12" s="22"/>
+      <c r="FQ12" s="22"/>
+      <c r="FR12" s="22"/>
+      <c r="FS12" s="22"/>
+      <c r="FT12" s="22"/>
+      <c r="FU12" s="39"/>
     </row>
-    <row r="13" spans="1:165" ht="55.35" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:177" ht="55.35" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B13" s="12" t="s">
         <v>33</v>
       </c>
@@ -5874,8 +6118,20 @@
       <c r="FG13" s="22"/>
       <c r="FH13" s="22"/>
       <c r="FI13" s="39"/>
+      <c r="FJ13" s="37"/>
+      <c r="FK13" s="38"/>
+      <c r="FL13" s="22"/>
+      <c r="FM13" s="22"/>
+      <c r="FN13" s="22"/>
+      <c r="FO13" s="22"/>
+      <c r="FP13" s="22"/>
+      <c r="FQ13" s="22"/>
+      <c r="FR13" s="22"/>
+      <c r="FS13" s="22"/>
+      <c r="FT13" s="22"/>
+      <c r="FU13" s="39"/>
     </row>
-    <row r="14" spans="1:165" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:177" x14ac:dyDescent="0.45">
       <c r="B14" s="45" t="s">
         <v>65</v>
       </c>
@@ -6042,8 +6298,20 @@
       <c r="FG14" s="22"/>
       <c r="FH14" s="22"/>
       <c r="FI14" s="39"/>
+      <c r="FJ14" s="37"/>
+      <c r="FK14" s="38"/>
+      <c r="FL14" s="22"/>
+      <c r="FM14" s="22"/>
+      <c r="FN14" s="22"/>
+      <c r="FO14" s="22"/>
+      <c r="FP14" s="22"/>
+      <c r="FQ14" s="22"/>
+      <c r="FR14" s="22"/>
+      <c r="FS14" s="22"/>
+      <c r="FT14" s="22"/>
+      <c r="FU14" s="39"/>
     </row>
-    <row r="15" spans="1:165" s="26" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:177" s="26" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A15" s="1"/>
       <c r="B15" s="23"/>
       <c r="C15" s="24" t="s">
@@ -6211,8 +6479,20 @@
       <c r="FG15" s="43"/>
       <c r="FH15" s="43"/>
       <c r="FI15" s="44"/>
+      <c r="FJ15" s="40"/>
+      <c r="FK15" s="41"/>
+      <c r="FL15" s="42"/>
+      <c r="FM15" s="42"/>
+      <c r="FN15" s="42"/>
+      <c r="FO15" s="42"/>
+      <c r="FP15" s="42"/>
+      <c r="FQ15" s="42"/>
+      <c r="FR15" s="42"/>
+      <c r="FS15" s="43"/>
+      <c r="FT15" s="43"/>
+      <c r="FU15" s="44"/>
     </row>
-    <row r="16" spans="1:165" s="26" customFormat="1" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:177" s="26" customFormat="1" ht="30.75" x14ac:dyDescent="0.45">
       <c r="A16" s="1"/>
       <c r="B16" s="23"/>
       <c r="C16" s="16" t="s">
@@ -6380,8 +6660,20 @@
       <c r="FG16" s="43"/>
       <c r="FH16" s="43"/>
       <c r="FI16" s="44"/>
+      <c r="FJ16" s="40"/>
+      <c r="FK16" s="41"/>
+      <c r="FL16" s="42"/>
+      <c r="FM16" s="42"/>
+      <c r="FN16" s="42"/>
+      <c r="FO16" s="42"/>
+      <c r="FP16" s="42"/>
+      <c r="FQ16" s="42"/>
+      <c r="FR16" s="42"/>
+      <c r="FS16" s="43"/>
+      <c r="FT16" s="43"/>
+      <c r="FU16" s="44"/>
     </row>
-    <row r="17" spans="1:165" s="26" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:177" s="26" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A17" s="1"/>
       <c r="B17" s="23"/>
       <c r="C17" s="24" t="s">
@@ -6549,8 +6841,20 @@
       <c r="FG17" s="43"/>
       <c r="FH17" s="43"/>
       <c r="FI17" s="44"/>
+      <c r="FJ17" s="40"/>
+      <c r="FK17" s="41"/>
+      <c r="FL17" s="42"/>
+      <c r="FM17" s="42"/>
+      <c r="FN17" s="42"/>
+      <c r="FO17" s="42"/>
+      <c r="FP17" s="42"/>
+      <c r="FQ17" s="42"/>
+      <c r="FR17" s="42"/>
+      <c r="FS17" s="43"/>
+      <c r="FT17" s="43"/>
+      <c r="FU17" s="44"/>
     </row>
-    <row r="18" spans="1:165" s="26" customFormat="1" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:177" s="26" customFormat="1" ht="30.75" x14ac:dyDescent="0.45">
       <c r="A18" s="1"/>
       <c r="B18" s="23"/>
       <c r="C18" s="16" t="s">
@@ -6718,8 +7022,20 @@
       <c r="FG18" s="43"/>
       <c r="FH18" s="43"/>
       <c r="FI18" s="44"/>
+      <c r="FJ18" s="40"/>
+      <c r="FK18" s="41"/>
+      <c r="FL18" s="42"/>
+      <c r="FM18" s="42"/>
+      <c r="FN18" s="42"/>
+      <c r="FO18" s="42"/>
+      <c r="FP18" s="42"/>
+      <c r="FQ18" s="42"/>
+      <c r="FR18" s="42"/>
+      <c r="FS18" s="43"/>
+      <c r="FT18" s="43"/>
+      <c r="FU18" s="44"/>
     </row>
-    <row r="19" spans="1:165" s="26" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:177" s="26" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A19" s="1"/>
       <c r="B19" s="23"/>
       <c r="C19" s="24" t="s">
@@ -6887,8 +7203,20 @@
       <c r="FG19" s="43"/>
       <c r="FH19" s="43"/>
       <c r="FI19" s="44"/>
+      <c r="FJ19" s="40"/>
+      <c r="FK19" s="41"/>
+      <c r="FL19" s="42"/>
+      <c r="FM19" s="42"/>
+      <c r="FN19" s="42"/>
+      <c r="FO19" s="42"/>
+      <c r="FP19" s="42"/>
+      <c r="FQ19" s="42"/>
+      <c r="FR19" s="42"/>
+      <c r="FS19" s="43"/>
+      <c r="FT19" s="43"/>
+      <c r="FU19" s="44"/>
     </row>
-    <row r="20" spans="1:165" s="26" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:177" s="26" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A20" s="1"/>
       <c r="B20" s="23"/>
       <c r="C20" s="24" t="s">
@@ -7056,8 +7384,20 @@
       <c r="FG20" s="43"/>
       <c r="FH20" s="43"/>
       <c r="FI20" s="44"/>
+      <c r="FJ20" s="40"/>
+      <c r="FK20" s="41"/>
+      <c r="FL20" s="42"/>
+      <c r="FM20" s="42"/>
+      <c r="FN20" s="42"/>
+      <c r="FO20" s="42"/>
+      <c r="FP20" s="42"/>
+      <c r="FQ20" s="42"/>
+      <c r="FR20" s="42"/>
+      <c r="FS20" s="43"/>
+      <c r="FT20" s="43"/>
+      <c r="FU20" s="44"/>
     </row>
-    <row r="21" spans="1:165" s="26" customFormat="1" ht="76.900000000000006" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:177" s="26" customFormat="1" ht="76.900000000000006" x14ac:dyDescent="0.45">
       <c r="A21" s="1"/>
       <c r="B21" s="23"/>
       <c r="C21" s="16" t="s">
@@ -7225,374 +7565,412 @@
       <c r="FG21" s="43"/>
       <c r="FH21" s="43"/>
       <c r="FI21" s="44"/>
+      <c r="FJ21" s="40"/>
+      <c r="FK21" s="41"/>
+      <c r="FL21" s="42"/>
+      <c r="FM21" s="42"/>
+      <c r="FN21" s="42"/>
+      <c r="FO21" s="42"/>
+      <c r="FP21" s="42"/>
+      <c r="FQ21" s="42"/>
+      <c r="FR21" s="42"/>
+      <c r="FS21" s="43"/>
+      <c r="FT21" s="43"/>
+      <c r="FU21" s="44"/>
     </row>
-    <row r="22" spans="1:165" s="2" customFormat="1" ht="84" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:177" s="2" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="1"/>
-      <c r="B22" s="72" t="s">
+      <c r="B22" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="73"/>
-      <c r="D22" s="70" t="s">
+      <c r="C22" s="74"/>
+      <c r="D22" s="71" t="s">
         <v>28</v>
       </c>
-      <c r="E22" s="70"/>
-      <c r="F22" s="70"/>
-      <c r="G22" s="70"/>
-      <c r="H22" s="70"/>
-      <c r="I22" s="71"/>
-      <c r="J22" s="63"/>
-      <c r="K22" s="64"/>
-      <c r="L22" s="65"/>
-      <c r="M22" s="65"/>
-      <c r="N22" s="65"/>
-      <c r="O22" s="65"/>
-      <c r="P22" s="65"/>
-      <c r="Q22" s="65"/>
-      <c r="R22" s="65"/>
-      <c r="S22" s="66"/>
-      <c r="T22" s="66"/>
-      <c r="U22" s="67"/>
-      <c r="V22" s="63"/>
-      <c r="W22" s="64"/>
-      <c r="X22" s="65"/>
-      <c r="Y22" s="65"/>
-      <c r="Z22" s="65"/>
-      <c r="AA22" s="65"/>
-      <c r="AB22" s="65"/>
-      <c r="AC22" s="65"/>
-      <c r="AD22" s="65"/>
-      <c r="AE22" s="66"/>
-      <c r="AF22" s="66"/>
-      <c r="AG22" s="67"/>
-      <c r="AH22" s="63"/>
-      <c r="AI22" s="64"/>
-      <c r="AJ22" s="65"/>
-      <c r="AK22" s="65"/>
-      <c r="AL22" s="65"/>
-      <c r="AM22" s="65"/>
-      <c r="AN22" s="65"/>
-      <c r="AO22" s="65"/>
-      <c r="AP22" s="65"/>
-      <c r="AQ22" s="66"/>
-      <c r="AR22" s="66"/>
-      <c r="AS22" s="67"/>
-      <c r="AT22" s="63"/>
-      <c r="AU22" s="64"/>
-      <c r="AV22" s="65"/>
-      <c r="AW22" s="65"/>
-      <c r="AX22" s="65"/>
-      <c r="AY22" s="65"/>
-      <c r="AZ22" s="65"/>
-      <c r="BA22" s="65"/>
-      <c r="BB22" s="65"/>
-      <c r="BC22" s="66"/>
-      <c r="BD22" s="66"/>
-      <c r="BE22" s="67"/>
-      <c r="BF22" s="63"/>
-      <c r="BG22" s="64"/>
-      <c r="BH22" s="65"/>
-      <c r="BI22" s="65"/>
-      <c r="BJ22" s="65"/>
-      <c r="BK22" s="65"/>
-      <c r="BL22" s="65"/>
-      <c r="BM22" s="65"/>
-      <c r="BN22" s="65"/>
-      <c r="BO22" s="66"/>
-      <c r="BP22" s="66"/>
-      <c r="BQ22" s="67"/>
-      <c r="BR22" s="63"/>
-      <c r="BS22" s="64"/>
-      <c r="BT22" s="65"/>
-      <c r="BU22" s="65"/>
-      <c r="BV22" s="65"/>
-      <c r="BW22" s="65"/>
-      <c r="BX22" s="65"/>
-      <c r="BY22" s="65"/>
-      <c r="BZ22" s="65"/>
-      <c r="CA22" s="66"/>
-      <c r="CB22" s="66"/>
-      <c r="CC22" s="67"/>
-      <c r="CD22" s="63"/>
-      <c r="CE22" s="64"/>
-      <c r="CF22" s="65"/>
-      <c r="CG22" s="65"/>
-      <c r="CH22" s="65"/>
-      <c r="CI22" s="65"/>
-      <c r="CJ22" s="65"/>
-      <c r="CK22" s="65"/>
-      <c r="CL22" s="65"/>
-      <c r="CM22" s="66"/>
-      <c r="CN22" s="66"/>
-      <c r="CO22" s="67"/>
-      <c r="CP22" s="63"/>
-      <c r="CQ22" s="64"/>
-      <c r="CR22" s="65"/>
-      <c r="CS22" s="65"/>
-      <c r="CT22" s="65"/>
-      <c r="CU22" s="65"/>
-      <c r="CV22" s="65"/>
-      <c r="CW22" s="65"/>
-      <c r="CX22" s="65"/>
-      <c r="CY22" s="66"/>
-      <c r="CZ22" s="66"/>
-      <c r="DA22" s="67"/>
-      <c r="DB22" s="63"/>
-      <c r="DC22" s="64"/>
-      <c r="DD22" s="65"/>
-      <c r="DE22" s="65"/>
-      <c r="DF22" s="65"/>
-      <c r="DG22" s="65"/>
-      <c r="DH22" s="65"/>
-      <c r="DI22" s="65"/>
-      <c r="DJ22" s="65"/>
-      <c r="DK22" s="66"/>
-      <c r="DL22" s="66"/>
-      <c r="DM22" s="67"/>
-      <c r="DN22" s="63"/>
-      <c r="DO22" s="64"/>
-      <c r="DP22" s="65"/>
-      <c r="DQ22" s="65"/>
-      <c r="DR22" s="65"/>
-      <c r="DS22" s="65"/>
-      <c r="DT22" s="65"/>
-      <c r="DU22" s="65"/>
-      <c r="DV22" s="65"/>
-      <c r="DW22" s="66"/>
-      <c r="DX22" s="66"/>
-      <c r="DY22" s="67"/>
-      <c r="DZ22" s="63"/>
-      <c r="EA22" s="64"/>
-      <c r="EB22" s="65"/>
-      <c r="EC22" s="65"/>
-      <c r="ED22" s="65"/>
-      <c r="EE22" s="65"/>
-      <c r="EF22" s="65"/>
-      <c r="EG22" s="65"/>
-      <c r="EH22" s="65"/>
-      <c r="EI22" s="66"/>
-      <c r="EJ22" s="66"/>
-      <c r="EK22" s="67"/>
-      <c r="EL22" s="63"/>
-      <c r="EM22" s="64"/>
-      <c r="EN22" s="65"/>
-      <c r="EO22" s="65"/>
-      <c r="EP22" s="65"/>
-      <c r="EQ22" s="65"/>
-      <c r="ER22" s="65"/>
-      <c r="ES22" s="65"/>
-      <c r="ET22" s="65"/>
-      <c r="EU22" s="66"/>
-      <c r="EV22" s="66"/>
-      <c r="EW22" s="67"/>
-      <c r="EX22" s="63"/>
-      <c r="EY22" s="64"/>
-      <c r="EZ22" s="65"/>
-      <c r="FA22" s="65"/>
-      <c r="FB22" s="65"/>
-      <c r="FC22" s="65"/>
-      <c r="FD22" s="65"/>
-      <c r="FE22" s="65"/>
-      <c r="FF22" s="65"/>
-      <c r="FG22" s="66"/>
-      <c r="FH22" s="66"/>
-      <c r="FI22" s="67"/>
+      <c r="E22" s="71"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="71"/>
+      <c r="I22" s="72"/>
+      <c r="J22" s="64"/>
+      <c r="K22" s="65"/>
+      <c r="L22" s="66"/>
+      <c r="M22" s="66"/>
+      <c r="N22" s="66"/>
+      <c r="O22" s="66"/>
+      <c r="P22" s="66"/>
+      <c r="Q22" s="66"/>
+      <c r="R22" s="66"/>
+      <c r="S22" s="67"/>
+      <c r="T22" s="67"/>
+      <c r="U22" s="68"/>
+      <c r="V22" s="64"/>
+      <c r="W22" s="65"/>
+      <c r="X22" s="66"/>
+      <c r="Y22" s="66"/>
+      <c r="Z22" s="66"/>
+      <c r="AA22" s="66"/>
+      <c r="AB22" s="66"/>
+      <c r="AC22" s="66"/>
+      <c r="AD22" s="66"/>
+      <c r="AE22" s="67"/>
+      <c r="AF22" s="67"/>
+      <c r="AG22" s="68"/>
+      <c r="AH22" s="64"/>
+      <c r="AI22" s="65"/>
+      <c r="AJ22" s="66"/>
+      <c r="AK22" s="66"/>
+      <c r="AL22" s="66"/>
+      <c r="AM22" s="66"/>
+      <c r="AN22" s="66"/>
+      <c r="AO22" s="66"/>
+      <c r="AP22" s="66"/>
+      <c r="AQ22" s="67"/>
+      <c r="AR22" s="67"/>
+      <c r="AS22" s="68"/>
+      <c r="AT22" s="64"/>
+      <c r="AU22" s="65"/>
+      <c r="AV22" s="66"/>
+      <c r="AW22" s="66"/>
+      <c r="AX22" s="66"/>
+      <c r="AY22" s="66"/>
+      <c r="AZ22" s="66"/>
+      <c r="BA22" s="66"/>
+      <c r="BB22" s="66"/>
+      <c r="BC22" s="67"/>
+      <c r="BD22" s="67"/>
+      <c r="BE22" s="68"/>
+      <c r="BF22" s="64"/>
+      <c r="BG22" s="65"/>
+      <c r="BH22" s="66"/>
+      <c r="BI22" s="66"/>
+      <c r="BJ22" s="66"/>
+      <c r="BK22" s="66"/>
+      <c r="BL22" s="66"/>
+      <c r="BM22" s="66"/>
+      <c r="BN22" s="66"/>
+      <c r="BO22" s="67"/>
+      <c r="BP22" s="67"/>
+      <c r="BQ22" s="68"/>
+      <c r="BR22" s="64"/>
+      <c r="BS22" s="65"/>
+      <c r="BT22" s="66"/>
+      <c r="BU22" s="66"/>
+      <c r="BV22" s="66"/>
+      <c r="BW22" s="66"/>
+      <c r="BX22" s="66"/>
+      <c r="BY22" s="66"/>
+      <c r="BZ22" s="66"/>
+      <c r="CA22" s="67"/>
+      <c r="CB22" s="67"/>
+      <c r="CC22" s="68"/>
+      <c r="CD22" s="64"/>
+      <c r="CE22" s="65"/>
+      <c r="CF22" s="66"/>
+      <c r="CG22" s="66"/>
+      <c r="CH22" s="66"/>
+      <c r="CI22" s="66"/>
+      <c r="CJ22" s="66"/>
+      <c r="CK22" s="66"/>
+      <c r="CL22" s="66"/>
+      <c r="CM22" s="67"/>
+      <c r="CN22" s="67"/>
+      <c r="CO22" s="68"/>
+      <c r="CP22" s="64"/>
+      <c r="CQ22" s="65"/>
+      <c r="CR22" s="66"/>
+      <c r="CS22" s="66"/>
+      <c r="CT22" s="66"/>
+      <c r="CU22" s="66"/>
+      <c r="CV22" s="66"/>
+      <c r="CW22" s="66"/>
+      <c r="CX22" s="66"/>
+      <c r="CY22" s="67"/>
+      <c r="CZ22" s="67"/>
+      <c r="DA22" s="68"/>
+      <c r="DB22" s="64"/>
+      <c r="DC22" s="65"/>
+      <c r="DD22" s="66"/>
+      <c r="DE22" s="66"/>
+      <c r="DF22" s="66"/>
+      <c r="DG22" s="66"/>
+      <c r="DH22" s="66"/>
+      <c r="DI22" s="66"/>
+      <c r="DJ22" s="66"/>
+      <c r="DK22" s="67"/>
+      <c r="DL22" s="67"/>
+      <c r="DM22" s="68"/>
+      <c r="DN22" s="64"/>
+      <c r="DO22" s="65"/>
+      <c r="DP22" s="66"/>
+      <c r="DQ22" s="66"/>
+      <c r="DR22" s="66"/>
+      <c r="DS22" s="66"/>
+      <c r="DT22" s="66"/>
+      <c r="DU22" s="66"/>
+      <c r="DV22" s="66"/>
+      <c r="DW22" s="67"/>
+      <c r="DX22" s="67"/>
+      <c r="DY22" s="68"/>
+      <c r="DZ22" s="64"/>
+      <c r="EA22" s="65"/>
+      <c r="EB22" s="66"/>
+      <c r="EC22" s="66"/>
+      <c r="ED22" s="66"/>
+      <c r="EE22" s="66"/>
+      <c r="EF22" s="66"/>
+      <c r="EG22" s="66"/>
+      <c r="EH22" s="66"/>
+      <c r="EI22" s="67"/>
+      <c r="EJ22" s="67"/>
+      <c r="EK22" s="68"/>
+      <c r="EL22" s="64"/>
+      <c r="EM22" s="65"/>
+      <c r="EN22" s="66"/>
+      <c r="EO22" s="66"/>
+      <c r="EP22" s="66"/>
+      <c r="EQ22" s="66"/>
+      <c r="ER22" s="66"/>
+      <c r="ES22" s="66"/>
+      <c r="ET22" s="66"/>
+      <c r="EU22" s="67"/>
+      <c r="EV22" s="67"/>
+      <c r="EW22" s="68"/>
+      <c r="EX22" s="64"/>
+      <c r="EY22" s="65"/>
+      <c r="EZ22" s="66"/>
+      <c r="FA22" s="66"/>
+      <c r="FB22" s="66"/>
+      <c r="FC22" s="66"/>
+      <c r="FD22" s="66"/>
+      <c r="FE22" s="66"/>
+      <c r="FF22" s="66"/>
+      <c r="FG22" s="67"/>
+      <c r="FH22" s="67"/>
+      <c r="FI22" s="68"/>
+      <c r="FJ22" s="64"/>
+      <c r="FK22" s="65"/>
+      <c r="FL22" s="66"/>
+      <c r="FM22" s="66"/>
+      <c r="FN22" s="66"/>
+      <c r="FO22" s="66"/>
+      <c r="FP22" s="66"/>
+      <c r="FQ22" s="66"/>
+      <c r="FR22" s="66"/>
+      <c r="FS22" s="67"/>
+      <c r="FT22" s="67"/>
+      <c r="FU22" s="68"/>
     </row>
-    <row r="23" spans="1:165" s="2" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:177" s="2" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="1"/>
-      <c r="B23" s="74" t="s">
+      <c r="B23" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="74"/>
-      <c r="D23" s="74"/>
-      <c r="E23" s="74"/>
-      <c r="F23" s="74"/>
-      <c r="G23" s="74"/>
-      <c r="H23" s="74"/>
-      <c r="I23" s="74"/>
-      <c r="J23" s="53">
+      <c r="C23" s="75"/>
+      <c r="D23" s="75"/>
+      <c r="E23" s="75"/>
+      <c r="F23" s="75"/>
+      <c r="G23" s="75"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="75"/>
+      <c r="J23" s="54">
         <v>0</v>
       </c>
-      <c r="K23" s="53"/>
-      <c r="L23" s="53"/>
-      <c r="M23" s="53"/>
-      <c r="N23" s="53"/>
-      <c r="O23" s="53"/>
-      <c r="P23" s="53"/>
-      <c r="Q23" s="53"/>
-      <c r="R23" s="53"/>
-      <c r="S23" s="53"/>
-      <c r="T23" s="53"/>
-      <c r="U23" s="53"/>
-      <c r="V23" s="53">
+      <c r="K23" s="54"/>
+      <c r="L23" s="54"/>
+      <c r="M23" s="54"/>
+      <c r="N23" s="54"/>
+      <c r="O23" s="54"/>
+      <c r="P23" s="54"/>
+      <c r="Q23" s="54"/>
+      <c r="R23" s="54"/>
+      <c r="S23" s="54"/>
+      <c r="T23" s="54"/>
+      <c r="U23" s="54"/>
+      <c r="V23" s="54">
         <v>0</v>
       </c>
-      <c r="W23" s="53"/>
-      <c r="X23" s="53"/>
-      <c r="Y23" s="53"/>
-      <c r="Z23" s="53"/>
-      <c r="AA23" s="53"/>
-      <c r="AB23" s="53"/>
-      <c r="AC23" s="53"/>
-      <c r="AD23" s="53"/>
-      <c r="AE23" s="53"/>
-      <c r="AF23" s="53"/>
-      <c r="AG23" s="53"/>
-      <c r="AH23" s="53">
+      <c r="W23" s="54"/>
+      <c r="X23" s="54"/>
+      <c r="Y23" s="54"/>
+      <c r="Z23" s="54"/>
+      <c r="AA23" s="54"/>
+      <c r="AB23" s="54"/>
+      <c r="AC23" s="54"/>
+      <c r="AD23" s="54"/>
+      <c r="AE23" s="54"/>
+      <c r="AF23" s="54"/>
+      <c r="AG23" s="54"/>
+      <c r="AH23" s="54">
         <v>0</v>
       </c>
-      <c r="AI23" s="53"/>
-      <c r="AJ23" s="53"/>
-      <c r="AK23" s="53"/>
-      <c r="AL23" s="53"/>
-      <c r="AM23" s="53"/>
-      <c r="AN23" s="53"/>
-      <c r="AO23" s="53"/>
-      <c r="AP23" s="53"/>
-      <c r="AQ23" s="53"/>
-      <c r="AR23" s="53"/>
-      <c r="AS23" s="53"/>
-      <c r="AT23" s="53">
+      <c r="AI23" s="54"/>
+      <c r="AJ23" s="54"/>
+      <c r="AK23" s="54"/>
+      <c r="AL23" s="54"/>
+      <c r="AM23" s="54"/>
+      <c r="AN23" s="54"/>
+      <c r="AO23" s="54"/>
+      <c r="AP23" s="54"/>
+      <c r="AQ23" s="54"/>
+      <c r="AR23" s="54"/>
+      <c r="AS23" s="54"/>
+      <c r="AT23" s="54">
         <v>0</v>
       </c>
-      <c r="AU23" s="53"/>
-      <c r="AV23" s="53"/>
-      <c r="AW23" s="53"/>
-      <c r="AX23" s="53"/>
-      <c r="AY23" s="53"/>
-      <c r="AZ23" s="53"/>
-      <c r="BA23" s="53"/>
-      <c r="BB23" s="53"/>
-      <c r="BC23" s="53"/>
-      <c r="BD23" s="53"/>
-      <c r="BE23" s="53"/>
-      <c r="BF23" s="53">
+      <c r="AU23" s="54"/>
+      <c r="AV23" s="54"/>
+      <c r="AW23" s="54"/>
+      <c r="AX23" s="54"/>
+      <c r="AY23" s="54"/>
+      <c r="AZ23" s="54"/>
+      <c r="BA23" s="54"/>
+      <c r="BB23" s="54"/>
+      <c r="BC23" s="54"/>
+      <c r="BD23" s="54"/>
+      <c r="BE23" s="54"/>
+      <c r="BF23" s="54">
         <v>0</v>
       </c>
-      <c r="BG23" s="53"/>
-      <c r="BH23" s="53"/>
-      <c r="BI23" s="53"/>
-      <c r="BJ23" s="53"/>
-      <c r="BK23" s="53"/>
-      <c r="BL23" s="53"/>
-      <c r="BM23" s="53"/>
-      <c r="BN23" s="53"/>
-      <c r="BO23" s="53"/>
-      <c r="BP23" s="53"/>
-      <c r="BQ23" s="53"/>
-      <c r="BR23" s="53">
+      <c r="BG23" s="54"/>
+      <c r="BH23" s="54"/>
+      <c r="BI23" s="54"/>
+      <c r="BJ23" s="54"/>
+      <c r="BK23" s="54"/>
+      <c r="BL23" s="54"/>
+      <c r="BM23" s="54"/>
+      <c r="BN23" s="54"/>
+      <c r="BO23" s="54"/>
+      <c r="BP23" s="54"/>
+      <c r="BQ23" s="54"/>
+      <c r="BR23" s="54">
         <v>0</v>
       </c>
-      <c r="BS23" s="53"/>
-      <c r="BT23" s="53"/>
-      <c r="BU23" s="53"/>
-      <c r="BV23" s="53"/>
-      <c r="BW23" s="53"/>
-      <c r="BX23" s="53"/>
-      <c r="BY23" s="53"/>
-      <c r="BZ23" s="53"/>
-      <c r="CA23" s="53"/>
-      <c r="CB23" s="53"/>
-      <c r="CC23" s="53"/>
-      <c r="CD23" s="53">
+      <c r="BS23" s="54"/>
+      <c r="BT23" s="54"/>
+      <c r="BU23" s="54"/>
+      <c r="BV23" s="54"/>
+      <c r="BW23" s="54"/>
+      <c r="BX23" s="54"/>
+      <c r="BY23" s="54"/>
+      <c r="BZ23" s="54"/>
+      <c r="CA23" s="54"/>
+      <c r="CB23" s="54"/>
+      <c r="CC23" s="54"/>
+      <c r="CD23" s="54">
         <v>0</v>
       </c>
-      <c r="CE23" s="53"/>
-      <c r="CF23" s="53"/>
-      <c r="CG23" s="53"/>
-      <c r="CH23" s="53"/>
-      <c r="CI23" s="53"/>
-      <c r="CJ23" s="53"/>
-      <c r="CK23" s="53"/>
-      <c r="CL23" s="53"/>
-      <c r="CM23" s="53"/>
-      <c r="CN23" s="53"/>
-      <c r="CO23" s="53"/>
-      <c r="CP23" s="53">
+      <c r="CE23" s="54"/>
+      <c r="CF23" s="54"/>
+      <c r="CG23" s="54"/>
+      <c r="CH23" s="54"/>
+      <c r="CI23" s="54"/>
+      <c r="CJ23" s="54"/>
+      <c r="CK23" s="54"/>
+      <c r="CL23" s="54"/>
+      <c r="CM23" s="54"/>
+      <c r="CN23" s="54"/>
+      <c r="CO23" s="54"/>
+      <c r="CP23" s="54">
         <v>0</v>
       </c>
-      <c r="CQ23" s="53"/>
-      <c r="CR23" s="53"/>
-      <c r="CS23" s="53"/>
-      <c r="CT23" s="53"/>
-      <c r="CU23" s="53"/>
-      <c r="CV23" s="53"/>
-      <c r="CW23" s="53"/>
-      <c r="CX23" s="53"/>
-      <c r="CY23" s="53"/>
-      <c r="CZ23" s="53"/>
-      <c r="DA23" s="53"/>
-      <c r="DB23" s="53">
+      <c r="CQ23" s="54"/>
+      <c r="CR23" s="54"/>
+      <c r="CS23" s="54"/>
+      <c r="CT23" s="54"/>
+      <c r="CU23" s="54"/>
+      <c r="CV23" s="54"/>
+      <c r="CW23" s="54"/>
+      <c r="CX23" s="54"/>
+      <c r="CY23" s="54"/>
+      <c r="CZ23" s="54"/>
+      <c r="DA23" s="54"/>
+      <c r="DB23" s="54">
         <v>0</v>
       </c>
-      <c r="DC23" s="53"/>
-      <c r="DD23" s="53"/>
-      <c r="DE23" s="53"/>
-      <c r="DF23" s="53"/>
-      <c r="DG23" s="53"/>
-      <c r="DH23" s="53"/>
-      <c r="DI23" s="53"/>
-      <c r="DJ23" s="53"/>
-      <c r="DK23" s="53"/>
-      <c r="DL23" s="53"/>
-      <c r="DM23" s="53"/>
-      <c r="DN23" s="53">
+      <c r="DC23" s="54"/>
+      <c r="DD23" s="54"/>
+      <c r="DE23" s="54"/>
+      <c r="DF23" s="54"/>
+      <c r="DG23" s="54"/>
+      <c r="DH23" s="54"/>
+      <c r="DI23" s="54"/>
+      <c r="DJ23" s="54"/>
+      <c r="DK23" s="54"/>
+      <c r="DL23" s="54"/>
+      <c r="DM23" s="54"/>
+      <c r="DN23" s="54">
         <v>0</v>
       </c>
-      <c r="DO23" s="53"/>
-      <c r="DP23" s="53"/>
-      <c r="DQ23" s="53"/>
-      <c r="DR23" s="53"/>
-      <c r="DS23" s="53"/>
-      <c r="DT23" s="53"/>
-      <c r="DU23" s="53"/>
-      <c r="DV23" s="53"/>
-      <c r="DW23" s="53"/>
-      <c r="DX23" s="53"/>
-      <c r="DY23" s="53"/>
-      <c r="DZ23" s="53">
+      <c r="DO23" s="54"/>
+      <c r="DP23" s="54"/>
+      <c r="DQ23" s="54"/>
+      <c r="DR23" s="54"/>
+      <c r="DS23" s="54"/>
+      <c r="DT23" s="54"/>
+      <c r="DU23" s="54"/>
+      <c r="DV23" s="54"/>
+      <c r="DW23" s="54"/>
+      <c r="DX23" s="54"/>
+      <c r="DY23" s="54"/>
+      <c r="DZ23" s="54">
         <v>0</v>
       </c>
-      <c r="EA23" s="53"/>
-      <c r="EB23" s="53"/>
-      <c r="EC23" s="53"/>
-      <c r="ED23" s="53"/>
-      <c r="EE23" s="53"/>
-      <c r="EF23" s="53"/>
-      <c r="EG23" s="53"/>
-      <c r="EH23" s="53"/>
-      <c r="EI23" s="53"/>
-      <c r="EJ23" s="53"/>
-      <c r="EK23" s="53"/>
-      <c r="EL23" s="53">
+      <c r="EA23" s="54"/>
+      <c r="EB23" s="54"/>
+      <c r="EC23" s="54"/>
+      <c r="ED23" s="54"/>
+      <c r="EE23" s="54"/>
+      <c r="EF23" s="54"/>
+      <c r="EG23" s="54"/>
+      <c r="EH23" s="54"/>
+      <c r="EI23" s="54"/>
+      <c r="EJ23" s="54"/>
+      <c r="EK23" s="54"/>
+      <c r="EL23" s="54">
         <v>0</v>
       </c>
-      <c r="EM23" s="53"/>
-      <c r="EN23" s="53"/>
-      <c r="EO23" s="53"/>
-      <c r="EP23" s="53"/>
-      <c r="EQ23" s="53"/>
-      <c r="ER23" s="53"/>
-      <c r="ES23" s="53"/>
-      <c r="ET23" s="53"/>
-      <c r="EU23" s="53"/>
-      <c r="EV23" s="53"/>
-      <c r="EW23" s="53"/>
-      <c r="EX23" s="53">
+      <c r="EM23" s="54"/>
+      <c r="EN23" s="54"/>
+      <c r="EO23" s="54"/>
+      <c r="EP23" s="54"/>
+      <c r="EQ23" s="54"/>
+      <c r="ER23" s="54"/>
+      <c r="ES23" s="54"/>
+      <c r="ET23" s="54"/>
+      <c r="EU23" s="54"/>
+      <c r="EV23" s="54"/>
+      <c r="EW23" s="54"/>
+      <c r="EX23" s="54">
         <v>0</v>
       </c>
-      <c r="EY23" s="53"/>
-      <c r="EZ23" s="53"/>
-      <c r="FA23" s="53"/>
-      <c r="FB23" s="53"/>
-      <c r="FC23" s="53"/>
-      <c r="FD23" s="53"/>
-      <c r="FE23" s="53"/>
-      <c r="FF23" s="53"/>
-      <c r="FG23" s="53"/>
-      <c r="FH23" s="53"/>
-      <c r="FI23" s="53"/>
+      <c r="EY23" s="54"/>
+      <c r="EZ23" s="54"/>
+      <c r="FA23" s="54"/>
+      <c r="FB23" s="54"/>
+      <c r="FC23" s="54"/>
+      <c r="FD23" s="54"/>
+      <c r="FE23" s="54"/>
+      <c r="FF23" s="54"/>
+      <c r="FG23" s="54"/>
+      <c r="FH23" s="54"/>
+      <c r="FI23" s="54"/>
+      <c r="FJ23" s="54">
+        <v>0</v>
+      </c>
+      <c r="FK23" s="54"/>
+      <c r="FL23" s="54"/>
+      <c r="FM23" s="54"/>
+      <c r="FN23" s="54"/>
+      <c r="FO23" s="54"/>
+      <c r="FP23" s="54"/>
+      <c r="FQ23" s="54"/>
+      <c r="FR23" s="54"/>
+      <c r="FS23" s="54"/>
+      <c r="FT23" s="54"/>
+      <c r="FU23" s="54"/>
     </row>
-    <row r="24" spans="1:165" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
@@ -7757,8 +8135,20 @@
       <c r="FG24" s="5"/>
       <c r="FH24" s="5"/>
       <c r="FI24" s="5"/>
+      <c r="FJ24" s="5"/>
+      <c r="FK24" s="5"/>
+      <c r="FL24" s="5"/>
+      <c r="FM24" s="5"/>
+      <c r="FN24" s="5"/>
+      <c r="FO24" s="5"/>
+      <c r="FP24" s="5"/>
+      <c r="FQ24" s="5"/>
+      <c r="FR24" s="5"/>
+      <c r="FS24" s="5"/>
+      <c r="FT24" s="5"/>
+      <c r="FU24" s="5"/>
     </row>
-    <row r="25" spans="1:165" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B25" s="4"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
@@ -7923,8 +8313,20 @@
       <c r="FG25" s="5"/>
       <c r="FH25" s="5"/>
       <c r="FI25" s="5"/>
+      <c r="FJ25" s="5"/>
+      <c r="FK25" s="5"/>
+      <c r="FL25" s="5"/>
+      <c r="FM25" s="5"/>
+      <c r="FN25" s="5"/>
+      <c r="FO25" s="5"/>
+      <c r="FP25" s="5"/>
+      <c r="FQ25" s="5"/>
+      <c r="FR25" s="5"/>
+      <c r="FS25" s="5"/>
+      <c r="FT25" s="5"/>
+      <c r="FU25" s="5"/>
     </row>
-    <row r="26" spans="1:165" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B26" s="4"/>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
@@ -8089,8 +8491,20 @@
       <c r="FG26" s="5"/>
       <c r="FH26" s="5"/>
       <c r="FI26" s="5"/>
+      <c r="FJ26" s="5"/>
+      <c r="FK26" s="5"/>
+      <c r="FL26" s="5"/>
+      <c r="FM26" s="5"/>
+      <c r="FN26" s="5"/>
+      <c r="FO26" s="5"/>
+      <c r="FP26" s="5"/>
+      <c r="FQ26" s="5"/>
+      <c r="FR26" s="5"/>
+      <c r="FS26" s="5"/>
+      <c r="FT26" s="5"/>
+      <c r="FU26" s="5"/>
     </row>
-    <row r="27" spans="1:165" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B27" s="4"/>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
@@ -8255,8 +8669,20 @@
       <c r="FG27" s="5"/>
       <c r="FH27" s="5"/>
       <c r="FI27" s="5"/>
+      <c r="FJ27" s="5"/>
+      <c r="FK27" s="5"/>
+      <c r="FL27" s="5"/>
+      <c r="FM27" s="5"/>
+      <c r="FN27" s="5"/>
+      <c r="FO27" s="5"/>
+      <c r="FP27" s="5"/>
+      <c r="FQ27" s="5"/>
+      <c r="FR27" s="5"/>
+      <c r="FS27" s="5"/>
+      <c r="FT27" s="5"/>
+      <c r="FU27" s="5"/>
     </row>
-    <row r="28" spans="1:165" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B28" s="4"/>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
@@ -8421,8 +8847,20 @@
       <c r="FG28" s="5"/>
       <c r="FH28" s="5"/>
       <c r="FI28" s="5"/>
+      <c r="FJ28" s="5"/>
+      <c r="FK28" s="5"/>
+      <c r="FL28" s="5"/>
+      <c r="FM28" s="5"/>
+      <c r="FN28" s="5"/>
+      <c r="FO28" s="5"/>
+      <c r="FP28" s="5"/>
+      <c r="FQ28" s="5"/>
+      <c r="FR28" s="5"/>
+      <c r="FS28" s="5"/>
+      <c r="FT28" s="5"/>
+      <c r="FU28" s="5"/>
     </row>
-    <row r="29" spans="1:165" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B29" s="4"/>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
@@ -8587,8 +9025,20 @@
       <c r="FG29" s="5"/>
       <c r="FH29" s="5"/>
       <c r="FI29" s="5"/>
+      <c r="FJ29" s="5"/>
+      <c r="FK29" s="5"/>
+      <c r="FL29" s="5"/>
+      <c r="FM29" s="5"/>
+      <c r="FN29" s="5"/>
+      <c r="FO29" s="5"/>
+      <c r="FP29" s="5"/>
+      <c r="FQ29" s="5"/>
+      <c r="FR29" s="5"/>
+      <c r="FS29" s="5"/>
+      <c r="FT29" s="5"/>
+      <c r="FU29" s="5"/>
     </row>
-    <row r="30" spans="1:165" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B30" s="4"/>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
@@ -8753,8 +9203,20 @@
       <c r="FG30" s="5"/>
       <c r="FH30" s="5"/>
       <c r="FI30" s="5"/>
+      <c r="FJ30" s="5"/>
+      <c r="FK30" s="5"/>
+      <c r="FL30" s="5"/>
+      <c r="FM30" s="5"/>
+      <c r="FN30" s="5"/>
+      <c r="FO30" s="5"/>
+      <c r="FP30" s="5"/>
+      <c r="FQ30" s="5"/>
+      <c r="FR30" s="5"/>
+      <c r="FS30" s="5"/>
+      <c r="FT30" s="5"/>
+      <c r="FU30" s="5"/>
     </row>
-    <row r="31" spans="1:165" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B31" s="4"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
@@ -8919,8 +9381,20 @@
       <c r="FG31" s="5"/>
       <c r="FH31" s="5"/>
       <c r="FI31" s="5"/>
+      <c r="FJ31" s="5"/>
+      <c r="FK31" s="5"/>
+      <c r="FL31" s="5"/>
+      <c r="FM31" s="5"/>
+      <c r="FN31" s="5"/>
+      <c r="FO31" s="5"/>
+      <c r="FP31" s="5"/>
+      <c r="FQ31" s="5"/>
+      <c r="FR31" s="5"/>
+      <c r="FS31" s="5"/>
+      <c r="FT31" s="5"/>
+      <c r="FU31" s="5"/>
     </row>
-    <row r="32" spans="1:165" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B32" s="4"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -9085,8 +9559,20 @@
       <c r="FG32" s="5"/>
       <c r="FH32" s="5"/>
       <c r="FI32" s="5"/>
+      <c r="FJ32" s="5"/>
+      <c r="FK32" s="5"/>
+      <c r="FL32" s="5"/>
+      <c r="FM32" s="5"/>
+      <c r="FN32" s="5"/>
+      <c r="FO32" s="5"/>
+      <c r="FP32" s="5"/>
+      <c r="FQ32" s="5"/>
+      <c r="FR32" s="5"/>
+      <c r="FS32" s="5"/>
+      <c r="FT32" s="5"/>
+      <c r="FU32" s="5"/>
     </row>
-    <row r="33" spans="2:165" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B33" s="4"/>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
@@ -9251,8 +9737,20 @@
       <c r="FG33" s="5"/>
       <c r="FH33" s="5"/>
       <c r="FI33" s="5"/>
+      <c r="FJ33" s="5"/>
+      <c r="FK33" s="5"/>
+      <c r="FL33" s="5"/>
+      <c r="FM33" s="5"/>
+      <c r="FN33" s="5"/>
+      <c r="FO33" s="5"/>
+      <c r="FP33" s="5"/>
+      <c r="FQ33" s="5"/>
+      <c r="FR33" s="5"/>
+      <c r="FS33" s="5"/>
+      <c r="FT33" s="5"/>
+      <c r="FU33" s="5"/>
     </row>
-    <row r="34" spans="2:165" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B34" s="4"/>
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
@@ -9417,8 +9915,20 @@
       <c r="FG34" s="5"/>
       <c r="FH34" s="5"/>
       <c r="FI34" s="5"/>
+      <c r="FJ34" s="5"/>
+      <c r="FK34" s="5"/>
+      <c r="FL34" s="5"/>
+      <c r="FM34" s="5"/>
+      <c r="FN34" s="5"/>
+      <c r="FO34" s="5"/>
+      <c r="FP34" s="5"/>
+      <c r="FQ34" s="5"/>
+      <c r="FR34" s="5"/>
+      <c r="FS34" s="5"/>
+      <c r="FT34" s="5"/>
+      <c r="FU34" s="5"/>
     </row>
-    <row r="35" spans="2:165" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B35" s="4"/>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
@@ -9583,8 +10093,20 @@
       <c r="FG35" s="5"/>
       <c r="FH35" s="5"/>
       <c r="FI35" s="5"/>
+      <c r="FJ35" s="5"/>
+      <c r="FK35" s="5"/>
+      <c r="FL35" s="5"/>
+      <c r="FM35" s="5"/>
+      <c r="FN35" s="5"/>
+      <c r="FO35" s="5"/>
+      <c r="FP35" s="5"/>
+      <c r="FQ35" s="5"/>
+      <c r="FR35" s="5"/>
+      <c r="FS35" s="5"/>
+      <c r="FT35" s="5"/>
+      <c r="FU35" s="5"/>
     </row>
-    <row r="36" spans="2:165" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B36" s="4"/>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
@@ -9749,8 +10271,20 @@
       <c r="FG36" s="5"/>
       <c r="FH36" s="5"/>
       <c r="FI36" s="5"/>
+      <c r="FJ36" s="5"/>
+      <c r="FK36" s="5"/>
+      <c r="FL36" s="5"/>
+      <c r="FM36" s="5"/>
+      <c r="FN36" s="5"/>
+      <c r="FO36" s="5"/>
+      <c r="FP36" s="5"/>
+      <c r="FQ36" s="5"/>
+      <c r="FR36" s="5"/>
+      <c r="FS36" s="5"/>
+      <c r="FT36" s="5"/>
+      <c r="FU36" s="5"/>
     </row>
-    <row r="37" spans="2:165" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B37" s="4"/>
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
@@ -9915,8 +10449,20 @@
       <c r="FG37" s="5"/>
       <c r="FH37" s="5"/>
       <c r="FI37" s="5"/>
+      <c r="FJ37" s="5"/>
+      <c r="FK37" s="5"/>
+      <c r="FL37" s="5"/>
+      <c r="FM37" s="5"/>
+      <c r="FN37" s="5"/>
+      <c r="FO37" s="5"/>
+      <c r="FP37" s="5"/>
+      <c r="FQ37" s="5"/>
+      <c r="FR37" s="5"/>
+      <c r="FS37" s="5"/>
+      <c r="FT37" s="5"/>
+      <c r="FU37" s="5"/>
     </row>
-    <row r="38" spans="2:165" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B38" s="4"/>
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
@@ -10081,8 +10627,20 @@
       <c r="FG38" s="5"/>
       <c r="FH38" s="5"/>
       <c r="FI38" s="5"/>
+      <c r="FJ38" s="5"/>
+      <c r="FK38" s="5"/>
+      <c r="FL38" s="5"/>
+      <c r="FM38" s="5"/>
+      <c r="FN38" s="5"/>
+      <c r="FO38" s="5"/>
+      <c r="FP38" s="5"/>
+      <c r="FQ38" s="5"/>
+      <c r="FR38" s="5"/>
+      <c r="FS38" s="5"/>
+      <c r="FT38" s="5"/>
+      <c r="FU38" s="5"/>
     </row>
-    <row r="39" spans="2:165" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B39" s="4"/>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
@@ -10247,8 +10805,20 @@
       <c r="FG39" s="5"/>
       <c r="FH39" s="5"/>
       <c r="FI39" s="5"/>
+      <c r="FJ39" s="5"/>
+      <c r="FK39" s="5"/>
+      <c r="FL39" s="5"/>
+      <c r="FM39" s="5"/>
+      <c r="FN39" s="5"/>
+      <c r="FO39" s="5"/>
+      <c r="FP39" s="5"/>
+      <c r="FQ39" s="5"/>
+      <c r="FR39" s="5"/>
+      <c r="FS39" s="5"/>
+      <c r="FT39" s="5"/>
+      <c r="FU39" s="5"/>
     </row>
-    <row r="40" spans="2:165" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B40" s="4"/>
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
@@ -10413,8 +10983,20 @@
       <c r="FG40" s="5"/>
       <c r="FH40" s="5"/>
       <c r="FI40" s="5"/>
+      <c r="FJ40" s="5"/>
+      <c r="FK40" s="5"/>
+      <c r="FL40" s="5"/>
+      <c r="FM40" s="5"/>
+      <c r="FN40" s="5"/>
+      <c r="FO40" s="5"/>
+      <c r="FP40" s="5"/>
+      <c r="FQ40" s="5"/>
+      <c r="FR40" s="5"/>
+      <c r="FS40" s="5"/>
+      <c r="FT40" s="5"/>
+      <c r="FU40" s="5"/>
     </row>
-    <row r="41" spans="2:165" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B41" s="4"/>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
@@ -10579,8 +11161,20 @@
       <c r="FG41" s="5"/>
       <c r="FH41" s="5"/>
       <c r="FI41" s="5"/>
+      <c r="FJ41" s="5"/>
+      <c r="FK41" s="5"/>
+      <c r="FL41" s="5"/>
+      <c r="FM41" s="5"/>
+      <c r="FN41" s="5"/>
+      <c r="FO41" s="5"/>
+      <c r="FP41" s="5"/>
+      <c r="FQ41" s="5"/>
+      <c r="FR41" s="5"/>
+      <c r="FS41" s="5"/>
+      <c r="FT41" s="5"/>
+      <c r="FU41" s="5"/>
     </row>
-    <row r="42" spans="2:165" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B42" s="4"/>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
@@ -10745,8 +11339,20 @@
       <c r="FG42" s="5"/>
       <c r="FH42" s="5"/>
       <c r="FI42" s="5"/>
+      <c r="FJ42" s="5"/>
+      <c r="FK42" s="5"/>
+      <c r="FL42" s="5"/>
+      <c r="FM42" s="5"/>
+      <c r="FN42" s="5"/>
+      <c r="FO42" s="5"/>
+      <c r="FP42" s="5"/>
+      <c r="FQ42" s="5"/>
+      <c r="FR42" s="5"/>
+      <c r="FS42" s="5"/>
+      <c r="FT42" s="5"/>
+      <c r="FU42" s="5"/>
     </row>
-    <row r="43" spans="2:165" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B43" s="4"/>
       <c r="C43" s="5"/>
       <c r="D43" s="5"/>
@@ -10911,8 +11517,20 @@
       <c r="FG43" s="5"/>
       <c r="FH43" s="5"/>
       <c r="FI43" s="5"/>
+      <c r="FJ43" s="5"/>
+      <c r="FK43" s="5"/>
+      <c r="FL43" s="5"/>
+      <c r="FM43" s="5"/>
+      <c r="FN43" s="5"/>
+      <c r="FO43" s="5"/>
+      <c r="FP43" s="5"/>
+      <c r="FQ43" s="5"/>
+      <c r="FR43" s="5"/>
+      <c r="FS43" s="5"/>
+      <c r="FT43" s="5"/>
+      <c r="FU43" s="5"/>
     </row>
-    <row r="44" spans="2:165" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B44" s="4"/>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
@@ -11077,8 +11695,20 @@
       <c r="FG44" s="5"/>
       <c r="FH44" s="5"/>
       <c r="FI44" s="5"/>
+      <c r="FJ44" s="5"/>
+      <c r="FK44" s="5"/>
+      <c r="FL44" s="5"/>
+      <c r="FM44" s="5"/>
+      <c r="FN44" s="5"/>
+      <c r="FO44" s="5"/>
+      <c r="FP44" s="5"/>
+      <c r="FQ44" s="5"/>
+      <c r="FR44" s="5"/>
+      <c r="FS44" s="5"/>
+      <c r="FT44" s="5"/>
+      <c r="FU44" s="5"/>
     </row>
-    <row r="45" spans="2:165" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B45" s="4"/>
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
@@ -11243,8 +11873,20 @@
       <c r="FG45" s="5"/>
       <c r="FH45" s="5"/>
       <c r="FI45" s="5"/>
+      <c r="FJ45" s="5"/>
+      <c r="FK45" s="5"/>
+      <c r="FL45" s="5"/>
+      <c r="FM45" s="5"/>
+      <c r="FN45" s="5"/>
+      <c r="FO45" s="5"/>
+      <c r="FP45" s="5"/>
+      <c r="FQ45" s="5"/>
+      <c r="FR45" s="5"/>
+      <c r="FS45" s="5"/>
+      <c r="FT45" s="5"/>
+      <c r="FU45" s="5"/>
     </row>
-    <row r="46" spans="2:165" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B46" s="4"/>
       <c r="C46" s="5"/>
       <c r="D46" s="5"/>
@@ -11409,9 +12051,24 @@
       <c r="FG46" s="5"/>
       <c r="FH46" s="5"/>
       <c r="FI46" s="5"/>
+      <c r="FJ46" s="5"/>
+      <c r="FK46" s="5"/>
+      <c r="FL46" s="5"/>
+      <c r="FM46" s="5"/>
+      <c r="FN46" s="5"/>
+      <c r="FO46" s="5"/>
+      <c r="FP46" s="5"/>
+      <c r="FQ46" s="5"/>
+      <c r="FR46" s="5"/>
+      <c r="FS46" s="5"/>
+      <c r="FT46" s="5"/>
+      <c r="FU46" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="45">
+  <mergeCells count="48">
+    <mergeCell ref="FJ2:FU2"/>
+    <mergeCell ref="FJ22:FU22"/>
+    <mergeCell ref="FJ23:FU23"/>
     <mergeCell ref="DB22:DM22"/>
     <mergeCell ref="DB2:DM2"/>
     <mergeCell ref="CP2:DA2"/>

--- a/activity/M01A02/M01A02_PuntoEstudioCaudales.xlsx
+++ b/activity/M01A02/M01A02_PuntoEstudioCaudales.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr updateLinks="never" codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D499D8D-B303-4176-87FA-EF432DA8E870}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBD15384-417E-4DFF-9299-A330A0D579E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Calificacion" sheetId="12" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Calificacion!$B$2:$F$20</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Detalle!$B$1:$U$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Detalle!$B$1:$V$23</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="68">
   <si>
     <t>J4660</t>
   </si>
@@ -290,14 +290,17 @@
   <si>
     <t>Grupo 14</t>
   </si>
+  <si>
+    <t>Q Ecológico, m³/s</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="31" x14ac:knownFonts="1">
@@ -1113,7 +1116,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -1156,10 +1159,10 @@
     <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1338,25 +1341,7 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="11" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1381,6 +1366,24 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1925,7 +1928,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1933,6 +1935,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2854,23 +2857,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EF50BAE-D7A1-4B9B-8511-69070389923C}">
   <sheetPr codeName="Hoja2"/>
   <dimension ref="B1:F21"/>
-  <sheetFormatPr defaultColWidth="11.33203125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="11.33203125" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="17" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" style="17" customWidth="1"/>
-    <col min="3" max="4" width="11.46484375" style="17" customWidth="1"/>
-    <col min="5" max="5" width="12.796875" style="17" customWidth="1"/>
-    <col min="6" max="6" width="11.46484375" style="17" customWidth="1"/>
+    <col min="3" max="4" width="11.44140625" style="17" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" style="17" customWidth="1"/>
+    <col min="6" max="6" width="11.44140625" style="17" customWidth="1"/>
     <col min="7" max="7" width="2.6640625" style="17" customWidth="1"/>
     <col min="8" max="16384" width="11.33203125" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:6" x14ac:dyDescent="0.3">
       <c r="F1" s="35" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="51" t="s">
         <v>61</v>
       </c>
@@ -2879,14 +2882,14 @@
       <c r="E2" s="51"/>
       <c r="F2" s="51"/>
     </row>
-    <row r="3" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="52"/>
       <c r="C3" s="52"/>
       <c r="D3" s="52"/>
       <c r="E3" s="52"/>
       <c r="F3" s="52"/>
     </row>
-    <row r="4" spans="2:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="29" t="s">
         <v>22</v>
       </c>
@@ -2903,7 +2906,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B5" s="18" t="s">
         <v>45</v>
       </c>
@@ -2920,7 +2923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B6" s="18" t="s">
         <v>46</v>
       </c>
@@ -2928,7 +2931,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="10">
-        <f>Detalle!V23*C6/5</f>
+        <f>Detalle!W23*C6/5</f>
         <v>0</v>
       </c>
       <c r="E6" s="33"/>
@@ -2937,7 +2940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B7" s="18" t="s">
         <v>47</v>
       </c>
@@ -2945,7 +2948,7 @@
         <v>5</v>
       </c>
       <c r="D7" s="10">
-        <f>Detalle!AH23*C7/5</f>
+        <f>Detalle!AJ23*C7/5</f>
         <v>0</v>
       </c>
       <c r="E7" s="33"/>
@@ -2954,7 +2957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B8" s="18" t="s">
         <v>48</v>
       </c>
@@ -2962,7 +2965,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="10">
-        <f>Detalle!AT23*C8/5</f>
+        <f>Detalle!AW23*C8/5</f>
         <v>0</v>
       </c>
       <c r="E8" s="33"/>
@@ -2971,7 +2974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B9" s="18" t="s">
         <v>49</v>
       </c>
@@ -2979,7 +2982,7 @@
         <v>5</v>
       </c>
       <c r="D9" s="10">
-        <f>Detalle!BF23*C9/5</f>
+        <f>Detalle!BJ23*C9/5</f>
         <v>0</v>
       </c>
       <c r="E9" s="33"/>
@@ -2988,7 +2991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B10" s="18" t="s">
         <v>52</v>
       </c>
@@ -2996,7 +2999,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="10">
-        <f>Detalle!BR23*C10/5</f>
+        <f>Detalle!BW23*C10/5</f>
         <v>0</v>
       </c>
       <c r="E10" s="33"/>
@@ -3005,7 +3008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B11" s="18" t="s">
         <v>53</v>
       </c>
@@ -3013,7 +3016,7 @@
         <v>5</v>
       </c>
       <c r="D11" s="10">
-        <f>Detalle!CD23*C11/5</f>
+        <f>Detalle!CJ23*C11/5</f>
         <v>0</v>
       </c>
       <c r="E11" s="33"/>
@@ -3022,7 +3025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B12" s="18" t="s">
         <v>54</v>
       </c>
@@ -3030,7 +3033,7 @@
         <v>5</v>
       </c>
       <c r="D12" s="10">
-        <f>Detalle!CP23*C12/5</f>
+        <f>Detalle!CW23*C12/5</f>
         <v>0</v>
       </c>
       <c r="E12" s="33"/>
@@ -3039,7 +3042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B13" s="18" t="s">
         <v>55</v>
       </c>
@@ -3047,7 +3050,7 @@
         <v>5</v>
       </c>
       <c r="D13" s="10">
-        <f>Detalle!DB23*C13/5</f>
+        <f>Detalle!DJ23*C13/5</f>
         <v>0</v>
       </c>
       <c r="E13" s="33"/>
@@ -3056,7 +3059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B14" s="18" t="s">
         <v>56</v>
       </c>
@@ -3064,7 +3067,7 @@
         <v>5</v>
       </c>
       <c r="D14" s="10">
-        <f>Detalle!DN23*C14/5</f>
+        <f>Detalle!DW23*C14/5</f>
         <v>0</v>
       </c>
       <c r="E14" s="33"/>
@@ -3073,7 +3076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B15" s="18" t="s">
         <v>57</v>
       </c>
@@ -3081,7 +3084,7 @@
         <v>5</v>
       </c>
       <c r="D15" s="10">
-        <f>Detalle!DZ23*C15/5</f>
+        <f>Detalle!EJ23*C15/5</f>
         <v>0</v>
       </c>
       <c r="E15" s="33"/>
@@ -3090,7 +3093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B16" s="18" t="s">
         <v>58</v>
       </c>
@@ -3098,7 +3101,7 @@
         <v>5</v>
       </c>
       <c r="D16" s="10">
-        <f>Detalle!EL23*C16/5</f>
+        <f>Detalle!EW23*C16/5</f>
         <v>0</v>
       </c>
       <c r="E16" s="33"/>
@@ -3107,7 +3110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="18" t="s">
         <v>59</v>
       </c>
@@ -3115,7 +3118,7 @@
         <v>5</v>
       </c>
       <c r="D17" s="10">
-        <f>Detalle!EX23*C17/5</f>
+        <f>Detalle!FJ23*C17/5</f>
         <v>0</v>
       </c>
       <c r="E17" s="33"/>
@@ -3124,7 +3127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="19" t="s">
         <v>66</v>
       </c>
@@ -3132,7 +3135,7 @@
         <v>5</v>
       </c>
       <c r="D18" s="28">
-        <f>Detalle!FJ23*C18/5</f>
+        <f>Detalle!FW23*C18/5</f>
         <v>0</v>
       </c>
       <c r="E18" s="34"/>
@@ -3141,7 +3144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="53" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F1," en GitHub."))</f>
         <v>Ir a actividad M01A02 en GitHub.</v>
@@ -3151,14 +3154,14 @@
       <c r="E19" s="53"/>
       <c r="F19" s="53"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20" s="53"/>
       <c r="C20" s="53"/>
       <c r="D20" s="53"/>
       <c r="E20" s="53"/>
       <c r="F20" s="53"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" s="32"/>
       <c r="C21" s="32"/>
       <c r="D21" s="32"/>
@@ -3183,70 +3186,92 @@
   <sheetPr codeName="Hoja1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:FU46"/>
-  <sheetFormatPr defaultColWidth="11.33203125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:GI46"/>
+  <sheetFormatPr defaultColWidth="11.33203125" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="6" customWidth="1"/>
     <col min="2" max="2" width="16.33203125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="46.1328125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="46.109375" style="5" customWidth="1"/>
     <col min="4" max="4" width="7.33203125" style="5" customWidth="1"/>
     <col min="5" max="6" width="4.6640625" style="5" customWidth="1"/>
     <col min="7" max="8" width="10" style="5" customWidth="1"/>
-    <col min="9" max="9" width="6.53125" style="5" customWidth="1"/>
+    <col min="9" max="9" width="6.5546875" style="5" customWidth="1"/>
     <col min="10" max="10" width="9.6640625" style="5" customWidth="1"/>
-    <col min="11" max="11" width="8.53125" style="5" customWidth="1"/>
-    <col min="12" max="12" width="10.1328125" style="5" customWidth="1"/>
-    <col min="13" max="18" width="8.53125" style="5" customWidth="1"/>
-    <col min="19" max="20" width="10" style="5" customWidth="1"/>
-    <col min="21" max="21" width="10.1328125" style="5" customWidth="1"/>
-    <col min="22" max="23" width="8.53125" style="5" customWidth="1"/>
-    <col min="24" max="30" width="10.1328125" style="5" customWidth="1"/>
-    <col min="31" max="32" width="10" style="5" customWidth="1"/>
-    <col min="33" max="33" width="10.1328125" style="5" customWidth="1"/>
-    <col min="34" max="35" width="8.53125" style="5" customWidth="1"/>
-    <col min="36" max="42" width="10.1328125" style="5" customWidth="1"/>
-    <col min="43" max="44" width="10" style="5" customWidth="1"/>
-    <col min="45" max="45" width="10.1328125" style="5" customWidth="1"/>
-    <col min="46" max="47" width="8.53125" style="5" customWidth="1"/>
-    <col min="48" max="54" width="10.1328125" style="5" customWidth="1"/>
-    <col min="55" max="56" width="10" style="5" customWidth="1"/>
-    <col min="57" max="57" width="10.1328125" style="5" customWidth="1"/>
-    <col min="58" max="58" width="8.53125" style="5" customWidth="1"/>
-    <col min="59" max="66" width="10.1328125" style="5" customWidth="1"/>
-    <col min="67" max="68" width="10" style="5" customWidth="1"/>
-    <col min="69" max="69" width="10.1328125" style="5" customWidth="1"/>
-    <col min="70" max="71" width="8.53125" style="5" customWidth="1"/>
-    <col min="72" max="78" width="10.1328125" style="5" customWidth="1"/>
-    <col min="79" max="80" width="10" style="5" customWidth="1"/>
-    <col min="81" max="81" width="10.1328125" style="5" customWidth="1"/>
-    <col min="82" max="82" width="8.53125" style="5" bestFit="1" customWidth="1"/>
-    <col min="83" max="83" width="8.53125" style="5" customWidth="1"/>
-    <col min="84" max="93" width="10.1328125" style="5" customWidth="1"/>
-    <col min="94" max="94" width="8.53125" style="5" bestFit="1" customWidth="1"/>
-    <col min="95" max="95" width="8.53125" style="5" customWidth="1"/>
-    <col min="96" max="105" width="10.1328125" style="5" customWidth="1"/>
-    <col min="106" max="106" width="8.53125" style="5" bestFit="1" customWidth="1"/>
-    <col min="107" max="107" width="8.53125" style="5" customWidth="1"/>
-    <col min="108" max="117" width="10.1328125" style="5" customWidth="1"/>
-    <col min="118" max="118" width="8.53125" style="5" bestFit="1" customWidth="1"/>
-    <col min="119" max="119" width="8.53125" style="5" customWidth="1"/>
-    <col min="120" max="129" width="10.1328125" style="5" customWidth="1"/>
-    <col min="130" max="130" width="8.53125" style="5" bestFit="1" customWidth="1"/>
-    <col min="131" max="131" width="8.53125" style="5" customWidth="1"/>
-    <col min="132" max="141" width="10.1328125" style="5" customWidth="1"/>
-    <col min="142" max="142" width="8.53125" style="5" bestFit="1" customWidth="1"/>
-    <col min="143" max="143" width="8.53125" style="5" customWidth="1"/>
-    <col min="144" max="153" width="10.1328125" style="5" customWidth="1"/>
-    <col min="154" max="154" width="8.53125" style="5" bestFit="1" customWidth="1"/>
-    <col min="155" max="155" width="8.53125" style="5" customWidth="1"/>
-    <col min="156" max="165" width="10.1328125" style="5" customWidth="1"/>
-    <col min="166" max="166" width="8.53125" style="5" bestFit="1" customWidth="1"/>
-    <col min="167" max="167" width="8.53125" style="5" customWidth="1"/>
-    <col min="168" max="177" width="10.1328125" style="5" customWidth="1"/>
-    <col min="178" max="16384" width="11.33203125" style="4"/>
+    <col min="11" max="11" width="8.5546875" style="5" customWidth="1"/>
+    <col min="12" max="12" width="10.109375" style="5" customWidth="1"/>
+    <col min="13" max="18" width="8.5546875" style="5" customWidth="1"/>
+    <col min="19" max="19" width="11.109375" style="5" customWidth="1"/>
+    <col min="20" max="21" width="10" style="5" customWidth="1"/>
+    <col min="22" max="22" width="10.109375" style="5" customWidth="1"/>
+    <col min="23" max="24" width="8.5546875" style="5" customWidth="1"/>
+    <col min="25" max="31" width="10.109375" style="5" customWidth="1"/>
+    <col min="32" max="32" width="11.109375" style="5" customWidth="1"/>
+    <col min="33" max="34" width="10" style="5" customWidth="1"/>
+    <col min="35" max="35" width="10.109375" style="5" customWidth="1"/>
+    <col min="36" max="37" width="8.5546875" style="5" customWidth="1"/>
+    <col min="38" max="44" width="10.109375" style="5" customWidth="1"/>
+    <col min="45" max="45" width="11.109375" style="5" customWidth="1"/>
+    <col min="46" max="47" width="10" style="5" customWidth="1"/>
+    <col min="48" max="48" width="10.109375" style="5" customWidth="1"/>
+    <col min="49" max="50" width="8.5546875" style="5" customWidth="1"/>
+    <col min="51" max="57" width="10.109375" style="5" customWidth="1"/>
+    <col min="58" max="58" width="11.109375" style="5" customWidth="1"/>
+    <col min="59" max="60" width="10" style="5" customWidth="1"/>
+    <col min="61" max="61" width="10.109375" style="5" customWidth="1"/>
+    <col min="62" max="62" width="8.5546875" style="5" customWidth="1"/>
+    <col min="63" max="70" width="10.109375" style="5" customWidth="1"/>
+    <col min="71" max="71" width="11.109375" style="5" customWidth="1"/>
+    <col min="72" max="73" width="10" style="5" customWidth="1"/>
+    <col min="74" max="74" width="10.109375" style="5" customWidth="1"/>
+    <col min="75" max="76" width="8.5546875" style="5" customWidth="1"/>
+    <col min="77" max="83" width="10.109375" style="5" customWidth="1"/>
+    <col min="84" max="84" width="11.109375" style="5" customWidth="1"/>
+    <col min="85" max="86" width="10" style="5" customWidth="1"/>
+    <col min="87" max="87" width="10.109375" style="5" customWidth="1"/>
+    <col min="88" max="88" width="8.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="8.5546875" style="5" customWidth="1"/>
+    <col min="90" max="96" width="10.109375" style="5" customWidth="1"/>
+    <col min="97" max="97" width="11.109375" style="5" customWidth="1"/>
+    <col min="98" max="100" width="10.109375" style="5" customWidth="1"/>
+    <col min="101" max="101" width="8.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="102" max="102" width="8.5546875" style="5" customWidth="1"/>
+    <col min="103" max="109" width="10.109375" style="5" customWidth="1"/>
+    <col min="110" max="110" width="11.109375" style="5" customWidth="1"/>
+    <col min="111" max="113" width="10.109375" style="5" customWidth="1"/>
+    <col min="114" max="114" width="8.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="115" max="115" width="8.5546875" style="5" customWidth="1"/>
+    <col min="116" max="122" width="10.109375" style="5" customWidth="1"/>
+    <col min="123" max="123" width="11.109375" style="5" customWidth="1"/>
+    <col min="124" max="126" width="10.109375" style="5" customWidth="1"/>
+    <col min="127" max="127" width="8.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="128" max="128" width="8.5546875" style="5" customWidth="1"/>
+    <col min="129" max="135" width="10.109375" style="5" customWidth="1"/>
+    <col min="136" max="136" width="11.109375" style="5" customWidth="1"/>
+    <col min="137" max="139" width="10.109375" style="5" customWidth="1"/>
+    <col min="140" max="140" width="8.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="141" max="141" width="8.5546875" style="5" customWidth="1"/>
+    <col min="142" max="148" width="10.109375" style="5" customWidth="1"/>
+    <col min="149" max="149" width="11.109375" style="5" customWidth="1"/>
+    <col min="150" max="152" width="10.109375" style="5" customWidth="1"/>
+    <col min="153" max="153" width="8.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="154" max="154" width="8.5546875" style="5" customWidth="1"/>
+    <col min="155" max="161" width="10.109375" style="5" customWidth="1"/>
+    <col min="162" max="162" width="11.109375" style="5" customWidth="1"/>
+    <col min="163" max="165" width="10.109375" style="5" customWidth="1"/>
+    <col min="166" max="166" width="8.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="167" max="167" width="8.5546875" style="5" customWidth="1"/>
+    <col min="168" max="174" width="10.109375" style="5" customWidth="1"/>
+    <col min="175" max="175" width="11.109375" style="5" customWidth="1"/>
+    <col min="176" max="178" width="10.109375" style="5" customWidth="1"/>
+    <col min="179" max="179" width="8.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="180" max="180" width="8.5546875" style="5" customWidth="1"/>
+    <col min="181" max="187" width="10.109375" style="5" customWidth="1"/>
+    <col min="188" max="188" width="11.109375" style="5" customWidth="1"/>
+    <col min="189" max="191" width="10.109375" style="5" customWidth="1"/>
+    <col min="192" max="16384" width="11.33203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:177" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:191" x14ac:dyDescent="0.3">
       <c r="A1" s="3"/>
       <c r="B1" s="7" t="str">
         <f>Calificacion!B2</f>
@@ -3269,7 +3294,7 @@
       <c r="S1" s="4"/>
       <c r="T1" s="4"/>
       <c r="U1" s="4"/>
-      <c r="X1" s="4"/>
+      <c r="V1" s="4"/>
       <c r="Y1" s="4"/>
       <c r="Z1" s="4"/>
       <c r="AA1" s="4"/>
@@ -3279,8 +3304,8 @@
       <c r="AE1" s="4"/>
       <c r="AF1" s="4"/>
       <c r="AG1" s="4"/>
-      <c r="AJ1" s="4"/>
-      <c r="AK1" s="4"/>
+      <c r="AH1" s="4"/>
+      <c r="AI1" s="4"/>
       <c r="AL1" s="4"/>
       <c r="AM1" s="4"/>
       <c r="AN1" s="4"/>
@@ -3289,9 +3314,9 @@
       <c r="AQ1" s="4"/>
       <c r="AR1" s="4"/>
       <c r="AS1" s="4"/>
+      <c r="AT1" s="4"/>
+      <c r="AU1" s="4"/>
       <c r="AV1" s="4"/>
-      <c r="AW1" s="4"/>
-      <c r="AX1" s="4"/>
       <c r="AY1" s="4"/>
       <c r="AZ1" s="4"/>
       <c r="BA1" s="4"/>
@@ -3299,56 +3324,58 @@
       <c r="BC1" s="4"/>
       <c r="BD1" s="4"/>
       <c r="BE1" s="4"/>
+      <c r="BF1" s="4"/>
+      <c r="BG1" s="4"/>
       <c r="BH1" s="4"/>
       <c r="BI1" s="4"/>
-      <c r="BJ1" s="4"/>
-      <c r="BK1" s="4"/>
       <c r="BL1" s="4"/>
       <c r="BM1" s="4"/>
       <c r="BN1" s="4"/>
       <c r="BO1" s="4"/>
       <c r="BP1" s="4"/>
       <c r="BQ1" s="4"/>
+      <c r="BR1" s="4"/>
+      <c r="BS1" s="4"/>
       <c r="BT1" s="4"/>
       <c r="BU1" s="4"/>
       <c r="BV1" s="4"/>
-      <c r="BW1" s="4"/>
-      <c r="BX1" s="4"/>
       <c r="BY1" s="4"/>
       <c r="BZ1" s="4"/>
       <c r="CA1" s="4"/>
       <c r="CB1" s="4"/>
       <c r="CC1" s="4"/>
+      <c r="CD1" s="4"/>
+      <c r="CE1" s="4"/>
       <c r="CF1" s="4"/>
       <c r="CG1" s="4"/>
       <c r="CH1" s="4"/>
       <c r="CI1" s="4"/>
-      <c r="CJ1" s="4"/>
-      <c r="CK1" s="4"/>
       <c r="CL1" s="4"/>
       <c r="CM1" s="4"/>
       <c r="CN1" s="4"/>
       <c r="CO1" s="4"/>
+      <c r="CP1" s="4"/>
+      <c r="CQ1" s="4"/>
       <c r="CR1" s="4"/>
       <c r="CS1" s="4"/>
       <c r="CT1" s="4"/>
       <c r="CU1" s="4"/>
       <c r="CV1" s="4"/>
-      <c r="CW1" s="4"/>
-      <c r="CX1" s="4"/>
       <c r="CY1" s="4"/>
       <c r="CZ1" s="4"/>
       <c r="DA1" s="4"/>
+      <c r="DB1" s="4"/>
+      <c r="DC1" s="4"/>
       <c r="DD1" s="4"/>
       <c r="DE1" s="4"/>
       <c r="DF1" s="4"/>
       <c r="DG1" s="4"/>
       <c r="DH1" s="4"/>
       <c r="DI1" s="4"/>
-      <c r="DJ1" s="4"/>
-      <c r="DK1" s="4"/>
       <c r="DL1" s="4"/>
       <c r="DM1" s="4"/>
+      <c r="DN1" s="4"/>
+      <c r="DO1" s="4"/>
       <c r="DP1" s="4"/>
       <c r="DQ1" s="4"/>
       <c r="DR1" s="4"/>
@@ -3356,9 +3383,9 @@
       <c r="DT1" s="4"/>
       <c r="DU1" s="4"/>
       <c r="DV1" s="4"/>
-      <c r="DW1" s="4"/>
-      <c r="DX1" s="4"/>
       <c r="DY1" s="4"/>
+      <c r="DZ1" s="4"/>
+      <c r="EA1" s="4"/>
       <c r="EB1" s="4"/>
       <c r="EC1" s="4"/>
       <c r="ED1" s="4"/>
@@ -3367,8 +3394,8 @@
       <c r="EG1" s="4"/>
       <c r="EH1" s="4"/>
       <c r="EI1" s="4"/>
-      <c r="EJ1" s="4"/>
-      <c r="EK1" s="4"/>
+      <c r="EL1" s="4"/>
+      <c r="EM1" s="4"/>
       <c r="EN1" s="4"/>
       <c r="EO1" s="4"/>
       <c r="EP1" s="4"/>
@@ -3378,7 +3405,7 @@
       <c r="ET1" s="4"/>
       <c r="EU1" s="4"/>
       <c r="EV1" s="4"/>
-      <c r="EW1" s="4"/>
+      <c r="EY1" s="4"/>
       <c r="EZ1" s="4"/>
       <c r="FA1" s="4"/>
       <c r="FB1" s="4"/>
@@ -3399,13 +3426,25 @@
       <c r="FS1" s="4"/>
       <c r="FT1" s="4"/>
       <c r="FU1" s="4"/>
+      <c r="FV1" s="4"/>
+      <c r="FY1" s="4"/>
+      <c r="FZ1" s="4"/>
+      <c r="GA1" s="4"/>
+      <c r="GB1" s="4"/>
+      <c r="GC1" s="4"/>
+      <c r="GD1" s="4"/>
+      <c r="GE1" s="4"/>
+      <c r="GF1" s="4"/>
+      <c r="GG1" s="4"/>
+      <c r="GH1" s="4"/>
+      <c r="GI1" s="4"/>
     </row>
-    <row r="2" spans="1:177" s="7" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:191" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="57" t="s">
+      <c r="C2" s="67" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="69" t="s">
@@ -3416,220 +3455,234 @@
       <c r="G2" s="69"/>
       <c r="H2" s="69"/>
       <c r="I2" s="70"/>
-      <c r="J2" s="59" t="str">
+      <c r="J2" s="54" t="str">
         <f>Calificacion!$B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="K2" s="60"/>
-      <c r="L2" s="61"/>
-      <c r="M2" s="61"/>
-      <c r="N2" s="61"/>
-      <c r="O2" s="61"/>
-      <c r="P2" s="61"/>
-      <c r="Q2" s="61"/>
-      <c r="R2" s="61"/>
-      <c r="S2" s="62"/>
-      <c r="T2" s="62"/>
-      <c r="U2" s="63"/>
-      <c r="V2" s="59" t="str">
+      <c r="K2" s="64"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="55"/>
+      <c r="R2" s="55"/>
+      <c r="S2" s="56"/>
+      <c r="T2" s="56"/>
+      <c r="U2" s="56"/>
+      <c r="V2" s="57"/>
+      <c r="W2" s="54" t="str">
         <f>Calificacion!$B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="W2" s="60"/>
-      <c r="X2" s="61"/>
-      <c r="Y2" s="61"/>
-      <c r="Z2" s="61"/>
-      <c r="AA2" s="61"/>
-      <c r="AB2" s="61"/>
-      <c r="AC2" s="61"/>
-      <c r="AD2" s="61"/>
-      <c r="AE2" s="62"/>
-      <c r="AF2" s="62"/>
-      <c r="AG2" s="63"/>
-      <c r="AH2" s="59" t="str">
+      <c r="X2" s="64"/>
+      <c r="Y2" s="55"/>
+      <c r="Z2" s="55"/>
+      <c r="AA2" s="55"/>
+      <c r="AB2" s="55"/>
+      <c r="AC2" s="55"/>
+      <c r="AD2" s="55"/>
+      <c r="AE2" s="55"/>
+      <c r="AF2" s="56"/>
+      <c r="AG2" s="56"/>
+      <c r="AH2" s="56"/>
+      <c r="AI2" s="57"/>
+      <c r="AJ2" s="54" t="str">
         <f>Calificacion!$B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="AI2" s="60"/>
-      <c r="AJ2" s="61"/>
-      <c r="AK2" s="61"/>
-      <c r="AL2" s="61"/>
-      <c r="AM2" s="61"/>
-      <c r="AN2" s="61"/>
-      <c r="AO2" s="61"/>
-      <c r="AP2" s="61"/>
-      <c r="AQ2" s="62"/>
-      <c r="AR2" s="62"/>
-      <c r="AS2" s="63"/>
-      <c r="AT2" s="59" t="str">
+      <c r="AK2" s="64"/>
+      <c r="AL2" s="55"/>
+      <c r="AM2" s="55"/>
+      <c r="AN2" s="55"/>
+      <c r="AO2" s="55"/>
+      <c r="AP2" s="55"/>
+      <c r="AQ2" s="55"/>
+      <c r="AR2" s="55"/>
+      <c r="AS2" s="56"/>
+      <c r="AT2" s="56"/>
+      <c r="AU2" s="56"/>
+      <c r="AV2" s="57"/>
+      <c r="AW2" s="54" t="str">
         <f>Calificacion!$B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="AU2" s="60"/>
-      <c r="AV2" s="61"/>
-      <c r="AW2" s="61"/>
-      <c r="AX2" s="61"/>
-      <c r="AY2" s="61"/>
-      <c r="AZ2" s="61"/>
-      <c r="BA2" s="61"/>
-      <c r="BB2" s="61"/>
-      <c r="BC2" s="62"/>
-      <c r="BD2" s="62"/>
-      <c r="BE2" s="63"/>
-      <c r="BF2" s="59" t="str">
+      <c r="AX2" s="64"/>
+      <c r="AY2" s="55"/>
+      <c r="AZ2" s="55"/>
+      <c r="BA2" s="55"/>
+      <c r="BB2" s="55"/>
+      <c r="BC2" s="55"/>
+      <c r="BD2" s="55"/>
+      <c r="BE2" s="55"/>
+      <c r="BF2" s="56"/>
+      <c r="BG2" s="56"/>
+      <c r="BH2" s="56"/>
+      <c r="BI2" s="57"/>
+      <c r="BJ2" s="54" t="str">
         <f>Calificacion!$B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="BG2" s="61"/>
-      <c r="BH2" s="61"/>
-      <c r="BI2" s="61"/>
-      <c r="BJ2" s="61"/>
-      <c r="BK2" s="61"/>
-      <c r="BL2" s="61"/>
-      <c r="BM2" s="61"/>
-      <c r="BN2" s="61"/>
-      <c r="BO2" s="62"/>
-      <c r="BP2" s="62"/>
-      <c r="BQ2" s="63"/>
-      <c r="BR2" s="59" t="str">
+      <c r="BK2" s="55"/>
+      <c r="BL2" s="55"/>
+      <c r="BM2" s="55"/>
+      <c r="BN2" s="55"/>
+      <c r="BO2" s="55"/>
+      <c r="BP2" s="55"/>
+      <c r="BQ2" s="55"/>
+      <c r="BR2" s="55"/>
+      <c r="BS2" s="56"/>
+      <c r="BT2" s="56"/>
+      <c r="BU2" s="56"/>
+      <c r="BV2" s="57"/>
+      <c r="BW2" s="54" t="str">
         <f>Calificacion!$B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="BS2" s="60"/>
-      <c r="BT2" s="61"/>
-      <c r="BU2" s="61"/>
-      <c r="BV2" s="61"/>
-      <c r="BW2" s="61"/>
-      <c r="BX2" s="61"/>
-      <c r="BY2" s="61"/>
-      <c r="BZ2" s="61"/>
-      <c r="CA2" s="62"/>
-      <c r="CB2" s="62"/>
-      <c r="CC2" s="63"/>
-      <c r="CD2" s="59" t="str">
+      <c r="BX2" s="64"/>
+      <c r="BY2" s="55"/>
+      <c r="BZ2" s="55"/>
+      <c r="CA2" s="55"/>
+      <c r="CB2" s="55"/>
+      <c r="CC2" s="55"/>
+      <c r="CD2" s="55"/>
+      <c r="CE2" s="55"/>
+      <c r="CF2" s="56"/>
+      <c r="CG2" s="56"/>
+      <c r="CH2" s="56"/>
+      <c r="CI2" s="57"/>
+      <c r="CJ2" s="54" t="str">
         <f>Calificacion!$B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="CE2" s="60"/>
-      <c r="CF2" s="61"/>
-      <c r="CG2" s="61"/>
-      <c r="CH2" s="61"/>
-      <c r="CI2" s="61"/>
-      <c r="CJ2" s="61"/>
-      <c r="CK2" s="61"/>
-      <c r="CL2" s="61"/>
-      <c r="CM2" s="62"/>
-      <c r="CN2" s="62"/>
-      <c r="CO2" s="63"/>
-      <c r="CP2" s="59" t="str">
+      <c r="CK2" s="64"/>
+      <c r="CL2" s="55"/>
+      <c r="CM2" s="55"/>
+      <c r="CN2" s="55"/>
+      <c r="CO2" s="55"/>
+      <c r="CP2" s="55"/>
+      <c r="CQ2" s="55"/>
+      <c r="CR2" s="55"/>
+      <c r="CS2" s="56"/>
+      <c r="CT2" s="56"/>
+      <c r="CU2" s="56"/>
+      <c r="CV2" s="57"/>
+      <c r="CW2" s="54" t="str">
         <f>Calificacion!$B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="CQ2" s="60"/>
-      <c r="CR2" s="61"/>
-      <c r="CS2" s="61"/>
-      <c r="CT2" s="61"/>
-      <c r="CU2" s="61"/>
-      <c r="CV2" s="61"/>
-      <c r="CW2" s="61"/>
-      <c r="CX2" s="61"/>
-      <c r="CY2" s="62"/>
-      <c r="CZ2" s="62"/>
-      <c r="DA2" s="63"/>
-      <c r="DB2" s="59" t="str">
+      <c r="CX2" s="64"/>
+      <c r="CY2" s="55"/>
+      <c r="CZ2" s="55"/>
+      <c r="DA2" s="55"/>
+      <c r="DB2" s="55"/>
+      <c r="DC2" s="55"/>
+      <c r="DD2" s="55"/>
+      <c r="DE2" s="55"/>
+      <c r="DF2" s="56"/>
+      <c r="DG2" s="56"/>
+      <c r="DH2" s="56"/>
+      <c r="DI2" s="57"/>
+      <c r="DJ2" s="54" t="str">
         <f>Calificacion!$B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="DC2" s="60"/>
-      <c r="DD2" s="61"/>
-      <c r="DE2" s="61"/>
-      <c r="DF2" s="61"/>
-      <c r="DG2" s="61"/>
-      <c r="DH2" s="61"/>
-      <c r="DI2" s="61"/>
-      <c r="DJ2" s="61"/>
-      <c r="DK2" s="62"/>
-      <c r="DL2" s="62"/>
-      <c r="DM2" s="63"/>
-      <c r="DN2" s="59" t="str">
+      <c r="DK2" s="64"/>
+      <c r="DL2" s="55"/>
+      <c r="DM2" s="55"/>
+      <c r="DN2" s="55"/>
+      <c r="DO2" s="55"/>
+      <c r="DP2" s="55"/>
+      <c r="DQ2" s="55"/>
+      <c r="DR2" s="55"/>
+      <c r="DS2" s="56"/>
+      <c r="DT2" s="56"/>
+      <c r="DU2" s="56"/>
+      <c r="DV2" s="57"/>
+      <c r="DW2" s="54" t="str">
         <f>Calificacion!$B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="DO2" s="60"/>
-      <c r="DP2" s="61"/>
-      <c r="DQ2" s="61"/>
-      <c r="DR2" s="61"/>
-      <c r="DS2" s="61"/>
-      <c r="DT2" s="61"/>
-      <c r="DU2" s="61"/>
-      <c r="DV2" s="61"/>
-      <c r="DW2" s="62"/>
-      <c r="DX2" s="62"/>
-      <c r="DY2" s="63"/>
-      <c r="DZ2" s="59" t="str">
+      <c r="DX2" s="64"/>
+      <c r="DY2" s="55"/>
+      <c r="DZ2" s="55"/>
+      <c r="EA2" s="55"/>
+      <c r="EB2" s="55"/>
+      <c r="EC2" s="55"/>
+      <c r="ED2" s="55"/>
+      <c r="EE2" s="55"/>
+      <c r="EF2" s="56"/>
+      <c r="EG2" s="56"/>
+      <c r="EH2" s="56"/>
+      <c r="EI2" s="57"/>
+      <c r="EJ2" s="54" t="str">
         <f>Calificacion!$B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="EA2" s="61"/>
-      <c r="EB2" s="61"/>
-      <c r="EC2" s="61"/>
-      <c r="ED2" s="61"/>
-      <c r="EE2" s="61"/>
-      <c r="EF2" s="61"/>
-      <c r="EG2" s="61"/>
-      <c r="EH2" s="61"/>
-      <c r="EI2" s="62"/>
-      <c r="EJ2" s="62"/>
-      <c r="EK2" s="63"/>
-      <c r="EL2" s="59" t="str">
+      <c r="EK2" s="55"/>
+      <c r="EL2" s="55"/>
+      <c r="EM2" s="55"/>
+      <c r="EN2" s="55"/>
+      <c r="EO2" s="55"/>
+      <c r="EP2" s="55"/>
+      <c r="EQ2" s="55"/>
+      <c r="ER2" s="55"/>
+      <c r="ES2" s="56"/>
+      <c r="ET2" s="56"/>
+      <c r="EU2" s="56"/>
+      <c r="EV2" s="57"/>
+      <c r="EW2" s="54" t="str">
         <f>Calificacion!$B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="EM2" s="61"/>
-      <c r="EN2" s="61"/>
-      <c r="EO2" s="61"/>
-      <c r="EP2" s="61"/>
-      <c r="EQ2" s="61"/>
-      <c r="ER2" s="61"/>
-      <c r="ES2" s="61"/>
-      <c r="ET2" s="61"/>
-      <c r="EU2" s="62"/>
-      <c r="EV2" s="62"/>
-      <c r="EW2" s="63"/>
-      <c r="EX2" s="59" t="str">
+      <c r="EX2" s="55"/>
+      <c r="EY2" s="55"/>
+      <c r="EZ2" s="55"/>
+      <c r="FA2" s="55"/>
+      <c r="FB2" s="55"/>
+      <c r="FC2" s="55"/>
+      <c r="FD2" s="55"/>
+      <c r="FE2" s="55"/>
+      <c r="FF2" s="56"/>
+      <c r="FG2" s="56"/>
+      <c r="FH2" s="56"/>
+      <c r="FI2" s="57"/>
+      <c r="FJ2" s="54" t="str">
         <f>Calificacion!$B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="EY2" s="61"/>
-      <c r="EZ2" s="61"/>
-      <c r="FA2" s="61"/>
-      <c r="FB2" s="61"/>
-      <c r="FC2" s="61"/>
-      <c r="FD2" s="61"/>
-      <c r="FE2" s="61"/>
-      <c r="FF2" s="61"/>
-      <c r="FG2" s="62"/>
-      <c r="FH2" s="62"/>
-      <c r="FI2" s="63"/>
-      <c r="FJ2" s="59" t="str">
+      <c r="FK2" s="55"/>
+      <c r="FL2" s="55"/>
+      <c r="FM2" s="55"/>
+      <c r="FN2" s="55"/>
+      <c r="FO2" s="55"/>
+      <c r="FP2" s="55"/>
+      <c r="FQ2" s="55"/>
+      <c r="FR2" s="55"/>
+      <c r="FS2" s="56"/>
+      <c r="FT2" s="56"/>
+      <c r="FU2" s="56"/>
+      <c r="FV2" s="57"/>
+      <c r="FW2" s="54" t="str">
         <f>Calificacion!$B18</f>
         <v>Grupo 14</v>
       </c>
-      <c r="FK2" s="61"/>
-      <c r="FL2" s="61"/>
-      <c r="FM2" s="61"/>
-      <c r="FN2" s="61"/>
-      <c r="FO2" s="61"/>
-      <c r="FP2" s="61"/>
-      <c r="FQ2" s="61"/>
-      <c r="FR2" s="61"/>
-      <c r="FS2" s="62"/>
-      <c r="FT2" s="62"/>
-      <c r="FU2" s="63"/>
+      <c r="FX2" s="55"/>
+      <c r="FY2" s="55"/>
+      <c r="FZ2" s="55"/>
+      <c r="GA2" s="55"/>
+      <c r="GB2" s="55"/>
+      <c r="GC2" s="55"/>
+      <c r="GD2" s="55"/>
+      <c r="GE2" s="55"/>
+      <c r="GF2" s="56"/>
+      <c r="GG2" s="56"/>
+      <c r="GH2" s="56"/>
+      <c r="GI2" s="57"/>
     </row>
-    <row r="3" spans="1:177" ht="30.75" x14ac:dyDescent="0.45">
-      <c r="B3" s="56"/>
-      <c r="C3" s="58"/>
+    <row r="3" spans="1:191" ht="45" x14ac:dyDescent="0.3">
+      <c r="B3" s="66"/>
+      <c r="C3" s="68"/>
       <c r="D3" s="8" t="s">
         <v>7</v>
       </c>
@@ -3676,436 +3729,436 @@
         <v>13</v>
       </c>
       <c r="S3" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="T3" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="T3" s="8" t="s">
+      <c r="U3" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="U3" s="11" t="s">
+      <c r="V3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="V3" s="15" t="s">
+      <c r="W3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="W3" s="27" t="s">
+      <c r="X3" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="X3" s="8" t="s">
+      <c r="Y3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="Y3" s="8" t="s">
+      <c r="Z3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="Z3" s="8" t="s">
+      <c r="AA3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AA3" s="8" t="s">
+      <c r="AB3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="AB3" s="8" t="s">
+      <c r="AC3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="AC3" s="8" t="s">
+      <c r="AD3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="AD3" s="8" t="s">
+      <c r="AE3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="AE3" s="8" t="s">
+      <c r="AF3" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="AG3" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="AF3" s="8" t="s">
+      <c r="AH3" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AG3" s="11" t="s">
+      <c r="AI3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="AH3" s="15" t="s">
+      <c r="AJ3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="AI3" s="27" t="s">
+      <c r="AK3" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="AJ3" s="8" t="s">
+      <c r="AL3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="AK3" s="8" t="s">
+      <c r="AM3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="AL3" s="8" t="s">
+      <c r="AN3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AM3" s="8" t="s">
+      <c r="AO3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="AN3" s="8" t="s">
+      <c r="AP3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="AO3" s="8" t="s">
+      <c r="AQ3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="AP3" s="8" t="s">
+      <c r="AR3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="AQ3" s="8" t="s">
+      <c r="AS3" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="AT3" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="AR3" s="8" t="s">
+      <c r="AU3" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="AS3" s="11" t="s">
+      <c r="AV3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="AT3" s="15" t="s">
+      <c r="AW3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="AU3" s="27" t="s">
+      <c r="AX3" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="AV3" s="8" t="s">
+      <c r="AY3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="AW3" s="8" t="s">
+      <c r="AZ3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="AX3" s="8" t="s">
+      <c r="BA3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="AY3" s="8" t="s">
+      <c r="BB3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="AZ3" s="8" t="s">
+      <c r="BC3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="BA3" s="8" t="s">
+      <c r="BD3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="BB3" s="8" t="s">
+      <c r="BE3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="BC3" s="8" t="s">
+      <c r="BF3" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="BG3" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="BD3" s="8" t="s">
+      <c r="BH3" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="BE3" s="11" t="s">
+      <c r="BI3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="BF3" s="15" t="s">
+      <c r="BJ3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="BG3" s="8" t="s">
+      <c r="BK3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="BH3" s="8" t="s">
+      <c r="BL3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="BI3" s="8" t="s">
+      <c r="BM3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="BJ3" s="8" t="s">
+      <c r="BN3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="BK3" s="8" t="s">
+      <c r="BO3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="BL3" s="8" t="s">
+      <c r="BP3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="BM3" s="8" t="s">
+      <c r="BQ3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="BN3" s="8" t="s">
+      <c r="BR3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="BO3" s="8" t="s">
+      <c r="BS3" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="BT3" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="BP3" s="8" t="s">
+      <c r="BU3" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="BQ3" s="11" t="s">
+      <c r="BV3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="BR3" s="15" t="s">
+      <c r="BW3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="BS3" s="27" t="s">
+      <c r="BX3" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="BT3" s="8" t="s">
+      <c r="BY3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="BU3" s="8" t="s">
+      <c r="BZ3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="BV3" s="8" t="s">
+      <c r="CA3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="BW3" s="8" t="s">
+      <c r="CB3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="BX3" s="8" t="s">
+      <c r="CC3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="BY3" s="8" t="s">
+      <c r="CD3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="BZ3" s="8" t="s">
+      <c r="CE3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="CA3" s="8" t="s">
+      <c r="CF3" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="CG3" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="CB3" s="8" t="s">
+      <c r="CH3" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="CC3" s="11" t="s">
+      <c r="CI3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="CD3" s="15" t="s">
+      <c r="CJ3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="CE3" s="27" t="s">
+      <c r="CK3" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="CF3" s="8" t="s">
+      <c r="CL3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="CG3" s="8" t="s">
+      <c r="CM3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="CH3" s="8" t="s">
+      <c r="CN3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="CI3" s="8" t="s">
+      <c r="CO3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="CJ3" s="8" t="s">
+      <c r="CP3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="CK3" s="8" t="s">
+      <c r="CQ3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="CL3" s="8" t="s">
+      <c r="CR3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="CM3" s="14" t="s">
+      <c r="CS3" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="CT3" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="CN3" s="14" t="s">
+      <c r="CU3" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="CO3" s="11" t="s">
+      <c r="CV3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="CP3" s="15" t="s">
+      <c r="CW3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="CQ3" s="27" t="s">
+      <c r="CX3" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="CR3" s="8" t="s">
+      <c r="CY3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="CS3" s="8" t="s">
+      <c r="CZ3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="CT3" s="8" t="s">
+      <c r="DA3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="CU3" s="8" t="s">
+      <c r="DB3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="CV3" s="8" t="s">
+      <c r="DC3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="CW3" s="8" t="s">
+      <c r="DD3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="CX3" s="8" t="s">
+      <c r="DE3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="CY3" s="14" t="s">
+      <c r="DF3" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="DG3" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="CZ3" s="14" t="s">
+      <c r="DH3" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="DA3" s="11" t="s">
+      <c r="DI3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="DB3" s="15" t="s">
+      <c r="DJ3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="DC3" s="27" t="s">
+      <c r="DK3" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="DD3" s="8" t="s">
+      <c r="DL3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="DE3" s="8" t="s">
+      <c r="DM3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="DF3" s="8" t="s">
+      <c r="DN3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="DG3" s="8" t="s">
+      <c r="DO3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="DH3" s="8" t="s">
+      <c r="DP3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="DI3" s="8" t="s">
+      <c r="DQ3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="DJ3" s="8" t="s">
+      <c r="DR3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="DK3" s="14" t="s">
+      <c r="DS3" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="DT3" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="DL3" s="14" t="s">
+      <c r="DU3" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="DM3" s="11" t="s">
+      <c r="DV3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="DN3" s="15" t="s">
+      <c r="DW3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="DO3" s="27" t="s">
+      <c r="DX3" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="DP3" s="8" t="s">
+      <c r="DY3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="DQ3" s="8" t="s">
+      <c r="DZ3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="DR3" s="8" t="s">
+      <c r="EA3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="DS3" s="8" t="s">
+      <c r="EB3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="DT3" s="8" t="s">
+      <c r="EC3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="DU3" s="8" t="s">
+      <c r="ED3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="DV3" s="8" t="s">
+      <c r="EE3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="DW3" s="14" t="s">
+      <c r="EF3" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="EG3" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="DX3" s="14" t="s">
+      <c r="EH3" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="DY3" s="11" t="s">
+      <c r="EI3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="DZ3" s="15" t="s">
+      <c r="EJ3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="EA3" s="27" t="s">
+      <c r="EK3" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="EB3" s="8" t="s">
+      <c r="EL3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="EC3" s="8" t="s">
+      <c r="EM3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="ED3" s="8" t="s">
+      <c r="EN3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="EE3" s="8" t="s">
+      <c r="EO3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="EF3" s="8" t="s">
+      <c r="EP3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="EG3" s="8" t="s">
+      <c r="EQ3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="EH3" s="8" t="s">
+      <c r="ER3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="EI3" s="14" t="s">
+      <c r="ES3" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="ET3" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="EJ3" s="14" t="s">
+      <c r="EU3" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="EK3" s="11" t="s">
+      <c r="EV3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="EL3" s="15" t="s">
+      <c r="EW3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="EM3" s="27" t="s">
+      <c r="EX3" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="EN3" s="8" t="s">
+      <c r="EY3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="EO3" s="8" t="s">
+      <c r="EZ3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="EP3" s="8" t="s">
+      <c r="FA3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="EQ3" s="8" t="s">
+      <c r="FB3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="ER3" s="8" t="s">
+      <c r="FC3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="ES3" s="8" t="s">
+      <c r="FD3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="ET3" s="8" t="s">
+      <c r="FE3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="EU3" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="EV3" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="EW3" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="EX3" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="EY3" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="EZ3" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="FA3" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="FB3" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="FC3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="FD3" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="FE3" s="8" t="s">
-        <v>12</v>
-      </c>
       <c r="FF3" s="8" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="FG3" s="14" t="s">
         <v>41</v>
@@ -4143,17 +4196,59 @@
       <c r="FR3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="FS3" s="14" t="s">
+      <c r="FS3" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="FT3" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="FT3" s="14" t="s">
+      <c r="FU3" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="FU3" s="11" t="s">
+      <c r="FV3" s="11" t="s">
         <v>20</v>
       </c>
+      <c r="FW3" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="FX3" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="FY3" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="FZ3" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="GA3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="GB3" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="GC3" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="GD3" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="GE3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="GF3" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="GG3" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="GH3" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="GI3" s="11" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="4" spans="1:177" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:191" x14ac:dyDescent="0.3">
       <c r="B4" s="12" t="s">
         <v>16</v>
       </c>
@@ -4194,12 +4289,12 @@
       <c r="R4" s="22"/>
       <c r="S4" s="22"/>
       <c r="T4" s="22"/>
-      <c r="U4" s="39"/>
-      <c r="V4" s="37">
+      <c r="U4" s="22"/>
+      <c r="V4" s="39"/>
+      <c r="W4" s="37">
         <v>0</v>
       </c>
-      <c r="W4" s="38"/>
-      <c r="X4" s="22"/>
+      <c r="X4" s="38"/>
       <c r="Y4" s="22"/>
       <c r="Z4" s="22"/>
       <c r="AA4" s="22"/>
@@ -4208,13 +4303,13 @@
       <c r="AD4" s="22"/>
       <c r="AE4" s="22"/>
       <c r="AF4" s="22"/>
-      <c r="AG4" s="39"/>
-      <c r="AH4" s="37">
+      <c r="AG4" s="22"/>
+      <c r="AH4" s="22"/>
+      <c r="AI4" s="39"/>
+      <c r="AJ4" s="37">
         <v>0</v>
       </c>
-      <c r="AI4" s="38"/>
-      <c r="AJ4" s="22"/>
-      <c r="AK4" s="22"/>
+      <c r="AK4" s="38"/>
       <c r="AL4" s="22"/>
       <c r="AM4" s="22"/>
       <c r="AN4" s="22"/>
@@ -4222,109 +4317,107 @@
       <c r="AP4" s="22"/>
       <c r="AQ4" s="22"/>
       <c r="AR4" s="22"/>
-      <c r="AS4" s="39"/>
-      <c r="AT4" s="37">
+      <c r="AS4" s="22"/>
+      <c r="AT4" s="22"/>
+      <c r="AU4" s="22"/>
+      <c r="AV4" s="39"/>
+      <c r="AW4" s="37">
         <v>0</v>
       </c>
-      <c r="AU4" s="38"/>
-      <c r="AV4" s="22"/>
-      <c r="AW4" s="22"/>
-      <c r="AX4" s="22"/>
+      <c r="AX4" s="38"/>
       <c r="AY4" s="22"/>
       <c r="AZ4" s="22"/>
       <c r="BA4" s="22"/>
       <c r="BB4" s="22"/>
       <c r="BC4" s="22"/>
       <c r="BD4" s="22"/>
-      <c r="BE4" s="39"/>
-      <c r="BF4" s="37">
+      <c r="BE4" s="22"/>
+      <c r="BF4" s="22"/>
+      <c r="BG4" s="22"/>
+      <c r="BH4" s="22"/>
+      <c r="BI4" s="39"/>
+      <c r="BJ4" s="37">
         <v>0</v>
       </c>
-      <c r="BG4" s="38"/>
-      <c r="BH4" s="22"/>
-      <c r="BI4" s="22"/>
-      <c r="BJ4" s="22"/>
-      <c r="BK4" s="22"/>
+      <c r="BK4" s="38"/>
       <c r="BL4" s="22"/>
       <c r="BM4" s="22"/>
       <c r="BN4" s="22"/>
       <c r="BO4" s="22"/>
       <c r="BP4" s="22"/>
-      <c r="BQ4" s="39"/>
-      <c r="BR4" s="37">
-        <v>0</v>
-      </c>
-      <c r="BS4" s="38"/>
+      <c r="BQ4" s="22"/>
+      <c r="BR4" s="22"/>
+      <c r="BS4" s="22"/>
       <c r="BT4" s="22"/>
       <c r="BU4" s="22"/>
-      <c r="BV4" s="22"/>
-      <c r="BW4" s="22"/>
-      <c r="BX4" s="22"/>
+      <c r="BV4" s="39"/>
+      <c r="BW4" s="37">
+        <v>0</v>
+      </c>
+      <c r="BX4" s="38"/>
       <c r="BY4" s="22"/>
       <c r="BZ4" s="22"/>
       <c r="CA4" s="22"/>
       <c r="CB4" s="22"/>
-      <c r="CC4" s="39"/>
-      <c r="CD4" s="37">
-        <v>0</v>
-      </c>
-      <c r="CE4" s="38"/>
+      <c r="CC4" s="22"/>
+      <c r="CD4" s="22"/>
+      <c r="CE4" s="22"/>
       <c r="CF4" s="22"/>
       <c r="CG4" s="22"/>
       <c r="CH4" s="22"/>
-      <c r="CI4" s="22"/>
-      <c r="CJ4" s="22"/>
-      <c r="CK4" s="22"/>
+      <c r="CI4" s="39"/>
+      <c r="CJ4" s="37">
+        <v>0</v>
+      </c>
+      <c r="CK4" s="38"/>
       <c r="CL4" s="22"/>
       <c r="CM4" s="22"/>
       <c r="CN4" s="22"/>
-      <c r="CO4" s="39"/>
-      <c r="CP4" s="37">
-        <v>0</v>
-      </c>
-      <c r="CQ4" s="38"/>
+      <c r="CO4" s="22"/>
+      <c r="CP4" s="22"/>
+      <c r="CQ4" s="22"/>
       <c r="CR4" s="22"/>
       <c r="CS4" s="22"/>
       <c r="CT4" s="22"/>
       <c r="CU4" s="22"/>
-      <c r="CV4" s="22"/>
-      <c r="CW4" s="22"/>
-      <c r="CX4" s="22"/>
+      <c r="CV4" s="39"/>
+      <c r="CW4" s="37">
+        <v>0</v>
+      </c>
+      <c r="CX4" s="38"/>
       <c r="CY4" s="22"/>
       <c r="CZ4" s="22"/>
-      <c r="DA4" s="39"/>
-      <c r="DB4" s="37">
-        <v>0</v>
-      </c>
-      <c r="DC4" s="38"/>
+      <c r="DA4" s="22"/>
+      <c r="DB4" s="22"/>
+      <c r="DC4" s="22"/>
       <c r="DD4" s="22"/>
       <c r="DE4" s="22"/>
       <c r="DF4" s="22"/>
       <c r="DG4" s="22"/>
       <c r="DH4" s="22"/>
-      <c r="DI4" s="22"/>
-      <c r="DJ4" s="22"/>
-      <c r="DK4" s="22"/>
+      <c r="DI4" s="39"/>
+      <c r="DJ4" s="37">
+        <v>0</v>
+      </c>
+      <c r="DK4" s="38"/>
       <c r="DL4" s="22"/>
-      <c r="DM4" s="39"/>
-      <c r="DN4" s="37">
-        <v>0</v>
-      </c>
-      <c r="DO4" s="38"/>
+      <c r="DM4" s="22"/>
+      <c r="DN4" s="22"/>
+      <c r="DO4" s="22"/>
       <c r="DP4" s="22"/>
       <c r="DQ4" s="22"/>
       <c r="DR4" s="22"/>
       <c r="DS4" s="22"/>
       <c r="DT4" s="22"/>
       <c r="DU4" s="22"/>
-      <c r="DV4" s="22"/>
-      <c r="DW4" s="22"/>
-      <c r="DX4" s="22"/>
-      <c r="DY4" s="39"/>
-      <c r="DZ4" s="37">
+      <c r="DV4" s="39"/>
+      <c r="DW4" s="37">
         <v>0</v>
       </c>
-      <c r="EA4" s="38"/>
+      <c r="DX4" s="38"/>
+      <c r="DY4" s="22"/>
+      <c r="DZ4" s="22"/>
+      <c r="EA4" s="22"/>
       <c r="EB4" s="22"/>
       <c r="EC4" s="22"/>
       <c r="ED4" s="22"/>
@@ -4332,13 +4425,13 @@
       <c r="EF4" s="22"/>
       <c r="EG4" s="22"/>
       <c r="EH4" s="22"/>
-      <c r="EI4" s="22"/>
-      <c r="EJ4" s="22"/>
-      <c r="EK4" s="39"/>
-      <c r="EL4" s="37">
+      <c r="EI4" s="39"/>
+      <c r="EJ4" s="37">
         <v>0</v>
       </c>
-      <c r="EM4" s="38"/>
+      <c r="EK4" s="38"/>
+      <c r="EL4" s="22"/>
+      <c r="EM4" s="22"/>
       <c r="EN4" s="22"/>
       <c r="EO4" s="22"/>
       <c r="EP4" s="22"/>
@@ -4347,12 +4440,12 @@
       <c r="ES4" s="22"/>
       <c r="ET4" s="22"/>
       <c r="EU4" s="22"/>
-      <c r="EV4" s="22"/>
-      <c r="EW4" s="39"/>
-      <c r="EX4" s="37">
+      <c r="EV4" s="39"/>
+      <c r="EW4" s="37">
         <v>0</v>
       </c>
-      <c r="EY4" s="38"/>
+      <c r="EX4" s="38"/>
+      <c r="EY4" s="22"/>
       <c r="EZ4" s="22"/>
       <c r="FA4" s="22"/>
       <c r="FB4" s="22"/>
@@ -4363,7 +4456,9 @@
       <c r="FG4" s="22"/>
       <c r="FH4" s="22"/>
       <c r="FI4" s="39"/>
-      <c r="FJ4" s="37"/>
+      <c r="FJ4" s="37">
+        <v>0</v>
+      </c>
       <c r="FK4" s="38"/>
       <c r="FL4" s="22"/>
       <c r="FM4" s="22"/>
@@ -4374,9 +4469,23 @@
       <c r="FR4" s="22"/>
       <c r="FS4" s="22"/>
       <c r="FT4" s="22"/>
-      <c r="FU4" s="39"/>
+      <c r="FU4" s="22"/>
+      <c r="FV4" s="39"/>
+      <c r="FW4" s="37"/>
+      <c r="FX4" s="38"/>
+      <c r="FY4" s="22"/>
+      <c r="FZ4" s="22"/>
+      <c r="GA4" s="22"/>
+      <c r="GB4" s="22"/>
+      <c r="GC4" s="22"/>
+      <c r="GD4" s="22"/>
+      <c r="GE4" s="22"/>
+      <c r="GF4" s="22"/>
+      <c r="GG4" s="22"/>
+      <c r="GH4" s="22"/>
+      <c r="GI4" s="39"/>
     </row>
-    <row r="5" spans="1:177" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:191" x14ac:dyDescent="0.3">
       <c r="B5" s="12" t="s">
         <v>17</v>
       </c>
@@ -4415,10 +4524,10 @@
       <c r="R5" s="22"/>
       <c r="S5" s="22"/>
       <c r="T5" s="22"/>
-      <c r="U5" s="39"/>
-      <c r="V5" s="37"/>
-      <c r="W5" s="38"/>
-      <c r="X5" s="22"/>
+      <c r="U5" s="22"/>
+      <c r="V5" s="39"/>
+      <c r="W5" s="37"/>
+      <c r="X5" s="38"/>
       <c r="Y5" s="22"/>
       <c r="Z5" s="22"/>
       <c r="AA5" s="22"/>
@@ -4427,11 +4536,11 @@
       <c r="AD5" s="22"/>
       <c r="AE5" s="22"/>
       <c r="AF5" s="22"/>
-      <c r="AG5" s="39"/>
-      <c r="AH5" s="37"/>
-      <c r="AI5" s="38"/>
-      <c r="AJ5" s="22"/>
-      <c r="AK5" s="22"/>
+      <c r="AG5" s="22"/>
+      <c r="AH5" s="22"/>
+      <c r="AI5" s="39"/>
+      <c r="AJ5" s="37"/>
+      <c r="AK5" s="38"/>
       <c r="AL5" s="22"/>
       <c r="AM5" s="22"/>
       <c r="AN5" s="22"/>
@@ -4439,93 +4548,93 @@
       <c r="AP5" s="22"/>
       <c r="AQ5" s="22"/>
       <c r="AR5" s="22"/>
-      <c r="AS5" s="39"/>
-      <c r="AT5" s="37"/>
-      <c r="AU5" s="38"/>
-      <c r="AV5" s="22"/>
-      <c r="AW5" s="22"/>
-      <c r="AX5" s="22"/>
+      <c r="AS5" s="22"/>
+      <c r="AT5" s="22"/>
+      <c r="AU5" s="22"/>
+      <c r="AV5" s="39"/>
+      <c r="AW5" s="37"/>
+      <c r="AX5" s="38"/>
       <c r="AY5" s="22"/>
       <c r="AZ5" s="22"/>
       <c r="BA5" s="22"/>
       <c r="BB5" s="22"/>
       <c r="BC5" s="22"/>
       <c r="BD5" s="22"/>
-      <c r="BE5" s="39"/>
-      <c r="BF5" s="37"/>
-      <c r="BG5" s="38"/>
+      <c r="BE5" s="22"/>
+      <c r="BF5" s="22"/>
+      <c r="BG5" s="22"/>
       <c r="BH5" s="22"/>
-      <c r="BI5" s="22"/>
-      <c r="BJ5" s="22"/>
-      <c r="BK5" s="22"/>
+      <c r="BI5" s="39"/>
+      <c r="BJ5" s="37"/>
+      <c r="BK5" s="38"/>
       <c r="BL5" s="22"/>
       <c r="BM5" s="22"/>
       <c r="BN5" s="22"/>
       <c r="BO5" s="22"/>
       <c r="BP5" s="22"/>
-      <c r="BQ5" s="39"/>
-      <c r="BR5" s="37"/>
-      <c r="BS5" s="38"/>
+      <c r="BQ5" s="22"/>
+      <c r="BR5" s="22"/>
+      <c r="BS5" s="22"/>
       <c r="BT5" s="22"/>
       <c r="BU5" s="22"/>
-      <c r="BV5" s="22"/>
-      <c r="BW5" s="22"/>
-      <c r="BX5" s="22"/>
+      <c r="BV5" s="39"/>
+      <c r="BW5" s="37"/>
+      <c r="BX5" s="38"/>
       <c r="BY5" s="22"/>
       <c r="BZ5" s="22"/>
       <c r="CA5" s="22"/>
       <c r="CB5" s="22"/>
-      <c r="CC5" s="39"/>
-      <c r="CD5" s="37"/>
-      <c r="CE5" s="38"/>
+      <c r="CC5" s="22"/>
+      <c r="CD5" s="22"/>
+      <c r="CE5" s="22"/>
       <c r="CF5" s="22"/>
       <c r="CG5" s="22"/>
       <c r="CH5" s="22"/>
-      <c r="CI5" s="22"/>
-      <c r="CJ5" s="22"/>
-      <c r="CK5" s="22"/>
+      <c r="CI5" s="39"/>
+      <c r="CJ5" s="37"/>
+      <c r="CK5" s="38"/>
       <c r="CL5" s="22"/>
       <c r="CM5" s="22"/>
       <c r="CN5" s="22"/>
-      <c r="CO5" s="39"/>
-      <c r="CP5" s="37"/>
-      <c r="CQ5" s="38"/>
+      <c r="CO5" s="22"/>
+      <c r="CP5" s="22"/>
+      <c r="CQ5" s="22"/>
       <c r="CR5" s="22"/>
       <c r="CS5" s="22"/>
       <c r="CT5" s="22"/>
       <c r="CU5" s="22"/>
-      <c r="CV5" s="22"/>
-      <c r="CW5" s="22"/>
-      <c r="CX5" s="22"/>
+      <c r="CV5" s="39"/>
+      <c r="CW5" s="37"/>
+      <c r="CX5" s="38"/>
       <c r="CY5" s="22"/>
       <c r="CZ5" s="22"/>
-      <c r="DA5" s="39"/>
-      <c r="DB5" s="37"/>
-      <c r="DC5" s="38"/>
+      <c r="DA5" s="22"/>
+      <c r="DB5" s="22"/>
+      <c r="DC5" s="22"/>
       <c r="DD5" s="22"/>
       <c r="DE5" s="22"/>
       <c r="DF5" s="22"/>
       <c r="DG5" s="22"/>
       <c r="DH5" s="22"/>
-      <c r="DI5" s="22"/>
-      <c r="DJ5" s="22"/>
-      <c r="DK5" s="22"/>
+      <c r="DI5" s="39"/>
+      <c r="DJ5" s="37"/>
+      <c r="DK5" s="38"/>
       <c r="DL5" s="22"/>
-      <c r="DM5" s="39"/>
-      <c r="DN5" s="37"/>
-      <c r="DO5" s="38"/>
+      <c r="DM5" s="22"/>
+      <c r="DN5" s="22"/>
+      <c r="DO5" s="22"/>
       <c r="DP5" s="22"/>
       <c r="DQ5" s="22"/>
       <c r="DR5" s="22"/>
       <c r="DS5" s="22"/>
       <c r="DT5" s="22"/>
       <c r="DU5" s="22"/>
-      <c r="DV5" s="22"/>
-      <c r="DW5" s="22"/>
-      <c r="DX5" s="22"/>
-      <c r="DY5" s="39"/>
-      <c r="DZ5" s="37"/>
-      <c r="EA5" s="38"/>
+      <c r="DV5" s="39"/>
+      <c r="DW5" s="37"/>
+      <c r="DX5" s="38"/>
+      <c r="DY5" s="22"/>
+      <c r="DZ5" s="22"/>
+      <c r="EA5" s="22"/>
       <c r="EB5" s="22"/>
       <c r="EC5" s="22"/>
       <c r="ED5" s="22"/>
@@ -4533,11 +4642,11 @@
       <c r="EF5" s="22"/>
       <c r="EG5" s="22"/>
       <c r="EH5" s="22"/>
-      <c r="EI5" s="22"/>
-      <c r="EJ5" s="22"/>
-      <c r="EK5" s="39"/>
-      <c r="EL5" s="37"/>
-      <c r="EM5" s="38"/>
+      <c r="EI5" s="39"/>
+      <c r="EJ5" s="37"/>
+      <c r="EK5" s="38"/>
+      <c r="EL5" s="22"/>
+      <c r="EM5" s="22"/>
       <c r="EN5" s="22"/>
       <c r="EO5" s="22"/>
       <c r="EP5" s="22"/>
@@ -4546,10 +4655,10 @@
       <c r="ES5" s="22"/>
       <c r="ET5" s="22"/>
       <c r="EU5" s="22"/>
-      <c r="EV5" s="22"/>
-      <c r="EW5" s="39"/>
-      <c r="EX5" s="37"/>
-      <c r="EY5" s="38"/>
+      <c r="EV5" s="39"/>
+      <c r="EW5" s="37"/>
+      <c r="EX5" s="38"/>
+      <c r="EY5" s="22"/>
       <c r="EZ5" s="22"/>
       <c r="FA5" s="22"/>
       <c r="FB5" s="22"/>
@@ -4571,9 +4680,23 @@
       <c r="FR5" s="22"/>
       <c r="FS5" s="22"/>
       <c r="FT5" s="22"/>
-      <c r="FU5" s="39"/>
+      <c r="FU5" s="22"/>
+      <c r="FV5" s="39"/>
+      <c r="FW5" s="37"/>
+      <c r="FX5" s="38"/>
+      <c r="FY5" s="22"/>
+      <c r="FZ5" s="22"/>
+      <c r="GA5" s="22"/>
+      <c r="GB5" s="22"/>
+      <c r="GC5" s="22"/>
+      <c r="GD5" s="22"/>
+      <c r="GE5" s="22"/>
+      <c r="GF5" s="22"/>
+      <c r="GG5" s="22"/>
+      <c r="GH5" s="22"/>
+      <c r="GI5" s="39"/>
     </row>
-    <row r="6" spans="1:177" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:191" x14ac:dyDescent="0.3">
       <c r="B6" s="12" t="s">
         <v>0</v>
       </c>
@@ -4612,10 +4735,10 @@
       <c r="R6" s="22"/>
       <c r="S6" s="22"/>
       <c r="T6" s="22"/>
-      <c r="U6" s="39"/>
-      <c r="V6" s="37"/>
-      <c r="W6" s="38"/>
-      <c r="X6" s="22"/>
+      <c r="U6" s="22"/>
+      <c r="V6" s="39"/>
+      <c r="W6" s="37"/>
+      <c r="X6" s="38"/>
       <c r="Y6" s="22"/>
       <c r="Z6" s="22"/>
       <c r="AA6" s="22"/>
@@ -4624,11 +4747,11 @@
       <c r="AD6" s="22"/>
       <c r="AE6" s="22"/>
       <c r="AF6" s="22"/>
-      <c r="AG6" s="39"/>
-      <c r="AH6" s="37"/>
-      <c r="AI6" s="38"/>
-      <c r="AJ6" s="22"/>
-      <c r="AK6" s="22"/>
+      <c r="AG6" s="22"/>
+      <c r="AH6" s="22"/>
+      <c r="AI6" s="39"/>
+      <c r="AJ6" s="37"/>
+      <c r="AK6" s="38"/>
       <c r="AL6" s="22"/>
       <c r="AM6" s="22"/>
       <c r="AN6" s="22"/>
@@ -4636,93 +4759,93 @@
       <c r="AP6" s="22"/>
       <c r="AQ6" s="22"/>
       <c r="AR6" s="22"/>
-      <c r="AS6" s="39"/>
-      <c r="AT6" s="37"/>
-      <c r="AU6" s="38"/>
-      <c r="AV6" s="22"/>
-      <c r="AW6" s="22"/>
-      <c r="AX6" s="22"/>
+      <c r="AS6" s="22"/>
+      <c r="AT6" s="22"/>
+      <c r="AU6" s="22"/>
+      <c r="AV6" s="39"/>
+      <c r="AW6" s="37"/>
+      <c r="AX6" s="38"/>
       <c r="AY6" s="22"/>
       <c r="AZ6" s="22"/>
       <c r="BA6" s="22"/>
       <c r="BB6" s="22"/>
       <c r="BC6" s="22"/>
       <c r="BD6" s="22"/>
-      <c r="BE6" s="39"/>
-      <c r="BF6" s="37"/>
-      <c r="BG6" s="38"/>
+      <c r="BE6" s="22"/>
+      <c r="BF6" s="22"/>
+      <c r="BG6" s="22"/>
       <c r="BH6" s="22"/>
-      <c r="BI6" s="22"/>
-      <c r="BJ6" s="22"/>
-      <c r="BK6" s="22"/>
+      <c r="BI6" s="39"/>
+      <c r="BJ6" s="37"/>
+      <c r="BK6" s="38"/>
       <c r="BL6" s="22"/>
       <c r="BM6" s="22"/>
       <c r="BN6" s="22"/>
       <c r="BO6" s="22"/>
       <c r="BP6" s="22"/>
-      <c r="BQ6" s="39"/>
-      <c r="BR6" s="37"/>
-      <c r="BS6" s="38"/>
+      <c r="BQ6" s="22"/>
+      <c r="BR6" s="22"/>
+      <c r="BS6" s="22"/>
       <c r="BT6" s="22"/>
       <c r="BU6" s="22"/>
-      <c r="BV6" s="22"/>
-      <c r="BW6" s="22"/>
-      <c r="BX6" s="22"/>
+      <c r="BV6" s="39"/>
+      <c r="BW6" s="37"/>
+      <c r="BX6" s="38"/>
       <c r="BY6" s="22"/>
       <c r="BZ6" s="22"/>
       <c r="CA6" s="22"/>
       <c r="CB6" s="22"/>
-      <c r="CC6" s="39"/>
-      <c r="CD6" s="37"/>
-      <c r="CE6" s="38"/>
+      <c r="CC6" s="22"/>
+      <c r="CD6" s="22"/>
+      <c r="CE6" s="22"/>
       <c r="CF6" s="22"/>
       <c r="CG6" s="22"/>
       <c r="CH6" s="22"/>
-      <c r="CI6" s="22"/>
-      <c r="CJ6" s="22"/>
-      <c r="CK6" s="22"/>
+      <c r="CI6" s="39"/>
+      <c r="CJ6" s="37"/>
+      <c r="CK6" s="38"/>
       <c r="CL6" s="22"/>
       <c r="CM6" s="22"/>
       <c r="CN6" s="22"/>
-      <c r="CO6" s="39"/>
-      <c r="CP6" s="37"/>
-      <c r="CQ6" s="38"/>
+      <c r="CO6" s="22"/>
+      <c r="CP6" s="22"/>
+      <c r="CQ6" s="22"/>
       <c r="CR6" s="22"/>
       <c r="CS6" s="22"/>
       <c r="CT6" s="22"/>
       <c r="CU6" s="22"/>
-      <c r="CV6" s="22"/>
-      <c r="CW6" s="22"/>
-      <c r="CX6" s="22"/>
+      <c r="CV6" s="39"/>
+      <c r="CW6" s="37"/>
+      <c r="CX6" s="38"/>
       <c r="CY6" s="22"/>
       <c r="CZ6" s="22"/>
-      <c r="DA6" s="39"/>
-      <c r="DB6" s="37"/>
-      <c r="DC6" s="38"/>
+      <c r="DA6" s="22"/>
+      <c r="DB6" s="22"/>
+      <c r="DC6" s="22"/>
       <c r="DD6" s="22"/>
       <c r="DE6" s="22"/>
       <c r="DF6" s="22"/>
       <c r="DG6" s="22"/>
       <c r="DH6" s="22"/>
-      <c r="DI6" s="22"/>
-      <c r="DJ6" s="22"/>
-      <c r="DK6" s="22"/>
+      <c r="DI6" s="39"/>
+      <c r="DJ6" s="37"/>
+      <c r="DK6" s="38"/>
       <c r="DL6" s="22"/>
-      <c r="DM6" s="39"/>
-      <c r="DN6" s="37"/>
-      <c r="DO6" s="38"/>
+      <c r="DM6" s="22"/>
+      <c r="DN6" s="22"/>
+      <c r="DO6" s="22"/>
       <c r="DP6" s="22"/>
       <c r="DQ6" s="22"/>
       <c r="DR6" s="22"/>
       <c r="DS6" s="22"/>
       <c r="DT6" s="22"/>
       <c r="DU6" s="22"/>
-      <c r="DV6" s="22"/>
-      <c r="DW6" s="22"/>
-      <c r="DX6" s="22"/>
-      <c r="DY6" s="39"/>
-      <c r="DZ6" s="37"/>
-      <c r="EA6" s="38"/>
+      <c r="DV6" s="39"/>
+      <c r="DW6" s="37"/>
+      <c r="DX6" s="38"/>
+      <c r="DY6" s="22"/>
+      <c r="DZ6" s="22"/>
+      <c r="EA6" s="22"/>
       <c r="EB6" s="22"/>
       <c r="EC6" s="22"/>
       <c r="ED6" s="22"/>
@@ -4730,11 +4853,11 @@
       <c r="EF6" s="22"/>
       <c r="EG6" s="22"/>
       <c r="EH6" s="22"/>
-      <c r="EI6" s="22"/>
-      <c r="EJ6" s="22"/>
-      <c r="EK6" s="39"/>
-      <c r="EL6" s="37"/>
-      <c r="EM6" s="38"/>
+      <c r="EI6" s="39"/>
+      <c r="EJ6" s="37"/>
+      <c r="EK6" s="38"/>
+      <c r="EL6" s="22"/>
+      <c r="EM6" s="22"/>
       <c r="EN6" s="22"/>
       <c r="EO6" s="22"/>
       <c r="EP6" s="22"/>
@@ -4743,10 +4866,10 @@
       <c r="ES6" s="22"/>
       <c r="ET6" s="22"/>
       <c r="EU6" s="22"/>
-      <c r="EV6" s="22"/>
-      <c r="EW6" s="39"/>
-      <c r="EX6" s="37"/>
-      <c r="EY6" s="38"/>
+      <c r="EV6" s="39"/>
+      <c r="EW6" s="37"/>
+      <c r="EX6" s="38"/>
+      <c r="EY6" s="22"/>
       <c r="EZ6" s="22"/>
       <c r="FA6" s="22"/>
       <c r="FB6" s="22"/>
@@ -4768,9 +4891,23 @@
       <c r="FR6" s="22"/>
       <c r="FS6" s="22"/>
       <c r="FT6" s="22"/>
-      <c r="FU6" s="39"/>
+      <c r="FU6" s="22"/>
+      <c r="FV6" s="39"/>
+      <c r="FW6" s="37"/>
+      <c r="FX6" s="38"/>
+      <c r="FY6" s="22"/>
+      <c r="FZ6" s="22"/>
+      <c r="GA6" s="22"/>
+      <c r="GB6" s="22"/>
+      <c r="GC6" s="22"/>
+      <c r="GD6" s="22"/>
+      <c r="GE6" s="22"/>
+      <c r="GF6" s="22"/>
+      <c r="GG6" s="22"/>
+      <c r="GH6" s="22"/>
+      <c r="GI6" s="39"/>
     </row>
-    <row r="7" spans="1:177" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:191" ht="45" x14ac:dyDescent="0.3">
       <c r="B7" s="12" t="s">
         <v>38</v>
       </c>
@@ -4809,10 +4946,10 @@
       <c r="R7" s="22"/>
       <c r="S7" s="22"/>
       <c r="T7" s="22"/>
-      <c r="U7" s="39"/>
-      <c r="V7" s="37"/>
-      <c r="W7" s="38"/>
-      <c r="X7" s="22"/>
+      <c r="U7" s="22"/>
+      <c r="V7" s="39"/>
+      <c r="W7" s="37"/>
+      <c r="X7" s="38"/>
       <c r="Y7" s="22"/>
       <c r="Z7" s="22"/>
       <c r="AA7" s="22"/>
@@ -4821,11 +4958,11 @@
       <c r="AD7" s="22"/>
       <c r="AE7" s="22"/>
       <c r="AF7" s="22"/>
-      <c r="AG7" s="39"/>
-      <c r="AH7" s="37"/>
-      <c r="AI7" s="38"/>
-      <c r="AJ7" s="22"/>
-      <c r="AK7" s="22"/>
+      <c r="AG7" s="22"/>
+      <c r="AH7" s="22"/>
+      <c r="AI7" s="39"/>
+      <c r="AJ7" s="37"/>
+      <c r="AK7" s="38"/>
       <c r="AL7" s="22"/>
       <c r="AM7" s="22"/>
       <c r="AN7" s="22"/>
@@ -4833,93 +4970,93 @@
       <c r="AP7" s="22"/>
       <c r="AQ7" s="22"/>
       <c r="AR7" s="22"/>
-      <c r="AS7" s="39"/>
-      <c r="AT7" s="37"/>
-      <c r="AU7" s="38"/>
-      <c r="AV7" s="22"/>
-      <c r="AW7" s="22"/>
-      <c r="AX7" s="22"/>
+      <c r="AS7" s="22"/>
+      <c r="AT7" s="22"/>
+      <c r="AU7" s="22"/>
+      <c r="AV7" s="39"/>
+      <c r="AW7" s="37"/>
+      <c r="AX7" s="38"/>
       <c r="AY7" s="22"/>
       <c r="AZ7" s="22"/>
       <c r="BA7" s="22"/>
       <c r="BB7" s="22"/>
       <c r="BC7" s="22"/>
       <c r="BD7" s="22"/>
-      <c r="BE7" s="39"/>
-      <c r="BF7" s="37"/>
-      <c r="BG7" s="38"/>
+      <c r="BE7" s="22"/>
+      <c r="BF7" s="22"/>
+      <c r="BG7" s="22"/>
       <c r="BH7" s="22"/>
-      <c r="BI7" s="22"/>
-      <c r="BJ7" s="22"/>
-      <c r="BK7" s="22"/>
+      <c r="BI7" s="39"/>
+      <c r="BJ7" s="37"/>
+      <c r="BK7" s="38"/>
       <c r="BL7" s="22"/>
       <c r="BM7" s="22"/>
       <c r="BN7" s="22"/>
       <c r="BO7" s="22"/>
       <c r="BP7" s="22"/>
-      <c r="BQ7" s="39"/>
-      <c r="BR7" s="37"/>
-      <c r="BS7" s="38"/>
+      <c r="BQ7" s="22"/>
+      <c r="BR7" s="22"/>
+      <c r="BS7" s="22"/>
       <c r="BT7" s="22"/>
       <c r="BU7" s="22"/>
-      <c r="BV7" s="22"/>
-      <c r="BW7" s="22"/>
-      <c r="BX7" s="22"/>
+      <c r="BV7" s="39"/>
+      <c r="BW7" s="37"/>
+      <c r="BX7" s="38"/>
       <c r="BY7" s="22"/>
       <c r="BZ7" s="22"/>
       <c r="CA7" s="22"/>
       <c r="CB7" s="22"/>
-      <c r="CC7" s="39"/>
-      <c r="CD7" s="37"/>
-      <c r="CE7" s="38"/>
+      <c r="CC7" s="22"/>
+      <c r="CD7" s="22"/>
+      <c r="CE7" s="22"/>
       <c r="CF7" s="22"/>
       <c r="CG7" s="22"/>
       <c r="CH7" s="22"/>
-      <c r="CI7" s="22"/>
-      <c r="CJ7" s="22"/>
-      <c r="CK7" s="22"/>
+      <c r="CI7" s="39"/>
+      <c r="CJ7" s="37"/>
+      <c r="CK7" s="38"/>
       <c r="CL7" s="22"/>
       <c r="CM7" s="22"/>
       <c r="CN7" s="22"/>
-      <c r="CO7" s="39"/>
-      <c r="CP7" s="37"/>
-      <c r="CQ7" s="38"/>
+      <c r="CO7" s="22"/>
+      <c r="CP7" s="22"/>
+      <c r="CQ7" s="22"/>
       <c r="CR7" s="22"/>
       <c r="CS7" s="22"/>
       <c r="CT7" s="22"/>
       <c r="CU7" s="22"/>
-      <c r="CV7" s="22"/>
-      <c r="CW7" s="22"/>
-      <c r="CX7" s="22"/>
+      <c r="CV7" s="39"/>
+      <c r="CW7" s="37"/>
+      <c r="CX7" s="38"/>
       <c r="CY7" s="22"/>
       <c r="CZ7" s="22"/>
-      <c r="DA7" s="39"/>
-      <c r="DB7" s="37"/>
-      <c r="DC7" s="38"/>
+      <c r="DA7" s="22"/>
+      <c r="DB7" s="22"/>
+      <c r="DC7" s="22"/>
       <c r="DD7" s="22"/>
       <c r="DE7" s="22"/>
       <c r="DF7" s="22"/>
       <c r="DG7" s="22"/>
       <c r="DH7" s="22"/>
-      <c r="DI7" s="22"/>
-      <c r="DJ7" s="22"/>
-      <c r="DK7" s="22"/>
+      <c r="DI7" s="39"/>
+      <c r="DJ7" s="37"/>
+      <c r="DK7" s="38"/>
       <c r="DL7" s="22"/>
-      <c r="DM7" s="39"/>
-      <c r="DN7" s="37"/>
-      <c r="DO7" s="38"/>
+      <c r="DM7" s="22"/>
+      <c r="DN7" s="22"/>
+      <c r="DO7" s="22"/>
       <c r="DP7" s="22"/>
       <c r="DQ7" s="22"/>
       <c r="DR7" s="22"/>
       <c r="DS7" s="22"/>
       <c r="DT7" s="22"/>
       <c r="DU7" s="22"/>
-      <c r="DV7" s="22"/>
-      <c r="DW7" s="22"/>
-      <c r="DX7" s="22"/>
-      <c r="DY7" s="39"/>
-      <c r="DZ7" s="37"/>
-      <c r="EA7" s="38"/>
+      <c r="DV7" s="39"/>
+      <c r="DW7" s="37"/>
+      <c r="DX7" s="38"/>
+      <c r="DY7" s="22"/>
+      <c r="DZ7" s="22"/>
+      <c r="EA7" s="22"/>
       <c r="EB7" s="22"/>
       <c r="EC7" s="22"/>
       <c r="ED7" s="22"/>
@@ -4927,11 +5064,11 @@
       <c r="EF7" s="22"/>
       <c r="EG7" s="22"/>
       <c r="EH7" s="22"/>
-      <c r="EI7" s="22"/>
-      <c r="EJ7" s="22"/>
-      <c r="EK7" s="39"/>
-      <c r="EL7" s="37"/>
-      <c r="EM7" s="38"/>
+      <c r="EI7" s="39"/>
+      <c r="EJ7" s="37"/>
+      <c r="EK7" s="38"/>
+      <c r="EL7" s="22"/>
+      <c r="EM7" s="22"/>
       <c r="EN7" s="22"/>
       <c r="EO7" s="22"/>
       <c r="EP7" s="22"/>
@@ -4940,10 +5077,10 @@
       <c r="ES7" s="22"/>
       <c r="ET7" s="22"/>
       <c r="EU7" s="22"/>
-      <c r="EV7" s="22"/>
-      <c r="EW7" s="39"/>
-      <c r="EX7" s="37"/>
-      <c r="EY7" s="38"/>
+      <c r="EV7" s="39"/>
+      <c r="EW7" s="37"/>
+      <c r="EX7" s="38"/>
+      <c r="EY7" s="22"/>
       <c r="EZ7" s="22"/>
       <c r="FA7" s="22"/>
       <c r="FB7" s="22"/>
@@ -4965,9 +5102,23 @@
       <c r="FR7" s="22"/>
       <c r="FS7" s="22"/>
       <c r="FT7" s="22"/>
-      <c r="FU7" s="39"/>
+      <c r="FU7" s="22"/>
+      <c r="FV7" s="39"/>
+      <c r="FW7" s="37"/>
+      <c r="FX7" s="38"/>
+      <c r="FY7" s="22"/>
+      <c r="FZ7" s="22"/>
+      <c r="GA7" s="22"/>
+      <c r="GB7" s="22"/>
+      <c r="GC7" s="22"/>
+      <c r="GD7" s="22"/>
+      <c r="GE7" s="22"/>
+      <c r="GF7" s="22"/>
+      <c r="GG7" s="22"/>
+      <c r="GH7" s="22"/>
+      <c r="GI7" s="39"/>
     </row>
-    <row r="8" spans="1:177" ht="46.15" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:191" ht="45" x14ac:dyDescent="0.3">
       <c r="B8" s="12" t="s">
         <v>38</v>
       </c>
@@ -5004,10 +5155,10 @@
       <c r="R8" s="22"/>
       <c r="S8" s="22"/>
       <c r="T8" s="22"/>
-      <c r="U8" s="39"/>
-      <c r="V8" s="37"/>
-      <c r="W8" s="38"/>
-      <c r="X8" s="22"/>
+      <c r="U8" s="22"/>
+      <c r="V8" s="39"/>
+      <c r="W8" s="37"/>
+      <c r="X8" s="38"/>
       <c r="Y8" s="22"/>
       <c r="Z8" s="22"/>
       <c r="AA8" s="22"/>
@@ -5016,11 +5167,11 @@
       <c r="AD8" s="22"/>
       <c r="AE8" s="22"/>
       <c r="AF8" s="22"/>
-      <c r="AG8" s="39"/>
-      <c r="AH8" s="37"/>
-      <c r="AI8" s="38"/>
-      <c r="AJ8" s="22"/>
-      <c r="AK8" s="22"/>
+      <c r="AG8" s="22"/>
+      <c r="AH8" s="22"/>
+      <c r="AI8" s="39"/>
+      <c r="AJ8" s="37"/>
+      <c r="AK8" s="38"/>
       <c r="AL8" s="22"/>
       <c r="AM8" s="22"/>
       <c r="AN8" s="22"/>
@@ -5028,93 +5179,93 @@
       <c r="AP8" s="22"/>
       <c r="AQ8" s="22"/>
       <c r="AR8" s="22"/>
-      <c r="AS8" s="39"/>
-      <c r="AT8" s="37"/>
-      <c r="AU8" s="38"/>
-      <c r="AV8" s="22"/>
-      <c r="AW8" s="22"/>
-      <c r="AX8" s="22"/>
+      <c r="AS8" s="22"/>
+      <c r="AT8" s="22"/>
+      <c r="AU8" s="22"/>
+      <c r="AV8" s="39"/>
+      <c r="AW8" s="37"/>
+      <c r="AX8" s="38"/>
       <c r="AY8" s="22"/>
       <c r="AZ8" s="22"/>
       <c r="BA8" s="22"/>
       <c r="BB8" s="22"/>
       <c r="BC8" s="22"/>
       <c r="BD8" s="22"/>
-      <c r="BE8" s="39"/>
-      <c r="BF8" s="37"/>
-      <c r="BG8" s="38"/>
+      <c r="BE8" s="22"/>
+      <c r="BF8" s="22"/>
+      <c r="BG8" s="22"/>
       <c r="BH8" s="22"/>
-      <c r="BI8" s="22"/>
-      <c r="BJ8" s="22"/>
-      <c r="BK8" s="22"/>
+      <c r="BI8" s="39"/>
+      <c r="BJ8" s="37"/>
+      <c r="BK8" s="38"/>
       <c r="BL8" s="22"/>
       <c r="BM8" s="22"/>
       <c r="BN8" s="22"/>
       <c r="BO8" s="22"/>
       <c r="BP8" s="22"/>
-      <c r="BQ8" s="39"/>
-      <c r="BR8" s="37"/>
-      <c r="BS8" s="38"/>
+      <c r="BQ8" s="22"/>
+      <c r="BR8" s="22"/>
+      <c r="BS8" s="22"/>
       <c r="BT8" s="22"/>
       <c r="BU8" s="22"/>
-      <c r="BV8" s="22"/>
-      <c r="BW8" s="22"/>
-      <c r="BX8" s="22"/>
+      <c r="BV8" s="39"/>
+      <c r="BW8" s="37"/>
+      <c r="BX8" s="38"/>
       <c r="BY8" s="22"/>
       <c r="BZ8" s="22"/>
       <c r="CA8" s="22"/>
       <c r="CB8" s="22"/>
-      <c r="CC8" s="39"/>
-      <c r="CD8" s="37"/>
-      <c r="CE8" s="38"/>
+      <c r="CC8" s="22"/>
+      <c r="CD8" s="22"/>
+      <c r="CE8" s="22"/>
       <c r="CF8" s="22"/>
       <c r="CG8" s="22"/>
       <c r="CH8" s="22"/>
-      <c r="CI8" s="22"/>
-      <c r="CJ8" s="22"/>
-      <c r="CK8" s="22"/>
+      <c r="CI8" s="39"/>
+      <c r="CJ8" s="37"/>
+      <c r="CK8" s="38"/>
       <c r="CL8" s="22"/>
       <c r="CM8" s="22"/>
       <c r="CN8" s="22"/>
-      <c r="CO8" s="39"/>
-      <c r="CP8" s="37"/>
-      <c r="CQ8" s="38"/>
+      <c r="CO8" s="22"/>
+      <c r="CP8" s="22"/>
+      <c r="CQ8" s="22"/>
       <c r="CR8" s="22"/>
       <c r="CS8" s="22"/>
       <c r="CT8" s="22"/>
       <c r="CU8" s="22"/>
-      <c r="CV8" s="22"/>
-      <c r="CW8" s="22"/>
-      <c r="CX8" s="22"/>
+      <c r="CV8" s="39"/>
+      <c r="CW8" s="37"/>
+      <c r="CX8" s="38"/>
       <c r="CY8" s="22"/>
       <c r="CZ8" s="22"/>
-      <c r="DA8" s="39"/>
-      <c r="DB8" s="37"/>
-      <c r="DC8" s="38"/>
+      <c r="DA8" s="22"/>
+      <c r="DB8" s="22"/>
+      <c r="DC8" s="22"/>
       <c r="DD8" s="22"/>
       <c r="DE8" s="22"/>
       <c r="DF8" s="22"/>
       <c r="DG8" s="22"/>
       <c r="DH8" s="22"/>
-      <c r="DI8" s="22"/>
-      <c r="DJ8" s="22"/>
-      <c r="DK8" s="22"/>
+      <c r="DI8" s="39"/>
+      <c r="DJ8" s="37"/>
+      <c r="DK8" s="38"/>
       <c r="DL8" s="22"/>
-      <c r="DM8" s="39"/>
-      <c r="DN8" s="37"/>
-      <c r="DO8" s="38"/>
+      <c r="DM8" s="22"/>
+      <c r="DN8" s="22"/>
+      <c r="DO8" s="22"/>
       <c r="DP8" s="22"/>
       <c r="DQ8" s="22"/>
       <c r="DR8" s="22"/>
       <c r="DS8" s="22"/>
       <c r="DT8" s="22"/>
       <c r="DU8" s="22"/>
-      <c r="DV8" s="22"/>
-      <c r="DW8" s="22"/>
-      <c r="DX8" s="22"/>
-      <c r="DY8" s="39"/>
-      <c r="DZ8" s="37"/>
-      <c r="EA8" s="38"/>
+      <c r="DV8" s="39"/>
+      <c r="DW8" s="37"/>
+      <c r="DX8" s="38"/>
+      <c r="DY8" s="22"/>
+      <c r="DZ8" s="22"/>
+      <c r="EA8" s="22"/>
       <c r="EB8" s="22"/>
       <c r="EC8" s="22"/>
       <c r="ED8" s="22"/>
@@ -5122,11 +5273,11 @@
       <c r="EF8" s="22"/>
       <c r="EG8" s="22"/>
       <c r="EH8" s="22"/>
-      <c r="EI8" s="22"/>
-      <c r="EJ8" s="22"/>
-      <c r="EK8" s="39"/>
-      <c r="EL8" s="37"/>
-      <c r="EM8" s="38"/>
+      <c r="EI8" s="39"/>
+      <c r="EJ8" s="37"/>
+      <c r="EK8" s="38"/>
+      <c r="EL8" s="22"/>
+      <c r="EM8" s="22"/>
       <c r="EN8" s="22"/>
       <c r="EO8" s="22"/>
       <c r="EP8" s="22"/>
@@ -5135,10 +5286,10 @@
       <c r="ES8" s="22"/>
       <c r="ET8" s="22"/>
       <c r="EU8" s="22"/>
-      <c r="EV8" s="22"/>
-      <c r="EW8" s="39"/>
-      <c r="EX8" s="37"/>
-      <c r="EY8" s="38"/>
+      <c r="EV8" s="39"/>
+      <c r="EW8" s="37"/>
+      <c r="EX8" s="38"/>
+      <c r="EY8" s="22"/>
       <c r="EZ8" s="22"/>
       <c r="FA8" s="22"/>
       <c r="FB8" s="22"/>
@@ -5160,9 +5311,23 @@
       <c r="FR8" s="22"/>
       <c r="FS8" s="22"/>
       <c r="FT8" s="22"/>
-      <c r="FU8" s="39"/>
+      <c r="FU8" s="22"/>
+      <c r="FV8" s="39"/>
+      <c r="FW8" s="37"/>
+      <c r="FX8" s="38"/>
+      <c r="FY8" s="22"/>
+      <c r="FZ8" s="22"/>
+      <c r="GA8" s="22"/>
+      <c r="GB8" s="22"/>
+      <c r="GC8" s="22"/>
+      <c r="GD8" s="22"/>
+      <c r="GE8" s="22"/>
+      <c r="GF8" s="22"/>
+      <c r="GG8" s="22"/>
+      <c r="GH8" s="22"/>
+      <c r="GI8" s="39"/>
     </row>
-    <row r="9" spans="1:177" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:191" x14ac:dyDescent="0.3">
       <c r="B9" s="12" t="s">
         <v>1</v>
       </c>
@@ -5201,10 +5366,10 @@
       <c r="R9" s="22"/>
       <c r="S9" s="22"/>
       <c r="T9" s="22"/>
-      <c r="U9" s="39"/>
-      <c r="V9" s="37"/>
-      <c r="W9" s="38"/>
-      <c r="X9" s="22"/>
+      <c r="U9" s="22"/>
+      <c r="V9" s="39"/>
+      <c r="W9" s="37"/>
+      <c r="X9" s="38"/>
       <c r="Y9" s="22"/>
       <c r="Z9" s="22"/>
       <c r="AA9" s="22"/>
@@ -5213,11 +5378,11 @@
       <c r="AD9" s="22"/>
       <c r="AE9" s="22"/>
       <c r="AF9" s="22"/>
-      <c r="AG9" s="39"/>
-      <c r="AH9" s="37"/>
-      <c r="AI9" s="38"/>
-      <c r="AJ9" s="22"/>
-      <c r="AK9" s="22"/>
+      <c r="AG9" s="22"/>
+      <c r="AH9" s="22"/>
+      <c r="AI9" s="39"/>
+      <c r="AJ9" s="37"/>
+      <c r="AK9" s="38"/>
       <c r="AL9" s="22"/>
       <c r="AM9" s="22"/>
       <c r="AN9" s="22"/>
@@ -5225,93 +5390,93 @@
       <c r="AP9" s="22"/>
       <c r="AQ9" s="22"/>
       <c r="AR9" s="22"/>
-      <c r="AS9" s="39"/>
-      <c r="AT9" s="37"/>
-      <c r="AU9" s="38"/>
-      <c r="AV9" s="22"/>
-      <c r="AW9" s="22"/>
-      <c r="AX9" s="22"/>
+      <c r="AS9" s="22"/>
+      <c r="AT9" s="22"/>
+      <c r="AU9" s="22"/>
+      <c r="AV9" s="39"/>
+      <c r="AW9" s="37"/>
+      <c r="AX9" s="38"/>
       <c r="AY9" s="22"/>
       <c r="AZ9" s="22"/>
       <c r="BA9" s="22"/>
       <c r="BB9" s="22"/>
       <c r="BC9" s="22"/>
       <c r="BD9" s="22"/>
-      <c r="BE9" s="39"/>
-      <c r="BF9" s="37"/>
-      <c r="BG9" s="38"/>
+      <c r="BE9" s="22"/>
+      <c r="BF9" s="22"/>
+      <c r="BG9" s="22"/>
       <c r="BH9" s="22"/>
-      <c r="BI9" s="22"/>
-      <c r="BJ9" s="22"/>
-      <c r="BK9" s="22"/>
+      <c r="BI9" s="39"/>
+      <c r="BJ9" s="37"/>
+      <c r="BK9" s="38"/>
       <c r="BL9" s="22"/>
       <c r="BM9" s="22"/>
       <c r="BN9" s="22"/>
       <c r="BO9" s="22"/>
       <c r="BP9" s="22"/>
-      <c r="BQ9" s="39"/>
-      <c r="BR9" s="37"/>
-      <c r="BS9" s="38"/>
+      <c r="BQ9" s="22"/>
+      <c r="BR9" s="22"/>
+      <c r="BS9" s="22"/>
       <c r="BT9" s="22"/>
       <c r="BU9" s="22"/>
-      <c r="BV9" s="22"/>
-      <c r="BW9" s="22"/>
-      <c r="BX9" s="22"/>
+      <c r="BV9" s="39"/>
+      <c r="BW9" s="37"/>
+      <c r="BX9" s="38"/>
       <c r="BY9" s="22"/>
       <c r="BZ9" s="22"/>
       <c r="CA9" s="22"/>
       <c r="CB9" s="22"/>
-      <c r="CC9" s="39"/>
-      <c r="CD9" s="37"/>
-      <c r="CE9" s="38"/>
+      <c r="CC9" s="22"/>
+      <c r="CD9" s="22"/>
+      <c r="CE9" s="22"/>
       <c r="CF9" s="22"/>
       <c r="CG9" s="22"/>
       <c r="CH9" s="22"/>
-      <c r="CI9" s="22"/>
-      <c r="CJ9" s="22"/>
-      <c r="CK9" s="22"/>
+      <c r="CI9" s="39"/>
+      <c r="CJ9" s="37"/>
+      <c r="CK9" s="38"/>
       <c r="CL9" s="22"/>
       <c r="CM9" s="22"/>
       <c r="CN9" s="22"/>
-      <c r="CO9" s="39"/>
-      <c r="CP9" s="37"/>
-      <c r="CQ9" s="38"/>
+      <c r="CO9" s="22"/>
+      <c r="CP9" s="22"/>
+      <c r="CQ9" s="22"/>
       <c r="CR9" s="22"/>
       <c r="CS9" s="22"/>
       <c r="CT9" s="22"/>
       <c r="CU9" s="22"/>
-      <c r="CV9" s="22"/>
-      <c r="CW9" s="22"/>
-      <c r="CX9" s="22"/>
+      <c r="CV9" s="39"/>
+      <c r="CW9" s="37"/>
+      <c r="CX9" s="38"/>
       <c r="CY9" s="22"/>
       <c r="CZ9" s="22"/>
-      <c r="DA9" s="39"/>
-      <c r="DB9" s="37"/>
-      <c r="DC9" s="38"/>
+      <c r="DA9" s="22"/>
+      <c r="DB9" s="22"/>
+      <c r="DC9" s="22"/>
       <c r="DD9" s="22"/>
       <c r="DE9" s="22"/>
       <c r="DF9" s="22"/>
       <c r="DG9" s="22"/>
       <c r="DH9" s="22"/>
-      <c r="DI9" s="22"/>
-      <c r="DJ9" s="22"/>
-      <c r="DK9" s="22"/>
+      <c r="DI9" s="39"/>
+      <c r="DJ9" s="37"/>
+      <c r="DK9" s="38"/>
       <c r="DL9" s="22"/>
-      <c r="DM9" s="39"/>
-      <c r="DN9" s="37"/>
-      <c r="DO9" s="38"/>
+      <c r="DM9" s="22"/>
+      <c r="DN9" s="22"/>
+      <c r="DO9" s="22"/>
       <c r="DP9" s="22"/>
       <c r="DQ9" s="22"/>
       <c r="DR9" s="22"/>
       <c r="DS9" s="22"/>
       <c r="DT9" s="22"/>
       <c r="DU9" s="22"/>
-      <c r="DV9" s="22"/>
-      <c r="DW9" s="22"/>
-      <c r="DX9" s="22"/>
-      <c r="DY9" s="39"/>
-      <c r="DZ9" s="37"/>
-      <c r="EA9" s="38"/>
+      <c r="DV9" s="39"/>
+      <c r="DW9" s="37"/>
+      <c r="DX9" s="38"/>
+      <c r="DY9" s="22"/>
+      <c r="DZ9" s="22"/>
+      <c r="EA9" s="22"/>
       <c r="EB9" s="22"/>
       <c r="EC9" s="22"/>
       <c r="ED9" s="22"/>
@@ -5319,11 +5484,11 @@
       <c r="EF9" s="22"/>
       <c r="EG9" s="22"/>
       <c r="EH9" s="22"/>
-      <c r="EI9" s="22"/>
-      <c r="EJ9" s="22"/>
-      <c r="EK9" s="39"/>
-      <c r="EL9" s="37"/>
-      <c r="EM9" s="38"/>
+      <c r="EI9" s="39"/>
+      <c r="EJ9" s="37"/>
+      <c r="EK9" s="38"/>
+      <c r="EL9" s="22"/>
+      <c r="EM9" s="22"/>
       <c r="EN9" s="22"/>
       <c r="EO9" s="22"/>
       <c r="EP9" s="22"/>
@@ -5332,10 +5497,10 @@
       <c r="ES9" s="22"/>
       <c r="ET9" s="22"/>
       <c r="EU9" s="22"/>
-      <c r="EV9" s="22"/>
-      <c r="EW9" s="39"/>
-      <c r="EX9" s="37"/>
-      <c r="EY9" s="38"/>
+      <c r="EV9" s="39"/>
+      <c r="EW9" s="37"/>
+      <c r="EX9" s="38"/>
+      <c r="EY9" s="22"/>
       <c r="EZ9" s="22"/>
       <c r="FA9" s="22"/>
       <c r="FB9" s="22"/>
@@ -5357,9 +5522,23 @@
       <c r="FR9" s="22"/>
       <c r="FS9" s="22"/>
       <c r="FT9" s="22"/>
-      <c r="FU9" s="39"/>
+      <c r="FU9" s="22"/>
+      <c r="FV9" s="39"/>
+      <c r="FW9" s="37"/>
+      <c r="FX9" s="38"/>
+      <c r="FY9" s="22"/>
+      <c r="FZ9" s="22"/>
+      <c r="GA9" s="22"/>
+      <c r="GB9" s="22"/>
+      <c r="GC9" s="22"/>
+      <c r="GD9" s="22"/>
+      <c r="GE9" s="22"/>
+      <c r="GF9" s="22"/>
+      <c r="GG9" s="22"/>
+      <c r="GH9" s="22"/>
+      <c r="GI9" s="39"/>
     </row>
-    <row r="10" spans="1:177" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:191" ht="30" x14ac:dyDescent="0.3">
       <c r="B10" s="12" t="s">
         <v>2</v>
       </c>
@@ -5398,10 +5577,10 @@
       <c r="R10" s="22"/>
       <c r="S10" s="22"/>
       <c r="T10" s="22"/>
-      <c r="U10" s="39"/>
-      <c r="V10" s="37"/>
-      <c r="W10" s="38"/>
-      <c r="X10" s="22"/>
+      <c r="U10" s="22"/>
+      <c r="V10" s="39"/>
+      <c r="W10" s="37"/>
+      <c r="X10" s="38"/>
       <c r="Y10" s="22"/>
       <c r="Z10" s="22"/>
       <c r="AA10" s="22"/>
@@ -5410,11 +5589,11 @@
       <c r="AD10" s="22"/>
       <c r="AE10" s="22"/>
       <c r="AF10" s="22"/>
-      <c r="AG10" s="39"/>
-      <c r="AH10" s="37"/>
-      <c r="AI10" s="38"/>
-      <c r="AJ10" s="22"/>
-      <c r="AK10" s="22"/>
+      <c r="AG10" s="22"/>
+      <c r="AH10" s="22"/>
+      <c r="AI10" s="39"/>
+      <c r="AJ10" s="37"/>
+      <c r="AK10" s="38"/>
       <c r="AL10" s="22"/>
       <c r="AM10" s="22"/>
       <c r="AN10" s="22"/>
@@ -5422,93 +5601,93 @@
       <c r="AP10" s="22"/>
       <c r="AQ10" s="22"/>
       <c r="AR10" s="22"/>
-      <c r="AS10" s="39"/>
-      <c r="AT10" s="37"/>
-      <c r="AU10" s="38"/>
-      <c r="AV10" s="22"/>
-      <c r="AW10" s="22"/>
-      <c r="AX10" s="22"/>
+      <c r="AS10" s="22"/>
+      <c r="AT10" s="22"/>
+      <c r="AU10" s="22"/>
+      <c r="AV10" s="39"/>
+      <c r="AW10" s="37"/>
+      <c r="AX10" s="38"/>
       <c r="AY10" s="22"/>
       <c r="AZ10" s="22"/>
       <c r="BA10" s="22"/>
       <c r="BB10" s="22"/>
       <c r="BC10" s="22"/>
       <c r="BD10" s="22"/>
-      <c r="BE10" s="39"/>
-      <c r="BF10" s="37"/>
-      <c r="BG10" s="38"/>
+      <c r="BE10" s="22"/>
+      <c r="BF10" s="22"/>
+      <c r="BG10" s="22"/>
       <c r="BH10" s="22"/>
-      <c r="BI10" s="22"/>
-      <c r="BJ10" s="22"/>
-      <c r="BK10" s="22"/>
+      <c r="BI10" s="39"/>
+      <c r="BJ10" s="37"/>
+      <c r="BK10" s="38"/>
       <c r="BL10" s="22"/>
       <c r="BM10" s="22"/>
       <c r="BN10" s="22"/>
       <c r="BO10" s="22"/>
       <c r="BP10" s="22"/>
-      <c r="BQ10" s="39"/>
-      <c r="BR10" s="37"/>
-      <c r="BS10" s="38"/>
+      <c r="BQ10" s="22"/>
+      <c r="BR10" s="22"/>
+      <c r="BS10" s="22"/>
       <c r="BT10" s="22"/>
       <c r="BU10" s="22"/>
-      <c r="BV10" s="22"/>
-      <c r="BW10" s="22"/>
-      <c r="BX10" s="22"/>
+      <c r="BV10" s="39"/>
+      <c r="BW10" s="37"/>
+      <c r="BX10" s="38"/>
       <c r="BY10" s="22"/>
       <c r="BZ10" s="22"/>
       <c r="CA10" s="22"/>
       <c r="CB10" s="22"/>
-      <c r="CC10" s="39"/>
-      <c r="CD10" s="37"/>
-      <c r="CE10" s="38"/>
+      <c r="CC10" s="22"/>
+      <c r="CD10" s="22"/>
+      <c r="CE10" s="22"/>
       <c r="CF10" s="22"/>
       <c r="CG10" s="22"/>
       <c r="CH10" s="22"/>
-      <c r="CI10" s="22"/>
-      <c r="CJ10" s="22"/>
-      <c r="CK10" s="22"/>
+      <c r="CI10" s="39"/>
+      <c r="CJ10" s="37"/>
+      <c r="CK10" s="38"/>
       <c r="CL10" s="22"/>
       <c r="CM10" s="22"/>
       <c r="CN10" s="22"/>
-      <c r="CO10" s="39"/>
-      <c r="CP10" s="37"/>
-      <c r="CQ10" s="38"/>
+      <c r="CO10" s="22"/>
+      <c r="CP10" s="22"/>
+      <c r="CQ10" s="22"/>
       <c r="CR10" s="22"/>
       <c r="CS10" s="22"/>
       <c r="CT10" s="22"/>
       <c r="CU10" s="22"/>
-      <c r="CV10" s="22"/>
-      <c r="CW10" s="22"/>
-      <c r="CX10" s="22"/>
+      <c r="CV10" s="39"/>
+      <c r="CW10" s="37"/>
+      <c r="CX10" s="38"/>
       <c r="CY10" s="22"/>
       <c r="CZ10" s="22"/>
-      <c r="DA10" s="39"/>
-      <c r="DB10" s="37"/>
-      <c r="DC10" s="38"/>
+      <c r="DA10" s="22"/>
+      <c r="DB10" s="22"/>
+      <c r="DC10" s="22"/>
       <c r="DD10" s="22"/>
       <c r="DE10" s="22"/>
       <c r="DF10" s="22"/>
       <c r="DG10" s="22"/>
       <c r="DH10" s="22"/>
-      <c r="DI10" s="22"/>
-      <c r="DJ10" s="22"/>
-      <c r="DK10" s="22"/>
+      <c r="DI10" s="39"/>
+      <c r="DJ10" s="37"/>
+      <c r="DK10" s="38"/>
       <c r="DL10" s="22"/>
-      <c r="DM10" s="39"/>
-      <c r="DN10" s="37"/>
-      <c r="DO10" s="38"/>
+      <c r="DM10" s="22"/>
+      <c r="DN10" s="22"/>
+      <c r="DO10" s="22"/>
       <c r="DP10" s="22"/>
       <c r="DQ10" s="22"/>
       <c r="DR10" s="22"/>
       <c r="DS10" s="22"/>
       <c r="DT10" s="22"/>
       <c r="DU10" s="22"/>
-      <c r="DV10" s="22"/>
-      <c r="DW10" s="22"/>
-      <c r="DX10" s="22"/>
-      <c r="DY10" s="39"/>
-      <c r="DZ10" s="37"/>
-      <c r="EA10" s="38"/>
+      <c r="DV10" s="39"/>
+      <c r="DW10" s="37"/>
+      <c r="DX10" s="38"/>
+      <c r="DY10" s="22"/>
+      <c r="DZ10" s="22"/>
+      <c r="EA10" s="22"/>
       <c r="EB10" s="22"/>
       <c r="EC10" s="22"/>
       <c r="ED10" s="22"/>
@@ -5516,11 +5695,11 @@
       <c r="EF10" s="22"/>
       <c r="EG10" s="22"/>
       <c r="EH10" s="22"/>
-      <c r="EI10" s="22"/>
-      <c r="EJ10" s="22"/>
-      <c r="EK10" s="39"/>
-      <c r="EL10" s="37"/>
-      <c r="EM10" s="38"/>
+      <c r="EI10" s="39"/>
+      <c r="EJ10" s="37"/>
+      <c r="EK10" s="38"/>
+      <c r="EL10" s="22"/>
+      <c r="EM10" s="22"/>
       <c r="EN10" s="22"/>
       <c r="EO10" s="22"/>
       <c r="EP10" s="22"/>
@@ -5529,10 +5708,10 @@
       <c r="ES10" s="22"/>
       <c r="ET10" s="22"/>
       <c r="EU10" s="22"/>
-      <c r="EV10" s="22"/>
-      <c r="EW10" s="39"/>
-      <c r="EX10" s="37"/>
-      <c r="EY10" s="38"/>
+      <c r="EV10" s="39"/>
+      <c r="EW10" s="37"/>
+      <c r="EX10" s="38"/>
+      <c r="EY10" s="22"/>
       <c r="EZ10" s="22"/>
       <c r="FA10" s="22"/>
       <c r="FB10" s="22"/>
@@ -5554,9 +5733,23 @@
       <c r="FR10" s="22"/>
       <c r="FS10" s="22"/>
       <c r="FT10" s="22"/>
-      <c r="FU10" s="39"/>
+      <c r="FU10" s="22"/>
+      <c r="FV10" s="39"/>
+      <c r="FW10" s="37"/>
+      <c r="FX10" s="38"/>
+      <c r="FY10" s="22"/>
+      <c r="FZ10" s="22"/>
+      <c r="GA10" s="22"/>
+      <c r="GB10" s="22"/>
+      <c r="GC10" s="22"/>
+      <c r="GD10" s="22"/>
+      <c r="GE10" s="22"/>
+      <c r="GF10" s="22"/>
+      <c r="GG10" s="22"/>
+      <c r="GH10" s="22"/>
+      <c r="GI10" s="39"/>
     </row>
-    <row r="11" spans="1:177" ht="33" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:191" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="12" t="s">
         <v>2</v>
       </c>
@@ -5593,10 +5786,10 @@
       <c r="R11" s="22"/>
       <c r="S11" s="22"/>
       <c r="T11" s="22"/>
-      <c r="U11" s="39"/>
-      <c r="V11" s="37"/>
-      <c r="W11" s="38"/>
-      <c r="X11" s="22"/>
+      <c r="U11" s="22"/>
+      <c r="V11" s="39"/>
+      <c r="W11" s="37"/>
+      <c r="X11" s="38"/>
       <c r="Y11" s="22"/>
       <c r="Z11" s="22"/>
       <c r="AA11" s="22"/>
@@ -5605,11 +5798,11 @@
       <c r="AD11" s="22"/>
       <c r="AE11" s="22"/>
       <c r="AF11" s="22"/>
-      <c r="AG11" s="39"/>
-      <c r="AH11" s="37"/>
-      <c r="AI11" s="38"/>
-      <c r="AJ11" s="22"/>
-      <c r="AK11" s="22"/>
+      <c r="AG11" s="22"/>
+      <c r="AH11" s="22"/>
+      <c r="AI11" s="39"/>
+      <c r="AJ11" s="37"/>
+      <c r="AK11" s="38"/>
       <c r="AL11" s="22"/>
       <c r="AM11" s="22"/>
       <c r="AN11" s="22"/>
@@ -5617,93 +5810,93 @@
       <c r="AP11" s="22"/>
       <c r="AQ11" s="22"/>
       <c r="AR11" s="22"/>
-      <c r="AS11" s="39"/>
-      <c r="AT11" s="37"/>
-      <c r="AU11" s="38"/>
-      <c r="AV11" s="22"/>
-      <c r="AW11" s="22"/>
-      <c r="AX11" s="22"/>
+      <c r="AS11" s="22"/>
+      <c r="AT11" s="22"/>
+      <c r="AU11" s="22"/>
+      <c r="AV11" s="39"/>
+      <c r="AW11" s="37"/>
+      <c r="AX11" s="38"/>
       <c r="AY11" s="22"/>
       <c r="AZ11" s="22"/>
       <c r="BA11" s="22"/>
       <c r="BB11" s="22"/>
       <c r="BC11" s="22"/>
       <c r="BD11" s="22"/>
-      <c r="BE11" s="39"/>
-      <c r="BF11" s="37"/>
-      <c r="BG11" s="38"/>
+      <c r="BE11" s="22"/>
+      <c r="BF11" s="22"/>
+      <c r="BG11" s="22"/>
       <c r="BH11" s="22"/>
-      <c r="BI11" s="22"/>
-      <c r="BJ11" s="22"/>
-      <c r="BK11" s="22"/>
+      <c r="BI11" s="39"/>
+      <c r="BJ11" s="37"/>
+      <c r="BK11" s="38"/>
       <c r="BL11" s="22"/>
       <c r="BM11" s="22"/>
       <c r="BN11" s="22"/>
       <c r="BO11" s="22"/>
       <c r="BP11" s="22"/>
-      <c r="BQ11" s="39"/>
-      <c r="BR11" s="37"/>
-      <c r="BS11" s="38"/>
+      <c r="BQ11" s="22"/>
+      <c r="BR11" s="22"/>
+      <c r="BS11" s="22"/>
       <c r="BT11" s="22"/>
       <c r="BU11" s="22"/>
-      <c r="BV11" s="22"/>
-      <c r="BW11" s="22"/>
-      <c r="BX11" s="22"/>
+      <c r="BV11" s="39"/>
+      <c r="BW11" s="37"/>
+      <c r="BX11" s="38"/>
       <c r="BY11" s="22"/>
       <c r="BZ11" s="22"/>
       <c r="CA11" s="22"/>
       <c r="CB11" s="22"/>
-      <c r="CC11" s="39"/>
-      <c r="CD11" s="37"/>
-      <c r="CE11" s="38"/>
+      <c r="CC11" s="22"/>
+      <c r="CD11" s="22"/>
+      <c r="CE11" s="22"/>
       <c r="CF11" s="22"/>
       <c r="CG11" s="22"/>
       <c r="CH11" s="22"/>
-      <c r="CI11" s="22"/>
-      <c r="CJ11" s="22"/>
-      <c r="CK11" s="22"/>
+      <c r="CI11" s="39"/>
+      <c r="CJ11" s="37"/>
+      <c r="CK11" s="38"/>
       <c r="CL11" s="22"/>
       <c r="CM11" s="22"/>
       <c r="CN11" s="22"/>
-      <c r="CO11" s="39"/>
-      <c r="CP11" s="37"/>
-      <c r="CQ11" s="38"/>
+      <c r="CO11" s="22"/>
+      <c r="CP11" s="22"/>
+      <c r="CQ11" s="22"/>
       <c r="CR11" s="22"/>
       <c r="CS11" s="22"/>
       <c r="CT11" s="22"/>
       <c r="CU11" s="22"/>
-      <c r="CV11" s="22"/>
-      <c r="CW11" s="22"/>
-      <c r="CX11" s="22"/>
+      <c r="CV11" s="39"/>
+      <c r="CW11" s="37"/>
+      <c r="CX11" s="38"/>
       <c r="CY11" s="22"/>
       <c r="CZ11" s="22"/>
-      <c r="DA11" s="39"/>
-      <c r="DB11" s="37"/>
-      <c r="DC11" s="38"/>
+      <c r="DA11" s="22"/>
+      <c r="DB11" s="22"/>
+      <c r="DC11" s="22"/>
       <c r="DD11" s="22"/>
       <c r="DE11" s="22"/>
       <c r="DF11" s="22"/>
       <c r="DG11" s="22"/>
       <c r="DH11" s="22"/>
-      <c r="DI11" s="22"/>
-      <c r="DJ11" s="22"/>
-      <c r="DK11" s="22"/>
+      <c r="DI11" s="39"/>
+      <c r="DJ11" s="37"/>
+      <c r="DK11" s="38"/>
       <c r="DL11" s="22"/>
-      <c r="DM11" s="39"/>
-      <c r="DN11" s="37"/>
-      <c r="DO11" s="38"/>
+      <c r="DM11" s="22"/>
+      <c r="DN11" s="22"/>
+      <c r="DO11" s="22"/>
       <c r="DP11" s="22"/>
       <c r="DQ11" s="22"/>
       <c r="DR11" s="22"/>
       <c r="DS11" s="22"/>
       <c r="DT11" s="22"/>
       <c r="DU11" s="22"/>
-      <c r="DV11" s="22"/>
-      <c r="DW11" s="22"/>
-      <c r="DX11" s="22"/>
-      <c r="DY11" s="39"/>
-      <c r="DZ11" s="37"/>
-      <c r="EA11" s="38"/>
+      <c r="DV11" s="39"/>
+      <c r="DW11" s="37"/>
+      <c r="DX11" s="38"/>
+      <c r="DY11" s="22"/>
+      <c r="DZ11" s="22"/>
+      <c r="EA11" s="22"/>
       <c r="EB11" s="22"/>
       <c r="EC11" s="22"/>
       <c r="ED11" s="22"/>
@@ -5711,11 +5904,11 @@
       <c r="EF11" s="22"/>
       <c r="EG11" s="22"/>
       <c r="EH11" s="22"/>
-      <c r="EI11" s="22"/>
-      <c r="EJ11" s="22"/>
-      <c r="EK11" s="39"/>
-      <c r="EL11" s="37"/>
-      <c r="EM11" s="38"/>
+      <c r="EI11" s="39"/>
+      <c r="EJ11" s="37"/>
+      <c r="EK11" s="38"/>
+      <c r="EL11" s="22"/>
+      <c r="EM11" s="22"/>
       <c r="EN11" s="22"/>
       <c r="EO11" s="22"/>
       <c r="EP11" s="22"/>
@@ -5724,10 +5917,10 @@
       <c r="ES11" s="22"/>
       <c r="ET11" s="22"/>
       <c r="EU11" s="22"/>
-      <c r="EV11" s="22"/>
-      <c r="EW11" s="39"/>
-      <c r="EX11" s="37"/>
-      <c r="EY11" s="38"/>
+      <c r="EV11" s="39"/>
+      <c r="EW11" s="37"/>
+      <c r="EX11" s="38"/>
+      <c r="EY11" s="22"/>
       <c r="EZ11" s="22"/>
       <c r="FA11" s="22"/>
       <c r="FB11" s="22"/>
@@ -5749,9 +5942,23 @@
       <c r="FR11" s="22"/>
       <c r="FS11" s="22"/>
       <c r="FT11" s="22"/>
-      <c r="FU11" s="39"/>
+      <c r="FU11" s="22"/>
+      <c r="FV11" s="39"/>
+      <c r="FW11" s="37"/>
+      <c r="FX11" s="38"/>
+      <c r="FY11" s="22"/>
+      <c r="FZ11" s="22"/>
+      <c r="GA11" s="22"/>
+      <c r="GB11" s="22"/>
+      <c r="GC11" s="22"/>
+      <c r="GD11" s="22"/>
+      <c r="GE11" s="22"/>
+      <c r="GF11" s="22"/>
+      <c r="GG11" s="22"/>
+      <c r="GH11" s="22"/>
+      <c r="GI11" s="39"/>
     </row>
-    <row r="12" spans="1:177" ht="65.55" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:191" ht="65.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="12" t="s">
         <v>32</v>
       </c>
@@ -5783,10 +5990,10 @@
       <c r="R12" s="22"/>
       <c r="S12" s="22"/>
       <c r="T12" s="22"/>
-      <c r="U12" s="39"/>
-      <c r="V12" s="37"/>
-      <c r="W12" s="38"/>
-      <c r="X12" s="22"/>
+      <c r="U12" s="22"/>
+      <c r="V12" s="39"/>
+      <c r="W12" s="37"/>
+      <c r="X12" s="38"/>
       <c r="Y12" s="22"/>
       <c r="Z12" s="22"/>
       <c r="AA12" s="22"/>
@@ -5795,11 +6002,11 @@
       <c r="AD12" s="22"/>
       <c r="AE12" s="22"/>
       <c r="AF12" s="22"/>
-      <c r="AG12" s="39"/>
-      <c r="AH12" s="37"/>
-      <c r="AI12" s="38"/>
-      <c r="AJ12" s="22"/>
-      <c r="AK12" s="22"/>
+      <c r="AG12" s="22"/>
+      <c r="AH12" s="22"/>
+      <c r="AI12" s="39"/>
+      <c r="AJ12" s="37"/>
+      <c r="AK12" s="38"/>
       <c r="AL12" s="22"/>
       <c r="AM12" s="22"/>
       <c r="AN12" s="22"/>
@@ -5807,93 +6014,93 @@
       <c r="AP12" s="22"/>
       <c r="AQ12" s="22"/>
       <c r="AR12" s="22"/>
-      <c r="AS12" s="39"/>
-      <c r="AT12" s="37"/>
-      <c r="AU12" s="38"/>
-      <c r="AV12" s="22"/>
-      <c r="AW12" s="22"/>
-      <c r="AX12" s="22"/>
+      <c r="AS12" s="22"/>
+      <c r="AT12" s="22"/>
+      <c r="AU12" s="22"/>
+      <c r="AV12" s="39"/>
+      <c r="AW12" s="37"/>
+      <c r="AX12" s="38"/>
       <c r="AY12" s="22"/>
       <c r="AZ12" s="22"/>
       <c r="BA12" s="22"/>
       <c r="BB12" s="22"/>
       <c r="BC12" s="22"/>
       <c r="BD12" s="22"/>
-      <c r="BE12" s="39"/>
-      <c r="BF12" s="37"/>
-      <c r="BG12" s="38"/>
+      <c r="BE12" s="22"/>
+      <c r="BF12" s="22"/>
+      <c r="BG12" s="22"/>
       <c r="BH12" s="22"/>
-      <c r="BI12" s="22"/>
-      <c r="BJ12" s="22"/>
-      <c r="BK12" s="22"/>
+      <c r="BI12" s="39"/>
+      <c r="BJ12" s="37"/>
+      <c r="BK12" s="38"/>
       <c r="BL12" s="22"/>
       <c r="BM12" s="22"/>
       <c r="BN12" s="22"/>
       <c r="BO12" s="22"/>
       <c r="BP12" s="22"/>
-      <c r="BQ12" s="39"/>
-      <c r="BR12" s="37"/>
-      <c r="BS12" s="38"/>
+      <c r="BQ12" s="22"/>
+      <c r="BR12" s="22"/>
+      <c r="BS12" s="22"/>
       <c r="BT12" s="22"/>
       <c r="BU12" s="22"/>
-      <c r="BV12" s="22"/>
-      <c r="BW12" s="22"/>
-      <c r="BX12" s="22"/>
+      <c r="BV12" s="39"/>
+      <c r="BW12" s="37"/>
+      <c r="BX12" s="38"/>
       <c r="BY12" s="22"/>
       <c r="BZ12" s="22"/>
       <c r="CA12" s="22"/>
       <c r="CB12" s="22"/>
-      <c r="CC12" s="39"/>
-      <c r="CD12" s="37"/>
-      <c r="CE12" s="38"/>
+      <c r="CC12" s="22"/>
+      <c r="CD12" s="22"/>
+      <c r="CE12" s="22"/>
       <c r="CF12" s="22"/>
       <c r="CG12" s="22"/>
       <c r="CH12" s="22"/>
-      <c r="CI12" s="22"/>
-      <c r="CJ12" s="22"/>
-      <c r="CK12" s="22"/>
+      <c r="CI12" s="39"/>
+      <c r="CJ12" s="37"/>
+      <c r="CK12" s="38"/>
       <c r="CL12" s="22"/>
       <c r="CM12" s="22"/>
       <c r="CN12" s="22"/>
-      <c r="CO12" s="39"/>
-      <c r="CP12" s="37"/>
-      <c r="CQ12" s="38"/>
+      <c r="CO12" s="22"/>
+      <c r="CP12" s="22"/>
+      <c r="CQ12" s="22"/>
       <c r="CR12" s="22"/>
       <c r="CS12" s="22"/>
       <c r="CT12" s="22"/>
       <c r="CU12" s="22"/>
-      <c r="CV12" s="22"/>
-      <c r="CW12" s="22"/>
-      <c r="CX12" s="22"/>
+      <c r="CV12" s="39"/>
+      <c r="CW12" s="37"/>
+      <c r="CX12" s="38"/>
       <c r="CY12" s="22"/>
       <c r="CZ12" s="22"/>
-      <c r="DA12" s="39"/>
-      <c r="DB12" s="37"/>
-      <c r="DC12" s="38"/>
+      <c r="DA12" s="22"/>
+      <c r="DB12" s="22"/>
+      <c r="DC12" s="22"/>
       <c r="DD12" s="22"/>
       <c r="DE12" s="22"/>
       <c r="DF12" s="22"/>
       <c r="DG12" s="22"/>
       <c r="DH12" s="22"/>
-      <c r="DI12" s="22"/>
-      <c r="DJ12" s="22"/>
-      <c r="DK12" s="22"/>
+      <c r="DI12" s="39"/>
+      <c r="DJ12" s="37"/>
+      <c r="DK12" s="38"/>
       <c r="DL12" s="22"/>
-      <c r="DM12" s="39"/>
-      <c r="DN12" s="37"/>
-      <c r="DO12" s="38"/>
+      <c r="DM12" s="22"/>
+      <c r="DN12" s="22"/>
+      <c r="DO12" s="22"/>
       <c r="DP12" s="22"/>
       <c r="DQ12" s="22"/>
       <c r="DR12" s="22"/>
       <c r="DS12" s="22"/>
       <c r="DT12" s="22"/>
       <c r="DU12" s="22"/>
-      <c r="DV12" s="22"/>
-      <c r="DW12" s="22"/>
-      <c r="DX12" s="22"/>
-      <c r="DY12" s="39"/>
-      <c r="DZ12" s="37"/>
-      <c r="EA12" s="38"/>
+      <c r="DV12" s="39"/>
+      <c r="DW12" s="37"/>
+      <c r="DX12" s="38"/>
+      <c r="DY12" s="22"/>
+      <c r="DZ12" s="22"/>
+      <c r="EA12" s="22"/>
       <c r="EB12" s="22"/>
       <c r="EC12" s="22"/>
       <c r="ED12" s="22"/>
@@ -5901,11 +6108,11 @@
       <c r="EF12" s="22"/>
       <c r="EG12" s="22"/>
       <c r="EH12" s="22"/>
-      <c r="EI12" s="22"/>
-      <c r="EJ12" s="22"/>
-      <c r="EK12" s="39"/>
-      <c r="EL12" s="37"/>
-      <c r="EM12" s="38"/>
+      <c r="EI12" s="39"/>
+      <c r="EJ12" s="37"/>
+      <c r="EK12" s="38"/>
+      <c r="EL12" s="22"/>
+      <c r="EM12" s="22"/>
       <c r="EN12" s="22"/>
       <c r="EO12" s="22"/>
       <c r="EP12" s="22"/>
@@ -5914,10 +6121,10 @@
       <c r="ES12" s="22"/>
       <c r="ET12" s="22"/>
       <c r="EU12" s="22"/>
-      <c r="EV12" s="22"/>
-      <c r="EW12" s="39"/>
-      <c r="EX12" s="37"/>
-      <c r="EY12" s="38"/>
+      <c r="EV12" s="39"/>
+      <c r="EW12" s="37"/>
+      <c r="EX12" s="38"/>
+      <c r="EY12" s="22"/>
       <c r="EZ12" s="22"/>
       <c r="FA12" s="22"/>
       <c r="FB12" s="22"/>
@@ -5939,9 +6146,23 @@
       <c r="FR12" s="22"/>
       <c r="FS12" s="22"/>
       <c r="FT12" s="22"/>
-      <c r="FU12" s="39"/>
+      <c r="FU12" s="22"/>
+      <c r="FV12" s="39"/>
+      <c r="FW12" s="37"/>
+      <c r="FX12" s="38"/>
+      <c r="FY12" s="22"/>
+      <c r="FZ12" s="22"/>
+      <c r="GA12" s="22"/>
+      <c r="GB12" s="22"/>
+      <c r="GC12" s="22"/>
+      <c r="GD12" s="22"/>
+      <c r="GE12" s="22"/>
+      <c r="GF12" s="22"/>
+      <c r="GG12" s="22"/>
+      <c r="GH12" s="22"/>
+      <c r="GI12" s="39"/>
     </row>
-    <row r="13" spans="1:177" ht="55.35" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:191" ht="55.35" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="12" t="s">
         <v>33</v>
       </c>
@@ -5973,10 +6194,10 @@
       <c r="R13" s="22"/>
       <c r="S13" s="22"/>
       <c r="T13" s="22"/>
-      <c r="U13" s="39"/>
-      <c r="V13" s="37"/>
-      <c r="W13" s="38"/>
-      <c r="X13" s="22"/>
+      <c r="U13" s="22"/>
+      <c r="V13" s="39"/>
+      <c r="W13" s="37"/>
+      <c r="X13" s="38"/>
       <c r="Y13" s="22"/>
       <c r="Z13" s="22"/>
       <c r="AA13" s="22"/>
@@ -5985,11 +6206,11 @@
       <c r="AD13" s="22"/>
       <c r="AE13" s="22"/>
       <c r="AF13" s="22"/>
-      <c r="AG13" s="39"/>
-      <c r="AH13" s="37"/>
-      <c r="AI13" s="38"/>
-      <c r="AJ13" s="22"/>
-      <c r="AK13" s="22"/>
+      <c r="AG13" s="22"/>
+      <c r="AH13" s="22"/>
+      <c r="AI13" s="39"/>
+      <c r="AJ13" s="37"/>
+      <c r="AK13" s="38"/>
       <c r="AL13" s="22"/>
       <c r="AM13" s="22"/>
       <c r="AN13" s="22"/>
@@ -5997,93 +6218,93 @@
       <c r="AP13" s="22"/>
       <c r="AQ13" s="22"/>
       <c r="AR13" s="22"/>
-      <c r="AS13" s="39"/>
-      <c r="AT13" s="37"/>
-      <c r="AU13" s="38"/>
-      <c r="AV13" s="22"/>
-      <c r="AW13" s="22"/>
-      <c r="AX13" s="22"/>
+      <c r="AS13" s="22"/>
+      <c r="AT13" s="22"/>
+      <c r="AU13" s="22"/>
+      <c r="AV13" s="39"/>
+      <c r="AW13" s="37"/>
+      <c r="AX13" s="38"/>
       <c r="AY13" s="22"/>
       <c r="AZ13" s="22"/>
       <c r="BA13" s="22"/>
       <c r="BB13" s="22"/>
       <c r="BC13" s="22"/>
       <c r="BD13" s="22"/>
-      <c r="BE13" s="39"/>
-      <c r="BF13" s="37"/>
-      <c r="BG13" s="38"/>
+      <c r="BE13" s="22"/>
+      <c r="BF13" s="22"/>
+      <c r="BG13" s="22"/>
       <c r="BH13" s="22"/>
-      <c r="BI13" s="22"/>
-      <c r="BJ13" s="22"/>
-      <c r="BK13" s="22"/>
+      <c r="BI13" s="39"/>
+      <c r="BJ13" s="37"/>
+      <c r="BK13" s="38"/>
       <c r="BL13" s="22"/>
       <c r="BM13" s="22"/>
       <c r="BN13" s="22"/>
       <c r="BO13" s="22"/>
       <c r="BP13" s="22"/>
-      <c r="BQ13" s="39"/>
-      <c r="BR13" s="37"/>
-      <c r="BS13" s="38"/>
+      <c r="BQ13" s="22"/>
+      <c r="BR13" s="22"/>
+      <c r="BS13" s="22"/>
       <c r="BT13" s="22"/>
       <c r="BU13" s="22"/>
-      <c r="BV13" s="22"/>
-      <c r="BW13" s="22"/>
-      <c r="BX13" s="22"/>
+      <c r="BV13" s="39"/>
+      <c r="BW13" s="37"/>
+      <c r="BX13" s="38"/>
       <c r="BY13" s="22"/>
       <c r="BZ13" s="22"/>
       <c r="CA13" s="22"/>
       <c r="CB13" s="22"/>
-      <c r="CC13" s="39"/>
-      <c r="CD13" s="37"/>
-      <c r="CE13" s="38"/>
+      <c r="CC13" s="22"/>
+      <c r="CD13" s="22"/>
+      <c r="CE13" s="22"/>
       <c r="CF13" s="22"/>
       <c r="CG13" s="22"/>
       <c r="CH13" s="22"/>
-      <c r="CI13" s="22"/>
-      <c r="CJ13" s="22"/>
-      <c r="CK13" s="22"/>
+      <c r="CI13" s="39"/>
+      <c r="CJ13" s="37"/>
+      <c r="CK13" s="38"/>
       <c r="CL13" s="22"/>
       <c r="CM13" s="22"/>
       <c r="CN13" s="22"/>
-      <c r="CO13" s="39"/>
-      <c r="CP13" s="37"/>
-      <c r="CQ13" s="38"/>
+      <c r="CO13" s="22"/>
+      <c r="CP13" s="22"/>
+      <c r="CQ13" s="22"/>
       <c r="CR13" s="22"/>
       <c r="CS13" s="22"/>
       <c r="CT13" s="22"/>
       <c r="CU13" s="22"/>
-      <c r="CV13" s="22"/>
-      <c r="CW13" s="22"/>
-      <c r="CX13" s="22"/>
+      <c r="CV13" s="39"/>
+      <c r="CW13" s="37"/>
+      <c r="CX13" s="38"/>
       <c r="CY13" s="22"/>
       <c r="CZ13" s="22"/>
-      <c r="DA13" s="39"/>
-      <c r="DB13" s="37"/>
-      <c r="DC13" s="38"/>
+      <c r="DA13" s="22"/>
+      <c r="DB13" s="22"/>
+      <c r="DC13" s="22"/>
       <c r="DD13" s="22"/>
       <c r="DE13" s="22"/>
       <c r="DF13" s="22"/>
       <c r="DG13" s="22"/>
       <c r="DH13" s="22"/>
-      <c r="DI13" s="22"/>
-      <c r="DJ13" s="22"/>
-      <c r="DK13" s="22"/>
+      <c r="DI13" s="39"/>
+      <c r="DJ13" s="37"/>
+      <c r="DK13" s="38"/>
       <c r="DL13" s="22"/>
-      <c r="DM13" s="39"/>
-      <c r="DN13" s="37"/>
-      <c r="DO13" s="38"/>
+      <c r="DM13" s="22"/>
+      <c r="DN13" s="22"/>
+      <c r="DO13" s="22"/>
       <c r="DP13" s="22"/>
       <c r="DQ13" s="22"/>
       <c r="DR13" s="22"/>
       <c r="DS13" s="22"/>
       <c r="DT13" s="22"/>
       <c r="DU13" s="22"/>
-      <c r="DV13" s="22"/>
-      <c r="DW13" s="22"/>
-      <c r="DX13" s="22"/>
-      <c r="DY13" s="39"/>
-      <c r="DZ13" s="37"/>
-      <c r="EA13" s="38"/>
+      <c r="DV13" s="39"/>
+      <c r="DW13" s="37"/>
+      <c r="DX13" s="38"/>
+      <c r="DY13" s="22"/>
+      <c r="DZ13" s="22"/>
+      <c r="EA13" s="22"/>
       <c r="EB13" s="22"/>
       <c r="EC13" s="22"/>
       <c r="ED13" s="22"/>
@@ -6091,11 +6312,11 @@
       <c r="EF13" s="22"/>
       <c r="EG13" s="22"/>
       <c r="EH13" s="22"/>
-      <c r="EI13" s="22"/>
-      <c r="EJ13" s="22"/>
-      <c r="EK13" s="39"/>
-      <c r="EL13" s="37"/>
-      <c r="EM13" s="38"/>
+      <c r="EI13" s="39"/>
+      <c r="EJ13" s="37"/>
+      <c r="EK13" s="38"/>
+      <c r="EL13" s="22"/>
+      <c r="EM13" s="22"/>
       <c r="EN13" s="22"/>
       <c r="EO13" s="22"/>
       <c r="EP13" s="22"/>
@@ -6104,10 +6325,10 @@
       <c r="ES13" s="22"/>
       <c r="ET13" s="22"/>
       <c r="EU13" s="22"/>
-      <c r="EV13" s="22"/>
-      <c r="EW13" s="39"/>
-      <c r="EX13" s="37"/>
-      <c r="EY13" s="38"/>
+      <c r="EV13" s="39"/>
+      <c r="EW13" s="37"/>
+      <c r="EX13" s="38"/>
+      <c r="EY13" s="22"/>
       <c r="EZ13" s="22"/>
       <c r="FA13" s="22"/>
       <c r="FB13" s="22"/>
@@ -6129,9 +6350,23 @@
       <c r="FR13" s="22"/>
       <c r="FS13" s="22"/>
       <c r="FT13" s="22"/>
-      <c r="FU13" s="39"/>
+      <c r="FU13" s="22"/>
+      <c r="FV13" s="39"/>
+      <c r="FW13" s="37"/>
+      <c r="FX13" s="38"/>
+      <c r="FY13" s="22"/>
+      <c r="FZ13" s="22"/>
+      <c r="GA13" s="22"/>
+      <c r="GB13" s="22"/>
+      <c r="GC13" s="22"/>
+      <c r="GD13" s="22"/>
+      <c r="GE13" s="22"/>
+      <c r="GF13" s="22"/>
+      <c r="GG13" s="22"/>
+      <c r="GH13" s="22"/>
+      <c r="GI13" s="39"/>
     </row>
-    <row r="14" spans="1:177" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:191" x14ac:dyDescent="0.3">
       <c r="B14" s="45" t="s">
         <v>65</v>
       </c>
@@ -6153,10 +6388,10 @@
       <c r="R14" s="22"/>
       <c r="S14" s="22"/>
       <c r="T14" s="22"/>
-      <c r="U14" s="39"/>
-      <c r="V14" s="37"/>
-      <c r="W14" s="38"/>
-      <c r="X14" s="22"/>
+      <c r="U14" s="22"/>
+      <c r="V14" s="39"/>
+      <c r="W14" s="37"/>
+      <c r="X14" s="38"/>
       <c r="Y14" s="22"/>
       <c r="Z14" s="22"/>
       <c r="AA14" s="22"/>
@@ -6165,11 +6400,11 @@
       <c r="AD14" s="22"/>
       <c r="AE14" s="22"/>
       <c r="AF14" s="22"/>
-      <c r="AG14" s="39"/>
-      <c r="AH14" s="37"/>
-      <c r="AI14" s="38"/>
-      <c r="AJ14" s="22"/>
-      <c r="AK14" s="22"/>
+      <c r="AG14" s="22"/>
+      <c r="AH14" s="22"/>
+      <c r="AI14" s="39"/>
+      <c r="AJ14" s="37"/>
+      <c r="AK14" s="38"/>
       <c r="AL14" s="22"/>
       <c r="AM14" s="22"/>
       <c r="AN14" s="22"/>
@@ -6177,93 +6412,93 @@
       <c r="AP14" s="22"/>
       <c r="AQ14" s="22"/>
       <c r="AR14" s="22"/>
-      <c r="AS14" s="39"/>
-      <c r="AT14" s="37"/>
-      <c r="AU14" s="38"/>
-      <c r="AV14" s="22"/>
-      <c r="AW14" s="22"/>
-      <c r="AX14" s="22"/>
+      <c r="AS14" s="22"/>
+      <c r="AT14" s="22"/>
+      <c r="AU14" s="22"/>
+      <c r="AV14" s="39"/>
+      <c r="AW14" s="37"/>
+      <c r="AX14" s="38"/>
       <c r="AY14" s="22"/>
       <c r="AZ14" s="22"/>
       <c r="BA14" s="22"/>
       <c r="BB14" s="22"/>
       <c r="BC14" s="22"/>
       <c r="BD14" s="22"/>
-      <c r="BE14" s="39"/>
-      <c r="BF14" s="37"/>
-      <c r="BG14" s="38"/>
+      <c r="BE14" s="22"/>
+      <c r="BF14" s="22"/>
+      <c r="BG14" s="22"/>
       <c r="BH14" s="22"/>
-      <c r="BI14" s="22"/>
-      <c r="BJ14" s="22"/>
-      <c r="BK14" s="22"/>
+      <c r="BI14" s="39"/>
+      <c r="BJ14" s="37"/>
+      <c r="BK14" s="38"/>
       <c r="BL14" s="22"/>
       <c r="BM14" s="22"/>
       <c r="BN14" s="22"/>
       <c r="BO14" s="22"/>
       <c r="BP14" s="22"/>
-      <c r="BQ14" s="39"/>
-      <c r="BR14" s="37"/>
-      <c r="BS14" s="38"/>
+      <c r="BQ14" s="22"/>
+      <c r="BR14" s="22"/>
+      <c r="BS14" s="22"/>
       <c r="BT14" s="22"/>
       <c r="BU14" s="22"/>
-      <c r="BV14" s="22"/>
-      <c r="BW14" s="22"/>
-      <c r="BX14" s="22"/>
+      <c r="BV14" s="39"/>
+      <c r="BW14" s="37"/>
+      <c r="BX14" s="38"/>
       <c r="BY14" s="22"/>
       <c r="BZ14" s="22"/>
       <c r="CA14" s="22"/>
       <c r="CB14" s="22"/>
-      <c r="CC14" s="39"/>
-      <c r="CD14" s="37"/>
-      <c r="CE14" s="38"/>
+      <c r="CC14" s="22"/>
+      <c r="CD14" s="22"/>
+      <c r="CE14" s="22"/>
       <c r="CF14" s="22"/>
       <c r="CG14" s="22"/>
       <c r="CH14" s="22"/>
-      <c r="CI14" s="22"/>
-      <c r="CJ14" s="22"/>
-      <c r="CK14" s="22"/>
+      <c r="CI14" s="39"/>
+      <c r="CJ14" s="37"/>
+      <c r="CK14" s="38"/>
       <c r="CL14" s="22"/>
       <c r="CM14" s="22"/>
       <c r="CN14" s="22"/>
-      <c r="CO14" s="39"/>
-      <c r="CP14" s="37"/>
-      <c r="CQ14" s="38"/>
+      <c r="CO14" s="22"/>
+      <c r="CP14" s="22"/>
+      <c r="CQ14" s="22"/>
       <c r="CR14" s="22"/>
       <c r="CS14" s="22"/>
       <c r="CT14" s="22"/>
       <c r="CU14" s="22"/>
-      <c r="CV14" s="22"/>
-      <c r="CW14" s="22"/>
-      <c r="CX14" s="22"/>
+      <c r="CV14" s="39"/>
+      <c r="CW14" s="37"/>
+      <c r="CX14" s="38"/>
       <c r="CY14" s="22"/>
       <c r="CZ14" s="22"/>
-      <c r="DA14" s="39"/>
-      <c r="DB14" s="37"/>
-      <c r="DC14" s="38"/>
+      <c r="DA14" s="22"/>
+      <c r="DB14" s="22"/>
+      <c r="DC14" s="22"/>
       <c r="DD14" s="22"/>
       <c r="DE14" s="22"/>
       <c r="DF14" s="22"/>
       <c r="DG14" s="22"/>
       <c r="DH14" s="22"/>
-      <c r="DI14" s="22"/>
-      <c r="DJ14" s="22"/>
-      <c r="DK14" s="22"/>
+      <c r="DI14" s="39"/>
+      <c r="DJ14" s="37"/>
+      <c r="DK14" s="38"/>
       <c r="DL14" s="22"/>
-      <c r="DM14" s="39"/>
-      <c r="DN14" s="37"/>
-      <c r="DO14" s="38"/>
+      <c r="DM14" s="22"/>
+      <c r="DN14" s="22"/>
+      <c r="DO14" s="22"/>
       <c r="DP14" s="22"/>
       <c r="DQ14" s="22"/>
       <c r="DR14" s="22"/>
       <c r="DS14" s="22"/>
       <c r="DT14" s="22"/>
       <c r="DU14" s="22"/>
-      <c r="DV14" s="22"/>
-      <c r="DW14" s="22"/>
-      <c r="DX14" s="22"/>
-      <c r="DY14" s="39"/>
-      <c r="DZ14" s="37"/>
-      <c r="EA14" s="38"/>
+      <c r="DV14" s="39"/>
+      <c r="DW14" s="37"/>
+      <c r="DX14" s="38"/>
+      <c r="DY14" s="22"/>
+      <c r="DZ14" s="22"/>
+      <c r="EA14" s="22"/>
       <c r="EB14" s="22"/>
       <c r="EC14" s="22"/>
       <c r="ED14" s="22"/>
@@ -6271,11 +6506,11 @@
       <c r="EF14" s="22"/>
       <c r="EG14" s="22"/>
       <c r="EH14" s="22"/>
-      <c r="EI14" s="22"/>
-      <c r="EJ14" s="22"/>
-      <c r="EK14" s="39"/>
-      <c r="EL14" s="37"/>
-      <c r="EM14" s="38"/>
+      <c r="EI14" s="39"/>
+      <c r="EJ14" s="37"/>
+      <c r="EK14" s="38"/>
+      <c r="EL14" s="22"/>
+      <c r="EM14" s="22"/>
       <c r="EN14" s="22"/>
       <c r="EO14" s="22"/>
       <c r="EP14" s="22"/>
@@ -6284,10 +6519,10 @@
       <c r="ES14" s="22"/>
       <c r="ET14" s="22"/>
       <c r="EU14" s="22"/>
-      <c r="EV14" s="22"/>
-      <c r="EW14" s="39"/>
-      <c r="EX14" s="37"/>
-      <c r="EY14" s="38"/>
+      <c r="EV14" s="39"/>
+      <c r="EW14" s="37"/>
+      <c r="EX14" s="38"/>
+      <c r="EY14" s="22"/>
       <c r="EZ14" s="22"/>
       <c r="FA14" s="22"/>
       <c r="FB14" s="22"/>
@@ -6309,9 +6544,23 @@
       <c r="FR14" s="22"/>
       <c r="FS14" s="22"/>
       <c r="FT14" s="22"/>
-      <c r="FU14" s="39"/>
+      <c r="FU14" s="22"/>
+      <c r="FV14" s="39"/>
+      <c r="FW14" s="37"/>
+      <c r="FX14" s="38"/>
+      <c r="FY14" s="22"/>
+      <c r="FZ14" s="22"/>
+      <c r="GA14" s="22"/>
+      <c r="GB14" s="22"/>
+      <c r="GC14" s="22"/>
+      <c r="GD14" s="22"/>
+      <c r="GE14" s="22"/>
+      <c r="GF14" s="22"/>
+      <c r="GG14" s="22"/>
+      <c r="GH14" s="22"/>
+      <c r="GI14" s="39"/>
     </row>
-    <row r="15" spans="1:177" s="26" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:191" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="23"/>
       <c r="C15" s="24" t="s">
@@ -6332,143 +6581,143 @@
       <c r="P15" s="42"/>
       <c r="Q15" s="42"/>
       <c r="R15" s="42"/>
-      <c r="S15" s="43"/>
+      <c r="S15" s="42"/>
       <c r="T15" s="43"/>
-      <c r="U15" s="44"/>
-      <c r="V15" s="40"/>
-      <c r="W15" s="41"/>
-      <c r="X15" s="42"/>
+      <c r="U15" s="43"/>
+      <c r="V15" s="44"/>
+      <c r="W15" s="40"/>
+      <c r="X15" s="41"/>
       <c r="Y15" s="42"/>
       <c r="Z15" s="42"/>
       <c r="AA15" s="42"/>
       <c r="AB15" s="42"/>
       <c r="AC15" s="42"/>
       <c r="AD15" s="42"/>
-      <c r="AE15" s="43"/>
-      <c r="AF15" s="43"/>
-      <c r="AG15" s="44"/>
-      <c r="AH15" s="40"/>
-      <c r="AI15" s="41"/>
-      <c r="AJ15" s="42"/>
-      <c r="AK15" s="42"/>
+      <c r="AE15" s="42"/>
+      <c r="AF15" s="42"/>
+      <c r="AG15" s="43"/>
+      <c r="AH15" s="43"/>
+      <c r="AI15" s="44"/>
+      <c r="AJ15" s="40"/>
+      <c r="AK15" s="41"/>
       <c r="AL15" s="42"/>
       <c r="AM15" s="42"/>
       <c r="AN15" s="42"/>
       <c r="AO15" s="42"/>
       <c r="AP15" s="42"/>
-      <c r="AQ15" s="43"/>
-      <c r="AR15" s="43"/>
-      <c r="AS15" s="44"/>
-      <c r="AT15" s="40"/>
-      <c r="AU15" s="41"/>
-      <c r="AV15" s="42"/>
-      <c r="AW15" s="42"/>
-      <c r="AX15" s="42"/>
+      <c r="AQ15" s="42"/>
+      <c r="AR15" s="42"/>
+      <c r="AS15" s="42"/>
+      <c r="AT15" s="43"/>
+      <c r="AU15" s="43"/>
+      <c r="AV15" s="44"/>
+      <c r="AW15" s="40"/>
+      <c r="AX15" s="41"/>
       <c r="AY15" s="42"/>
       <c r="AZ15" s="42"/>
       <c r="BA15" s="42"/>
       <c r="BB15" s="42"/>
-      <c r="BC15" s="43"/>
-      <c r="BD15" s="43"/>
-      <c r="BE15" s="44"/>
-      <c r="BF15" s="40"/>
-      <c r="BG15" s="41"/>
-      <c r="BH15" s="42"/>
-      <c r="BI15" s="42"/>
-      <c r="BJ15" s="42"/>
-      <c r="BK15" s="42"/>
+      <c r="BC15" s="42"/>
+      <c r="BD15" s="42"/>
+      <c r="BE15" s="42"/>
+      <c r="BF15" s="42"/>
+      <c r="BG15" s="43"/>
+      <c r="BH15" s="43"/>
+      <c r="BI15" s="44"/>
+      <c r="BJ15" s="40"/>
+      <c r="BK15" s="41"/>
       <c r="BL15" s="42"/>
       <c r="BM15" s="42"/>
       <c r="BN15" s="42"/>
-      <c r="BO15" s="43"/>
-      <c r="BP15" s="43"/>
-      <c r="BQ15" s="44"/>
-      <c r="BR15" s="40"/>
-      <c r="BS15" s="41"/>
-      <c r="BT15" s="42"/>
-      <c r="BU15" s="42"/>
-      <c r="BV15" s="42"/>
-      <c r="BW15" s="42"/>
-      <c r="BX15" s="42"/>
+      <c r="BO15" s="42"/>
+      <c r="BP15" s="42"/>
+      <c r="BQ15" s="42"/>
+      <c r="BR15" s="42"/>
+      <c r="BS15" s="42"/>
+      <c r="BT15" s="43"/>
+      <c r="BU15" s="43"/>
+      <c r="BV15" s="44"/>
+      <c r="BW15" s="40"/>
+      <c r="BX15" s="41"/>
       <c r="BY15" s="42"/>
       <c r="BZ15" s="42"/>
-      <c r="CA15" s="43"/>
-      <c r="CB15" s="43"/>
-      <c r="CC15" s="44"/>
-      <c r="CD15" s="40"/>
-      <c r="CE15" s="41"/>
+      <c r="CA15" s="42"/>
+      <c r="CB15" s="42"/>
+      <c r="CC15" s="42"/>
+      <c r="CD15" s="42"/>
+      <c r="CE15" s="42"/>
       <c r="CF15" s="42"/>
-      <c r="CG15" s="42"/>
-      <c r="CH15" s="42"/>
-      <c r="CI15" s="42"/>
-      <c r="CJ15" s="42"/>
-      <c r="CK15" s="42"/>
+      <c r="CG15" s="43"/>
+      <c r="CH15" s="43"/>
+      <c r="CI15" s="44"/>
+      <c r="CJ15" s="40"/>
+      <c r="CK15" s="41"/>
       <c r="CL15" s="42"/>
-      <c r="CM15" s="43"/>
-      <c r="CN15" s="43"/>
-      <c r="CO15" s="44"/>
-      <c r="CP15" s="40"/>
-      <c r="CQ15" s="41"/>
+      <c r="CM15" s="42"/>
+      <c r="CN15" s="42"/>
+      <c r="CO15" s="42"/>
+      <c r="CP15" s="42"/>
+      <c r="CQ15" s="42"/>
       <c r="CR15" s="42"/>
       <c r="CS15" s="42"/>
-      <c r="CT15" s="42"/>
-      <c r="CU15" s="42"/>
-      <c r="CV15" s="42"/>
-      <c r="CW15" s="42"/>
-      <c r="CX15" s="42"/>
-      <c r="CY15" s="43"/>
-      <c r="CZ15" s="43"/>
-      <c r="DA15" s="44"/>
-      <c r="DB15" s="40"/>
-      <c r="DC15" s="41"/>
+      <c r="CT15" s="43"/>
+      <c r="CU15" s="43"/>
+      <c r="CV15" s="44"/>
+      <c r="CW15" s="40"/>
+      <c r="CX15" s="41"/>
+      <c r="CY15" s="42"/>
+      <c r="CZ15" s="42"/>
+      <c r="DA15" s="42"/>
+      <c r="DB15" s="42"/>
+      <c r="DC15" s="42"/>
       <c r="DD15" s="42"/>
       <c r="DE15" s="42"/>
       <c r="DF15" s="42"/>
-      <c r="DG15" s="42"/>
-      <c r="DH15" s="42"/>
-      <c r="DI15" s="42"/>
-      <c r="DJ15" s="42"/>
-      <c r="DK15" s="43"/>
-      <c r="DL15" s="43"/>
-      <c r="DM15" s="44"/>
-      <c r="DN15" s="40"/>
-      <c r="DO15" s="41"/>
+      <c r="DG15" s="43"/>
+      <c r="DH15" s="43"/>
+      <c r="DI15" s="44"/>
+      <c r="DJ15" s="40"/>
+      <c r="DK15" s="41"/>
+      <c r="DL15" s="42"/>
+      <c r="DM15" s="42"/>
+      <c r="DN15" s="42"/>
+      <c r="DO15" s="42"/>
       <c r="DP15" s="42"/>
       <c r="DQ15" s="42"/>
       <c r="DR15" s="42"/>
       <c r="DS15" s="42"/>
-      <c r="DT15" s="42"/>
-      <c r="DU15" s="42"/>
-      <c r="DV15" s="42"/>
-      <c r="DW15" s="43"/>
-      <c r="DX15" s="43"/>
-      <c r="DY15" s="44"/>
-      <c r="DZ15" s="40"/>
-      <c r="EA15" s="41"/>
+      <c r="DT15" s="43"/>
+      <c r="DU15" s="43"/>
+      <c r="DV15" s="44"/>
+      <c r="DW15" s="40"/>
+      <c r="DX15" s="41"/>
+      <c r="DY15" s="42"/>
+      <c r="DZ15" s="42"/>
+      <c r="EA15" s="42"/>
       <c r="EB15" s="42"/>
       <c r="EC15" s="42"/>
       <c r="ED15" s="42"/>
       <c r="EE15" s="42"/>
       <c r="EF15" s="42"/>
-      <c r="EG15" s="42"/>
-      <c r="EH15" s="42"/>
-      <c r="EI15" s="43"/>
-      <c r="EJ15" s="43"/>
-      <c r="EK15" s="44"/>
-      <c r="EL15" s="40"/>
-      <c r="EM15" s="41"/>
+      <c r="EG15" s="43"/>
+      <c r="EH15" s="43"/>
+      <c r="EI15" s="44"/>
+      <c r="EJ15" s="40"/>
+      <c r="EK15" s="41"/>
+      <c r="EL15" s="42"/>
+      <c r="EM15" s="42"/>
       <c r="EN15" s="42"/>
       <c r="EO15" s="42"/>
       <c r="EP15" s="42"/>
       <c r="EQ15" s="42"/>
       <c r="ER15" s="42"/>
       <c r="ES15" s="42"/>
-      <c r="ET15" s="42"/>
+      <c r="ET15" s="43"/>
       <c r="EU15" s="43"/>
-      <c r="EV15" s="43"/>
-      <c r="EW15" s="44"/>
-      <c r="EX15" s="40"/>
-      <c r="EY15" s="41"/>
+      <c r="EV15" s="44"/>
+      <c r="EW15" s="40"/>
+      <c r="EX15" s="41"/>
+      <c r="EY15" s="42"/>
       <c r="EZ15" s="42"/>
       <c r="FA15" s="42"/>
       <c r="FB15" s="42"/>
@@ -6488,11 +6737,25 @@
       <c r="FP15" s="42"/>
       <c r="FQ15" s="42"/>
       <c r="FR15" s="42"/>
-      <c r="FS15" s="43"/>
+      <c r="FS15" s="42"/>
       <c r="FT15" s="43"/>
-      <c r="FU15" s="44"/>
+      <c r="FU15" s="43"/>
+      <c r="FV15" s="44"/>
+      <c r="FW15" s="40"/>
+      <c r="FX15" s="41"/>
+      <c r="FY15" s="42"/>
+      <c r="FZ15" s="42"/>
+      <c r="GA15" s="42"/>
+      <c r="GB15" s="42"/>
+      <c r="GC15" s="42"/>
+      <c r="GD15" s="42"/>
+      <c r="GE15" s="42"/>
+      <c r="GF15" s="42"/>
+      <c r="GG15" s="43"/>
+      <c r="GH15" s="43"/>
+      <c r="GI15" s="44"/>
     </row>
-    <row r="16" spans="1:177" s="26" customFormat="1" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:191" s="26" customFormat="1" ht="30" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="23"/>
       <c r="C16" s="16" t="s">
@@ -6513,143 +6776,143 @@
       <c r="P16" s="42"/>
       <c r="Q16" s="42"/>
       <c r="R16" s="42"/>
-      <c r="S16" s="43"/>
+      <c r="S16" s="42"/>
       <c r="T16" s="43"/>
-      <c r="U16" s="44"/>
-      <c r="V16" s="40"/>
-      <c r="W16" s="41"/>
-      <c r="X16" s="42"/>
+      <c r="U16" s="43"/>
+      <c r="V16" s="44"/>
+      <c r="W16" s="40"/>
+      <c r="X16" s="41"/>
       <c r="Y16" s="42"/>
       <c r="Z16" s="42"/>
       <c r="AA16" s="42"/>
       <c r="AB16" s="42"/>
       <c r="AC16" s="42"/>
       <c r="AD16" s="42"/>
-      <c r="AE16" s="43"/>
-      <c r="AF16" s="43"/>
-      <c r="AG16" s="44"/>
-      <c r="AH16" s="40"/>
-      <c r="AI16" s="41"/>
-      <c r="AJ16" s="42"/>
-      <c r="AK16" s="42"/>
+      <c r="AE16" s="42"/>
+      <c r="AF16" s="42"/>
+      <c r="AG16" s="43"/>
+      <c r="AH16" s="43"/>
+      <c r="AI16" s="44"/>
+      <c r="AJ16" s="40"/>
+      <c r="AK16" s="41"/>
       <c r="AL16" s="42"/>
       <c r="AM16" s="42"/>
       <c r="AN16" s="42"/>
       <c r="AO16" s="42"/>
       <c r="AP16" s="42"/>
-      <c r="AQ16" s="43"/>
-      <c r="AR16" s="43"/>
-      <c r="AS16" s="44"/>
-      <c r="AT16" s="40"/>
-      <c r="AU16" s="41"/>
-      <c r="AV16" s="42"/>
-      <c r="AW16" s="42"/>
-      <c r="AX16" s="42"/>
+      <c r="AQ16" s="42"/>
+      <c r="AR16" s="42"/>
+      <c r="AS16" s="42"/>
+      <c r="AT16" s="43"/>
+      <c r="AU16" s="43"/>
+      <c r="AV16" s="44"/>
+      <c r="AW16" s="40"/>
+      <c r="AX16" s="41"/>
       <c r="AY16" s="42"/>
       <c r="AZ16" s="42"/>
       <c r="BA16" s="42"/>
       <c r="BB16" s="42"/>
-      <c r="BC16" s="43"/>
-      <c r="BD16" s="43"/>
-      <c r="BE16" s="44"/>
-      <c r="BF16" s="40"/>
-      <c r="BG16" s="41"/>
-      <c r="BH16" s="42"/>
-      <c r="BI16" s="42"/>
-      <c r="BJ16" s="42"/>
-      <c r="BK16" s="42"/>
+      <c r="BC16" s="42"/>
+      <c r="BD16" s="42"/>
+      <c r="BE16" s="42"/>
+      <c r="BF16" s="42"/>
+      <c r="BG16" s="43"/>
+      <c r="BH16" s="43"/>
+      <c r="BI16" s="44"/>
+      <c r="BJ16" s="40"/>
+      <c r="BK16" s="41"/>
       <c r="BL16" s="42"/>
       <c r="BM16" s="42"/>
       <c r="BN16" s="42"/>
-      <c r="BO16" s="43"/>
-      <c r="BP16" s="43"/>
-      <c r="BQ16" s="44"/>
-      <c r="BR16" s="40"/>
-      <c r="BS16" s="41"/>
-      <c r="BT16" s="42"/>
-      <c r="BU16" s="42"/>
-      <c r="BV16" s="42"/>
-      <c r="BW16" s="42"/>
-      <c r="BX16" s="42"/>
+      <c r="BO16" s="42"/>
+      <c r="BP16" s="42"/>
+      <c r="BQ16" s="42"/>
+      <c r="BR16" s="42"/>
+      <c r="BS16" s="42"/>
+      <c r="BT16" s="43"/>
+      <c r="BU16" s="43"/>
+      <c r="BV16" s="44"/>
+      <c r="BW16" s="40"/>
+      <c r="BX16" s="41"/>
       <c r="BY16" s="42"/>
       <c r="BZ16" s="42"/>
-      <c r="CA16" s="43"/>
-      <c r="CB16" s="43"/>
-      <c r="CC16" s="44"/>
-      <c r="CD16" s="40"/>
-      <c r="CE16" s="41"/>
+      <c r="CA16" s="42"/>
+      <c r="CB16" s="42"/>
+      <c r="CC16" s="42"/>
+      <c r="CD16" s="42"/>
+      <c r="CE16" s="42"/>
       <c r="CF16" s="42"/>
-      <c r="CG16" s="42"/>
-      <c r="CH16" s="42"/>
-      <c r="CI16" s="42"/>
-      <c r="CJ16" s="42"/>
-      <c r="CK16" s="42"/>
+      <c r="CG16" s="43"/>
+      <c r="CH16" s="43"/>
+      <c r="CI16" s="44"/>
+      <c r="CJ16" s="40"/>
+      <c r="CK16" s="41"/>
       <c r="CL16" s="42"/>
-      <c r="CM16" s="43"/>
-      <c r="CN16" s="43"/>
-      <c r="CO16" s="44"/>
-      <c r="CP16" s="40"/>
-      <c r="CQ16" s="41"/>
+      <c r="CM16" s="42"/>
+      <c r="CN16" s="42"/>
+      <c r="CO16" s="42"/>
+      <c r="CP16" s="42"/>
+      <c r="CQ16" s="42"/>
       <c r="CR16" s="42"/>
       <c r="CS16" s="42"/>
-      <c r="CT16" s="42"/>
-      <c r="CU16" s="42"/>
-      <c r="CV16" s="42"/>
-      <c r="CW16" s="42"/>
-      <c r="CX16" s="42"/>
-      <c r="CY16" s="43"/>
-      <c r="CZ16" s="43"/>
-      <c r="DA16" s="44"/>
-      <c r="DB16" s="40"/>
-      <c r="DC16" s="41"/>
+      <c r="CT16" s="43"/>
+      <c r="CU16" s="43"/>
+      <c r="CV16" s="44"/>
+      <c r="CW16" s="40"/>
+      <c r="CX16" s="41"/>
+      <c r="CY16" s="42"/>
+      <c r="CZ16" s="42"/>
+      <c r="DA16" s="42"/>
+      <c r="DB16" s="42"/>
+      <c r="DC16" s="42"/>
       <c r="DD16" s="42"/>
       <c r="DE16" s="42"/>
       <c r="DF16" s="42"/>
-      <c r="DG16" s="42"/>
-      <c r="DH16" s="42"/>
-      <c r="DI16" s="42"/>
-      <c r="DJ16" s="42"/>
-      <c r="DK16" s="43"/>
-      <c r="DL16" s="43"/>
-      <c r="DM16" s="44"/>
-      <c r="DN16" s="40"/>
-      <c r="DO16" s="41"/>
+      <c r="DG16" s="43"/>
+      <c r="DH16" s="43"/>
+      <c r="DI16" s="44"/>
+      <c r="DJ16" s="40"/>
+      <c r="DK16" s="41"/>
+      <c r="DL16" s="42"/>
+      <c r="DM16" s="42"/>
+      <c r="DN16" s="42"/>
+      <c r="DO16" s="42"/>
       <c r="DP16" s="42"/>
       <c r="DQ16" s="42"/>
       <c r="DR16" s="42"/>
       <c r="DS16" s="42"/>
-      <c r="DT16" s="42"/>
-      <c r="DU16" s="42"/>
-      <c r="DV16" s="42"/>
-      <c r="DW16" s="43"/>
-      <c r="DX16" s="43"/>
-      <c r="DY16" s="44"/>
-      <c r="DZ16" s="40"/>
-      <c r="EA16" s="41"/>
+      <c r="DT16" s="43"/>
+      <c r="DU16" s="43"/>
+      <c r="DV16" s="44"/>
+      <c r="DW16" s="40"/>
+      <c r="DX16" s="41"/>
+      <c r="DY16" s="42"/>
+      <c r="DZ16" s="42"/>
+      <c r="EA16" s="42"/>
       <c r="EB16" s="42"/>
       <c r="EC16" s="42"/>
       <c r="ED16" s="42"/>
       <c r="EE16" s="42"/>
       <c r="EF16" s="42"/>
-      <c r="EG16" s="42"/>
-      <c r="EH16" s="42"/>
-      <c r="EI16" s="43"/>
-      <c r="EJ16" s="43"/>
-      <c r="EK16" s="44"/>
-      <c r="EL16" s="40"/>
-      <c r="EM16" s="41"/>
+      <c r="EG16" s="43"/>
+      <c r="EH16" s="43"/>
+      <c r="EI16" s="44"/>
+      <c r="EJ16" s="40"/>
+      <c r="EK16" s="41"/>
+      <c r="EL16" s="42"/>
+      <c r="EM16" s="42"/>
       <c r="EN16" s="42"/>
       <c r="EO16" s="42"/>
       <c r="EP16" s="42"/>
       <c r="EQ16" s="42"/>
       <c r="ER16" s="42"/>
       <c r="ES16" s="42"/>
-      <c r="ET16" s="42"/>
+      <c r="ET16" s="43"/>
       <c r="EU16" s="43"/>
-      <c r="EV16" s="43"/>
-      <c r="EW16" s="44"/>
-      <c r="EX16" s="40"/>
-      <c r="EY16" s="41"/>
+      <c r="EV16" s="44"/>
+      <c r="EW16" s="40"/>
+      <c r="EX16" s="41"/>
+      <c r="EY16" s="42"/>
       <c r="EZ16" s="42"/>
       <c r="FA16" s="42"/>
       <c r="FB16" s="42"/>
@@ -6669,11 +6932,25 @@
       <c r="FP16" s="42"/>
       <c r="FQ16" s="42"/>
       <c r="FR16" s="42"/>
-      <c r="FS16" s="43"/>
+      <c r="FS16" s="42"/>
       <c r="FT16" s="43"/>
-      <c r="FU16" s="44"/>
+      <c r="FU16" s="43"/>
+      <c r="FV16" s="44"/>
+      <c r="FW16" s="40"/>
+      <c r="FX16" s="41"/>
+      <c r="FY16" s="42"/>
+      <c r="FZ16" s="42"/>
+      <c r="GA16" s="42"/>
+      <c r="GB16" s="42"/>
+      <c r="GC16" s="42"/>
+      <c r="GD16" s="42"/>
+      <c r="GE16" s="42"/>
+      <c r="GF16" s="42"/>
+      <c r="GG16" s="43"/>
+      <c r="GH16" s="43"/>
+      <c r="GI16" s="44"/>
     </row>
-    <row r="17" spans="1:177" s="26" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:191" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="23"/>
       <c r="C17" s="24" t="s">
@@ -6694,143 +6971,143 @@
       <c r="P17" s="42"/>
       <c r="Q17" s="42"/>
       <c r="R17" s="42"/>
-      <c r="S17" s="43"/>
+      <c r="S17" s="42"/>
       <c r="T17" s="43"/>
-      <c r="U17" s="44"/>
-      <c r="V17" s="40"/>
-      <c r="W17" s="41"/>
-      <c r="X17" s="42"/>
+      <c r="U17" s="43"/>
+      <c r="V17" s="44"/>
+      <c r="W17" s="40"/>
+      <c r="X17" s="41"/>
       <c r="Y17" s="42"/>
       <c r="Z17" s="42"/>
       <c r="AA17" s="42"/>
       <c r="AB17" s="42"/>
       <c r="AC17" s="42"/>
       <c r="AD17" s="42"/>
-      <c r="AE17" s="43"/>
-      <c r="AF17" s="43"/>
-      <c r="AG17" s="44"/>
-      <c r="AH17" s="40"/>
-      <c r="AI17" s="41"/>
-      <c r="AJ17" s="42"/>
-      <c r="AK17" s="42"/>
+      <c r="AE17" s="42"/>
+      <c r="AF17" s="42"/>
+      <c r="AG17" s="43"/>
+      <c r="AH17" s="43"/>
+      <c r="AI17" s="44"/>
+      <c r="AJ17" s="40"/>
+      <c r="AK17" s="41"/>
       <c r="AL17" s="42"/>
       <c r="AM17" s="42"/>
       <c r="AN17" s="42"/>
       <c r="AO17" s="42"/>
       <c r="AP17" s="42"/>
-      <c r="AQ17" s="43"/>
-      <c r="AR17" s="43"/>
-      <c r="AS17" s="44"/>
-      <c r="AT17" s="40"/>
-      <c r="AU17" s="41"/>
-      <c r="AV17" s="42"/>
-      <c r="AW17" s="42"/>
-      <c r="AX17" s="42"/>
+      <c r="AQ17" s="42"/>
+      <c r="AR17" s="42"/>
+      <c r="AS17" s="42"/>
+      <c r="AT17" s="43"/>
+      <c r="AU17" s="43"/>
+      <c r="AV17" s="44"/>
+      <c r="AW17" s="40"/>
+      <c r="AX17" s="41"/>
       <c r="AY17" s="42"/>
       <c r="AZ17" s="42"/>
       <c r="BA17" s="42"/>
       <c r="BB17" s="42"/>
-      <c r="BC17" s="43"/>
-      <c r="BD17" s="43"/>
-      <c r="BE17" s="44"/>
-      <c r="BF17" s="40"/>
-      <c r="BG17" s="41"/>
-      <c r="BH17" s="42"/>
-      <c r="BI17" s="42"/>
-      <c r="BJ17" s="42"/>
-      <c r="BK17" s="42"/>
+      <c r="BC17" s="42"/>
+      <c r="BD17" s="42"/>
+      <c r="BE17" s="42"/>
+      <c r="BF17" s="42"/>
+      <c r="BG17" s="43"/>
+      <c r="BH17" s="43"/>
+      <c r="BI17" s="44"/>
+      <c r="BJ17" s="40"/>
+      <c r="BK17" s="41"/>
       <c r="BL17" s="42"/>
       <c r="BM17" s="42"/>
       <c r="BN17" s="42"/>
-      <c r="BO17" s="43"/>
-      <c r="BP17" s="43"/>
-      <c r="BQ17" s="44"/>
-      <c r="BR17" s="40"/>
-      <c r="BS17" s="41"/>
-      <c r="BT17" s="42"/>
-      <c r="BU17" s="42"/>
-      <c r="BV17" s="42"/>
-      <c r="BW17" s="42"/>
-      <c r="BX17" s="42"/>
+      <c r="BO17" s="42"/>
+      <c r="BP17" s="42"/>
+      <c r="BQ17" s="42"/>
+      <c r="BR17" s="42"/>
+      <c r="BS17" s="42"/>
+      <c r="BT17" s="43"/>
+      <c r="BU17" s="43"/>
+      <c r="BV17" s="44"/>
+      <c r="BW17" s="40"/>
+      <c r="BX17" s="41"/>
       <c r="BY17" s="42"/>
       <c r="BZ17" s="42"/>
-      <c r="CA17" s="43"/>
-      <c r="CB17" s="43"/>
-      <c r="CC17" s="44"/>
-      <c r="CD17" s="40"/>
-      <c r="CE17" s="41"/>
+      <c r="CA17" s="42"/>
+      <c r="CB17" s="42"/>
+      <c r="CC17" s="42"/>
+      <c r="CD17" s="42"/>
+      <c r="CE17" s="42"/>
       <c r="CF17" s="42"/>
-      <c r="CG17" s="42"/>
-      <c r="CH17" s="42"/>
-      <c r="CI17" s="42"/>
-      <c r="CJ17" s="42"/>
-      <c r="CK17" s="42"/>
+      <c r="CG17" s="43"/>
+      <c r="CH17" s="43"/>
+      <c r="CI17" s="44"/>
+      <c r="CJ17" s="40"/>
+      <c r="CK17" s="41"/>
       <c r="CL17" s="42"/>
-      <c r="CM17" s="43"/>
-      <c r="CN17" s="43"/>
-      <c r="CO17" s="44"/>
-      <c r="CP17" s="40"/>
-      <c r="CQ17" s="41"/>
+      <c r="CM17" s="42"/>
+      <c r="CN17" s="42"/>
+      <c r="CO17" s="42"/>
+      <c r="CP17" s="42"/>
+      <c r="CQ17" s="42"/>
       <c r="CR17" s="42"/>
       <c r="CS17" s="42"/>
-      <c r="CT17" s="42"/>
-      <c r="CU17" s="42"/>
-      <c r="CV17" s="42"/>
-      <c r="CW17" s="42"/>
-      <c r="CX17" s="42"/>
-      <c r="CY17" s="43"/>
-      <c r="CZ17" s="43"/>
-      <c r="DA17" s="44"/>
-      <c r="DB17" s="40"/>
-      <c r="DC17" s="41"/>
+      <c r="CT17" s="43"/>
+      <c r="CU17" s="43"/>
+      <c r="CV17" s="44"/>
+      <c r="CW17" s="40"/>
+      <c r="CX17" s="41"/>
+      <c r="CY17" s="42"/>
+      <c r="CZ17" s="42"/>
+      <c r="DA17" s="42"/>
+      <c r="DB17" s="42"/>
+      <c r="DC17" s="42"/>
       <c r="DD17" s="42"/>
       <c r="DE17" s="42"/>
       <c r="DF17" s="42"/>
-      <c r="DG17" s="42"/>
-      <c r="DH17" s="42"/>
-      <c r="DI17" s="42"/>
-      <c r="DJ17" s="42"/>
-      <c r="DK17" s="43"/>
-      <c r="DL17" s="43"/>
-      <c r="DM17" s="44"/>
-      <c r="DN17" s="40"/>
-      <c r="DO17" s="41"/>
+      <c r="DG17" s="43"/>
+      <c r="DH17" s="43"/>
+      <c r="DI17" s="44"/>
+      <c r="DJ17" s="40"/>
+      <c r="DK17" s="41"/>
+      <c r="DL17" s="42"/>
+      <c r="DM17" s="42"/>
+      <c r="DN17" s="42"/>
+      <c r="DO17" s="42"/>
       <c r="DP17" s="42"/>
       <c r="DQ17" s="42"/>
       <c r="DR17" s="42"/>
       <c r="DS17" s="42"/>
-      <c r="DT17" s="42"/>
-      <c r="DU17" s="42"/>
-      <c r="DV17" s="42"/>
-      <c r="DW17" s="43"/>
-      <c r="DX17" s="43"/>
-      <c r="DY17" s="44"/>
-      <c r="DZ17" s="40"/>
-      <c r="EA17" s="41"/>
+      <c r="DT17" s="43"/>
+      <c r="DU17" s="43"/>
+      <c r="DV17" s="44"/>
+      <c r="DW17" s="40"/>
+      <c r="DX17" s="41"/>
+      <c r="DY17" s="42"/>
+      <c r="DZ17" s="42"/>
+      <c r="EA17" s="42"/>
       <c r="EB17" s="42"/>
       <c r="EC17" s="42"/>
       <c r="ED17" s="42"/>
       <c r="EE17" s="42"/>
       <c r="EF17" s="42"/>
-      <c r="EG17" s="42"/>
-      <c r="EH17" s="42"/>
-      <c r="EI17" s="43"/>
-      <c r="EJ17" s="43"/>
-      <c r="EK17" s="44"/>
-      <c r="EL17" s="40"/>
-      <c r="EM17" s="41"/>
+      <c r="EG17" s="43"/>
+      <c r="EH17" s="43"/>
+      <c r="EI17" s="44"/>
+      <c r="EJ17" s="40"/>
+      <c r="EK17" s="41"/>
+      <c r="EL17" s="42"/>
+      <c r="EM17" s="42"/>
       <c r="EN17" s="42"/>
       <c r="EO17" s="42"/>
       <c r="EP17" s="42"/>
       <c r="EQ17" s="42"/>
       <c r="ER17" s="42"/>
       <c r="ES17" s="42"/>
-      <c r="ET17" s="42"/>
+      <c r="ET17" s="43"/>
       <c r="EU17" s="43"/>
-      <c r="EV17" s="43"/>
-      <c r="EW17" s="44"/>
-      <c r="EX17" s="40"/>
-      <c r="EY17" s="41"/>
+      <c r="EV17" s="44"/>
+      <c r="EW17" s="40"/>
+      <c r="EX17" s="41"/>
+      <c r="EY17" s="42"/>
       <c r="EZ17" s="42"/>
       <c r="FA17" s="42"/>
       <c r="FB17" s="42"/>
@@ -6850,11 +7127,25 @@
       <c r="FP17" s="42"/>
       <c r="FQ17" s="42"/>
       <c r="FR17" s="42"/>
-      <c r="FS17" s="43"/>
+      <c r="FS17" s="42"/>
       <c r="FT17" s="43"/>
-      <c r="FU17" s="44"/>
+      <c r="FU17" s="43"/>
+      <c r="FV17" s="44"/>
+      <c r="FW17" s="40"/>
+      <c r="FX17" s="41"/>
+      <c r="FY17" s="42"/>
+      <c r="FZ17" s="42"/>
+      <c r="GA17" s="42"/>
+      <c r="GB17" s="42"/>
+      <c r="GC17" s="42"/>
+      <c r="GD17" s="42"/>
+      <c r="GE17" s="42"/>
+      <c r="GF17" s="42"/>
+      <c r="GG17" s="43"/>
+      <c r="GH17" s="43"/>
+      <c r="GI17" s="44"/>
     </row>
-    <row r="18" spans="1:177" s="26" customFormat="1" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:191" s="26" customFormat="1" ht="30" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="23"/>
       <c r="C18" s="16" t="s">
@@ -6875,143 +7166,143 @@
       <c r="P18" s="42"/>
       <c r="Q18" s="42"/>
       <c r="R18" s="42"/>
-      <c r="S18" s="43"/>
+      <c r="S18" s="42"/>
       <c r="T18" s="43"/>
-      <c r="U18" s="44"/>
-      <c r="V18" s="40"/>
-      <c r="W18" s="41"/>
-      <c r="X18" s="42"/>
+      <c r="U18" s="43"/>
+      <c r="V18" s="44"/>
+      <c r="W18" s="40"/>
+      <c r="X18" s="41"/>
       <c r="Y18" s="42"/>
       <c r="Z18" s="42"/>
       <c r="AA18" s="42"/>
       <c r="AB18" s="42"/>
       <c r="AC18" s="42"/>
       <c r="AD18" s="42"/>
-      <c r="AE18" s="43"/>
-      <c r="AF18" s="43"/>
-      <c r="AG18" s="44"/>
-      <c r="AH18" s="40"/>
-      <c r="AI18" s="41"/>
-      <c r="AJ18" s="42"/>
-      <c r="AK18" s="42"/>
+      <c r="AE18" s="42"/>
+      <c r="AF18" s="42"/>
+      <c r="AG18" s="43"/>
+      <c r="AH18" s="43"/>
+      <c r="AI18" s="44"/>
+      <c r="AJ18" s="40"/>
+      <c r="AK18" s="41"/>
       <c r="AL18" s="42"/>
       <c r="AM18" s="42"/>
       <c r="AN18" s="42"/>
       <c r="AO18" s="42"/>
       <c r="AP18" s="42"/>
-      <c r="AQ18" s="43"/>
-      <c r="AR18" s="43"/>
-      <c r="AS18" s="44"/>
-      <c r="AT18" s="40"/>
-      <c r="AU18" s="41"/>
-      <c r="AV18" s="42"/>
-      <c r="AW18" s="42"/>
-      <c r="AX18" s="42"/>
+      <c r="AQ18" s="42"/>
+      <c r="AR18" s="42"/>
+      <c r="AS18" s="42"/>
+      <c r="AT18" s="43"/>
+      <c r="AU18" s="43"/>
+      <c r="AV18" s="44"/>
+      <c r="AW18" s="40"/>
+      <c r="AX18" s="41"/>
       <c r="AY18" s="42"/>
       <c r="AZ18" s="42"/>
       <c r="BA18" s="42"/>
       <c r="BB18" s="42"/>
-      <c r="BC18" s="43"/>
-      <c r="BD18" s="43"/>
-      <c r="BE18" s="44"/>
-      <c r="BF18" s="40"/>
-      <c r="BG18" s="41"/>
-      <c r="BH18" s="42"/>
-      <c r="BI18" s="42"/>
-      <c r="BJ18" s="42"/>
-      <c r="BK18" s="42"/>
+      <c r="BC18" s="42"/>
+      <c r="BD18" s="42"/>
+      <c r="BE18" s="42"/>
+      <c r="BF18" s="42"/>
+      <c r="BG18" s="43"/>
+      <c r="BH18" s="43"/>
+      <c r="BI18" s="44"/>
+      <c r="BJ18" s="40"/>
+      <c r="BK18" s="41"/>
       <c r="BL18" s="42"/>
       <c r="BM18" s="42"/>
       <c r="BN18" s="42"/>
-      <c r="BO18" s="43"/>
-      <c r="BP18" s="43"/>
-      <c r="BQ18" s="44"/>
-      <c r="BR18" s="40"/>
-      <c r="BS18" s="41"/>
-      <c r="BT18" s="42"/>
-      <c r="BU18" s="42"/>
-      <c r="BV18" s="42"/>
-      <c r="BW18" s="42"/>
-      <c r="BX18" s="42"/>
+      <c r="BO18" s="42"/>
+      <c r="BP18" s="42"/>
+      <c r="BQ18" s="42"/>
+      <c r="BR18" s="42"/>
+      <c r="BS18" s="42"/>
+      <c r="BT18" s="43"/>
+      <c r="BU18" s="43"/>
+      <c r="BV18" s="44"/>
+      <c r="BW18" s="40"/>
+      <c r="BX18" s="41"/>
       <c r="BY18" s="42"/>
       <c r="BZ18" s="42"/>
-      <c r="CA18" s="43"/>
-      <c r="CB18" s="43"/>
-      <c r="CC18" s="44"/>
-      <c r="CD18" s="40"/>
-      <c r="CE18" s="41"/>
+      <c r="CA18" s="42"/>
+      <c r="CB18" s="42"/>
+      <c r="CC18" s="42"/>
+      <c r="CD18" s="42"/>
+      <c r="CE18" s="42"/>
       <c r="CF18" s="42"/>
-      <c r="CG18" s="42"/>
-      <c r="CH18" s="42"/>
-      <c r="CI18" s="42"/>
-      <c r="CJ18" s="42"/>
-      <c r="CK18" s="42"/>
+      <c r="CG18" s="43"/>
+      <c r="CH18" s="43"/>
+      <c r="CI18" s="44"/>
+      <c r="CJ18" s="40"/>
+      <c r="CK18" s="41"/>
       <c r="CL18" s="42"/>
-      <c r="CM18" s="43"/>
-      <c r="CN18" s="43"/>
-      <c r="CO18" s="44"/>
-      <c r="CP18" s="40"/>
-      <c r="CQ18" s="41"/>
+      <c r="CM18" s="42"/>
+      <c r="CN18" s="42"/>
+      <c r="CO18" s="42"/>
+      <c r="CP18" s="42"/>
+      <c r="CQ18" s="42"/>
       <c r="CR18" s="42"/>
       <c r="CS18" s="42"/>
-      <c r="CT18" s="42"/>
-      <c r="CU18" s="42"/>
-      <c r="CV18" s="42"/>
-      <c r="CW18" s="42"/>
-      <c r="CX18" s="42"/>
-      <c r="CY18" s="43"/>
-      <c r="CZ18" s="43"/>
-      <c r="DA18" s="44"/>
-      <c r="DB18" s="40"/>
-      <c r="DC18" s="41"/>
+      <c r="CT18" s="43"/>
+      <c r="CU18" s="43"/>
+      <c r="CV18" s="44"/>
+      <c r="CW18" s="40"/>
+      <c r="CX18" s="41"/>
+      <c r="CY18" s="42"/>
+      <c r="CZ18" s="42"/>
+      <c r="DA18" s="42"/>
+      <c r="DB18" s="42"/>
+      <c r="DC18" s="42"/>
       <c r="DD18" s="42"/>
       <c r="DE18" s="42"/>
       <c r="DF18" s="42"/>
-      <c r="DG18" s="42"/>
-      <c r="DH18" s="42"/>
-      <c r="DI18" s="42"/>
-      <c r="DJ18" s="42"/>
-      <c r="DK18" s="43"/>
-      <c r="DL18" s="43"/>
-      <c r="DM18" s="44"/>
-      <c r="DN18" s="40"/>
-      <c r="DO18" s="41"/>
+      <c r="DG18" s="43"/>
+      <c r="DH18" s="43"/>
+      <c r="DI18" s="44"/>
+      <c r="DJ18" s="40"/>
+      <c r="DK18" s="41"/>
+      <c r="DL18" s="42"/>
+      <c r="DM18" s="42"/>
+      <c r="DN18" s="42"/>
+      <c r="DO18" s="42"/>
       <c r="DP18" s="42"/>
       <c r="DQ18" s="42"/>
       <c r="DR18" s="42"/>
       <c r="DS18" s="42"/>
-      <c r="DT18" s="42"/>
-      <c r="DU18" s="42"/>
-      <c r="DV18" s="42"/>
-      <c r="DW18" s="43"/>
-      <c r="DX18" s="43"/>
-      <c r="DY18" s="44"/>
-      <c r="DZ18" s="40"/>
-      <c r="EA18" s="41"/>
+      <c r="DT18" s="43"/>
+      <c r="DU18" s="43"/>
+      <c r="DV18" s="44"/>
+      <c r="DW18" s="40"/>
+      <c r="DX18" s="41"/>
+      <c r="DY18" s="42"/>
+      <c r="DZ18" s="42"/>
+      <c r="EA18" s="42"/>
       <c r="EB18" s="42"/>
       <c r="EC18" s="42"/>
       <c r="ED18" s="42"/>
       <c r="EE18" s="42"/>
       <c r="EF18" s="42"/>
-      <c r="EG18" s="42"/>
-      <c r="EH18" s="42"/>
-      <c r="EI18" s="43"/>
-      <c r="EJ18" s="43"/>
-      <c r="EK18" s="44"/>
-      <c r="EL18" s="40"/>
-      <c r="EM18" s="41"/>
+      <c r="EG18" s="43"/>
+      <c r="EH18" s="43"/>
+      <c r="EI18" s="44"/>
+      <c r="EJ18" s="40"/>
+      <c r="EK18" s="41"/>
+      <c r="EL18" s="42"/>
+      <c r="EM18" s="42"/>
       <c r="EN18" s="42"/>
       <c r="EO18" s="42"/>
       <c r="EP18" s="42"/>
       <c r="EQ18" s="42"/>
       <c r="ER18" s="42"/>
       <c r="ES18" s="42"/>
-      <c r="ET18" s="42"/>
+      <c r="ET18" s="43"/>
       <c r="EU18" s="43"/>
-      <c r="EV18" s="43"/>
-      <c r="EW18" s="44"/>
-      <c r="EX18" s="40"/>
-      <c r="EY18" s="41"/>
+      <c r="EV18" s="44"/>
+      <c r="EW18" s="40"/>
+      <c r="EX18" s="41"/>
+      <c r="EY18" s="42"/>
       <c r="EZ18" s="42"/>
       <c r="FA18" s="42"/>
       <c r="FB18" s="42"/>
@@ -7031,11 +7322,25 @@
       <c r="FP18" s="42"/>
       <c r="FQ18" s="42"/>
       <c r="FR18" s="42"/>
-      <c r="FS18" s="43"/>
+      <c r="FS18" s="42"/>
       <c r="FT18" s="43"/>
-      <c r="FU18" s="44"/>
+      <c r="FU18" s="43"/>
+      <c r="FV18" s="44"/>
+      <c r="FW18" s="40"/>
+      <c r="FX18" s="41"/>
+      <c r="FY18" s="42"/>
+      <c r="FZ18" s="42"/>
+      <c r="GA18" s="42"/>
+      <c r="GB18" s="42"/>
+      <c r="GC18" s="42"/>
+      <c r="GD18" s="42"/>
+      <c r="GE18" s="42"/>
+      <c r="GF18" s="42"/>
+      <c r="GG18" s="43"/>
+      <c r="GH18" s="43"/>
+      <c r="GI18" s="44"/>
     </row>
-    <row r="19" spans="1:177" s="26" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:191" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="23"/>
       <c r="C19" s="24" t="s">
@@ -7056,143 +7361,143 @@
       <c r="P19" s="42"/>
       <c r="Q19" s="42"/>
       <c r="R19" s="42"/>
-      <c r="S19" s="43"/>
+      <c r="S19" s="42"/>
       <c r="T19" s="43"/>
-      <c r="U19" s="44"/>
-      <c r="V19" s="40"/>
-      <c r="W19" s="41"/>
-      <c r="X19" s="42"/>
+      <c r="U19" s="43"/>
+      <c r="V19" s="44"/>
+      <c r="W19" s="40"/>
+      <c r="X19" s="41"/>
       <c r="Y19" s="42"/>
       <c r="Z19" s="42"/>
       <c r="AA19" s="42"/>
       <c r="AB19" s="42"/>
       <c r="AC19" s="42"/>
       <c r="AD19" s="42"/>
-      <c r="AE19" s="43"/>
-      <c r="AF19" s="43"/>
-      <c r="AG19" s="44"/>
-      <c r="AH19" s="40"/>
-      <c r="AI19" s="41"/>
-      <c r="AJ19" s="42"/>
-      <c r="AK19" s="42"/>
+      <c r="AE19" s="42"/>
+      <c r="AF19" s="42"/>
+      <c r="AG19" s="43"/>
+      <c r="AH19" s="43"/>
+      <c r="AI19" s="44"/>
+      <c r="AJ19" s="40"/>
+      <c r="AK19" s="41"/>
       <c r="AL19" s="42"/>
       <c r="AM19" s="42"/>
       <c r="AN19" s="42"/>
       <c r="AO19" s="42"/>
       <c r="AP19" s="42"/>
-      <c r="AQ19" s="43"/>
-      <c r="AR19" s="43"/>
-      <c r="AS19" s="44"/>
-      <c r="AT19" s="40"/>
-      <c r="AU19" s="41"/>
-      <c r="AV19" s="42"/>
-      <c r="AW19" s="42"/>
-      <c r="AX19" s="42"/>
+      <c r="AQ19" s="42"/>
+      <c r="AR19" s="42"/>
+      <c r="AS19" s="42"/>
+      <c r="AT19" s="43"/>
+      <c r="AU19" s="43"/>
+      <c r="AV19" s="44"/>
+      <c r="AW19" s="40"/>
+      <c r="AX19" s="41"/>
       <c r="AY19" s="42"/>
       <c r="AZ19" s="42"/>
       <c r="BA19" s="42"/>
       <c r="BB19" s="42"/>
-      <c r="BC19" s="43"/>
-      <c r="BD19" s="43"/>
-      <c r="BE19" s="44"/>
-      <c r="BF19" s="40"/>
-      <c r="BG19" s="41"/>
-      <c r="BH19" s="42"/>
-      <c r="BI19" s="42"/>
-      <c r="BJ19" s="42"/>
-      <c r="BK19" s="42"/>
+      <c r="BC19" s="42"/>
+      <c r="BD19" s="42"/>
+      <c r="BE19" s="42"/>
+      <c r="BF19" s="42"/>
+      <c r="BG19" s="43"/>
+      <c r="BH19" s="43"/>
+      <c r="BI19" s="44"/>
+      <c r="BJ19" s="40"/>
+      <c r="BK19" s="41"/>
       <c r="BL19" s="42"/>
       <c r="BM19" s="42"/>
       <c r="BN19" s="42"/>
-      <c r="BO19" s="43"/>
-      <c r="BP19" s="43"/>
-      <c r="BQ19" s="44"/>
-      <c r="BR19" s="40"/>
-      <c r="BS19" s="41"/>
-      <c r="BT19" s="42"/>
-      <c r="BU19" s="42"/>
-      <c r="BV19" s="42"/>
-      <c r="BW19" s="42"/>
-      <c r="BX19" s="42"/>
+      <c r="BO19" s="42"/>
+      <c r="BP19" s="42"/>
+      <c r="BQ19" s="42"/>
+      <c r="BR19" s="42"/>
+      <c r="BS19" s="42"/>
+      <c r="BT19" s="43"/>
+      <c r="BU19" s="43"/>
+      <c r="BV19" s="44"/>
+      <c r="BW19" s="40"/>
+      <c r="BX19" s="41"/>
       <c r="BY19" s="42"/>
       <c r="BZ19" s="42"/>
-      <c r="CA19" s="43"/>
-      <c r="CB19" s="43"/>
-      <c r="CC19" s="44"/>
-      <c r="CD19" s="40"/>
-      <c r="CE19" s="41"/>
+      <c r="CA19" s="42"/>
+      <c r="CB19" s="42"/>
+      <c r="CC19" s="42"/>
+      <c r="CD19" s="42"/>
+      <c r="CE19" s="42"/>
       <c r="CF19" s="42"/>
-      <c r="CG19" s="42"/>
-      <c r="CH19" s="42"/>
-      <c r="CI19" s="42"/>
-      <c r="CJ19" s="42"/>
-      <c r="CK19" s="42"/>
+      <c r="CG19" s="43"/>
+      <c r="CH19" s="43"/>
+      <c r="CI19" s="44"/>
+      <c r="CJ19" s="40"/>
+      <c r="CK19" s="41"/>
       <c r="CL19" s="42"/>
-      <c r="CM19" s="43"/>
-      <c r="CN19" s="43"/>
-      <c r="CO19" s="44"/>
-      <c r="CP19" s="40"/>
-      <c r="CQ19" s="41"/>
+      <c r="CM19" s="42"/>
+      <c r="CN19" s="42"/>
+      <c r="CO19" s="42"/>
+      <c r="CP19" s="42"/>
+      <c r="CQ19" s="42"/>
       <c r="CR19" s="42"/>
       <c r="CS19" s="42"/>
-      <c r="CT19" s="42"/>
-      <c r="CU19" s="42"/>
-      <c r="CV19" s="42"/>
-      <c r="CW19" s="42"/>
-      <c r="CX19" s="42"/>
-      <c r="CY19" s="43"/>
-      <c r="CZ19" s="43"/>
-      <c r="DA19" s="44"/>
-      <c r="DB19" s="40"/>
-      <c r="DC19" s="41"/>
+      <c r="CT19" s="43"/>
+      <c r="CU19" s="43"/>
+      <c r="CV19" s="44"/>
+      <c r="CW19" s="40"/>
+      <c r="CX19" s="41"/>
+      <c r="CY19" s="42"/>
+      <c r="CZ19" s="42"/>
+      <c r="DA19" s="42"/>
+      <c r="DB19" s="42"/>
+      <c r="DC19" s="42"/>
       <c r="DD19" s="42"/>
       <c r="DE19" s="42"/>
       <c r="DF19" s="42"/>
-      <c r="DG19" s="42"/>
-      <c r="DH19" s="42"/>
-      <c r="DI19" s="42"/>
-      <c r="DJ19" s="42"/>
-      <c r="DK19" s="43"/>
-      <c r="DL19" s="43"/>
-      <c r="DM19" s="44"/>
-      <c r="DN19" s="40"/>
-      <c r="DO19" s="41"/>
+      <c r="DG19" s="43"/>
+      <c r="DH19" s="43"/>
+      <c r="DI19" s="44"/>
+      <c r="DJ19" s="40"/>
+      <c r="DK19" s="41"/>
+      <c r="DL19" s="42"/>
+      <c r="DM19" s="42"/>
+      <c r="DN19" s="42"/>
+      <c r="DO19" s="42"/>
       <c r="DP19" s="42"/>
       <c r="DQ19" s="42"/>
       <c r="DR19" s="42"/>
       <c r="DS19" s="42"/>
-      <c r="DT19" s="42"/>
-      <c r="DU19" s="42"/>
-      <c r="DV19" s="42"/>
-      <c r="DW19" s="43"/>
-      <c r="DX19" s="43"/>
-      <c r="DY19" s="44"/>
-      <c r="DZ19" s="40"/>
-      <c r="EA19" s="41"/>
+      <c r="DT19" s="43"/>
+      <c r="DU19" s="43"/>
+      <c r="DV19" s="44"/>
+      <c r="DW19" s="40"/>
+      <c r="DX19" s="41"/>
+      <c r="DY19" s="42"/>
+      <c r="DZ19" s="42"/>
+      <c r="EA19" s="42"/>
       <c r="EB19" s="42"/>
       <c r="EC19" s="42"/>
       <c r="ED19" s="42"/>
       <c r="EE19" s="42"/>
       <c r="EF19" s="42"/>
-      <c r="EG19" s="42"/>
-      <c r="EH19" s="42"/>
-      <c r="EI19" s="43"/>
-      <c r="EJ19" s="43"/>
-      <c r="EK19" s="44"/>
-      <c r="EL19" s="40"/>
-      <c r="EM19" s="41"/>
+      <c r="EG19" s="43"/>
+      <c r="EH19" s="43"/>
+      <c r="EI19" s="44"/>
+      <c r="EJ19" s="40"/>
+      <c r="EK19" s="41"/>
+      <c r="EL19" s="42"/>
+      <c r="EM19" s="42"/>
       <c r="EN19" s="42"/>
       <c r="EO19" s="42"/>
       <c r="EP19" s="42"/>
       <c r="EQ19" s="42"/>
       <c r="ER19" s="42"/>
       <c r="ES19" s="42"/>
-      <c r="ET19" s="42"/>
+      <c r="ET19" s="43"/>
       <c r="EU19" s="43"/>
-      <c r="EV19" s="43"/>
-      <c r="EW19" s="44"/>
-      <c r="EX19" s="40"/>
-      <c r="EY19" s="41"/>
+      <c r="EV19" s="44"/>
+      <c r="EW19" s="40"/>
+      <c r="EX19" s="41"/>
+      <c r="EY19" s="42"/>
       <c r="EZ19" s="42"/>
       <c r="FA19" s="42"/>
       <c r="FB19" s="42"/>
@@ -7212,11 +7517,25 @@
       <c r="FP19" s="42"/>
       <c r="FQ19" s="42"/>
       <c r="FR19" s="42"/>
-      <c r="FS19" s="43"/>
+      <c r="FS19" s="42"/>
       <c r="FT19" s="43"/>
-      <c r="FU19" s="44"/>
+      <c r="FU19" s="43"/>
+      <c r="FV19" s="44"/>
+      <c r="FW19" s="40"/>
+      <c r="FX19" s="41"/>
+      <c r="FY19" s="42"/>
+      <c r="FZ19" s="42"/>
+      <c r="GA19" s="42"/>
+      <c r="GB19" s="42"/>
+      <c r="GC19" s="42"/>
+      <c r="GD19" s="42"/>
+      <c r="GE19" s="42"/>
+      <c r="GF19" s="42"/>
+      <c r="GG19" s="43"/>
+      <c r="GH19" s="43"/>
+      <c r="GI19" s="44"/>
     </row>
-    <row r="20" spans="1:177" s="26" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:191" s="26" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="23"/>
       <c r="C20" s="24" t="s">
@@ -7237,143 +7556,143 @@
       <c r="P20" s="42"/>
       <c r="Q20" s="42"/>
       <c r="R20" s="42"/>
-      <c r="S20" s="43"/>
+      <c r="S20" s="42"/>
       <c r="T20" s="43"/>
-      <c r="U20" s="44"/>
-      <c r="V20" s="40"/>
-      <c r="W20" s="41"/>
-      <c r="X20" s="42"/>
+      <c r="U20" s="43"/>
+      <c r="V20" s="44"/>
+      <c r="W20" s="40"/>
+      <c r="X20" s="41"/>
       <c r="Y20" s="42"/>
       <c r="Z20" s="42"/>
       <c r="AA20" s="42"/>
       <c r="AB20" s="42"/>
       <c r="AC20" s="42"/>
       <c r="AD20" s="42"/>
-      <c r="AE20" s="43"/>
-      <c r="AF20" s="43"/>
-      <c r="AG20" s="44"/>
-      <c r="AH20" s="40"/>
-      <c r="AI20" s="41"/>
-      <c r="AJ20" s="42"/>
-      <c r="AK20" s="42"/>
+      <c r="AE20" s="42"/>
+      <c r="AF20" s="42"/>
+      <c r="AG20" s="43"/>
+      <c r="AH20" s="43"/>
+      <c r="AI20" s="44"/>
+      <c r="AJ20" s="40"/>
+      <c r="AK20" s="41"/>
       <c r="AL20" s="42"/>
       <c r="AM20" s="42"/>
       <c r="AN20" s="42"/>
       <c r="AO20" s="42"/>
       <c r="AP20" s="42"/>
-      <c r="AQ20" s="43"/>
-      <c r="AR20" s="43"/>
-      <c r="AS20" s="44"/>
-      <c r="AT20" s="40"/>
-      <c r="AU20" s="41"/>
-      <c r="AV20" s="42"/>
-      <c r="AW20" s="42"/>
-      <c r="AX20" s="42"/>
+      <c r="AQ20" s="42"/>
+      <c r="AR20" s="42"/>
+      <c r="AS20" s="42"/>
+      <c r="AT20" s="43"/>
+      <c r="AU20" s="43"/>
+      <c r="AV20" s="44"/>
+      <c r="AW20" s="40"/>
+      <c r="AX20" s="41"/>
       <c r="AY20" s="42"/>
       <c r="AZ20" s="42"/>
       <c r="BA20" s="42"/>
       <c r="BB20" s="42"/>
-      <c r="BC20" s="43"/>
-      <c r="BD20" s="43"/>
-      <c r="BE20" s="44"/>
-      <c r="BF20" s="40"/>
-      <c r="BG20" s="41"/>
-      <c r="BH20" s="42"/>
-      <c r="BI20" s="42"/>
-      <c r="BJ20" s="42"/>
-      <c r="BK20" s="42"/>
+      <c r="BC20" s="42"/>
+      <c r="BD20" s="42"/>
+      <c r="BE20" s="42"/>
+      <c r="BF20" s="42"/>
+      <c r="BG20" s="43"/>
+      <c r="BH20" s="43"/>
+      <c r="BI20" s="44"/>
+      <c r="BJ20" s="40"/>
+      <c r="BK20" s="41"/>
       <c r="BL20" s="42"/>
       <c r="BM20" s="42"/>
       <c r="BN20" s="42"/>
-      <c r="BO20" s="43"/>
-      <c r="BP20" s="43"/>
-      <c r="BQ20" s="44"/>
-      <c r="BR20" s="40"/>
-      <c r="BS20" s="41"/>
-      <c r="BT20" s="42"/>
-      <c r="BU20" s="42"/>
-      <c r="BV20" s="42"/>
-      <c r="BW20" s="42"/>
-      <c r="BX20" s="42"/>
+      <c r="BO20" s="42"/>
+      <c r="BP20" s="42"/>
+      <c r="BQ20" s="42"/>
+      <c r="BR20" s="42"/>
+      <c r="BS20" s="42"/>
+      <c r="BT20" s="43"/>
+      <c r="BU20" s="43"/>
+      <c r="BV20" s="44"/>
+      <c r="BW20" s="40"/>
+      <c r="BX20" s="41"/>
       <c r="BY20" s="42"/>
       <c r="BZ20" s="42"/>
-      <c r="CA20" s="43"/>
-      <c r="CB20" s="43"/>
-      <c r="CC20" s="44"/>
-      <c r="CD20" s="40"/>
-      <c r="CE20" s="41"/>
+      <c r="CA20" s="42"/>
+      <c r="CB20" s="42"/>
+      <c r="CC20" s="42"/>
+      <c r="CD20" s="42"/>
+      <c r="CE20" s="42"/>
       <c r="CF20" s="42"/>
-      <c r="CG20" s="42"/>
-      <c r="CH20" s="42"/>
-      <c r="CI20" s="42"/>
-      <c r="CJ20" s="42"/>
-      <c r="CK20" s="42"/>
+      <c r="CG20" s="43"/>
+      <c r="CH20" s="43"/>
+      <c r="CI20" s="44"/>
+      <c r="CJ20" s="40"/>
+      <c r="CK20" s="41"/>
       <c r="CL20" s="42"/>
-      <c r="CM20" s="43"/>
-      <c r="CN20" s="43"/>
-      <c r="CO20" s="44"/>
-      <c r="CP20" s="40"/>
-      <c r="CQ20" s="41"/>
+      <c r="CM20" s="42"/>
+      <c r="CN20" s="42"/>
+      <c r="CO20" s="42"/>
+      <c r="CP20" s="42"/>
+      <c r="CQ20" s="42"/>
       <c r="CR20" s="42"/>
       <c r="CS20" s="42"/>
-      <c r="CT20" s="42"/>
-      <c r="CU20" s="42"/>
-      <c r="CV20" s="42"/>
-      <c r="CW20" s="42"/>
-      <c r="CX20" s="42"/>
-      <c r="CY20" s="43"/>
-      <c r="CZ20" s="43"/>
-      <c r="DA20" s="44"/>
-      <c r="DB20" s="40"/>
-      <c r="DC20" s="41"/>
+      <c r="CT20" s="43"/>
+      <c r="CU20" s="43"/>
+      <c r="CV20" s="44"/>
+      <c r="CW20" s="40"/>
+      <c r="CX20" s="41"/>
+      <c r="CY20" s="42"/>
+      <c r="CZ20" s="42"/>
+      <c r="DA20" s="42"/>
+      <c r="DB20" s="42"/>
+      <c r="DC20" s="42"/>
       <c r="DD20" s="42"/>
       <c r="DE20" s="42"/>
       <c r="DF20" s="42"/>
-      <c r="DG20" s="42"/>
-      <c r="DH20" s="42"/>
-      <c r="DI20" s="42"/>
-      <c r="DJ20" s="42"/>
-      <c r="DK20" s="43"/>
-      <c r="DL20" s="43"/>
-      <c r="DM20" s="44"/>
-      <c r="DN20" s="40"/>
-      <c r="DO20" s="41"/>
+      <c r="DG20" s="43"/>
+      <c r="DH20" s="43"/>
+      <c r="DI20" s="44"/>
+      <c r="DJ20" s="40"/>
+      <c r="DK20" s="41"/>
+      <c r="DL20" s="42"/>
+      <c r="DM20" s="42"/>
+      <c r="DN20" s="42"/>
+      <c r="DO20" s="42"/>
       <c r="DP20" s="42"/>
       <c r="DQ20" s="42"/>
       <c r="DR20" s="42"/>
       <c r="DS20" s="42"/>
-      <c r="DT20" s="42"/>
-      <c r="DU20" s="42"/>
-      <c r="DV20" s="42"/>
-      <c r="DW20" s="43"/>
-      <c r="DX20" s="43"/>
-      <c r="DY20" s="44"/>
-      <c r="DZ20" s="40"/>
-      <c r="EA20" s="41"/>
+      <c r="DT20" s="43"/>
+      <c r="DU20" s="43"/>
+      <c r="DV20" s="44"/>
+      <c r="DW20" s="40"/>
+      <c r="DX20" s="41"/>
+      <c r="DY20" s="42"/>
+      <c r="DZ20" s="42"/>
+      <c r="EA20" s="42"/>
       <c r="EB20" s="42"/>
       <c r="EC20" s="42"/>
       <c r="ED20" s="42"/>
       <c r="EE20" s="42"/>
       <c r="EF20" s="42"/>
-      <c r="EG20" s="42"/>
-      <c r="EH20" s="42"/>
-      <c r="EI20" s="43"/>
-      <c r="EJ20" s="43"/>
-      <c r="EK20" s="44"/>
-      <c r="EL20" s="40"/>
-      <c r="EM20" s="41"/>
+      <c r="EG20" s="43"/>
+      <c r="EH20" s="43"/>
+      <c r="EI20" s="44"/>
+      <c r="EJ20" s="40"/>
+      <c r="EK20" s="41"/>
+      <c r="EL20" s="42"/>
+      <c r="EM20" s="42"/>
       <c r="EN20" s="42"/>
       <c r="EO20" s="42"/>
       <c r="EP20" s="42"/>
       <c r="EQ20" s="42"/>
       <c r="ER20" s="42"/>
       <c r="ES20" s="42"/>
-      <c r="ET20" s="42"/>
+      <c r="ET20" s="43"/>
       <c r="EU20" s="43"/>
-      <c r="EV20" s="43"/>
-      <c r="EW20" s="44"/>
-      <c r="EX20" s="40"/>
-      <c r="EY20" s="41"/>
+      <c r="EV20" s="44"/>
+      <c r="EW20" s="40"/>
+      <c r="EX20" s="41"/>
+      <c r="EY20" s="42"/>
       <c r="EZ20" s="42"/>
       <c r="FA20" s="42"/>
       <c r="FB20" s="42"/>
@@ -7393,11 +7712,25 @@
       <c r="FP20" s="42"/>
       <c r="FQ20" s="42"/>
       <c r="FR20" s="42"/>
-      <c r="FS20" s="43"/>
+      <c r="FS20" s="42"/>
       <c r="FT20" s="43"/>
-      <c r="FU20" s="44"/>
+      <c r="FU20" s="43"/>
+      <c r="FV20" s="44"/>
+      <c r="FW20" s="40"/>
+      <c r="FX20" s="41"/>
+      <c r="FY20" s="42"/>
+      <c r="FZ20" s="42"/>
+      <c r="GA20" s="42"/>
+      <c r="GB20" s="42"/>
+      <c r="GC20" s="42"/>
+      <c r="GD20" s="42"/>
+      <c r="GE20" s="42"/>
+      <c r="GF20" s="42"/>
+      <c r="GG20" s="43"/>
+      <c r="GH20" s="43"/>
+      <c r="GI20" s="44"/>
     </row>
-    <row r="21" spans="1:177" s="26" customFormat="1" ht="76.900000000000006" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:191" s="26" customFormat="1" ht="90" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="23"/>
       <c r="C21" s="16" t="s">
@@ -7418,143 +7751,143 @@
       <c r="P21" s="42"/>
       <c r="Q21" s="42"/>
       <c r="R21" s="42"/>
-      <c r="S21" s="43"/>
+      <c r="S21" s="42"/>
       <c r="T21" s="43"/>
-      <c r="U21" s="44"/>
-      <c r="V21" s="40"/>
-      <c r="W21" s="41"/>
-      <c r="X21" s="42"/>
+      <c r="U21" s="43"/>
+      <c r="V21" s="44"/>
+      <c r="W21" s="40"/>
+      <c r="X21" s="41"/>
       <c r="Y21" s="42"/>
       <c r="Z21" s="42"/>
       <c r="AA21" s="42"/>
       <c r="AB21" s="42"/>
       <c r="AC21" s="42"/>
       <c r="AD21" s="42"/>
-      <c r="AE21" s="43"/>
-      <c r="AF21" s="43"/>
-      <c r="AG21" s="44"/>
-      <c r="AH21" s="40"/>
-      <c r="AI21" s="41"/>
-      <c r="AJ21" s="42"/>
-      <c r="AK21" s="42"/>
+      <c r="AE21" s="42"/>
+      <c r="AF21" s="42"/>
+      <c r="AG21" s="43"/>
+      <c r="AH21" s="43"/>
+      <c r="AI21" s="44"/>
+      <c r="AJ21" s="40"/>
+      <c r="AK21" s="41"/>
       <c r="AL21" s="42"/>
       <c r="AM21" s="42"/>
       <c r="AN21" s="42"/>
       <c r="AO21" s="42"/>
       <c r="AP21" s="42"/>
-      <c r="AQ21" s="43"/>
-      <c r="AR21" s="43"/>
-      <c r="AS21" s="44"/>
-      <c r="AT21" s="40"/>
-      <c r="AU21" s="41"/>
-      <c r="AV21" s="42"/>
-      <c r="AW21" s="42"/>
-      <c r="AX21" s="42"/>
+      <c r="AQ21" s="42"/>
+      <c r="AR21" s="42"/>
+      <c r="AS21" s="42"/>
+      <c r="AT21" s="43"/>
+      <c r="AU21" s="43"/>
+      <c r="AV21" s="44"/>
+      <c r="AW21" s="40"/>
+      <c r="AX21" s="41"/>
       <c r="AY21" s="42"/>
       <c r="AZ21" s="42"/>
       <c r="BA21" s="42"/>
       <c r="BB21" s="42"/>
-      <c r="BC21" s="43"/>
-      <c r="BD21" s="43"/>
-      <c r="BE21" s="44"/>
-      <c r="BF21" s="40"/>
-      <c r="BG21" s="41"/>
-      <c r="BH21" s="42"/>
-      <c r="BI21" s="42"/>
-      <c r="BJ21" s="42"/>
-      <c r="BK21" s="42"/>
+      <c r="BC21" s="42"/>
+      <c r="BD21" s="42"/>
+      <c r="BE21" s="42"/>
+      <c r="BF21" s="42"/>
+      <c r="BG21" s="43"/>
+      <c r="BH21" s="43"/>
+      <c r="BI21" s="44"/>
+      <c r="BJ21" s="40"/>
+      <c r="BK21" s="41"/>
       <c r="BL21" s="42"/>
       <c r="BM21" s="42"/>
       <c r="BN21" s="42"/>
-      <c r="BO21" s="43"/>
-      <c r="BP21" s="43"/>
-      <c r="BQ21" s="44"/>
-      <c r="BR21" s="40"/>
-      <c r="BS21" s="41"/>
-      <c r="BT21" s="42"/>
-      <c r="BU21" s="42"/>
-      <c r="BV21" s="42"/>
-      <c r="BW21" s="42"/>
-      <c r="BX21" s="42"/>
+      <c r="BO21" s="42"/>
+      <c r="BP21" s="42"/>
+      <c r="BQ21" s="42"/>
+      <c r="BR21" s="42"/>
+      <c r="BS21" s="42"/>
+      <c r="BT21" s="43"/>
+      <c r="BU21" s="43"/>
+      <c r="BV21" s="44"/>
+      <c r="BW21" s="40"/>
+      <c r="BX21" s="41"/>
       <c r="BY21" s="42"/>
       <c r="BZ21" s="42"/>
-      <c r="CA21" s="43"/>
-      <c r="CB21" s="43"/>
-      <c r="CC21" s="44"/>
-      <c r="CD21" s="40"/>
-      <c r="CE21" s="41"/>
+      <c r="CA21" s="42"/>
+      <c r="CB21" s="42"/>
+      <c r="CC21" s="42"/>
+      <c r="CD21" s="42"/>
+      <c r="CE21" s="42"/>
       <c r="CF21" s="42"/>
-      <c r="CG21" s="42"/>
-      <c r="CH21" s="42"/>
-      <c r="CI21" s="42"/>
-      <c r="CJ21" s="42"/>
-      <c r="CK21" s="42"/>
+      <c r="CG21" s="43"/>
+      <c r="CH21" s="43"/>
+      <c r="CI21" s="44"/>
+      <c r="CJ21" s="40"/>
+      <c r="CK21" s="41"/>
       <c r="CL21" s="42"/>
-      <c r="CM21" s="43"/>
-      <c r="CN21" s="43"/>
-      <c r="CO21" s="44"/>
-      <c r="CP21" s="40"/>
-      <c r="CQ21" s="41"/>
+      <c r="CM21" s="42"/>
+      <c r="CN21" s="42"/>
+      <c r="CO21" s="42"/>
+      <c r="CP21" s="42"/>
+      <c r="CQ21" s="42"/>
       <c r="CR21" s="42"/>
       <c r="CS21" s="42"/>
-      <c r="CT21" s="42"/>
-      <c r="CU21" s="42"/>
-      <c r="CV21" s="42"/>
-      <c r="CW21" s="42"/>
-      <c r="CX21" s="42"/>
-      <c r="CY21" s="43"/>
-      <c r="CZ21" s="43"/>
-      <c r="DA21" s="44"/>
-      <c r="DB21" s="40"/>
-      <c r="DC21" s="41"/>
+      <c r="CT21" s="43"/>
+      <c r="CU21" s="43"/>
+      <c r="CV21" s="44"/>
+      <c r="CW21" s="40"/>
+      <c r="CX21" s="41"/>
+      <c r="CY21" s="42"/>
+      <c r="CZ21" s="42"/>
+      <c r="DA21" s="42"/>
+      <c r="DB21" s="42"/>
+      <c r="DC21" s="42"/>
       <c r="DD21" s="42"/>
       <c r="DE21" s="42"/>
       <c r="DF21" s="42"/>
-      <c r="DG21" s="42"/>
-      <c r="DH21" s="42"/>
-      <c r="DI21" s="42"/>
-      <c r="DJ21" s="42"/>
-      <c r="DK21" s="43"/>
-      <c r="DL21" s="43"/>
-      <c r="DM21" s="44"/>
-      <c r="DN21" s="40"/>
-      <c r="DO21" s="41"/>
+      <c r="DG21" s="43"/>
+      <c r="DH21" s="43"/>
+      <c r="DI21" s="44"/>
+      <c r="DJ21" s="40"/>
+      <c r="DK21" s="41"/>
+      <c r="DL21" s="42"/>
+      <c r="DM21" s="42"/>
+      <c r="DN21" s="42"/>
+      <c r="DO21" s="42"/>
       <c r="DP21" s="42"/>
       <c r="DQ21" s="42"/>
       <c r="DR21" s="42"/>
       <c r="DS21" s="42"/>
-      <c r="DT21" s="42"/>
-      <c r="DU21" s="42"/>
-      <c r="DV21" s="42"/>
-      <c r="DW21" s="43"/>
-      <c r="DX21" s="43"/>
-      <c r="DY21" s="44"/>
-      <c r="DZ21" s="40"/>
-      <c r="EA21" s="41"/>
+      <c r="DT21" s="43"/>
+      <c r="DU21" s="43"/>
+      <c r="DV21" s="44"/>
+      <c r="DW21" s="40"/>
+      <c r="DX21" s="41"/>
+      <c r="DY21" s="42"/>
+      <c r="DZ21" s="42"/>
+      <c r="EA21" s="42"/>
       <c r="EB21" s="42"/>
       <c r="EC21" s="42"/>
       <c r="ED21" s="42"/>
       <c r="EE21" s="42"/>
       <c r="EF21" s="42"/>
-      <c r="EG21" s="42"/>
-      <c r="EH21" s="42"/>
-      <c r="EI21" s="43"/>
-      <c r="EJ21" s="43"/>
-      <c r="EK21" s="44"/>
-      <c r="EL21" s="40"/>
-      <c r="EM21" s="41"/>
+      <c r="EG21" s="43"/>
+      <c r="EH21" s="43"/>
+      <c r="EI21" s="44"/>
+      <c r="EJ21" s="40"/>
+      <c r="EK21" s="41"/>
+      <c r="EL21" s="42"/>
+      <c r="EM21" s="42"/>
       <c r="EN21" s="42"/>
       <c r="EO21" s="42"/>
       <c r="EP21" s="42"/>
       <c r="EQ21" s="42"/>
       <c r="ER21" s="42"/>
       <c r="ES21" s="42"/>
-      <c r="ET21" s="42"/>
+      <c r="ET21" s="43"/>
       <c r="EU21" s="43"/>
-      <c r="EV21" s="43"/>
-      <c r="EW21" s="44"/>
-      <c r="EX21" s="40"/>
-      <c r="EY21" s="41"/>
+      <c r="EV21" s="44"/>
+      <c r="EW21" s="40"/>
+      <c r="EX21" s="41"/>
+      <c r="EY21" s="42"/>
       <c r="EZ21" s="42"/>
       <c r="FA21" s="42"/>
       <c r="FB21" s="42"/>
@@ -7574,11 +7907,25 @@
       <c r="FP21" s="42"/>
       <c r="FQ21" s="42"/>
       <c r="FR21" s="42"/>
-      <c r="FS21" s="43"/>
+      <c r="FS21" s="42"/>
       <c r="FT21" s="43"/>
-      <c r="FU21" s="44"/>
+      <c r="FU21" s="43"/>
+      <c r="FV21" s="44"/>
+      <c r="FW21" s="40"/>
+      <c r="FX21" s="41"/>
+      <c r="FY21" s="42"/>
+      <c r="FZ21" s="42"/>
+      <c r="GA21" s="42"/>
+      <c r="GB21" s="42"/>
+      <c r="GC21" s="42"/>
+      <c r="GD21" s="42"/>
+      <c r="GE21" s="42"/>
+      <c r="GF21" s="42"/>
+      <c r="GG21" s="43"/>
+      <c r="GH21" s="43"/>
+      <c r="GI21" s="44"/>
     </row>
-    <row r="22" spans="1:177" s="2" customFormat="1" ht="40.15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:191" s="2" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="73" t="s">
         <v>29</v>
@@ -7592,176 +7939,190 @@
       <c r="G22" s="71"/>
       <c r="H22" s="71"/>
       <c r="I22" s="72"/>
-      <c r="J22" s="64"/>
-      <c r="K22" s="65"/>
-      <c r="L22" s="66"/>
-      <c r="M22" s="66"/>
-      <c r="N22" s="66"/>
-      <c r="O22" s="66"/>
-      <c r="P22" s="66"/>
-      <c r="Q22" s="66"/>
-      <c r="R22" s="66"/>
-      <c r="S22" s="67"/>
-      <c r="T22" s="67"/>
-      <c r="U22" s="68"/>
-      <c r="V22" s="64"/>
-      <c r="W22" s="65"/>
-      <c r="X22" s="66"/>
-      <c r="Y22" s="66"/>
-      <c r="Z22" s="66"/>
-      <c r="AA22" s="66"/>
-      <c r="AB22" s="66"/>
-      <c r="AC22" s="66"/>
-      <c r="AD22" s="66"/>
-      <c r="AE22" s="67"/>
-      <c r="AF22" s="67"/>
-      <c r="AG22" s="68"/>
-      <c r="AH22" s="64"/>
-      <c r="AI22" s="65"/>
-      <c r="AJ22" s="66"/>
-      <c r="AK22" s="66"/>
-      <c r="AL22" s="66"/>
-      <c r="AM22" s="66"/>
-      <c r="AN22" s="66"/>
-      <c r="AO22" s="66"/>
-      <c r="AP22" s="66"/>
-      <c r="AQ22" s="67"/>
-      <c r="AR22" s="67"/>
-      <c r="AS22" s="68"/>
-      <c r="AT22" s="64"/>
-      <c r="AU22" s="65"/>
-      <c r="AV22" s="66"/>
-      <c r="AW22" s="66"/>
-      <c r="AX22" s="66"/>
-      <c r="AY22" s="66"/>
-      <c r="AZ22" s="66"/>
-      <c r="BA22" s="66"/>
-      <c r="BB22" s="66"/>
-      <c r="BC22" s="67"/>
-      <c r="BD22" s="67"/>
-      <c r="BE22" s="68"/>
-      <c r="BF22" s="64"/>
-      <c r="BG22" s="65"/>
-      <c r="BH22" s="66"/>
-      <c r="BI22" s="66"/>
-      <c r="BJ22" s="66"/>
-      <c r="BK22" s="66"/>
-      <c r="BL22" s="66"/>
-      <c r="BM22" s="66"/>
-      <c r="BN22" s="66"/>
-      <c r="BO22" s="67"/>
-      <c r="BP22" s="67"/>
-      <c r="BQ22" s="68"/>
-      <c r="BR22" s="64"/>
-      <c r="BS22" s="65"/>
-      <c r="BT22" s="66"/>
-      <c r="BU22" s="66"/>
-      <c r="BV22" s="66"/>
-      <c r="BW22" s="66"/>
-      <c r="BX22" s="66"/>
-      <c r="BY22" s="66"/>
-      <c r="BZ22" s="66"/>
-      <c r="CA22" s="67"/>
-      <c r="CB22" s="67"/>
-      <c r="CC22" s="68"/>
-      <c r="CD22" s="64"/>
-      <c r="CE22" s="65"/>
-      <c r="CF22" s="66"/>
-      <c r="CG22" s="66"/>
-      <c r="CH22" s="66"/>
-      <c r="CI22" s="66"/>
-      <c r="CJ22" s="66"/>
-      <c r="CK22" s="66"/>
-      <c r="CL22" s="66"/>
-      <c r="CM22" s="67"/>
-      <c r="CN22" s="67"/>
-      <c r="CO22" s="68"/>
-      <c r="CP22" s="64"/>
-      <c r="CQ22" s="65"/>
-      <c r="CR22" s="66"/>
-      <c r="CS22" s="66"/>
-      <c r="CT22" s="66"/>
-      <c r="CU22" s="66"/>
-      <c r="CV22" s="66"/>
-      <c r="CW22" s="66"/>
-      <c r="CX22" s="66"/>
-      <c r="CY22" s="67"/>
-      <c r="CZ22" s="67"/>
-      <c r="DA22" s="68"/>
-      <c r="DB22" s="64"/>
-      <c r="DC22" s="65"/>
-      <c r="DD22" s="66"/>
-      <c r="DE22" s="66"/>
-      <c r="DF22" s="66"/>
-      <c r="DG22" s="66"/>
-      <c r="DH22" s="66"/>
-      <c r="DI22" s="66"/>
-      <c r="DJ22" s="66"/>
-      <c r="DK22" s="67"/>
-      <c r="DL22" s="67"/>
-      <c r="DM22" s="68"/>
-      <c r="DN22" s="64"/>
-      <c r="DO22" s="65"/>
-      <c r="DP22" s="66"/>
-      <c r="DQ22" s="66"/>
-      <c r="DR22" s="66"/>
-      <c r="DS22" s="66"/>
-      <c r="DT22" s="66"/>
-      <c r="DU22" s="66"/>
-      <c r="DV22" s="66"/>
-      <c r="DW22" s="67"/>
-      <c r="DX22" s="67"/>
-      <c r="DY22" s="68"/>
-      <c r="DZ22" s="64"/>
-      <c r="EA22" s="65"/>
-      <c r="EB22" s="66"/>
-      <c r="EC22" s="66"/>
-      <c r="ED22" s="66"/>
-      <c r="EE22" s="66"/>
-      <c r="EF22" s="66"/>
-      <c r="EG22" s="66"/>
-      <c r="EH22" s="66"/>
-      <c r="EI22" s="67"/>
-      <c r="EJ22" s="67"/>
-      <c r="EK22" s="68"/>
-      <c r="EL22" s="64"/>
-      <c r="EM22" s="65"/>
-      <c r="EN22" s="66"/>
-      <c r="EO22" s="66"/>
-      <c r="EP22" s="66"/>
-      <c r="EQ22" s="66"/>
-      <c r="ER22" s="66"/>
-      <c r="ES22" s="66"/>
-      <c r="ET22" s="66"/>
-      <c r="EU22" s="67"/>
-      <c r="EV22" s="67"/>
-      <c r="EW22" s="68"/>
-      <c r="EX22" s="64"/>
-      <c r="EY22" s="65"/>
-      <c r="EZ22" s="66"/>
-      <c r="FA22" s="66"/>
-      <c r="FB22" s="66"/>
-      <c r="FC22" s="66"/>
-      <c r="FD22" s="66"/>
-      <c r="FE22" s="66"/>
-      <c r="FF22" s="66"/>
-      <c r="FG22" s="67"/>
-      <c r="FH22" s="67"/>
-      <c r="FI22" s="68"/>
-      <c r="FJ22" s="64"/>
-      <c r="FK22" s="65"/>
-      <c r="FL22" s="66"/>
-      <c r="FM22" s="66"/>
-      <c r="FN22" s="66"/>
-      <c r="FO22" s="66"/>
-      <c r="FP22" s="66"/>
-      <c r="FQ22" s="66"/>
-      <c r="FR22" s="66"/>
-      <c r="FS22" s="67"/>
-      <c r="FT22" s="67"/>
-      <c r="FU22" s="68"/>
+      <c r="J22" s="58"/>
+      <c r="K22" s="59"/>
+      <c r="L22" s="60"/>
+      <c r="M22" s="60"/>
+      <c r="N22" s="60"/>
+      <c r="O22" s="60"/>
+      <c r="P22" s="60"/>
+      <c r="Q22" s="60"/>
+      <c r="R22" s="60"/>
+      <c r="S22" s="61"/>
+      <c r="T22" s="61"/>
+      <c r="U22" s="61"/>
+      <c r="V22" s="62"/>
+      <c r="W22" s="58"/>
+      <c r="X22" s="59"/>
+      <c r="Y22" s="60"/>
+      <c r="Z22" s="60"/>
+      <c r="AA22" s="60"/>
+      <c r="AB22" s="60"/>
+      <c r="AC22" s="60"/>
+      <c r="AD22" s="60"/>
+      <c r="AE22" s="60"/>
+      <c r="AF22" s="61"/>
+      <c r="AG22" s="61"/>
+      <c r="AH22" s="61"/>
+      <c r="AI22" s="62"/>
+      <c r="AJ22" s="58"/>
+      <c r="AK22" s="59"/>
+      <c r="AL22" s="60"/>
+      <c r="AM22" s="60"/>
+      <c r="AN22" s="60"/>
+      <c r="AO22" s="60"/>
+      <c r="AP22" s="60"/>
+      <c r="AQ22" s="60"/>
+      <c r="AR22" s="60"/>
+      <c r="AS22" s="61"/>
+      <c r="AT22" s="61"/>
+      <c r="AU22" s="61"/>
+      <c r="AV22" s="62"/>
+      <c r="AW22" s="58"/>
+      <c r="AX22" s="59"/>
+      <c r="AY22" s="60"/>
+      <c r="AZ22" s="60"/>
+      <c r="BA22" s="60"/>
+      <c r="BB22" s="60"/>
+      <c r="BC22" s="60"/>
+      <c r="BD22" s="60"/>
+      <c r="BE22" s="60"/>
+      <c r="BF22" s="61"/>
+      <c r="BG22" s="61"/>
+      <c r="BH22" s="61"/>
+      <c r="BI22" s="62"/>
+      <c r="BJ22" s="58"/>
+      <c r="BK22" s="59"/>
+      <c r="BL22" s="60"/>
+      <c r="BM22" s="60"/>
+      <c r="BN22" s="60"/>
+      <c r="BO22" s="60"/>
+      <c r="BP22" s="60"/>
+      <c r="BQ22" s="60"/>
+      <c r="BR22" s="60"/>
+      <c r="BS22" s="61"/>
+      <c r="BT22" s="61"/>
+      <c r="BU22" s="61"/>
+      <c r="BV22" s="62"/>
+      <c r="BW22" s="58"/>
+      <c r="BX22" s="59"/>
+      <c r="BY22" s="60"/>
+      <c r="BZ22" s="60"/>
+      <c r="CA22" s="60"/>
+      <c r="CB22" s="60"/>
+      <c r="CC22" s="60"/>
+      <c r="CD22" s="60"/>
+      <c r="CE22" s="60"/>
+      <c r="CF22" s="61"/>
+      <c r="CG22" s="61"/>
+      <c r="CH22" s="61"/>
+      <c r="CI22" s="62"/>
+      <c r="CJ22" s="58"/>
+      <c r="CK22" s="59"/>
+      <c r="CL22" s="60"/>
+      <c r="CM22" s="60"/>
+      <c r="CN22" s="60"/>
+      <c r="CO22" s="60"/>
+      <c r="CP22" s="60"/>
+      <c r="CQ22" s="60"/>
+      <c r="CR22" s="60"/>
+      <c r="CS22" s="61"/>
+      <c r="CT22" s="61"/>
+      <c r="CU22" s="61"/>
+      <c r="CV22" s="62"/>
+      <c r="CW22" s="58"/>
+      <c r="CX22" s="59"/>
+      <c r="CY22" s="60"/>
+      <c r="CZ22" s="60"/>
+      <c r="DA22" s="60"/>
+      <c r="DB22" s="60"/>
+      <c r="DC22" s="60"/>
+      <c r="DD22" s="60"/>
+      <c r="DE22" s="60"/>
+      <c r="DF22" s="61"/>
+      <c r="DG22" s="61"/>
+      <c r="DH22" s="61"/>
+      <c r="DI22" s="62"/>
+      <c r="DJ22" s="58"/>
+      <c r="DK22" s="59"/>
+      <c r="DL22" s="60"/>
+      <c r="DM22" s="60"/>
+      <c r="DN22" s="60"/>
+      <c r="DO22" s="60"/>
+      <c r="DP22" s="60"/>
+      <c r="DQ22" s="60"/>
+      <c r="DR22" s="60"/>
+      <c r="DS22" s="61"/>
+      <c r="DT22" s="61"/>
+      <c r="DU22" s="61"/>
+      <c r="DV22" s="62"/>
+      <c r="DW22" s="58"/>
+      <c r="DX22" s="59"/>
+      <c r="DY22" s="60"/>
+      <c r="DZ22" s="60"/>
+      <c r="EA22" s="60"/>
+      <c r="EB22" s="60"/>
+      <c r="EC22" s="60"/>
+      <c r="ED22" s="60"/>
+      <c r="EE22" s="60"/>
+      <c r="EF22" s="61"/>
+      <c r="EG22" s="61"/>
+      <c r="EH22" s="61"/>
+      <c r="EI22" s="62"/>
+      <c r="EJ22" s="58"/>
+      <c r="EK22" s="59"/>
+      <c r="EL22" s="60"/>
+      <c r="EM22" s="60"/>
+      <c r="EN22" s="60"/>
+      <c r="EO22" s="60"/>
+      <c r="EP22" s="60"/>
+      <c r="EQ22" s="60"/>
+      <c r="ER22" s="60"/>
+      <c r="ES22" s="61"/>
+      <c r="ET22" s="61"/>
+      <c r="EU22" s="61"/>
+      <c r="EV22" s="62"/>
+      <c r="EW22" s="58"/>
+      <c r="EX22" s="59"/>
+      <c r="EY22" s="60"/>
+      <c r="EZ22" s="60"/>
+      <c r="FA22" s="60"/>
+      <c r="FB22" s="60"/>
+      <c r="FC22" s="60"/>
+      <c r="FD22" s="60"/>
+      <c r="FE22" s="60"/>
+      <c r="FF22" s="61"/>
+      <c r="FG22" s="61"/>
+      <c r="FH22" s="61"/>
+      <c r="FI22" s="62"/>
+      <c r="FJ22" s="58"/>
+      <c r="FK22" s="59"/>
+      <c r="FL22" s="60"/>
+      <c r="FM22" s="60"/>
+      <c r="FN22" s="60"/>
+      <c r="FO22" s="60"/>
+      <c r="FP22" s="60"/>
+      <c r="FQ22" s="60"/>
+      <c r="FR22" s="60"/>
+      <c r="FS22" s="61"/>
+      <c r="FT22" s="61"/>
+      <c r="FU22" s="61"/>
+      <c r="FV22" s="62"/>
+      <c r="FW22" s="58"/>
+      <c r="FX22" s="59"/>
+      <c r="FY22" s="60"/>
+      <c r="FZ22" s="60"/>
+      <c r="GA22" s="60"/>
+      <c r="GB22" s="60"/>
+      <c r="GC22" s="60"/>
+      <c r="GD22" s="60"/>
+      <c r="GE22" s="60"/>
+      <c r="GF22" s="61"/>
+      <c r="GG22" s="61"/>
+      <c r="GH22" s="61"/>
+      <c r="GI22" s="62"/>
     </row>
-    <row r="23" spans="1:177" s="2" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:191" s="2" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="75" t="s">
         <v>21</v>
@@ -7773,204 +8134,218 @@
       <c r="G23" s="75"/>
       <c r="H23" s="75"/>
       <c r="I23" s="75"/>
-      <c r="J23" s="54">
+      <c r="J23" s="63">
         <v>0</v>
       </c>
-      <c r="K23" s="54"/>
-      <c r="L23" s="54"/>
-      <c r="M23" s="54"/>
-      <c r="N23" s="54"/>
-      <c r="O23" s="54"/>
-      <c r="P23" s="54"/>
-      <c r="Q23" s="54"/>
-      <c r="R23" s="54"/>
-      <c r="S23" s="54"/>
-      <c r="T23" s="54"/>
-      <c r="U23" s="54"/>
-      <c r="V23" s="54">
+      <c r="K23" s="63"/>
+      <c r="L23" s="63"/>
+      <c r="M23" s="63"/>
+      <c r="N23" s="63"/>
+      <c r="O23" s="63"/>
+      <c r="P23" s="63"/>
+      <c r="Q23" s="63"/>
+      <c r="R23" s="63"/>
+      <c r="S23" s="63"/>
+      <c r="T23" s="63"/>
+      <c r="U23" s="63"/>
+      <c r="V23" s="63"/>
+      <c r="W23" s="63">
         <v>0</v>
       </c>
-      <c r="W23" s="54"/>
-      <c r="X23" s="54"/>
-      <c r="Y23" s="54"/>
-      <c r="Z23" s="54"/>
-      <c r="AA23" s="54"/>
-      <c r="AB23" s="54"/>
-      <c r="AC23" s="54"/>
-      <c r="AD23" s="54"/>
-      <c r="AE23" s="54"/>
-      <c r="AF23" s="54"/>
-      <c r="AG23" s="54"/>
-      <c r="AH23" s="54">
+      <c r="X23" s="63"/>
+      <c r="Y23" s="63"/>
+      <c r="Z23" s="63"/>
+      <c r="AA23" s="63"/>
+      <c r="AB23" s="63"/>
+      <c r="AC23" s="63"/>
+      <c r="AD23" s="63"/>
+      <c r="AE23" s="63"/>
+      <c r="AF23" s="63"/>
+      <c r="AG23" s="63"/>
+      <c r="AH23" s="63"/>
+      <c r="AI23" s="63"/>
+      <c r="AJ23" s="63">
         <v>0</v>
       </c>
-      <c r="AI23" s="54"/>
-      <c r="AJ23" s="54"/>
-      <c r="AK23" s="54"/>
-      <c r="AL23" s="54"/>
-      <c r="AM23" s="54"/>
-      <c r="AN23" s="54"/>
-      <c r="AO23" s="54"/>
-      <c r="AP23" s="54"/>
-      <c r="AQ23" s="54"/>
-      <c r="AR23" s="54"/>
-      <c r="AS23" s="54"/>
-      <c r="AT23" s="54">
+      <c r="AK23" s="63"/>
+      <c r="AL23" s="63"/>
+      <c r="AM23" s="63"/>
+      <c r="AN23" s="63"/>
+      <c r="AO23" s="63"/>
+      <c r="AP23" s="63"/>
+      <c r="AQ23" s="63"/>
+      <c r="AR23" s="63"/>
+      <c r="AS23" s="63"/>
+      <c r="AT23" s="63"/>
+      <c r="AU23" s="63"/>
+      <c r="AV23" s="63"/>
+      <c r="AW23" s="63">
         <v>0</v>
       </c>
-      <c r="AU23" s="54"/>
-      <c r="AV23" s="54"/>
-      <c r="AW23" s="54"/>
-      <c r="AX23" s="54"/>
-      <c r="AY23" s="54"/>
-      <c r="AZ23" s="54"/>
-      <c r="BA23" s="54"/>
-      <c r="BB23" s="54"/>
-      <c r="BC23" s="54"/>
-      <c r="BD23" s="54"/>
-      <c r="BE23" s="54"/>
-      <c r="BF23" s="54">
+      <c r="AX23" s="63"/>
+      <c r="AY23" s="63"/>
+      <c r="AZ23" s="63"/>
+      <c r="BA23" s="63"/>
+      <c r="BB23" s="63"/>
+      <c r="BC23" s="63"/>
+      <c r="BD23" s="63"/>
+      <c r="BE23" s="63"/>
+      <c r="BF23" s="63"/>
+      <c r="BG23" s="63"/>
+      <c r="BH23" s="63"/>
+      <c r="BI23" s="63"/>
+      <c r="BJ23" s="63">
         <v>0</v>
       </c>
-      <c r="BG23" s="54"/>
-      <c r="BH23" s="54"/>
-      <c r="BI23" s="54"/>
-      <c r="BJ23" s="54"/>
-      <c r="BK23" s="54"/>
-      <c r="BL23" s="54"/>
-      <c r="BM23" s="54"/>
-      <c r="BN23" s="54"/>
-      <c r="BO23" s="54"/>
-      <c r="BP23" s="54"/>
-      <c r="BQ23" s="54"/>
-      <c r="BR23" s="54">
+      <c r="BK23" s="63"/>
+      <c r="BL23" s="63"/>
+      <c r="BM23" s="63"/>
+      <c r="BN23" s="63"/>
+      <c r="BO23" s="63"/>
+      <c r="BP23" s="63"/>
+      <c r="BQ23" s="63"/>
+      <c r="BR23" s="63"/>
+      <c r="BS23" s="63"/>
+      <c r="BT23" s="63"/>
+      <c r="BU23" s="63"/>
+      <c r="BV23" s="63"/>
+      <c r="BW23" s="63">
         <v>0</v>
       </c>
-      <c r="BS23" s="54"/>
-      <c r="BT23" s="54"/>
-      <c r="BU23" s="54"/>
-      <c r="BV23" s="54"/>
-      <c r="BW23" s="54"/>
-      <c r="BX23" s="54"/>
-      <c r="BY23" s="54"/>
-      <c r="BZ23" s="54"/>
-      <c r="CA23" s="54"/>
-      <c r="CB23" s="54"/>
-      <c r="CC23" s="54"/>
-      <c r="CD23" s="54">
+      <c r="BX23" s="63"/>
+      <c r="BY23" s="63"/>
+      <c r="BZ23" s="63"/>
+      <c r="CA23" s="63"/>
+      <c r="CB23" s="63"/>
+      <c r="CC23" s="63"/>
+      <c r="CD23" s="63"/>
+      <c r="CE23" s="63"/>
+      <c r="CF23" s="63"/>
+      <c r="CG23" s="63"/>
+      <c r="CH23" s="63"/>
+      <c r="CI23" s="63"/>
+      <c r="CJ23" s="63">
         <v>0</v>
       </c>
-      <c r="CE23" s="54"/>
-      <c r="CF23" s="54"/>
-      <c r="CG23" s="54"/>
-      <c r="CH23" s="54"/>
-      <c r="CI23" s="54"/>
-      <c r="CJ23" s="54"/>
-      <c r="CK23" s="54"/>
-      <c r="CL23" s="54"/>
-      <c r="CM23" s="54"/>
-      <c r="CN23" s="54"/>
-      <c r="CO23" s="54"/>
-      <c r="CP23" s="54">
+      <c r="CK23" s="63"/>
+      <c r="CL23" s="63"/>
+      <c r="CM23" s="63"/>
+      <c r="CN23" s="63"/>
+      <c r="CO23" s="63"/>
+      <c r="CP23" s="63"/>
+      <c r="CQ23" s="63"/>
+      <c r="CR23" s="63"/>
+      <c r="CS23" s="63"/>
+      <c r="CT23" s="63"/>
+      <c r="CU23" s="63"/>
+      <c r="CV23" s="63"/>
+      <c r="CW23" s="63">
         <v>0</v>
       </c>
-      <c r="CQ23" s="54"/>
-      <c r="CR23" s="54"/>
-      <c r="CS23" s="54"/>
-      <c r="CT23" s="54"/>
-      <c r="CU23" s="54"/>
-      <c r="CV23" s="54"/>
-      <c r="CW23" s="54"/>
-      <c r="CX23" s="54"/>
-      <c r="CY23" s="54"/>
-      <c r="CZ23" s="54"/>
-      <c r="DA23" s="54"/>
-      <c r="DB23" s="54">
+      <c r="CX23" s="63"/>
+      <c r="CY23" s="63"/>
+      <c r="CZ23" s="63"/>
+      <c r="DA23" s="63"/>
+      <c r="DB23" s="63"/>
+      <c r="DC23" s="63"/>
+      <c r="DD23" s="63"/>
+      <c r="DE23" s="63"/>
+      <c r="DF23" s="63"/>
+      <c r="DG23" s="63"/>
+      <c r="DH23" s="63"/>
+      <c r="DI23" s="63"/>
+      <c r="DJ23" s="63">
         <v>0</v>
       </c>
-      <c r="DC23" s="54"/>
-      <c r="DD23" s="54"/>
-      <c r="DE23" s="54"/>
-      <c r="DF23" s="54"/>
-      <c r="DG23" s="54"/>
-      <c r="DH23" s="54"/>
-      <c r="DI23" s="54"/>
-      <c r="DJ23" s="54"/>
-      <c r="DK23" s="54"/>
-      <c r="DL23" s="54"/>
-      <c r="DM23" s="54"/>
-      <c r="DN23" s="54">
+      <c r="DK23" s="63"/>
+      <c r="DL23" s="63"/>
+      <c r="DM23" s="63"/>
+      <c r="DN23" s="63"/>
+      <c r="DO23" s="63"/>
+      <c r="DP23" s="63"/>
+      <c r="DQ23" s="63"/>
+      <c r="DR23" s="63"/>
+      <c r="DS23" s="63"/>
+      <c r="DT23" s="63"/>
+      <c r="DU23" s="63"/>
+      <c r="DV23" s="63"/>
+      <c r="DW23" s="63">
         <v>0</v>
       </c>
-      <c r="DO23" s="54"/>
-      <c r="DP23" s="54"/>
-      <c r="DQ23" s="54"/>
-      <c r="DR23" s="54"/>
-      <c r="DS23" s="54"/>
-      <c r="DT23" s="54"/>
-      <c r="DU23" s="54"/>
-      <c r="DV23" s="54"/>
-      <c r="DW23" s="54"/>
-      <c r="DX23" s="54"/>
-      <c r="DY23" s="54"/>
-      <c r="DZ23" s="54">
+      <c r="DX23" s="63"/>
+      <c r="DY23" s="63"/>
+      <c r="DZ23" s="63"/>
+      <c r="EA23" s="63"/>
+      <c r="EB23" s="63"/>
+      <c r="EC23" s="63"/>
+      <c r="ED23" s="63"/>
+      <c r="EE23" s="63"/>
+      <c r="EF23" s="63"/>
+      <c r="EG23" s="63"/>
+      <c r="EH23" s="63"/>
+      <c r="EI23" s="63"/>
+      <c r="EJ23" s="63">
         <v>0</v>
       </c>
-      <c r="EA23" s="54"/>
-      <c r="EB23" s="54"/>
-      <c r="EC23" s="54"/>
-      <c r="ED23" s="54"/>
-      <c r="EE23" s="54"/>
-      <c r="EF23" s="54"/>
-      <c r="EG23" s="54"/>
-      <c r="EH23" s="54"/>
-      <c r="EI23" s="54"/>
-      <c r="EJ23" s="54"/>
-      <c r="EK23" s="54"/>
-      <c r="EL23" s="54">
+      <c r="EK23" s="63"/>
+      <c r="EL23" s="63"/>
+      <c r="EM23" s="63"/>
+      <c r="EN23" s="63"/>
+      <c r="EO23" s="63"/>
+      <c r="EP23" s="63"/>
+      <c r="EQ23" s="63"/>
+      <c r="ER23" s="63"/>
+      <c r="ES23" s="63"/>
+      <c r="ET23" s="63"/>
+      <c r="EU23" s="63"/>
+      <c r="EV23" s="63"/>
+      <c r="EW23" s="63">
         <v>0</v>
       </c>
-      <c r="EM23" s="54"/>
-      <c r="EN23" s="54"/>
-      <c r="EO23" s="54"/>
-      <c r="EP23" s="54"/>
-      <c r="EQ23" s="54"/>
-      <c r="ER23" s="54"/>
-      <c r="ES23" s="54"/>
-      <c r="ET23" s="54"/>
-      <c r="EU23" s="54"/>
-      <c r="EV23" s="54"/>
-      <c r="EW23" s="54"/>
-      <c r="EX23" s="54">
+      <c r="EX23" s="63"/>
+      <c r="EY23" s="63"/>
+      <c r="EZ23" s="63"/>
+      <c r="FA23" s="63"/>
+      <c r="FB23" s="63"/>
+      <c r="FC23" s="63"/>
+      <c r="FD23" s="63"/>
+      <c r="FE23" s="63"/>
+      <c r="FF23" s="63"/>
+      <c r="FG23" s="63"/>
+      <c r="FH23" s="63"/>
+      <c r="FI23" s="63"/>
+      <c r="FJ23" s="63">
         <v>0</v>
       </c>
-      <c r="EY23" s="54"/>
-      <c r="EZ23" s="54"/>
-      <c r="FA23" s="54"/>
-      <c r="FB23" s="54"/>
-      <c r="FC23" s="54"/>
-      <c r="FD23" s="54"/>
-      <c r="FE23" s="54"/>
-      <c r="FF23" s="54"/>
-      <c r="FG23" s="54"/>
-      <c r="FH23" s="54"/>
-      <c r="FI23" s="54"/>
-      <c r="FJ23" s="54">
+      <c r="FK23" s="63"/>
+      <c r="FL23" s="63"/>
+      <c r="FM23" s="63"/>
+      <c r="FN23" s="63"/>
+      <c r="FO23" s="63"/>
+      <c r="FP23" s="63"/>
+      <c r="FQ23" s="63"/>
+      <c r="FR23" s="63"/>
+      <c r="FS23" s="63"/>
+      <c r="FT23" s="63"/>
+      <c r="FU23" s="63"/>
+      <c r="FV23" s="63"/>
+      <c r="FW23" s="63">
         <v>0</v>
       </c>
-      <c r="FK23" s="54"/>
-      <c r="FL23" s="54"/>
-      <c r="FM23" s="54"/>
-      <c r="FN23" s="54"/>
-      <c r="FO23" s="54"/>
-      <c r="FP23" s="54"/>
-      <c r="FQ23" s="54"/>
-      <c r="FR23" s="54"/>
-      <c r="FS23" s="54"/>
-      <c r="FT23" s="54"/>
-      <c r="FU23" s="54"/>
+      <c r="FX23" s="63"/>
+      <c r="FY23" s="63"/>
+      <c r="FZ23" s="63"/>
+      <c r="GA23" s="63"/>
+      <c r="GB23" s="63"/>
+      <c r="GC23" s="63"/>
+      <c r="GD23" s="63"/>
+      <c r="GE23" s="63"/>
+      <c r="GF23" s="63"/>
+      <c r="GG23" s="63"/>
+      <c r="GH23" s="63"/>
+      <c r="GI23" s="63"/>
     </row>
-    <row r="24" spans="1:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
@@ -8147,8 +8522,22 @@
       <c r="FS24" s="5"/>
       <c r="FT24" s="5"/>
       <c r="FU24" s="5"/>
+      <c r="FV24" s="5"/>
+      <c r="FW24" s="5"/>
+      <c r="FX24" s="5"/>
+      <c r="FY24" s="5"/>
+      <c r="FZ24" s="5"/>
+      <c r="GA24" s="5"/>
+      <c r="GB24" s="5"/>
+      <c r="GC24" s="5"/>
+      <c r="GD24" s="5"/>
+      <c r="GE24" s="5"/>
+      <c r="GF24" s="5"/>
+      <c r="GG24" s="5"/>
+      <c r="GH24" s="5"/>
+      <c r="GI24" s="5"/>
     </row>
-    <row r="25" spans="1:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
@@ -8325,8 +8714,22 @@
       <c r="FS25" s="5"/>
       <c r="FT25" s="5"/>
       <c r="FU25" s="5"/>
+      <c r="FV25" s="5"/>
+      <c r="FW25" s="5"/>
+      <c r="FX25" s="5"/>
+      <c r="FY25" s="5"/>
+      <c r="FZ25" s="5"/>
+      <c r="GA25" s="5"/>
+      <c r="GB25" s="5"/>
+      <c r="GC25" s="5"/>
+      <c r="GD25" s="5"/>
+      <c r="GE25" s="5"/>
+      <c r="GF25" s="5"/>
+      <c r="GG25" s="5"/>
+      <c r="GH25" s="5"/>
+      <c r="GI25" s="5"/>
     </row>
-    <row r="26" spans="1:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4"/>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
@@ -8503,8 +8906,22 @@
       <c r="FS26" s="5"/>
       <c r="FT26" s="5"/>
       <c r="FU26" s="5"/>
+      <c r="FV26" s="5"/>
+      <c r="FW26" s="5"/>
+      <c r="FX26" s="5"/>
+      <c r="FY26" s="5"/>
+      <c r="FZ26" s="5"/>
+      <c r="GA26" s="5"/>
+      <c r="GB26" s="5"/>
+      <c r="GC26" s="5"/>
+      <c r="GD26" s="5"/>
+      <c r="GE26" s="5"/>
+      <c r="GF26" s="5"/>
+      <c r="GG26" s="5"/>
+      <c r="GH26" s="5"/>
+      <c r="GI26" s="5"/>
     </row>
-    <row r="27" spans="1:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4"/>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
@@ -8681,8 +9098,22 @@
       <c r="FS27" s="5"/>
       <c r="FT27" s="5"/>
       <c r="FU27" s="5"/>
+      <c r="FV27" s="5"/>
+      <c r="FW27" s="5"/>
+      <c r="FX27" s="5"/>
+      <c r="FY27" s="5"/>
+      <c r="FZ27" s="5"/>
+      <c r="GA27" s="5"/>
+      <c r="GB27" s="5"/>
+      <c r="GC27" s="5"/>
+      <c r="GD27" s="5"/>
+      <c r="GE27" s="5"/>
+      <c r="GF27" s="5"/>
+      <c r="GG27" s="5"/>
+      <c r="GH27" s="5"/>
+      <c r="GI27" s="5"/>
     </row>
-    <row r="28" spans="1:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4"/>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
@@ -8859,8 +9290,22 @@
       <c r="FS28" s="5"/>
       <c r="FT28" s="5"/>
       <c r="FU28" s="5"/>
+      <c r="FV28" s="5"/>
+      <c r="FW28" s="5"/>
+      <c r="FX28" s="5"/>
+      <c r="FY28" s="5"/>
+      <c r="FZ28" s="5"/>
+      <c r="GA28" s="5"/>
+      <c r="GB28" s="5"/>
+      <c r="GC28" s="5"/>
+      <c r="GD28" s="5"/>
+      <c r="GE28" s="5"/>
+      <c r="GF28" s="5"/>
+      <c r="GG28" s="5"/>
+      <c r="GH28" s="5"/>
+      <c r="GI28" s="5"/>
     </row>
-    <row r="29" spans="1:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B29" s="4"/>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
@@ -9037,8 +9482,22 @@
       <c r="FS29" s="5"/>
       <c r="FT29" s="5"/>
       <c r="FU29" s="5"/>
+      <c r="FV29" s="5"/>
+      <c r="FW29" s="5"/>
+      <c r="FX29" s="5"/>
+      <c r="FY29" s="5"/>
+      <c r="FZ29" s="5"/>
+      <c r="GA29" s="5"/>
+      <c r="GB29" s="5"/>
+      <c r="GC29" s="5"/>
+      <c r="GD29" s="5"/>
+      <c r="GE29" s="5"/>
+      <c r="GF29" s="5"/>
+      <c r="GG29" s="5"/>
+      <c r="GH29" s="5"/>
+      <c r="GI29" s="5"/>
     </row>
-    <row r="30" spans="1:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B30" s="4"/>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
@@ -9215,8 +9674,22 @@
       <c r="FS30" s="5"/>
       <c r="FT30" s="5"/>
       <c r="FU30" s="5"/>
+      <c r="FV30" s="5"/>
+      <c r="FW30" s="5"/>
+      <c r="FX30" s="5"/>
+      <c r="FY30" s="5"/>
+      <c r="FZ30" s="5"/>
+      <c r="GA30" s="5"/>
+      <c r="GB30" s="5"/>
+      <c r="GC30" s="5"/>
+      <c r="GD30" s="5"/>
+      <c r="GE30" s="5"/>
+      <c r="GF30" s="5"/>
+      <c r="GG30" s="5"/>
+      <c r="GH30" s="5"/>
+      <c r="GI30" s="5"/>
     </row>
-    <row r="31" spans="1:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B31" s="4"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
@@ -9393,8 +9866,22 @@
       <c r="FS31" s="5"/>
       <c r="FT31" s="5"/>
       <c r="FU31" s="5"/>
+      <c r="FV31" s="5"/>
+      <c r="FW31" s="5"/>
+      <c r="FX31" s="5"/>
+      <c r="FY31" s="5"/>
+      <c r="FZ31" s="5"/>
+      <c r="GA31" s="5"/>
+      <c r="GB31" s="5"/>
+      <c r="GC31" s="5"/>
+      <c r="GD31" s="5"/>
+      <c r="GE31" s="5"/>
+      <c r="GF31" s="5"/>
+      <c r="GG31" s="5"/>
+      <c r="GH31" s="5"/>
+      <c r="GI31" s="5"/>
     </row>
-    <row r="32" spans="1:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B32" s="4"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -9571,8 +10058,22 @@
       <c r="FS32" s="5"/>
       <c r="FT32" s="5"/>
       <c r="FU32" s="5"/>
+      <c r="FV32" s="5"/>
+      <c r="FW32" s="5"/>
+      <c r="FX32" s="5"/>
+      <c r="FY32" s="5"/>
+      <c r="FZ32" s="5"/>
+      <c r="GA32" s="5"/>
+      <c r="GB32" s="5"/>
+      <c r="GC32" s="5"/>
+      <c r="GD32" s="5"/>
+      <c r="GE32" s="5"/>
+      <c r="GF32" s="5"/>
+      <c r="GG32" s="5"/>
+      <c r="GH32" s="5"/>
+      <c r="GI32" s="5"/>
     </row>
-    <row r="33" spans="2:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B33" s="4"/>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
@@ -9749,8 +10250,22 @@
       <c r="FS33" s="5"/>
       <c r="FT33" s="5"/>
       <c r="FU33" s="5"/>
+      <c r="FV33" s="5"/>
+      <c r="FW33" s="5"/>
+      <c r="FX33" s="5"/>
+      <c r="FY33" s="5"/>
+      <c r="FZ33" s="5"/>
+      <c r="GA33" s="5"/>
+      <c r="GB33" s="5"/>
+      <c r="GC33" s="5"/>
+      <c r="GD33" s="5"/>
+      <c r="GE33" s="5"/>
+      <c r="GF33" s="5"/>
+      <c r="GG33" s="5"/>
+      <c r="GH33" s="5"/>
+      <c r="GI33" s="5"/>
     </row>
-    <row r="34" spans="2:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B34" s="4"/>
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
@@ -9927,8 +10442,22 @@
       <c r="FS34" s="5"/>
       <c r="FT34" s="5"/>
       <c r="FU34" s="5"/>
+      <c r="FV34" s="5"/>
+      <c r="FW34" s="5"/>
+      <c r="FX34" s="5"/>
+      <c r="FY34" s="5"/>
+      <c r="FZ34" s="5"/>
+      <c r="GA34" s="5"/>
+      <c r="GB34" s="5"/>
+      <c r="GC34" s="5"/>
+      <c r="GD34" s="5"/>
+      <c r="GE34" s="5"/>
+      <c r="GF34" s="5"/>
+      <c r="GG34" s="5"/>
+      <c r="GH34" s="5"/>
+      <c r="GI34" s="5"/>
     </row>
-    <row r="35" spans="2:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B35" s="4"/>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
@@ -10105,8 +10634,22 @@
       <c r="FS35" s="5"/>
       <c r="FT35" s="5"/>
       <c r="FU35" s="5"/>
+      <c r="FV35" s="5"/>
+      <c r="FW35" s="5"/>
+      <c r="FX35" s="5"/>
+      <c r="FY35" s="5"/>
+      <c r="FZ35" s="5"/>
+      <c r="GA35" s="5"/>
+      <c r="GB35" s="5"/>
+      <c r="GC35" s="5"/>
+      <c r="GD35" s="5"/>
+      <c r="GE35" s="5"/>
+      <c r="GF35" s="5"/>
+      <c r="GG35" s="5"/>
+      <c r="GH35" s="5"/>
+      <c r="GI35" s="5"/>
     </row>
-    <row r="36" spans="2:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B36" s="4"/>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
@@ -10283,8 +10826,22 @@
       <c r="FS36" s="5"/>
       <c r="FT36" s="5"/>
       <c r="FU36" s="5"/>
+      <c r="FV36" s="5"/>
+      <c r="FW36" s="5"/>
+      <c r="FX36" s="5"/>
+      <c r="FY36" s="5"/>
+      <c r="FZ36" s="5"/>
+      <c r="GA36" s="5"/>
+      <c r="GB36" s="5"/>
+      <c r="GC36" s="5"/>
+      <c r="GD36" s="5"/>
+      <c r="GE36" s="5"/>
+      <c r="GF36" s="5"/>
+      <c r="GG36" s="5"/>
+      <c r="GH36" s="5"/>
+      <c r="GI36" s="5"/>
     </row>
-    <row r="37" spans="2:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B37" s="4"/>
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
@@ -10461,8 +11018,22 @@
       <c r="FS37" s="5"/>
       <c r="FT37" s="5"/>
       <c r="FU37" s="5"/>
+      <c r="FV37" s="5"/>
+      <c r="FW37" s="5"/>
+      <c r="FX37" s="5"/>
+      <c r="FY37" s="5"/>
+      <c r="FZ37" s="5"/>
+      <c r="GA37" s="5"/>
+      <c r="GB37" s="5"/>
+      <c r="GC37" s="5"/>
+      <c r="GD37" s="5"/>
+      <c r="GE37" s="5"/>
+      <c r="GF37" s="5"/>
+      <c r="GG37" s="5"/>
+      <c r="GH37" s="5"/>
+      <c r="GI37" s="5"/>
     </row>
-    <row r="38" spans="2:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B38" s="4"/>
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
@@ -10639,8 +11210,22 @@
       <c r="FS38" s="5"/>
       <c r="FT38" s="5"/>
       <c r="FU38" s="5"/>
+      <c r="FV38" s="5"/>
+      <c r="FW38" s="5"/>
+      <c r="FX38" s="5"/>
+      <c r="FY38" s="5"/>
+      <c r="FZ38" s="5"/>
+      <c r="GA38" s="5"/>
+      <c r="GB38" s="5"/>
+      <c r="GC38" s="5"/>
+      <c r="GD38" s="5"/>
+      <c r="GE38" s="5"/>
+      <c r="GF38" s="5"/>
+      <c r="GG38" s="5"/>
+      <c r="GH38" s="5"/>
+      <c r="GI38" s="5"/>
     </row>
-    <row r="39" spans="2:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B39" s="4"/>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
@@ -10817,8 +11402,22 @@
       <c r="FS39" s="5"/>
       <c r="FT39" s="5"/>
       <c r="FU39" s="5"/>
+      <c r="FV39" s="5"/>
+      <c r="FW39" s="5"/>
+      <c r="FX39" s="5"/>
+      <c r="FY39" s="5"/>
+      <c r="FZ39" s="5"/>
+      <c r="GA39" s="5"/>
+      <c r="GB39" s="5"/>
+      <c r="GC39" s="5"/>
+      <c r="GD39" s="5"/>
+      <c r="GE39" s="5"/>
+      <c r="GF39" s="5"/>
+      <c r="GG39" s="5"/>
+      <c r="GH39" s="5"/>
+      <c r="GI39" s="5"/>
     </row>
-    <row r="40" spans="2:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B40" s="4"/>
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
@@ -10995,8 +11594,22 @@
       <c r="FS40" s="5"/>
       <c r="FT40" s="5"/>
       <c r="FU40" s="5"/>
+      <c r="FV40" s="5"/>
+      <c r="FW40" s="5"/>
+      <c r="FX40" s="5"/>
+      <c r="FY40" s="5"/>
+      <c r="FZ40" s="5"/>
+      <c r="GA40" s="5"/>
+      <c r="GB40" s="5"/>
+      <c r="GC40" s="5"/>
+      <c r="GD40" s="5"/>
+      <c r="GE40" s="5"/>
+      <c r="GF40" s="5"/>
+      <c r="GG40" s="5"/>
+      <c r="GH40" s="5"/>
+      <c r="GI40" s="5"/>
     </row>
-    <row r="41" spans="2:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B41" s="4"/>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
@@ -11173,8 +11786,22 @@
       <c r="FS41" s="5"/>
       <c r="FT41" s="5"/>
       <c r="FU41" s="5"/>
+      <c r="FV41" s="5"/>
+      <c r="FW41" s="5"/>
+      <c r="FX41" s="5"/>
+      <c r="FY41" s="5"/>
+      <c r="FZ41" s="5"/>
+      <c r="GA41" s="5"/>
+      <c r="GB41" s="5"/>
+      <c r="GC41" s="5"/>
+      <c r="GD41" s="5"/>
+      <c r="GE41" s="5"/>
+      <c r="GF41" s="5"/>
+      <c r="GG41" s="5"/>
+      <c r="GH41" s="5"/>
+      <c r="GI41" s="5"/>
     </row>
-    <row r="42" spans="2:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B42" s="4"/>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
@@ -11351,8 +11978,22 @@
       <c r="FS42" s="5"/>
       <c r="FT42" s="5"/>
       <c r="FU42" s="5"/>
+      <c r="FV42" s="5"/>
+      <c r="FW42" s="5"/>
+      <c r="FX42" s="5"/>
+      <c r="FY42" s="5"/>
+      <c r="FZ42" s="5"/>
+      <c r="GA42" s="5"/>
+      <c r="GB42" s="5"/>
+      <c r="GC42" s="5"/>
+      <c r="GD42" s="5"/>
+      <c r="GE42" s="5"/>
+      <c r="GF42" s="5"/>
+      <c r="GG42" s="5"/>
+      <c r="GH42" s="5"/>
+      <c r="GI42" s="5"/>
     </row>
-    <row r="43" spans="2:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B43" s="4"/>
       <c r="C43" s="5"/>
       <c r="D43" s="5"/>
@@ -11529,8 +12170,22 @@
       <c r="FS43" s="5"/>
       <c r="FT43" s="5"/>
       <c r="FU43" s="5"/>
+      <c r="FV43" s="5"/>
+      <c r="FW43" s="5"/>
+      <c r="FX43" s="5"/>
+      <c r="FY43" s="5"/>
+      <c r="FZ43" s="5"/>
+      <c r="GA43" s="5"/>
+      <c r="GB43" s="5"/>
+      <c r="GC43" s="5"/>
+      <c r="GD43" s="5"/>
+      <c r="GE43" s="5"/>
+      <c r="GF43" s="5"/>
+      <c r="GG43" s="5"/>
+      <c r="GH43" s="5"/>
+      <c r="GI43" s="5"/>
     </row>
-    <row r="44" spans="2:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B44" s="4"/>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
@@ -11707,8 +12362,22 @@
       <c r="FS44" s="5"/>
       <c r="FT44" s="5"/>
       <c r="FU44" s="5"/>
+      <c r="FV44" s="5"/>
+      <c r="FW44" s="5"/>
+      <c r="FX44" s="5"/>
+      <c r="FY44" s="5"/>
+      <c r="FZ44" s="5"/>
+      <c r="GA44" s="5"/>
+      <c r="GB44" s="5"/>
+      <c r="GC44" s="5"/>
+      <c r="GD44" s="5"/>
+      <c r="GE44" s="5"/>
+      <c r="GF44" s="5"/>
+      <c r="GG44" s="5"/>
+      <c r="GH44" s="5"/>
+      <c r="GI44" s="5"/>
     </row>
-    <row r="45" spans="2:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B45" s="4"/>
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
@@ -11885,8 +12554,22 @@
       <c r="FS45" s="5"/>
       <c r="FT45" s="5"/>
       <c r="FU45" s="5"/>
+      <c r="FV45" s="5"/>
+      <c r="FW45" s="5"/>
+      <c r="FX45" s="5"/>
+      <c r="FY45" s="5"/>
+      <c r="FZ45" s="5"/>
+      <c r="GA45" s="5"/>
+      <c r="GB45" s="5"/>
+      <c r="GC45" s="5"/>
+      <c r="GD45" s="5"/>
+      <c r="GE45" s="5"/>
+      <c r="GF45" s="5"/>
+      <c r="GG45" s="5"/>
+      <c r="GH45" s="5"/>
+      <c r="GI45" s="5"/>
     </row>
-    <row r="46" spans="2:177" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B46" s="4"/>
       <c r="C46" s="5"/>
       <c r="D46" s="5"/>
@@ -12063,57 +12746,71 @@
       <c r="FS46" s="5"/>
       <c r="FT46" s="5"/>
       <c r="FU46" s="5"/>
+      <c r="FV46" s="5"/>
+      <c r="FW46" s="5"/>
+      <c r="FX46" s="5"/>
+      <c r="FY46" s="5"/>
+      <c r="FZ46" s="5"/>
+      <c r="GA46" s="5"/>
+      <c r="GB46" s="5"/>
+      <c r="GC46" s="5"/>
+      <c r="GD46" s="5"/>
+      <c r="GE46" s="5"/>
+      <c r="GF46" s="5"/>
+      <c r="GG46" s="5"/>
+      <c r="GH46" s="5"/>
+      <c r="GI46" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="FJ2:FU2"/>
-    <mergeCell ref="FJ22:FU22"/>
-    <mergeCell ref="FJ23:FU23"/>
-    <mergeCell ref="DB22:DM22"/>
-    <mergeCell ref="DB2:DM2"/>
-    <mergeCell ref="CP2:DA2"/>
-    <mergeCell ref="BF2:BQ2"/>
-    <mergeCell ref="V2:AG2"/>
-    <mergeCell ref="CP22:DA22"/>
-    <mergeCell ref="CD2:CO2"/>
-    <mergeCell ref="CD22:CO22"/>
-    <mergeCell ref="BR2:CC2"/>
-    <mergeCell ref="BR22:CC22"/>
-    <mergeCell ref="BF22:BQ22"/>
-    <mergeCell ref="AT2:BE2"/>
-    <mergeCell ref="AT22:BE22"/>
-    <mergeCell ref="AH2:AS2"/>
-    <mergeCell ref="AH22:AS22"/>
-    <mergeCell ref="V22:AG22"/>
-    <mergeCell ref="DN22:DY22"/>
-    <mergeCell ref="DZ22:EK22"/>
-    <mergeCell ref="EL22:EW22"/>
-    <mergeCell ref="EL2:EW2"/>
-    <mergeCell ref="EX2:FI2"/>
-    <mergeCell ref="EX22:FI22"/>
-    <mergeCell ref="DZ2:EK2"/>
-    <mergeCell ref="DN2:DY2"/>
+    <mergeCell ref="BJ23:BV23"/>
+    <mergeCell ref="BW23:CI23"/>
+    <mergeCell ref="CJ23:CV23"/>
+    <mergeCell ref="FJ23:FV23"/>
+    <mergeCell ref="CW23:DI23"/>
+    <mergeCell ref="DJ23:DV23"/>
+    <mergeCell ref="DW23:EI23"/>
+    <mergeCell ref="EJ23:EV23"/>
+    <mergeCell ref="EW23:FI23"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="C2:C3"/>
-    <mergeCell ref="AH23:AS23"/>
-    <mergeCell ref="AT23:BE23"/>
-    <mergeCell ref="J2:U2"/>
-    <mergeCell ref="J22:U22"/>
-    <mergeCell ref="J23:U23"/>
-    <mergeCell ref="V23:AG23"/>
+    <mergeCell ref="AJ23:AV23"/>
+    <mergeCell ref="AW23:BI23"/>
+    <mergeCell ref="J2:V2"/>
+    <mergeCell ref="J22:V22"/>
+    <mergeCell ref="J23:V23"/>
+    <mergeCell ref="W23:AI23"/>
     <mergeCell ref="D2:I2"/>
     <mergeCell ref="D22:I22"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="B23:I23"/>
-    <mergeCell ref="BF23:BQ23"/>
-    <mergeCell ref="BR23:CC23"/>
-    <mergeCell ref="CD23:CO23"/>
-    <mergeCell ref="EX23:FI23"/>
-    <mergeCell ref="CP23:DA23"/>
-    <mergeCell ref="DB23:DM23"/>
-    <mergeCell ref="DN23:DY23"/>
-    <mergeCell ref="DZ23:EK23"/>
-    <mergeCell ref="EL23:EW23"/>
+    <mergeCell ref="CW2:DI2"/>
+    <mergeCell ref="BJ2:BV2"/>
+    <mergeCell ref="W2:AI2"/>
+    <mergeCell ref="CW22:DI22"/>
+    <mergeCell ref="CJ2:CV2"/>
+    <mergeCell ref="CJ22:CV22"/>
+    <mergeCell ref="BW2:CI2"/>
+    <mergeCell ref="BW22:CI22"/>
+    <mergeCell ref="BJ22:BV22"/>
+    <mergeCell ref="AW2:BI2"/>
+    <mergeCell ref="AW22:BI22"/>
+    <mergeCell ref="AJ2:AV2"/>
+    <mergeCell ref="AJ22:AV22"/>
+    <mergeCell ref="W22:AI22"/>
+    <mergeCell ref="FW2:GI2"/>
+    <mergeCell ref="FW22:GI22"/>
+    <mergeCell ref="FW23:GI23"/>
+    <mergeCell ref="DJ22:DV22"/>
+    <mergeCell ref="DJ2:DV2"/>
+    <mergeCell ref="DW22:EI22"/>
+    <mergeCell ref="EJ22:EV22"/>
+    <mergeCell ref="EW22:FI22"/>
+    <mergeCell ref="EW2:FI2"/>
+    <mergeCell ref="FJ2:FV2"/>
+    <mergeCell ref="FJ22:FV22"/>
+    <mergeCell ref="EJ2:EV2"/>
+    <mergeCell ref="DW2:EI2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="62" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/activity/M01A02/M01A02_PuntoEstudioCaudales.xlsx
+++ b/activity/M01A02/M01A02_PuntoEstudioCaudales.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29304"/>
   <workbookPr updateLinks="never" codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBD15384-417E-4DFF-9299-A330A0D579E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37373CFC-828A-4AA1-BE3A-6988156E0877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Calificacion" sheetId="12" r:id="rId1"/>
@@ -276,9 +276,6 @@
     <t>Calificación 1.2. Modelación hidrológica para obtención de caudales de diseño e hidrogramas para tránsito de crecientes</t>
   </si>
   <si>
-    <t>Crear la capa geográfica shapefile de localización de puntos de estudio.</t>
-  </si>
-  <si>
     <t>Libro R.HCMC.PuntoEstudio.xlsx</t>
   </si>
   <si>
@@ -293,14 +290,17 @@
   <si>
     <t>Q Ecológico, m³/s</t>
   </si>
+  <si>
+    <t>Crear la capa geográfica shapefile de localización de puntos de estudio. R.HCMC.PuntoEstudio.shp</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="31" x14ac:knownFonts="1">
@@ -1116,7 +1116,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -1159,10 +1159,10 @@
     <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1341,7 +1341,25 @@
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="2" fontId="11" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1366,24 +1384,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="2" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1928,6 +1928,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1935,7 +1936,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2857,23 +2857,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EF50BAE-D7A1-4B9B-8511-69070389923C}">
   <sheetPr codeName="Hoja2"/>
   <dimension ref="B1:F21"/>
-  <sheetFormatPr defaultColWidth="11.33203125" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.33203125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="17" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" style="17" customWidth="1"/>
-    <col min="3" max="4" width="11.44140625" style="17" customWidth="1"/>
-    <col min="5" max="5" width="12.77734375" style="17" customWidth="1"/>
-    <col min="6" max="6" width="11.44140625" style="17" customWidth="1"/>
+    <col min="3" max="4" width="11.46484375" style="17" customWidth="1"/>
+    <col min="5" max="5" width="12.796875" style="17" customWidth="1"/>
+    <col min="6" max="6" width="11.46484375" style="17" customWidth="1"/>
     <col min="7" max="7" width="2.6640625" style="17" customWidth="1"/>
     <col min="8" max="16384" width="11.33203125" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:6" x14ac:dyDescent="0.45">
       <c r="F1" s="35" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="51" t="s">
         <v>61</v>
       </c>
@@ -2882,14 +2882,14 @@
       <c r="E2" s="51"/>
       <c r="F2" s="51"/>
     </row>
-    <row r="3" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B3" s="52"/>
       <c r="C3" s="52"/>
       <c r="D3" s="52"/>
       <c r="E3" s="52"/>
       <c r="F3" s="52"/>
     </row>
-    <row r="4" spans="2:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="29" t="s">
         <v>22</v>
       </c>
@@ -2906,7 +2906,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B5" s="18" t="s">
         <v>45</v>
       </c>
@@ -2923,7 +2923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B6" s="18" t="s">
         <v>46</v>
       </c>
@@ -2940,7 +2940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B7" s="18" t="s">
         <v>47</v>
       </c>
@@ -2957,7 +2957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B8" s="18" t="s">
         <v>48</v>
       </c>
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B9" s="18" t="s">
         <v>49</v>
       </c>
@@ -2991,7 +2991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B10" s="18" t="s">
         <v>52</v>
       </c>
@@ -3008,7 +3008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B11" s="18" t="s">
         <v>53</v>
       </c>
@@ -3025,7 +3025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B12" s="18" t="s">
         <v>54</v>
       </c>
@@ -3042,7 +3042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B13" s="18" t="s">
         <v>55</v>
       </c>
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B14" s="18" t="s">
         <v>56</v>
       </c>
@@ -3076,7 +3076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B15" s="18" t="s">
         <v>57</v>
       </c>
@@ -3093,7 +3093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B16" s="18" t="s">
         <v>58</v>
       </c>
@@ -3110,7 +3110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B17" s="18" t="s">
         <v>59</v>
       </c>
@@ -3127,9 +3127,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B18" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C18" s="34">
         <v>5</v>
@@ -3144,7 +3144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B19" s="53" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F1," en GitHub."))</f>
         <v>Ir a actividad M01A02 en GitHub.</v>
@@ -3154,14 +3154,14 @@
       <c r="E19" s="53"/>
       <c r="F19" s="53"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B20" s="53"/>
       <c r="C20" s="53"/>
       <c r="D20" s="53"/>
       <c r="E20" s="53"/>
       <c r="F20" s="53"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B21" s="32"/>
       <c r="C21" s="32"/>
       <c r="D21" s="32"/>
@@ -3187,91 +3187,91 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:GI46"/>
-  <sheetFormatPr defaultColWidth="11.33203125" defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.33203125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="6" customWidth="1"/>
     <col min="2" max="2" width="16.33203125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="46.109375" style="5" customWidth="1"/>
+    <col min="3" max="3" width="46.1328125" style="5" customWidth="1"/>
     <col min="4" max="4" width="7.33203125" style="5" customWidth="1"/>
     <col min="5" max="6" width="4.6640625" style="5" customWidth="1"/>
     <col min="7" max="8" width="10" style="5" customWidth="1"/>
-    <col min="9" max="9" width="6.5546875" style="5" customWidth="1"/>
+    <col min="9" max="9" width="6.53125" style="5" customWidth="1"/>
     <col min="10" max="10" width="9.6640625" style="5" customWidth="1"/>
-    <col min="11" max="11" width="8.5546875" style="5" customWidth="1"/>
-    <col min="12" max="12" width="10.109375" style="5" customWidth="1"/>
-    <col min="13" max="18" width="8.5546875" style="5" customWidth="1"/>
-    <col min="19" max="19" width="11.109375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="8.53125" style="5" customWidth="1"/>
+    <col min="12" max="12" width="10.1328125" style="5" customWidth="1"/>
+    <col min="13" max="18" width="8.53125" style="5" customWidth="1"/>
+    <col min="19" max="19" width="11.1328125" style="5" customWidth="1"/>
     <col min="20" max="21" width="10" style="5" customWidth="1"/>
-    <col min="22" max="22" width="10.109375" style="5" customWidth="1"/>
-    <col min="23" max="24" width="8.5546875" style="5" customWidth="1"/>
-    <col min="25" max="31" width="10.109375" style="5" customWidth="1"/>
-    <col min="32" max="32" width="11.109375" style="5" customWidth="1"/>
+    <col min="22" max="22" width="10.1328125" style="5" customWidth="1"/>
+    <col min="23" max="24" width="8.53125" style="5" customWidth="1"/>
+    <col min="25" max="31" width="10.1328125" style="5" customWidth="1"/>
+    <col min="32" max="32" width="11.1328125" style="5" customWidth="1"/>
     <col min="33" max="34" width="10" style="5" customWidth="1"/>
-    <col min="35" max="35" width="10.109375" style="5" customWidth="1"/>
-    <col min="36" max="37" width="8.5546875" style="5" customWidth="1"/>
-    <col min="38" max="44" width="10.109375" style="5" customWidth="1"/>
-    <col min="45" max="45" width="11.109375" style="5" customWidth="1"/>
+    <col min="35" max="35" width="10.1328125" style="5" customWidth="1"/>
+    <col min="36" max="37" width="8.53125" style="5" customWidth="1"/>
+    <col min="38" max="44" width="10.1328125" style="5" customWidth="1"/>
+    <col min="45" max="45" width="11.1328125" style="5" customWidth="1"/>
     <col min="46" max="47" width="10" style="5" customWidth="1"/>
-    <col min="48" max="48" width="10.109375" style="5" customWidth="1"/>
-    <col min="49" max="50" width="8.5546875" style="5" customWidth="1"/>
-    <col min="51" max="57" width="10.109375" style="5" customWidth="1"/>
-    <col min="58" max="58" width="11.109375" style="5" customWidth="1"/>
+    <col min="48" max="48" width="10.1328125" style="5" customWidth="1"/>
+    <col min="49" max="50" width="8.53125" style="5" customWidth="1"/>
+    <col min="51" max="57" width="10.1328125" style="5" customWidth="1"/>
+    <col min="58" max="58" width="11.1328125" style="5" customWidth="1"/>
     <col min="59" max="60" width="10" style="5" customWidth="1"/>
-    <col min="61" max="61" width="10.109375" style="5" customWidth="1"/>
-    <col min="62" max="62" width="8.5546875" style="5" customWidth="1"/>
-    <col min="63" max="70" width="10.109375" style="5" customWidth="1"/>
-    <col min="71" max="71" width="11.109375" style="5" customWidth="1"/>
+    <col min="61" max="61" width="10.1328125" style="5" customWidth="1"/>
+    <col min="62" max="62" width="8.53125" style="5" customWidth="1"/>
+    <col min="63" max="70" width="10.1328125" style="5" customWidth="1"/>
+    <col min="71" max="71" width="11.1328125" style="5" customWidth="1"/>
     <col min="72" max="73" width="10" style="5" customWidth="1"/>
-    <col min="74" max="74" width="10.109375" style="5" customWidth="1"/>
-    <col min="75" max="76" width="8.5546875" style="5" customWidth="1"/>
-    <col min="77" max="83" width="10.109375" style="5" customWidth="1"/>
-    <col min="84" max="84" width="11.109375" style="5" customWidth="1"/>
+    <col min="74" max="74" width="10.1328125" style="5" customWidth="1"/>
+    <col min="75" max="76" width="8.53125" style="5" customWidth="1"/>
+    <col min="77" max="83" width="10.1328125" style="5" customWidth="1"/>
+    <col min="84" max="84" width="11.1328125" style="5" customWidth="1"/>
     <col min="85" max="86" width="10" style="5" customWidth="1"/>
-    <col min="87" max="87" width="10.109375" style="5" customWidth="1"/>
-    <col min="88" max="88" width="8.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="89" max="89" width="8.5546875" style="5" customWidth="1"/>
-    <col min="90" max="96" width="10.109375" style="5" customWidth="1"/>
-    <col min="97" max="97" width="11.109375" style="5" customWidth="1"/>
-    <col min="98" max="100" width="10.109375" style="5" customWidth="1"/>
-    <col min="101" max="101" width="8.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="102" max="102" width="8.5546875" style="5" customWidth="1"/>
-    <col min="103" max="109" width="10.109375" style="5" customWidth="1"/>
-    <col min="110" max="110" width="11.109375" style="5" customWidth="1"/>
-    <col min="111" max="113" width="10.109375" style="5" customWidth="1"/>
-    <col min="114" max="114" width="8.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="115" max="115" width="8.5546875" style="5" customWidth="1"/>
-    <col min="116" max="122" width="10.109375" style="5" customWidth="1"/>
-    <col min="123" max="123" width="11.109375" style="5" customWidth="1"/>
-    <col min="124" max="126" width="10.109375" style="5" customWidth="1"/>
-    <col min="127" max="127" width="8.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="128" max="128" width="8.5546875" style="5" customWidth="1"/>
-    <col min="129" max="135" width="10.109375" style="5" customWidth="1"/>
-    <col min="136" max="136" width="11.109375" style="5" customWidth="1"/>
-    <col min="137" max="139" width="10.109375" style="5" customWidth="1"/>
-    <col min="140" max="140" width="8.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="141" max="141" width="8.5546875" style="5" customWidth="1"/>
-    <col min="142" max="148" width="10.109375" style="5" customWidth="1"/>
-    <col min="149" max="149" width="11.109375" style="5" customWidth="1"/>
-    <col min="150" max="152" width="10.109375" style="5" customWidth="1"/>
-    <col min="153" max="153" width="8.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="154" max="154" width="8.5546875" style="5" customWidth="1"/>
-    <col min="155" max="161" width="10.109375" style="5" customWidth="1"/>
-    <col min="162" max="162" width="11.109375" style="5" customWidth="1"/>
-    <col min="163" max="165" width="10.109375" style="5" customWidth="1"/>
-    <col min="166" max="166" width="8.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="167" max="167" width="8.5546875" style="5" customWidth="1"/>
-    <col min="168" max="174" width="10.109375" style="5" customWidth="1"/>
-    <col min="175" max="175" width="11.109375" style="5" customWidth="1"/>
-    <col min="176" max="178" width="10.109375" style="5" customWidth="1"/>
-    <col min="179" max="179" width="8.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="180" max="180" width="8.5546875" style="5" customWidth="1"/>
-    <col min="181" max="187" width="10.109375" style="5" customWidth="1"/>
-    <col min="188" max="188" width="11.109375" style="5" customWidth="1"/>
-    <col min="189" max="191" width="10.109375" style="5" customWidth="1"/>
+    <col min="87" max="87" width="10.1328125" style="5" customWidth="1"/>
+    <col min="88" max="88" width="8.53125" style="5" bestFit="1" customWidth="1"/>
+    <col min="89" max="89" width="8.53125" style="5" customWidth="1"/>
+    <col min="90" max="96" width="10.1328125" style="5" customWidth="1"/>
+    <col min="97" max="97" width="11.1328125" style="5" customWidth="1"/>
+    <col min="98" max="100" width="10.1328125" style="5" customWidth="1"/>
+    <col min="101" max="101" width="8.53125" style="5" bestFit="1" customWidth="1"/>
+    <col min="102" max="102" width="8.53125" style="5" customWidth="1"/>
+    <col min="103" max="109" width="10.1328125" style="5" customWidth="1"/>
+    <col min="110" max="110" width="11.1328125" style="5" customWidth="1"/>
+    <col min="111" max="113" width="10.1328125" style="5" customWidth="1"/>
+    <col min="114" max="114" width="8.53125" style="5" bestFit="1" customWidth="1"/>
+    <col min="115" max="115" width="8.53125" style="5" customWidth="1"/>
+    <col min="116" max="122" width="10.1328125" style="5" customWidth="1"/>
+    <col min="123" max="123" width="11.1328125" style="5" customWidth="1"/>
+    <col min="124" max="126" width="10.1328125" style="5" customWidth="1"/>
+    <col min="127" max="127" width="8.53125" style="5" bestFit="1" customWidth="1"/>
+    <col min="128" max="128" width="8.53125" style="5" customWidth="1"/>
+    <col min="129" max="135" width="10.1328125" style="5" customWidth="1"/>
+    <col min="136" max="136" width="11.1328125" style="5" customWidth="1"/>
+    <col min="137" max="139" width="10.1328125" style="5" customWidth="1"/>
+    <col min="140" max="140" width="8.53125" style="5" bestFit="1" customWidth="1"/>
+    <col min="141" max="141" width="8.53125" style="5" customWidth="1"/>
+    <col min="142" max="148" width="10.1328125" style="5" customWidth="1"/>
+    <col min="149" max="149" width="11.1328125" style="5" customWidth="1"/>
+    <col min="150" max="152" width="10.1328125" style="5" customWidth="1"/>
+    <col min="153" max="153" width="8.53125" style="5" bestFit="1" customWidth="1"/>
+    <col min="154" max="154" width="8.53125" style="5" customWidth="1"/>
+    <col min="155" max="161" width="10.1328125" style="5" customWidth="1"/>
+    <col min="162" max="162" width="11.1328125" style="5" customWidth="1"/>
+    <col min="163" max="165" width="10.1328125" style="5" customWidth="1"/>
+    <col min="166" max="166" width="8.53125" style="5" bestFit="1" customWidth="1"/>
+    <col min="167" max="167" width="8.53125" style="5" customWidth="1"/>
+    <col min="168" max="174" width="10.1328125" style="5" customWidth="1"/>
+    <col min="175" max="175" width="11.1328125" style="5" customWidth="1"/>
+    <col min="176" max="178" width="10.1328125" style="5" customWidth="1"/>
+    <col min="179" max="179" width="8.53125" style="5" bestFit="1" customWidth="1"/>
+    <col min="180" max="180" width="8.53125" style="5" customWidth="1"/>
+    <col min="181" max="187" width="10.1328125" style="5" customWidth="1"/>
+    <col min="188" max="188" width="11.1328125" style="5" customWidth="1"/>
+    <col min="189" max="191" width="10.1328125" style="5" customWidth="1"/>
     <col min="192" max="16384" width="11.33203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:191" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:191" x14ac:dyDescent="0.45">
       <c r="A1" s="3"/>
       <c r="B1" s="7" t="str">
         <f>Calificacion!B2</f>
@@ -3439,12 +3439,12 @@
       <c r="GH1" s="4"/>
       <c r="GI1" s="4"/>
     </row>
-    <row r="2" spans="1:191" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:191" s="7" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="6"/>
-      <c r="B2" s="65" t="s">
+      <c r="B2" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="57" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="69" t="s">
@@ -3455,234 +3455,234 @@
       <c r="G2" s="69"/>
       <c r="H2" s="69"/>
       <c r="I2" s="70"/>
-      <c r="J2" s="54" t="str">
+      <c r="J2" s="59" t="str">
         <f>Calificacion!$B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="K2" s="64"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="55"/>
-      <c r="Q2" s="55"/>
-      <c r="R2" s="55"/>
-      <c r="S2" s="56"/>
-      <c r="T2" s="56"/>
-      <c r="U2" s="56"/>
-      <c r="V2" s="57"/>
-      <c r="W2" s="54" t="str">
+      <c r="K2" s="60"/>
+      <c r="L2" s="61"/>
+      <c r="M2" s="61"/>
+      <c r="N2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="61"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="62"/>
+      <c r="T2" s="62"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="63"/>
+      <c r="W2" s="59" t="str">
         <f>Calificacion!$B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="X2" s="64"/>
-      <c r="Y2" s="55"/>
-      <c r="Z2" s="55"/>
-      <c r="AA2" s="55"/>
-      <c r="AB2" s="55"/>
-      <c r="AC2" s="55"/>
-      <c r="AD2" s="55"/>
-      <c r="AE2" s="55"/>
-      <c r="AF2" s="56"/>
-      <c r="AG2" s="56"/>
-      <c r="AH2" s="56"/>
-      <c r="AI2" s="57"/>
-      <c r="AJ2" s="54" t="str">
+      <c r="X2" s="60"/>
+      <c r="Y2" s="61"/>
+      <c r="Z2" s="61"/>
+      <c r="AA2" s="61"/>
+      <c r="AB2" s="61"/>
+      <c r="AC2" s="61"/>
+      <c r="AD2" s="61"/>
+      <c r="AE2" s="61"/>
+      <c r="AF2" s="62"/>
+      <c r="AG2" s="62"/>
+      <c r="AH2" s="62"/>
+      <c r="AI2" s="63"/>
+      <c r="AJ2" s="59" t="str">
         <f>Calificacion!$B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="AK2" s="64"/>
-      <c r="AL2" s="55"/>
-      <c r="AM2" s="55"/>
-      <c r="AN2" s="55"/>
-      <c r="AO2" s="55"/>
-      <c r="AP2" s="55"/>
-      <c r="AQ2" s="55"/>
-      <c r="AR2" s="55"/>
-      <c r="AS2" s="56"/>
-      <c r="AT2" s="56"/>
-      <c r="AU2" s="56"/>
-      <c r="AV2" s="57"/>
-      <c r="AW2" s="54" t="str">
+      <c r="AK2" s="60"/>
+      <c r="AL2" s="61"/>
+      <c r="AM2" s="61"/>
+      <c r="AN2" s="61"/>
+      <c r="AO2" s="61"/>
+      <c r="AP2" s="61"/>
+      <c r="AQ2" s="61"/>
+      <c r="AR2" s="61"/>
+      <c r="AS2" s="62"/>
+      <c r="AT2" s="62"/>
+      <c r="AU2" s="62"/>
+      <c r="AV2" s="63"/>
+      <c r="AW2" s="59" t="str">
         <f>Calificacion!$B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="AX2" s="64"/>
-      <c r="AY2" s="55"/>
-      <c r="AZ2" s="55"/>
-      <c r="BA2" s="55"/>
-      <c r="BB2" s="55"/>
-      <c r="BC2" s="55"/>
-      <c r="BD2" s="55"/>
-      <c r="BE2" s="55"/>
-      <c r="BF2" s="56"/>
-      <c r="BG2" s="56"/>
-      <c r="BH2" s="56"/>
-      <c r="BI2" s="57"/>
-      <c r="BJ2" s="54" t="str">
+      <c r="AX2" s="60"/>
+      <c r="AY2" s="61"/>
+      <c r="AZ2" s="61"/>
+      <c r="BA2" s="61"/>
+      <c r="BB2" s="61"/>
+      <c r="BC2" s="61"/>
+      <c r="BD2" s="61"/>
+      <c r="BE2" s="61"/>
+      <c r="BF2" s="62"/>
+      <c r="BG2" s="62"/>
+      <c r="BH2" s="62"/>
+      <c r="BI2" s="63"/>
+      <c r="BJ2" s="59" t="str">
         <f>Calificacion!$B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="BK2" s="55"/>
-      <c r="BL2" s="55"/>
-      <c r="BM2" s="55"/>
-      <c r="BN2" s="55"/>
-      <c r="BO2" s="55"/>
-      <c r="BP2" s="55"/>
-      <c r="BQ2" s="55"/>
-      <c r="BR2" s="55"/>
-      <c r="BS2" s="56"/>
-      <c r="BT2" s="56"/>
-      <c r="BU2" s="56"/>
-      <c r="BV2" s="57"/>
-      <c r="BW2" s="54" t="str">
+      <c r="BK2" s="61"/>
+      <c r="BL2" s="61"/>
+      <c r="BM2" s="61"/>
+      <c r="BN2" s="61"/>
+      <c r="BO2" s="61"/>
+      <c r="BP2" s="61"/>
+      <c r="BQ2" s="61"/>
+      <c r="BR2" s="61"/>
+      <c r="BS2" s="62"/>
+      <c r="BT2" s="62"/>
+      <c r="BU2" s="62"/>
+      <c r="BV2" s="63"/>
+      <c r="BW2" s="59" t="str">
         <f>Calificacion!$B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="BX2" s="64"/>
-      <c r="BY2" s="55"/>
-      <c r="BZ2" s="55"/>
-      <c r="CA2" s="55"/>
-      <c r="CB2" s="55"/>
-      <c r="CC2" s="55"/>
-      <c r="CD2" s="55"/>
-      <c r="CE2" s="55"/>
-      <c r="CF2" s="56"/>
-      <c r="CG2" s="56"/>
-      <c r="CH2" s="56"/>
-      <c r="CI2" s="57"/>
-      <c r="CJ2" s="54" t="str">
+      <c r="BX2" s="60"/>
+      <c r="BY2" s="61"/>
+      <c r="BZ2" s="61"/>
+      <c r="CA2" s="61"/>
+      <c r="CB2" s="61"/>
+      <c r="CC2" s="61"/>
+      <c r="CD2" s="61"/>
+      <c r="CE2" s="61"/>
+      <c r="CF2" s="62"/>
+      <c r="CG2" s="62"/>
+      <c r="CH2" s="62"/>
+      <c r="CI2" s="63"/>
+      <c r="CJ2" s="59" t="str">
         <f>Calificacion!$B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="CK2" s="64"/>
-      <c r="CL2" s="55"/>
-      <c r="CM2" s="55"/>
-      <c r="CN2" s="55"/>
-      <c r="CO2" s="55"/>
-      <c r="CP2" s="55"/>
-      <c r="CQ2" s="55"/>
-      <c r="CR2" s="55"/>
-      <c r="CS2" s="56"/>
-      <c r="CT2" s="56"/>
-      <c r="CU2" s="56"/>
-      <c r="CV2" s="57"/>
-      <c r="CW2" s="54" t="str">
+      <c r="CK2" s="60"/>
+      <c r="CL2" s="61"/>
+      <c r="CM2" s="61"/>
+      <c r="CN2" s="61"/>
+      <c r="CO2" s="61"/>
+      <c r="CP2" s="61"/>
+      <c r="CQ2" s="61"/>
+      <c r="CR2" s="61"/>
+      <c r="CS2" s="62"/>
+      <c r="CT2" s="62"/>
+      <c r="CU2" s="62"/>
+      <c r="CV2" s="63"/>
+      <c r="CW2" s="59" t="str">
         <f>Calificacion!$B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="CX2" s="64"/>
-      <c r="CY2" s="55"/>
-      <c r="CZ2" s="55"/>
-      <c r="DA2" s="55"/>
-      <c r="DB2" s="55"/>
-      <c r="DC2" s="55"/>
-      <c r="DD2" s="55"/>
-      <c r="DE2" s="55"/>
-      <c r="DF2" s="56"/>
-      <c r="DG2" s="56"/>
-      <c r="DH2" s="56"/>
-      <c r="DI2" s="57"/>
-      <c r="DJ2" s="54" t="str">
+      <c r="CX2" s="60"/>
+      <c r="CY2" s="61"/>
+      <c r="CZ2" s="61"/>
+      <c r="DA2" s="61"/>
+      <c r="DB2" s="61"/>
+      <c r="DC2" s="61"/>
+      <c r="DD2" s="61"/>
+      <c r="DE2" s="61"/>
+      <c r="DF2" s="62"/>
+      <c r="DG2" s="62"/>
+      <c r="DH2" s="62"/>
+      <c r="DI2" s="63"/>
+      <c r="DJ2" s="59" t="str">
         <f>Calificacion!$B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="DK2" s="64"/>
-      <c r="DL2" s="55"/>
-      <c r="DM2" s="55"/>
-      <c r="DN2" s="55"/>
-      <c r="DO2" s="55"/>
-      <c r="DP2" s="55"/>
-      <c r="DQ2" s="55"/>
-      <c r="DR2" s="55"/>
-      <c r="DS2" s="56"/>
-      <c r="DT2" s="56"/>
-      <c r="DU2" s="56"/>
-      <c r="DV2" s="57"/>
-      <c r="DW2" s="54" t="str">
+      <c r="DK2" s="60"/>
+      <c r="DL2" s="61"/>
+      <c r="DM2" s="61"/>
+      <c r="DN2" s="61"/>
+      <c r="DO2" s="61"/>
+      <c r="DP2" s="61"/>
+      <c r="DQ2" s="61"/>
+      <c r="DR2" s="61"/>
+      <c r="DS2" s="62"/>
+      <c r="DT2" s="62"/>
+      <c r="DU2" s="62"/>
+      <c r="DV2" s="63"/>
+      <c r="DW2" s="59" t="str">
         <f>Calificacion!$B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="DX2" s="64"/>
-      <c r="DY2" s="55"/>
-      <c r="DZ2" s="55"/>
-      <c r="EA2" s="55"/>
-      <c r="EB2" s="55"/>
-      <c r="EC2" s="55"/>
-      <c r="ED2" s="55"/>
-      <c r="EE2" s="55"/>
-      <c r="EF2" s="56"/>
-      <c r="EG2" s="56"/>
-      <c r="EH2" s="56"/>
-      <c r="EI2" s="57"/>
-      <c r="EJ2" s="54" t="str">
+      <c r="DX2" s="60"/>
+      <c r="DY2" s="61"/>
+      <c r="DZ2" s="61"/>
+      <c r="EA2" s="61"/>
+      <c r="EB2" s="61"/>
+      <c r="EC2" s="61"/>
+      <c r="ED2" s="61"/>
+      <c r="EE2" s="61"/>
+      <c r="EF2" s="62"/>
+      <c r="EG2" s="62"/>
+      <c r="EH2" s="62"/>
+      <c r="EI2" s="63"/>
+      <c r="EJ2" s="59" t="str">
         <f>Calificacion!$B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="EK2" s="55"/>
-      <c r="EL2" s="55"/>
-      <c r="EM2" s="55"/>
-      <c r="EN2" s="55"/>
-      <c r="EO2" s="55"/>
-      <c r="EP2" s="55"/>
-      <c r="EQ2" s="55"/>
-      <c r="ER2" s="55"/>
-      <c r="ES2" s="56"/>
-      <c r="ET2" s="56"/>
-      <c r="EU2" s="56"/>
-      <c r="EV2" s="57"/>
-      <c r="EW2" s="54" t="str">
+      <c r="EK2" s="61"/>
+      <c r="EL2" s="61"/>
+      <c r="EM2" s="61"/>
+      <c r="EN2" s="61"/>
+      <c r="EO2" s="61"/>
+      <c r="EP2" s="61"/>
+      <c r="EQ2" s="61"/>
+      <c r="ER2" s="61"/>
+      <c r="ES2" s="62"/>
+      <c r="ET2" s="62"/>
+      <c r="EU2" s="62"/>
+      <c r="EV2" s="63"/>
+      <c r="EW2" s="59" t="str">
         <f>Calificacion!$B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="EX2" s="55"/>
-      <c r="EY2" s="55"/>
-      <c r="EZ2" s="55"/>
-      <c r="FA2" s="55"/>
-      <c r="FB2" s="55"/>
-      <c r="FC2" s="55"/>
-      <c r="FD2" s="55"/>
-      <c r="FE2" s="55"/>
-      <c r="FF2" s="56"/>
-      <c r="FG2" s="56"/>
-      <c r="FH2" s="56"/>
-      <c r="FI2" s="57"/>
-      <c r="FJ2" s="54" t="str">
+      <c r="EX2" s="61"/>
+      <c r="EY2" s="61"/>
+      <c r="EZ2" s="61"/>
+      <c r="FA2" s="61"/>
+      <c r="FB2" s="61"/>
+      <c r="FC2" s="61"/>
+      <c r="FD2" s="61"/>
+      <c r="FE2" s="61"/>
+      <c r="FF2" s="62"/>
+      <c r="FG2" s="62"/>
+      <c r="FH2" s="62"/>
+      <c r="FI2" s="63"/>
+      <c r="FJ2" s="59" t="str">
         <f>Calificacion!$B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="FK2" s="55"/>
-      <c r="FL2" s="55"/>
-      <c r="FM2" s="55"/>
-      <c r="FN2" s="55"/>
-      <c r="FO2" s="55"/>
-      <c r="FP2" s="55"/>
-      <c r="FQ2" s="55"/>
-      <c r="FR2" s="55"/>
-      <c r="FS2" s="56"/>
-      <c r="FT2" s="56"/>
-      <c r="FU2" s="56"/>
-      <c r="FV2" s="57"/>
-      <c r="FW2" s="54" t="str">
+      <c r="FK2" s="61"/>
+      <c r="FL2" s="61"/>
+      <c r="FM2" s="61"/>
+      <c r="FN2" s="61"/>
+      <c r="FO2" s="61"/>
+      <c r="FP2" s="61"/>
+      <c r="FQ2" s="61"/>
+      <c r="FR2" s="61"/>
+      <c r="FS2" s="62"/>
+      <c r="FT2" s="62"/>
+      <c r="FU2" s="62"/>
+      <c r="FV2" s="63"/>
+      <c r="FW2" s="59" t="str">
         <f>Calificacion!$B18</f>
         <v>Grupo 14</v>
       </c>
-      <c r="FX2" s="55"/>
-      <c r="FY2" s="55"/>
-      <c r="FZ2" s="55"/>
-      <c r="GA2" s="55"/>
-      <c r="GB2" s="55"/>
-      <c r="GC2" s="55"/>
-      <c r="GD2" s="55"/>
-      <c r="GE2" s="55"/>
-      <c r="GF2" s="56"/>
-      <c r="GG2" s="56"/>
-      <c r="GH2" s="56"/>
-      <c r="GI2" s="57"/>
+      <c r="FX2" s="61"/>
+      <c r="FY2" s="61"/>
+      <c r="FZ2" s="61"/>
+      <c r="GA2" s="61"/>
+      <c r="GB2" s="61"/>
+      <c r="GC2" s="61"/>
+      <c r="GD2" s="61"/>
+      <c r="GE2" s="61"/>
+      <c r="GF2" s="62"/>
+      <c r="GG2" s="62"/>
+      <c r="GH2" s="62"/>
+      <c r="GI2" s="63"/>
     </row>
-    <row r="3" spans="1:191" ht="45" x14ac:dyDescent="0.3">
-      <c r="B3" s="66"/>
-      <c r="C3" s="68"/>
+    <row r="3" spans="1:191" ht="30.75" x14ac:dyDescent="0.45">
+      <c r="B3" s="56"/>
+      <c r="C3" s="58"/>
       <c r="D3" s="8" t="s">
         <v>7</v>
       </c>
@@ -3729,7 +3729,7 @@
         <v>13</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T3" s="8" t="s">
         <v>41</v>
@@ -3768,7 +3768,7 @@
         <v>13</v>
       </c>
       <c r="AF3" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AG3" s="8" t="s">
         <v>41</v>
@@ -3807,7 +3807,7 @@
         <v>13</v>
       </c>
       <c r="AS3" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AT3" s="8" t="s">
         <v>41</v>
@@ -3846,7 +3846,7 @@
         <v>13</v>
       </c>
       <c r="BF3" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="BG3" s="8" t="s">
         <v>41</v>
@@ -3885,7 +3885,7 @@
         <v>13</v>
       </c>
       <c r="BS3" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="BT3" s="8" t="s">
         <v>41</v>
@@ -3924,7 +3924,7 @@
         <v>13</v>
       </c>
       <c r="CF3" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="CG3" s="8" t="s">
         <v>41</v>
@@ -3963,7 +3963,7 @@
         <v>13</v>
       </c>
       <c r="CS3" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="CT3" s="14" t="s">
         <v>41</v>
@@ -4002,7 +4002,7 @@
         <v>13</v>
       </c>
       <c r="DF3" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="DG3" s="14" t="s">
         <v>41</v>
@@ -4041,7 +4041,7 @@
         <v>13</v>
       </c>
       <c r="DS3" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="DT3" s="14" t="s">
         <v>41</v>
@@ -4080,7 +4080,7 @@
         <v>13</v>
       </c>
       <c r="EF3" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="EG3" s="14" t="s">
         <v>41</v>
@@ -4119,7 +4119,7 @@
         <v>13</v>
       </c>
       <c r="ES3" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="ET3" s="14" t="s">
         <v>41</v>
@@ -4158,7 +4158,7 @@
         <v>13</v>
       </c>
       <c r="FF3" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="FG3" s="14" t="s">
         <v>41</v>
@@ -4197,7 +4197,7 @@
         <v>13</v>
       </c>
       <c r="FS3" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="FT3" s="14" t="s">
         <v>41</v>
@@ -4236,7 +4236,7 @@
         <v>13</v>
       </c>
       <c r="GF3" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="GG3" s="14" t="s">
         <v>41</v>
@@ -4248,7 +4248,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:191" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:191" x14ac:dyDescent="0.45">
       <c r="B4" s="12" t="s">
         <v>16</v>
       </c>
@@ -4485,7 +4485,7 @@
       <c r="GH4" s="22"/>
       <c r="GI4" s="39"/>
     </row>
-    <row r="5" spans="1:191" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:191" x14ac:dyDescent="0.45">
       <c r="B5" s="12" t="s">
         <v>17</v>
       </c>
@@ -4696,7 +4696,7 @@
       <c r="GH5" s="22"/>
       <c r="GI5" s="39"/>
     </row>
-    <row r="6" spans="1:191" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:191" x14ac:dyDescent="0.45">
       <c r="B6" s="12" t="s">
         <v>0</v>
       </c>
@@ -4907,7 +4907,7 @@
       <c r="GH6" s="22"/>
       <c r="GI6" s="39"/>
     </row>
-    <row r="7" spans="1:191" ht="45" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:191" ht="46.15" x14ac:dyDescent="0.45">
       <c r="B7" s="12" t="s">
         <v>38</v>
       </c>
@@ -5118,7 +5118,7 @@
       <c r="GH7" s="22"/>
       <c r="GI7" s="39"/>
     </row>
-    <row r="8" spans="1:191" ht="45" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:191" ht="46.15" x14ac:dyDescent="0.45">
       <c r="B8" s="12" t="s">
         <v>38</v>
       </c>
@@ -5327,7 +5327,7 @@
       <c r="GH8" s="22"/>
       <c r="GI8" s="39"/>
     </row>
-    <row r="9" spans="1:191" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:191" x14ac:dyDescent="0.45">
       <c r="B9" s="12" t="s">
         <v>1</v>
       </c>
@@ -5538,7 +5538,7 @@
       <c r="GH9" s="22"/>
       <c r="GI9" s="39"/>
     </row>
-    <row r="10" spans="1:191" ht="30" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:191" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B10" s="12" t="s">
         <v>2</v>
       </c>
@@ -5749,7 +5749,7 @@
       <c r="GH10" s="22"/>
       <c r="GI10" s="39"/>
     </row>
-    <row r="11" spans="1:191" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:191" ht="33" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B11" s="12" t="s">
         <v>2</v>
       </c>
@@ -5958,7 +5958,7 @@
       <c r="GH11" s="22"/>
       <c r="GI11" s="39"/>
     </row>
-    <row r="12" spans="1:191" ht="65.55" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:191" ht="65.55" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B12" s="12" t="s">
         <v>32</v>
       </c>
@@ -6162,7 +6162,7 @@
       <c r="GH12" s="22"/>
       <c r="GI12" s="39"/>
     </row>
-    <row r="13" spans="1:191" ht="55.35" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:191" ht="55.35" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B13" s="12" t="s">
         <v>33</v>
       </c>
@@ -6366,9 +6366,9 @@
       <c r="GH13" s="22"/>
       <c r="GI13" s="39"/>
     </row>
-    <row r="14" spans="1:191" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:191" x14ac:dyDescent="0.45">
       <c r="B14" s="45" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="47"/>
@@ -6560,7 +6560,7 @@
       <c r="GH14" s="22"/>
       <c r="GI14" s="39"/>
     </row>
-    <row r="15" spans="1:191" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:191" s="26" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A15" s="1"/>
       <c r="B15" s="23"/>
       <c r="C15" s="24" t="s">
@@ -6755,11 +6755,11 @@
       <c r="GH15" s="43"/>
       <c r="GI15" s="44"/>
     </row>
-    <row r="16" spans="1:191" s="26" customFormat="1" ht="30" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:191" s="26" customFormat="1" ht="30.75" x14ac:dyDescent="0.45">
       <c r="A16" s="1"/>
       <c r="B16" s="23"/>
       <c r="C16" s="16" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D16" s="24"/>
       <c r="E16" s="24"/>
@@ -6950,11 +6950,11 @@
       <c r="GH16" s="43"/>
       <c r="GI16" s="44"/>
     </row>
-    <row r="17" spans="1:191" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:191" s="26" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A17" s="1"/>
       <c r="B17" s="23"/>
       <c r="C17" s="24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" s="24"/>
       <c r="E17" s="24"/>
@@ -7145,7 +7145,7 @@
       <c r="GH17" s="43"/>
       <c r="GI17" s="44"/>
     </row>
-    <row r="18" spans="1:191" s="26" customFormat="1" ht="30" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:191" s="26" customFormat="1" ht="30.75" x14ac:dyDescent="0.45">
       <c r="A18" s="1"/>
       <c r="B18" s="23"/>
       <c r="C18" s="16" t="s">
@@ -7340,7 +7340,7 @@
       <c r="GH18" s="43"/>
       <c r="GI18" s="44"/>
     </row>
-    <row r="19" spans="1:191" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:191" s="26" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A19" s="1"/>
       <c r="B19" s="23"/>
       <c r="C19" s="24" t="s">
@@ -7535,7 +7535,7 @@
       <c r="GH19" s="43"/>
       <c r="GI19" s="44"/>
     </row>
-    <row r="20" spans="1:191" s="26" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:191" s="26" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A20" s="1"/>
       <c r="B20" s="23"/>
       <c r="C20" s="24" t="s">
@@ -7730,11 +7730,11 @@
       <c r="GH20" s="43"/>
       <c r="GI20" s="44"/>
     </row>
-    <row r="21" spans="1:191" s="26" customFormat="1" ht="90" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:191" s="26" customFormat="1" ht="76.900000000000006" x14ac:dyDescent="0.45">
       <c r="A21" s="1"/>
       <c r="B21" s="23"/>
       <c r="C21" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D21" s="24"/>
       <c r="E21" s="24"/>
@@ -7925,7 +7925,7 @@
       <c r="GH21" s="43"/>
       <c r="GI21" s="44"/>
     </row>
-    <row r="22" spans="1:191" s="2" customFormat="1" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:191" s="2" customFormat="1" ht="40.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="1"/>
       <c r="B22" s="73" t="s">
         <v>29</v>
@@ -7939,190 +7939,190 @@
       <c r="G22" s="71"/>
       <c r="H22" s="71"/>
       <c r="I22" s="72"/>
-      <c r="J22" s="58"/>
-      <c r="K22" s="59"/>
-      <c r="L22" s="60"/>
-      <c r="M22" s="60"/>
-      <c r="N22" s="60"/>
-      <c r="O22" s="60"/>
-      <c r="P22" s="60"/>
-      <c r="Q22" s="60"/>
-      <c r="R22" s="60"/>
-      <c r="S22" s="61"/>
-      <c r="T22" s="61"/>
-      <c r="U22" s="61"/>
-      <c r="V22" s="62"/>
-      <c r="W22" s="58"/>
-      <c r="X22" s="59"/>
-      <c r="Y22" s="60"/>
-      <c r="Z22" s="60"/>
-      <c r="AA22" s="60"/>
-      <c r="AB22" s="60"/>
-      <c r="AC22" s="60"/>
-      <c r="AD22" s="60"/>
-      <c r="AE22" s="60"/>
-      <c r="AF22" s="61"/>
-      <c r="AG22" s="61"/>
-      <c r="AH22" s="61"/>
-      <c r="AI22" s="62"/>
-      <c r="AJ22" s="58"/>
-      <c r="AK22" s="59"/>
-      <c r="AL22" s="60"/>
-      <c r="AM22" s="60"/>
-      <c r="AN22" s="60"/>
-      <c r="AO22" s="60"/>
-      <c r="AP22" s="60"/>
-      <c r="AQ22" s="60"/>
-      <c r="AR22" s="60"/>
-      <c r="AS22" s="61"/>
-      <c r="AT22" s="61"/>
-      <c r="AU22" s="61"/>
-      <c r="AV22" s="62"/>
-      <c r="AW22" s="58"/>
-      <c r="AX22" s="59"/>
-      <c r="AY22" s="60"/>
-      <c r="AZ22" s="60"/>
-      <c r="BA22" s="60"/>
-      <c r="BB22" s="60"/>
-      <c r="BC22" s="60"/>
-      <c r="BD22" s="60"/>
-      <c r="BE22" s="60"/>
-      <c r="BF22" s="61"/>
-      <c r="BG22" s="61"/>
-      <c r="BH22" s="61"/>
-      <c r="BI22" s="62"/>
-      <c r="BJ22" s="58"/>
-      <c r="BK22" s="59"/>
-      <c r="BL22" s="60"/>
-      <c r="BM22" s="60"/>
-      <c r="BN22" s="60"/>
-      <c r="BO22" s="60"/>
-      <c r="BP22" s="60"/>
-      <c r="BQ22" s="60"/>
-      <c r="BR22" s="60"/>
-      <c r="BS22" s="61"/>
-      <c r="BT22" s="61"/>
-      <c r="BU22" s="61"/>
-      <c r="BV22" s="62"/>
-      <c r="BW22" s="58"/>
-      <c r="BX22" s="59"/>
-      <c r="BY22" s="60"/>
-      <c r="BZ22" s="60"/>
-      <c r="CA22" s="60"/>
-      <c r="CB22" s="60"/>
-      <c r="CC22" s="60"/>
-      <c r="CD22" s="60"/>
-      <c r="CE22" s="60"/>
-      <c r="CF22" s="61"/>
-      <c r="CG22" s="61"/>
-      <c r="CH22" s="61"/>
-      <c r="CI22" s="62"/>
-      <c r="CJ22" s="58"/>
-      <c r="CK22" s="59"/>
-      <c r="CL22" s="60"/>
-      <c r="CM22" s="60"/>
-      <c r="CN22" s="60"/>
-      <c r="CO22" s="60"/>
-      <c r="CP22" s="60"/>
-      <c r="CQ22" s="60"/>
-      <c r="CR22" s="60"/>
-      <c r="CS22" s="61"/>
-      <c r="CT22" s="61"/>
-      <c r="CU22" s="61"/>
-      <c r="CV22" s="62"/>
-      <c r="CW22" s="58"/>
-      <c r="CX22" s="59"/>
-      <c r="CY22" s="60"/>
-      <c r="CZ22" s="60"/>
-      <c r="DA22" s="60"/>
-      <c r="DB22" s="60"/>
-      <c r="DC22" s="60"/>
-      <c r="DD22" s="60"/>
-      <c r="DE22" s="60"/>
-      <c r="DF22" s="61"/>
-      <c r="DG22" s="61"/>
-      <c r="DH22" s="61"/>
-      <c r="DI22" s="62"/>
-      <c r="DJ22" s="58"/>
-      <c r="DK22" s="59"/>
-      <c r="DL22" s="60"/>
-      <c r="DM22" s="60"/>
-      <c r="DN22" s="60"/>
-      <c r="DO22" s="60"/>
-      <c r="DP22" s="60"/>
-      <c r="DQ22" s="60"/>
-      <c r="DR22" s="60"/>
-      <c r="DS22" s="61"/>
-      <c r="DT22" s="61"/>
-      <c r="DU22" s="61"/>
-      <c r="DV22" s="62"/>
-      <c r="DW22" s="58"/>
-      <c r="DX22" s="59"/>
-      <c r="DY22" s="60"/>
-      <c r="DZ22" s="60"/>
-      <c r="EA22" s="60"/>
-      <c r="EB22" s="60"/>
-      <c r="EC22" s="60"/>
-      <c r="ED22" s="60"/>
-      <c r="EE22" s="60"/>
-      <c r="EF22" s="61"/>
-      <c r="EG22" s="61"/>
-      <c r="EH22" s="61"/>
-      <c r="EI22" s="62"/>
-      <c r="EJ22" s="58"/>
-      <c r="EK22" s="59"/>
-      <c r="EL22" s="60"/>
-      <c r="EM22" s="60"/>
-      <c r="EN22" s="60"/>
-      <c r="EO22" s="60"/>
-      <c r="EP22" s="60"/>
-      <c r="EQ22" s="60"/>
-      <c r="ER22" s="60"/>
-      <c r="ES22" s="61"/>
-      <c r="ET22" s="61"/>
-      <c r="EU22" s="61"/>
-      <c r="EV22" s="62"/>
-      <c r="EW22" s="58"/>
-      <c r="EX22" s="59"/>
-      <c r="EY22" s="60"/>
-      <c r="EZ22" s="60"/>
-      <c r="FA22" s="60"/>
-      <c r="FB22" s="60"/>
-      <c r="FC22" s="60"/>
-      <c r="FD22" s="60"/>
-      <c r="FE22" s="60"/>
-      <c r="FF22" s="61"/>
-      <c r="FG22" s="61"/>
-      <c r="FH22" s="61"/>
-      <c r="FI22" s="62"/>
-      <c r="FJ22" s="58"/>
-      <c r="FK22" s="59"/>
-      <c r="FL22" s="60"/>
-      <c r="FM22" s="60"/>
-      <c r="FN22" s="60"/>
-      <c r="FO22" s="60"/>
-      <c r="FP22" s="60"/>
-      <c r="FQ22" s="60"/>
-      <c r="FR22" s="60"/>
-      <c r="FS22" s="61"/>
-      <c r="FT22" s="61"/>
-      <c r="FU22" s="61"/>
-      <c r="FV22" s="62"/>
-      <c r="FW22" s="58"/>
-      <c r="FX22" s="59"/>
-      <c r="FY22" s="60"/>
-      <c r="FZ22" s="60"/>
-      <c r="GA22" s="60"/>
-      <c r="GB22" s="60"/>
-      <c r="GC22" s="60"/>
-      <c r="GD22" s="60"/>
-      <c r="GE22" s="60"/>
-      <c r="GF22" s="61"/>
-      <c r="GG22" s="61"/>
-      <c r="GH22" s="61"/>
-      <c r="GI22" s="62"/>
+      <c r="J22" s="64"/>
+      <c r="K22" s="65"/>
+      <c r="L22" s="66"/>
+      <c r="M22" s="66"/>
+      <c r="N22" s="66"/>
+      <c r="O22" s="66"/>
+      <c r="P22" s="66"/>
+      <c r="Q22" s="66"/>
+      <c r="R22" s="66"/>
+      <c r="S22" s="67"/>
+      <c r="T22" s="67"/>
+      <c r="U22" s="67"/>
+      <c r="V22" s="68"/>
+      <c r="W22" s="64"/>
+      <c r="X22" s="65"/>
+      <c r="Y22" s="66"/>
+      <c r="Z22" s="66"/>
+      <c r="AA22" s="66"/>
+      <c r="AB22" s="66"/>
+      <c r="AC22" s="66"/>
+      <c r="AD22" s="66"/>
+      <c r="AE22" s="66"/>
+      <c r="AF22" s="67"/>
+      <c r="AG22" s="67"/>
+      <c r="AH22" s="67"/>
+      <c r="AI22" s="68"/>
+      <c r="AJ22" s="64"/>
+      <c r="AK22" s="65"/>
+      <c r="AL22" s="66"/>
+      <c r="AM22" s="66"/>
+      <c r="AN22" s="66"/>
+      <c r="AO22" s="66"/>
+      <c r="AP22" s="66"/>
+      <c r="AQ22" s="66"/>
+      <c r="AR22" s="66"/>
+      <c r="AS22" s="67"/>
+      <c r="AT22" s="67"/>
+      <c r="AU22" s="67"/>
+      <c r="AV22" s="68"/>
+      <c r="AW22" s="64"/>
+      <c r="AX22" s="65"/>
+      <c r="AY22" s="66"/>
+      <c r="AZ22" s="66"/>
+      <c r="BA22" s="66"/>
+      <c r="BB22" s="66"/>
+      <c r="BC22" s="66"/>
+      <c r="BD22" s="66"/>
+      <c r="BE22" s="66"/>
+      <c r="BF22" s="67"/>
+      <c r="BG22" s="67"/>
+      <c r="BH22" s="67"/>
+      <c r="BI22" s="68"/>
+      <c r="BJ22" s="64"/>
+      <c r="BK22" s="65"/>
+      <c r="BL22" s="66"/>
+      <c r="BM22" s="66"/>
+      <c r="BN22" s="66"/>
+      <c r="BO22" s="66"/>
+      <c r="BP22" s="66"/>
+      <c r="BQ22" s="66"/>
+      <c r="BR22" s="66"/>
+      <c r="BS22" s="67"/>
+      <c r="BT22" s="67"/>
+      <c r="BU22" s="67"/>
+      <c r="BV22" s="68"/>
+      <c r="BW22" s="64"/>
+      <c r="BX22" s="65"/>
+      <c r="BY22" s="66"/>
+      <c r="BZ22" s="66"/>
+      <c r="CA22" s="66"/>
+      <c r="CB22" s="66"/>
+      <c r="CC22" s="66"/>
+      <c r="CD22" s="66"/>
+      <c r="CE22" s="66"/>
+      <c r="CF22" s="67"/>
+      <c r="CG22" s="67"/>
+      <c r="CH22" s="67"/>
+      <c r="CI22" s="68"/>
+      <c r="CJ22" s="64"/>
+      <c r="CK22" s="65"/>
+      <c r="CL22" s="66"/>
+      <c r="CM22" s="66"/>
+      <c r="CN22" s="66"/>
+      <c r="CO22" s="66"/>
+      <c r="CP22" s="66"/>
+      <c r="CQ22" s="66"/>
+      <c r="CR22" s="66"/>
+      <c r="CS22" s="67"/>
+      <c r="CT22" s="67"/>
+      <c r="CU22" s="67"/>
+      <c r="CV22" s="68"/>
+      <c r="CW22" s="64"/>
+      <c r="CX22" s="65"/>
+      <c r="CY22" s="66"/>
+      <c r="CZ22" s="66"/>
+      <c r="DA22" s="66"/>
+      <c r="DB22" s="66"/>
+      <c r="DC22" s="66"/>
+      <c r="DD22" s="66"/>
+      <c r="DE22" s="66"/>
+      <c r="DF22" s="67"/>
+      <c r="DG22" s="67"/>
+      <c r="DH22" s="67"/>
+      <c r="DI22" s="68"/>
+      <c r="DJ22" s="64"/>
+      <c r="DK22" s="65"/>
+      <c r="DL22" s="66"/>
+      <c r="DM22" s="66"/>
+      <c r="DN22" s="66"/>
+      <c r="DO22" s="66"/>
+      <c r="DP22" s="66"/>
+      <c r="DQ22" s="66"/>
+      <c r="DR22" s="66"/>
+      <c r="DS22" s="67"/>
+      <c r="DT22" s="67"/>
+      <c r="DU22" s="67"/>
+      <c r="DV22" s="68"/>
+      <c r="DW22" s="64"/>
+      <c r="DX22" s="65"/>
+      <c r="DY22" s="66"/>
+      <c r="DZ22" s="66"/>
+      <c r="EA22" s="66"/>
+      <c r="EB22" s="66"/>
+      <c r="EC22" s="66"/>
+      <c r="ED22" s="66"/>
+      <c r="EE22" s="66"/>
+      <c r="EF22" s="67"/>
+      <c r="EG22" s="67"/>
+      <c r="EH22" s="67"/>
+      <c r="EI22" s="68"/>
+      <c r="EJ22" s="64"/>
+      <c r="EK22" s="65"/>
+      <c r="EL22" s="66"/>
+      <c r="EM22" s="66"/>
+      <c r="EN22" s="66"/>
+      <c r="EO22" s="66"/>
+      <c r="EP22" s="66"/>
+      <c r="EQ22" s="66"/>
+      <c r="ER22" s="66"/>
+      <c r="ES22" s="67"/>
+      <c r="ET22" s="67"/>
+      <c r="EU22" s="67"/>
+      <c r="EV22" s="68"/>
+      <c r="EW22" s="64"/>
+      <c r="EX22" s="65"/>
+      <c r="EY22" s="66"/>
+      <c r="EZ22" s="66"/>
+      <c r="FA22" s="66"/>
+      <c r="FB22" s="66"/>
+      <c r="FC22" s="66"/>
+      <c r="FD22" s="66"/>
+      <c r="FE22" s="66"/>
+      <c r="FF22" s="67"/>
+      <c r="FG22" s="67"/>
+      <c r="FH22" s="67"/>
+      <c r="FI22" s="68"/>
+      <c r="FJ22" s="64"/>
+      <c r="FK22" s="65"/>
+      <c r="FL22" s="66"/>
+      <c r="FM22" s="66"/>
+      <c r="FN22" s="66"/>
+      <c r="FO22" s="66"/>
+      <c r="FP22" s="66"/>
+      <c r="FQ22" s="66"/>
+      <c r="FR22" s="66"/>
+      <c r="FS22" s="67"/>
+      <c r="FT22" s="67"/>
+      <c r="FU22" s="67"/>
+      <c r="FV22" s="68"/>
+      <c r="FW22" s="64"/>
+      <c r="FX22" s="65"/>
+      <c r="FY22" s="66"/>
+      <c r="FZ22" s="66"/>
+      <c r="GA22" s="66"/>
+      <c r="GB22" s="66"/>
+      <c r="GC22" s="66"/>
+      <c r="GD22" s="66"/>
+      <c r="GE22" s="66"/>
+      <c r="GF22" s="67"/>
+      <c r="GG22" s="67"/>
+      <c r="GH22" s="67"/>
+      <c r="GI22" s="68"/>
     </row>
-    <row r="23" spans="1:191" s="2" customFormat="1" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:191" s="2" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="1"/>
       <c r="B23" s="75" t="s">
         <v>21</v>
@@ -8134,218 +8134,218 @@
       <c r="G23" s="75"/>
       <c r="H23" s="75"/>
       <c r="I23" s="75"/>
-      <c r="J23" s="63">
+      <c r="J23" s="54">
         <v>0</v>
       </c>
-      <c r="K23" s="63"/>
-      <c r="L23" s="63"/>
-      <c r="M23" s="63"/>
-      <c r="N23" s="63"/>
-      <c r="O23" s="63"/>
-      <c r="P23" s="63"/>
-      <c r="Q23" s="63"/>
-      <c r="R23" s="63"/>
-      <c r="S23" s="63"/>
-      <c r="T23" s="63"/>
-      <c r="U23" s="63"/>
-      <c r="V23" s="63"/>
-      <c r="W23" s="63">
+      <c r="K23" s="54"/>
+      <c r="L23" s="54"/>
+      <c r="M23" s="54"/>
+      <c r="N23" s="54"/>
+      <c r="O23" s="54"/>
+      <c r="P23" s="54"/>
+      <c r="Q23" s="54"/>
+      <c r="R23" s="54"/>
+      <c r="S23" s="54"/>
+      <c r="T23" s="54"/>
+      <c r="U23" s="54"/>
+      <c r="V23" s="54"/>
+      <c r="W23" s="54">
         <v>0</v>
       </c>
-      <c r="X23" s="63"/>
-      <c r="Y23" s="63"/>
-      <c r="Z23" s="63"/>
-      <c r="AA23" s="63"/>
-      <c r="AB23" s="63"/>
-      <c r="AC23" s="63"/>
-      <c r="AD23" s="63"/>
-      <c r="AE23" s="63"/>
-      <c r="AF23" s="63"/>
-      <c r="AG23" s="63"/>
-      <c r="AH23" s="63"/>
-      <c r="AI23" s="63"/>
-      <c r="AJ23" s="63">
+      <c r="X23" s="54"/>
+      <c r="Y23" s="54"/>
+      <c r="Z23" s="54"/>
+      <c r="AA23" s="54"/>
+      <c r="AB23" s="54"/>
+      <c r="AC23" s="54"/>
+      <c r="AD23" s="54"/>
+      <c r="AE23" s="54"/>
+      <c r="AF23" s="54"/>
+      <c r="AG23" s="54"/>
+      <c r="AH23" s="54"/>
+      <c r="AI23" s="54"/>
+      <c r="AJ23" s="54">
         <v>0</v>
       </c>
-      <c r="AK23" s="63"/>
-      <c r="AL23" s="63"/>
-      <c r="AM23" s="63"/>
-      <c r="AN23" s="63"/>
-      <c r="AO23" s="63"/>
-      <c r="AP23" s="63"/>
-      <c r="AQ23" s="63"/>
-      <c r="AR23" s="63"/>
-      <c r="AS23" s="63"/>
-      <c r="AT23" s="63"/>
-      <c r="AU23" s="63"/>
-      <c r="AV23" s="63"/>
-      <c r="AW23" s="63">
+      <c r="AK23" s="54"/>
+      <c r="AL23" s="54"/>
+      <c r="AM23" s="54"/>
+      <c r="AN23" s="54"/>
+      <c r="AO23" s="54"/>
+      <c r="AP23" s="54"/>
+      <c r="AQ23" s="54"/>
+      <c r="AR23" s="54"/>
+      <c r="AS23" s="54"/>
+      <c r="AT23" s="54"/>
+      <c r="AU23" s="54"/>
+      <c r="AV23" s="54"/>
+      <c r="AW23" s="54">
         <v>0</v>
       </c>
-      <c r="AX23" s="63"/>
-      <c r="AY23" s="63"/>
-      <c r="AZ23" s="63"/>
-      <c r="BA23" s="63"/>
-      <c r="BB23" s="63"/>
-      <c r="BC23" s="63"/>
-      <c r="BD23" s="63"/>
-      <c r="BE23" s="63"/>
-      <c r="BF23" s="63"/>
-      <c r="BG23" s="63"/>
-      <c r="BH23" s="63"/>
-      <c r="BI23" s="63"/>
-      <c r="BJ23" s="63">
+      <c r="AX23" s="54"/>
+      <c r="AY23" s="54"/>
+      <c r="AZ23" s="54"/>
+      <c r="BA23" s="54"/>
+      <c r="BB23" s="54"/>
+      <c r="BC23" s="54"/>
+      <c r="BD23" s="54"/>
+      <c r="BE23" s="54"/>
+      <c r="BF23" s="54"/>
+      <c r="BG23" s="54"/>
+      <c r="BH23" s="54"/>
+      <c r="BI23" s="54"/>
+      <c r="BJ23" s="54">
         <v>0</v>
       </c>
-      <c r="BK23" s="63"/>
-      <c r="BL23" s="63"/>
-      <c r="BM23" s="63"/>
-      <c r="BN23" s="63"/>
-      <c r="BO23" s="63"/>
-      <c r="BP23" s="63"/>
-      <c r="BQ23" s="63"/>
-      <c r="BR23" s="63"/>
-      <c r="BS23" s="63"/>
-      <c r="BT23" s="63"/>
-      <c r="BU23" s="63"/>
-      <c r="BV23" s="63"/>
-      <c r="BW23" s="63">
+      <c r="BK23" s="54"/>
+      <c r="BL23" s="54"/>
+      <c r="BM23" s="54"/>
+      <c r="BN23" s="54"/>
+      <c r="BO23" s="54"/>
+      <c r="BP23" s="54"/>
+      <c r="BQ23" s="54"/>
+      <c r="BR23" s="54"/>
+      <c r="BS23" s="54"/>
+      <c r="BT23" s="54"/>
+      <c r="BU23" s="54"/>
+      <c r="BV23" s="54"/>
+      <c r="BW23" s="54">
         <v>0</v>
       </c>
-      <c r="BX23" s="63"/>
-      <c r="BY23" s="63"/>
-      <c r="BZ23" s="63"/>
-      <c r="CA23" s="63"/>
-      <c r="CB23" s="63"/>
-      <c r="CC23" s="63"/>
-      <c r="CD23" s="63"/>
-      <c r="CE23" s="63"/>
-      <c r="CF23" s="63"/>
-      <c r="CG23" s="63"/>
-      <c r="CH23" s="63"/>
-      <c r="CI23" s="63"/>
-      <c r="CJ23" s="63">
+      <c r="BX23" s="54"/>
+      <c r="BY23" s="54"/>
+      <c r="BZ23" s="54"/>
+      <c r="CA23" s="54"/>
+      <c r="CB23" s="54"/>
+      <c r="CC23" s="54"/>
+      <c r="CD23" s="54"/>
+      <c r="CE23" s="54"/>
+      <c r="CF23" s="54"/>
+      <c r="CG23" s="54"/>
+      <c r="CH23" s="54"/>
+      <c r="CI23" s="54"/>
+      <c r="CJ23" s="54">
         <v>0</v>
       </c>
-      <c r="CK23" s="63"/>
-      <c r="CL23" s="63"/>
-      <c r="CM23" s="63"/>
-      <c r="CN23" s="63"/>
-      <c r="CO23" s="63"/>
-      <c r="CP23" s="63"/>
-      <c r="CQ23" s="63"/>
-      <c r="CR23" s="63"/>
-      <c r="CS23" s="63"/>
-      <c r="CT23" s="63"/>
-      <c r="CU23" s="63"/>
-      <c r="CV23" s="63"/>
-      <c r="CW23" s="63">
+      <c r="CK23" s="54"/>
+      <c r="CL23" s="54"/>
+      <c r="CM23" s="54"/>
+      <c r="CN23" s="54"/>
+      <c r="CO23" s="54"/>
+      <c r="CP23" s="54"/>
+      <c r="CQ23" s="54"/>
+      <c r="CR23" s="54"/>
+      <c r="CS23" s="54"/>
+      <c r="CT23" s="54"/>
+      <c r="CU23" s="54"/>
+      <c r="CV23" s="54"/>
+      <c r="CW23" s="54">
         <v>0</v>
       </c>
-      <c r="CX23" s="63"/>
-      <c r="CY23" s="63"/>
-      <c r="CZ23" s="63"/>
-      <c r="DA23" s="63"/>
-      <c r="DB23" s="63"/>
-      <c r="DC23" s="63"/>
-      <c r="DD23" s="63"/>
-      <c r="DE23" s="63"/>
-      <c r="DF23" s="63"/>
-      <c r="DG23" s="63"/>
-      <c r="DH23" s="63"/>
-      <c r="DI23" s="63"/>
-      <c r="DJ23" s="63">
+      <c r="CX23" s="54"/>
+      <c r="CY23" s="54"/>
+      <c r="CZ23" s="54"/>
+      <c r="DA23" s="54"/>
+      <c r="DB23" s="54"/>
+      <c r="DC23" s="54"/>
+      <c r="DD23" s="54"/>
+      <c r="DE23" s="54"/>
+      <c r="DF23" s="54"/>
+      <c r="DG23" s="54"/>
+      <c r="DH23" s="54"/>
+      <c r="DI23" s="54"/>
+      <c r="DJ23" s="54">
         <v>0</v>
       </c>
-      <c r="DK23" s="63"/>
-      <c r="DL23" s="63"/>
-      <c r="DM23" s="63"/>
-      <c r="DN23" s="63"/>
-      <c r="DO23" s="63"/>
-      <c r="DP23" s="63"/>
-      <c r="DQ23" s="63"/>
-      <c r="DR23" s="63"/>
-      <c r="DS23" s="63"/>
-      <c r="DT23" s="63"/>
-      <c r="DU23" s="63"/>
-      <c r="DV23" s="63"/>
-      <c r="DW23" s="63">
+      <c r="DK23" s="54"/>
+      <c r="DL23" s="54"/>
+      <c r="DM23" s="54"/>
+      <c r="DN23" s="54"/>
+      <c r="DO23" s="54"/>
+      <c r="DP23" s="54"/>
+      <c r="DQ23" s="54"/>
+      <c r="DR23" s="54"/>
+      <c r="DS23" s="54"/>
+      <c r="DT23" s="54"/>
+      <c r="DU23" s="54"/>
+      <c r="DV23" s="54"/>
+      <c r="DW23" s="54">
         <v>0</v>
       </c>
-      <c r="DX23" s="63"/>
-      <c r="DY23" s="63"/>
-      <c r="DZ23" s="63"/>
-      <c r="EA23" s="63"/>
-      <c r="EB23" s="63"/>
-      <c r="EC23" s="63"/>
-      <c r="ED23" s="63"/>
-      <c r="EE23" s="63"/>
-      <c r="EF23" s="63"/>
-      <c r="EG23" s="63"/>
-      <c r="EH23" s="63"/>
-      <c r="EI23" s="63"/>
-      <c r="EJ23" s="63">
+      <c r="DX23" s="54"/>
+      <c r="DY23" s="54"/>
+      <c r="DZ23" s="54"/>
+      <c r="EA23" s="54"/>
+      <c r="EB23" s="54"/>
+      <c r="EC23" s="54"/>
+      <c r="ED23" s="54"/>
+      <c r="EE23" s="54"/>
+      <c r="EF23" s="54"/>
+      <c r="EG23" s="54"/>
+      <c r="EH23" s="54"/>
+      <c r="EI23" s="54"/>
+      <c r="EJ23" s="54">
         <v>0</v>
       </c>
-      <c r="EK23" s="63"/>
-      <c r="EL23" s="63"/>
-      <c r="EM23" s="63"/>
-      <c r="EN23" s="63"/>
-      <c r="EO23" s="63"/>
-      <c r="EP23" s="63"/>
-      <c r="EQ23" s="63"/>
-      <c r="ER23" s="63"/>
-      <c r="ES23" s="63"/>
-      <c r="ET23" s="63"/>
-      <c r="EU23" s="63"/>
-      <c r="EV23" s="63"/>
-      <c r="EW23" s="63">
+      <c r="EK23" s="54"/>
+      <c r="EL23" s="54"/>
+      <c r="EM23" s="54"/>
+      <c r="EN23" s="54"/>
+      <c r="EO23" s="54"/>
+      <c r="EP23" s="54"/>
+      <c r="EQ23" s="54"/>
+      <c r="ER23" s="54"/>
+      <c r="ES23" s="54"/>
+      <c r="ET23" s="54"/>
+      <c r="EU23" s="54"/>
+      <c r="EV23" s="54"/>
+      <c r="EW23" s="54">
         <v>0</v>
       </c>
-      <c r="EX23" s="63"/>
-      <c r="EY23" s="63"/>
-      <c r="EZ23" s="63"/>
-      <c r="FA23" s="63"/>
-      <c r="FB23" s="63"/>
-      <c r="FC23" s="63"/>
-      <c r="FD23" s="63"/>
-      <c r="FE23" s="63"/>
-      <c r="FF23" s="63"/>
-      <c r="FG23" s="63"/>
-      <c r="FH23" s="63"/>
-      <c r="FI23" s="63"/>
-      <c r="FJ23" s="63">
+      <c r="EX23" s="54"/>
+      <c r="EY23" s="54"/>
+      <c r="EZ23" s="54"/>
+      <c r="FA23" s="54"/>
+      <c r="FB23" s="54"/>
+      <c r="FC23" s="54"/>
+      <c r="FD23" s="54"/>
+      <c r="FE23" s="54"/>
+      <c r="FF23" s="54"/>
+      <c r="FG23" s="54"/>
+      <c r="FH23" s="54"/>
+      <c r="FI23" s="54"/>
+      <c r="FJ23" s="54">
         <v>0</v>
       </c>
-      <c r="FK23" s="63"/>
-      <c r="FL23" s="63"/>
-      <c r="FM23" s="63"/>
-      <c r="FN23" s="63"/>
-      <c r="FO23" s="63"/>
-      <c r="FP23" s="63"/>
-      <c r="FQ23" s="63"/>
-      <c r="FR23" s="63"/>
-      <c r="FS23" s="63"/>
-      <c r="FT23" s="63"/>
-      <c r="FU23" s="63"/>
-      <c r="FV23" s="63"/>
-      <c r="FW23" s="63">
+      <c r="FK23" s="54"/>
+      <c r="FL23" s="54"/>
+      <c r="FM23" s="54"/>
+      <c r="FN23" s="54"/>
+      <c r="FO23" s="54"/>
+      <c r="FP23" s="54"/>
+      <c r="FQ23" s="54"/>
+      <c r="FR23" s="54"/>
+      <c r="FS23" s="54"/>
+      <c r="FT23" s="54"/>
+      <c r="FU23" s="54"/>
+      <c r="FV23" s="54"/>
+      <c r="FW23" s="54">
         <v>0</v>
       </c>
-      <c r="FX23" s="63"/>
-      <c r="FY23" s="63"/>
-      <c r="FZ23" s="63"/>
-      <c r="GA23" s="63"/>
-      <c r="GB23" s="63"/>
-      <c r="GC23" s="63"/>
-      <c r="GD23" s="63"/>
-      <c r="GE23" s="63"/>
-      <c r="GF23" s="63"/>
-      <c r="GG23" s="63"/>
-      <c r="GH23" s="63"/>
-      <c r="GI23" s="63"/>
+      <c r="FX23" s="54"/>
+      <c r="FY23" s="54"/>
+      <c r="FZ23" s="54"/>
+      <c r="GA23" s="54"/>
+      <c r="GB23" s="54"/>
+      <c r="GC23" s="54"/>
+      <c r="GD23" s="54"/>
+      <c r="GE23" s="54"/>
+      <c r="GF23" s="54"/>
+      <c r="GG23" s="54"/>
+      <c r="GH23" s="54"/>
+      <c r="GI23" s="54"/>
     </row>
-    <row r="24" spans="1:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:191" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
@@ -8537,7 +8537,7 @@
       <c r="GH24" s="5"/>
       <c r="GI24" s="5"/>
     </row>
-    <row r="25" spans="1:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:191" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B25" s="4"/>
       <c r="C25" s="5"/>
       <c r="D25" s="5"/>
@@ -8729,7 +8729,7 @@
       <c r="GH25" s="5"/>
       <c r="GI25" s="5"/>
     </row>
-    <row r="26" spans="1:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:191" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B26" s="4"/>
       <c r="C26" s="5"/>
       <c r="D26" s="5"/>
@@ -8921,7 +8921,7 @@
       <c r="GH26" s="5"/>
       <c r="GI26" s="5"/>
     </row>
-    <row r="27" spans="1:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:191" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B27" s="4"/>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
@@ -9113,7 +9113,7 @@
       <c r="GH27" s="5"/>
       <c r="GI27" s="5"/>
     </row>
-    <row r="28" spans="1:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:191" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B28" s="4"/>
       <c r="C28" s="5"/>
       <c r="D28" s="5"/>
@@ -9305,7 +9305,7 @@
       <c r="GH28" s="5"/>
       <c r="GI28" s="5"/>
     </row>
-    <row r="29" spans="1:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:191" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B29" s="4"/>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
@@ -9497,7 +9497,7 @@
       <c r="GH29" s="5"/>
       <c r="GI29" s="5"/>
     </row>
-    <row r="30" spans="1:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:191" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B30" s="4"/>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
@@ -9689,7 +9689,7 @@
       <c r="GH30" s="5"/>
       <c r="GI30" s="5"/>
     </row>
-    <row r="31" spans="1:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:191" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B31" s="4"/>
       <c r="C31" s="5"/>
       <c r="D31" s="5"/>
@@ -9881,7 +9881,7 @@
       <c r="GH31" s="5"/>
       <c r="GI31" s="5"/>
     </row>
-    <row r="32" spans="1:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:191" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B32" s="4"/>
       <c r="C32" s="5"/>
       <c r="D32" s="5"/>
@@ -10073,7 +10073,7 @@
       <c r="GH32" s="5"/>
       <c r="GI32" s="5"/>
     </row>
-    <row r="33" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B33" s="4"/>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
@@ -10265,7 +10265,7 @@
       <c r="GH33" s="5"/>
       <c r="GI33" s="5"/>
     </row>
-    <row r="34" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B34" s="4"/>
       <c r="C34" s="5"/>
       <c r="D34" s="5"/>
@@ -10457,7 +10457,7 @@
       <c r="GH34" s="5"/>
       <c r="GI34" s="5"/>
     </row>
-    <row r="35" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B35" s="4"/>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
@@ -10649,7 +10649,7 @@
       <c r="GH35" s="5"/>
       <c r="GI35" s="5"/>
     </row>
-    <row r="36" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B36" s="4"/>
       <c r="C36" s="5"/>
       <c r="D36" s="5"/>
@@ -10841,7 +10841,7 @@
       <c r="GH36" s="5"/>
       <c r="GI36" s="5"/>
     </row>
-    <row r="37" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B37" s="4"/>
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
@@ -11033,7 +11033,7 @@
       <c r="GH37" s="5"/>
       <c r="GI37" s="5"/>
     </row>
-    <row r="38" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B38" s="4"/>
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
@@ -11225,7 +11225,7 @@
       <c r="GH38" s="5"/>
       <c r="GI38" s="5"/>
     </row>
-    <row r="39" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B39" s="4"/>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
@@ -11417,7 +11417,7 @@
       <c r="GH39" s="5"/>
       <c r="GI39" s="5"/>
     </row>
-    <row r="40" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B40" s="4"/>
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
@@ -11609,7 +11609,7 @@
       <c r="GH40" s="5"/>
       <c r="GI40" s="5"/>
     </row>
-    <row r="41" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B41" s="4"/>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
@@ -11801,7 +11801,7 @@
       <c r="GH41" s="5"/>
       <c r="GI41" s="5"/>
     </row>
-    <row r="42" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B42" s="4"/>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
@@ -11993,7 +11993,7 @@
       <c r="GH42" s="5"/>
       <c r="GI42" s="5"/>
     </row>
-    <row r="43" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B43" s="4"/>
       <c r="C43" s="5"/>
       <c r="D43" s="5"/>
@@ -12185,7 +12185,7 @@
       <c r="GH43" s="5"/>
       <c r="GI43" s="5"/>
     </row>
-    <row r="44" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B44" s="4"/>
       <c r="C44" s="5"/>
       <c r="D44" s="5"/>
@@ -12377,7 +12377,7 @@
       <c r="GH44" s="5"/>
       <c r="GI44" s="5"/>
     </row>
-    <row r="45" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B45" s="4"/>
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
@@ -12569,7 +12569,7 @@
       <c r="GH45" s="5"/>
       <c r="GI45" s="5"/>
     </row>
-    <row r="46" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:191" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B46" s="4"/>
       <c r="C46" s="5"/>
       <c r="D46" s="5"/>
@@ -12763,27 +12763,19 @@
     </row>
   </sheetData>
   <mergeCells count="48">
-    <mergeCell ref="BJ23:BV23"/>
-    <mergeCell ref="BW23:CI23"/>
-    <mergeCell ref="CJ23:CV23"/>
-    <mergeCell ref="FJ23:FV23"/>
-    <mergeCell ref="CW23:DI23"/>
-    <mergeCell ref="DJ23:DV23"/>
-    <mergeCell ref="DW23:EI23"/>
-    <mergeCell ref="EJ23:EV23"/>
-    <mergeCell ref="EW23:FI23"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="AJ23:AV23"/>
-    <mergeCell ref="AW23:BI23"/>
-    <mergeCell ref="J2:V2"/>
-    <mergeCell ref="J22:V22"/>
-    <mergeCell ref="J23:V23"/>
-    <mergeCell ref="W23:AI23"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="D22:I22"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:I23"/>
+    <mergeCell ref="FW2:GI2"/>
+    <mergeCell ref="FW22:GI22"/>
+    <mergeCell ref="FW23:GI23"/>
+    <mergeCell ref="DJ22:DV22"/>
+    <mergeCell ref="DJ2:DV2"/>
+    <mergeCell ref="DW22:EI22"/>
+    <mergeCell ref="EJ22:EV22"/>
+    <mergeCell ref="EW22:FI22"/>
+    <mergeCell ref="EW2:FI2"/>
+    <mergeCell ref="FJ2:FV2"/>
+    <mergeCell ref="FJ22:FV22"/>
+    <mergeCell ref="EJ2:EV2"/>
+    <mergeCell ref="DW2:EI2"/>
     <mergeCell ref="CW2:DI2"/>
     <mergeCell ref="BJ2:BV2"/>
     <mergeCell ref="W2:AI2"/>
@@ -12798,19 +12790,27 @@
     <mergeCell ref="AJ2:AV2"/>
     <mergeCell ref="AJ22:AV22"/>
     <mergeCell ref="W22:AI22"/>
-    <mergeCell ref="FW2:GI2"/>
-    <mergeCell ref="FW22:GI22"/>
-    <mergeCell ref="FW23:GI23"/>
-    <mergeCell ref="DJ22:DV22"/>
-    <mergeCell ref="DJ2:DV2"/>
-    <mergeCell ref="DW22:EI22"/>
-    <mergeCell ref="EJ22:EV22"/>
-    <mergeCell ref="EW22:FI22"/>
-    <mergeCell ref="EW2:FI2"/>
-    <mergeCell ref="FJ2:FV2"/>
-    <mergeCell ref="FJ22:FV22"/>
-    <mergeCell ref="EJ2:EV2"/>
-    <mergeCell ref="DW2:EI2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="AJ23:AV23"/>
+    <mergeCell ref="AW23:BI23"/>
+    <mergeCell ref="J2:V2"/>
+    <mergeCell ref="J22:V22"/>
+    <mergeCell ref="J23:V23"/>
+    <mergeCell ref="W23:AI23"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="D22:I22"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:I23"/>
+    <mergeCell ref="BJ23:BV23"/>
+    <mergeCell ref="BW23:CI23"/>
+    <mergeCell ref="CJ23:CV23"/>
+    <mergeCell ref="FJ23:FV23"/>
+    <mergeCell ref="CW23:DI23"/>
+    <mergeCell ref="DJ23:DV23"/>
+    <mergeCell ref="DW23:EI23"/>
+    <mergeCell ref="EJ23:EV23"/>
+    <mergeCell ref="EW23:FI23"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="62" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
